--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="323">
   <si>
     <t>Production Line</t>
   </si>
@@ -77,202 +77,169 @@
     <t>INT3</t>
   </si>
   <si>
-    <t>910728614</t>
-  </si>
-  <si>
-    <t>910728754</t>
-  </si>
-  <si>
-    <t>910728783</t>
-  </si>
-  <si>
-    <t>910730952</t>
-  </si>
-  <si>
-    <t>910731174</t>
-  </si>
-  <si>
-    <t>910731092</t>
-  </si>
-  <si>
-    <t>910730950</t>
-  </si>
-  <si>
-    <t>910731190</t>
-  </si>
-  <si>
-    <t>910731146</t>
-  </si>
-  <si>
-    <t>910730970</t>
-  </si>
-  <si>
-    <t>910728859</t>
-  </si>
-  <si>
-    <t>910728848</t>
-  </si>
-  <si>
-    <t>910728860</t>
-  </si>
-  <si>
-    <t>910731193</t>
-  </si>
-  <si>
-    <t>910731148</t>
-  </si>
-  <si>
-    <t>910730972</t>
-  </si>
-  <si>
-    <t>910730971</t>
-  </si>
-  <si>
-    <t>910731147</t>
-  </si>
-  <si>
-    <t>910731172</t>
-  </si>
-  <si>
-    <t>910728980</t>
-  </si>
-  <si>
-    <t>910731062</t>
-  </si>
-  <si>
-    <t>910731115</t>
-  </si>
-  <si>
-    <t>910731102</t>
-  </si>
-  <si>
-    <t>910730963</t>
-  </si>
-  <si>
-    <t>910730943</t>
-  </si>
-  <si>
-    <t>910731125</t>
-  </si>
-  <si>
-    <t>910731168</t>
-  </si>
-  <si>
-    <t>910731183</t>
-  </si>
-  <si>
-    <t>910731220</t>
-  </si>
-  <si>
-    <t>910731319</t>
-  </si>
-  <si>
-    <t>910731238</t>
-  </si>
-  <si>
-    <t>910731304</t>
-  </si>
-  <si>
-    <t>910731210</t>
-  </si>
-  <si>
-    <t>910731292</t>
-  </si>
-  <si>
-    <t>910731221</t>
-  </si>
-  <si>
-    <t>910731293</t>
-  </si>
-  <si>
-    <t>910728866</t>
-  </si>
-  <si>
-    <t>910728931</t>
-  </si>
-  <si>
-    <t>910728784</t>
-  </si>
-  <si>
-    <t>910728850</t>
-  </si>
-  <si>
-    <t>910731057</t>
-  </si>
-  <si>
-    <t>910730961</t>
-  </si>
-  <si>
-    <t>910731031</t>
+    <t>910712428</t>
+  </si>
+  <si>
+    <t>910712578</t>
+  </si>
+  <si>
+    <t>910712440</t>
+  </si>
+  <si>
+    <t>910717114</t>
+  </si>
+  <si>
+    <t>910717201</t>
+  </si>
+  <si>
+    <t>910717256</t>
+  </si>
+  <si>
+    <t>910717224</t>
+  </si>
+  <si>
+    <t>910717296</t>
+  </si>
+  <si>
+    <t>910717276</t>
+  </si>
+  <si>
+    <t>910715043</t>
+  </si>
+  <si>
+    <t>910714990</t>
+  </si>
+  <si>
+    <t>910717240</t>
+  </si>
+  <si>
+    <t>910717241</t>
+  </si>
+  <si>
+    <t>910717202</t>
+  </si>
+  <si>
+    <t>910717225</t>
+  </si>
+  <si>
+    <t>910715191</t>
+  </si>
+  <si>
+    <t>910715241</t>
+  </si>
+  <si>
+    <t>910715257</t>
+  </si>
+  <si>
+    <t>910715048</t>
+  </si>
+  <si>
+    <t>910715049</t>
+  </si>
+  <si>
+    <t>910715240</t>
+  </si>
+  <si>
+    <t>910717359</t>
+  </si>
+  <si>
+    <t>910717252</t>
+  </si>
+  <si>
+    <t>910715192</t>
+  </si>
+  <si>
+    <t>910717302</t>
+  </si>
+  <si>
+    <t>910717300</t>
+  </si>
+  <si>
+    <t>910717257</t>
+  </si>
+  <si>
+    <t>910717251</t>
+  </si>
+  <si>
+    <t>910717377</t>
+  </si>
+  <si>
+    <t>910717299</t>
+  </si>
+  <si>
+    <t>910717417</t>
+  </si>
+  <si>
+    <t>910714830</t>
+  </si>
+  <si>
+    <t>910714891</t>
+  </si>
+  <si>
+    <t>910717129</t>
+  </si>
+  <si>
+    <t>910717198</t>
   </si>
   <si>
     <t>83900263</t>
   </si>
   <si>
-    <t>83900258</t>
+    <t>83900260</t>
   </si>
   <si>
     <t>83900262</t>
   </si>
   <si>
-    <t>83900261</t>
-  </si>
-  <si>
-    <t>83900207</t>
-  </si>
-  <si>
-    <t>83900259</t>
-  </si>
-  <si>
-    <t>80880903</t>
-  </si>
-  <si>
-    <t>80880893</t>
-  </si>
-  <si>
-    <t>80880901</t>
-  </si>
-  <si>
-    <t>80880900</t>
-  </si>
-  <si>
-    <t>80880914</t>
+    <t>80880885</t>
+  </si>
+  <si>
+    <t>80879287</t>
+  </si>
+  <si>
+    <t>80879283</t>
+  </si>
+  <si>
+    <t>80889640</t>
+  </si>
+  <si>
+    <t>80889635</t>
+  </si>
+  <si>
+    <t>80879278</t>
+  </si>
+  <si>
+    <t>80879268</t>
+  </si>
+  <si>
+    <t>80879274</t>
+  </si>
+  <si>
+    <t>80879282</t>
+  </si>
+  <si>
+    <t>80896348</t>
+  </si>
+  <si>
+    <t>80880898</t>
   </si>
   <si>
     <t>80880904</t>
   </si>
   <si>
-    <t>80879274</t>
-  </si>
-  <si>
-    <t>80879275</t>
-  </si>
-  <si>
-    <t>80879288</t>
-  </si>
-  <si>
-    <t>80879278</t>
-  </si>
-  <si>
-    <t>80879287</t>
-  </si>
-  <si>
-    <t>80879283</t>
-  </si>
-  <si>
-    <t>80880910</t>
-  </si>
-  <si>
-    <t>80880916</t>
+    <t>80880902</t>
+  </si>
+  <si>
+    <t>80880883</t>
+  </si>
+  <si>
+    <t>80880881</t>
   </si>
   <si>
     <t>80841061</t>
   </si>
   <si>
-    <t>80841060</t>
-  </si>
-  <si>
-    <t>80851522</t>
+    <t>80830098</t>
   </si>
   <si>
     <t>80878378</t>
@@ -281,70 +248,61 @@
     <t>H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
+    <t>H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
-    <t>H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 180ML X 56 AHF IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 180ML X 56 LF IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 300ML X30 CM IN DM GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 340ML X30 CM IN GST</t>
+    <t>H&amp;S SHM 72ML X 48 AHF IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650ML X 12 SSC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 180MLX56 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 400MLX30 HS LC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 75 ML X 48 HS DR IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
   </si>
   <si>
     <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
   </si>
   <si>
-    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 340ML X 30 HS LT IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 180ML X 56 HS LT IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 650ML X 12 SSC IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 650ML X12 AHF IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 650ML X12 CM IN GST</t>
+    <t>H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 72 ML X 48 CM IN GST</t>
   </si>
   <si>
     <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
   </si>
   <si>
-    <t>PNTN COND 200MLX 24 HS SS IN PC25</t>
-  </si>
-  <si>
-    <t>PNTN COND 100MLX 24 HS HF IN AMJ25</t>
+    <t>PNTN 3MM BIOTIN COND 200MLX24 IN</t>
   </si>
   <si>
     <t>PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
@@ -455,69 +413,42 @@
     <t>B035</t>
   </si>
   <si>
-    <t>B036</t>
-  </si>
-  <si>
-    <t>B037</t>
-  </si>
-  <si>
-    <t>B038</t>
-  </si>
-  <si>
-    <t>B039</t>
-  </si>
-  <si>
-    <t>B040</t>
-  </si>
-  <si>
-    <t>B041</t>
-  </si>
-  <si>
-    <t>B042</t>
-  </si>
-  <si>
-    <t>B043</t>
-  </si>
-  <si>
     <t>21470269</t>
   </si>
   <si>
-    <t>21448509</t>
-  </si>
-  <si>
     <t>21453170</t>
   </si>
   <si>
-    <t>21470270</t>
+    <t>21417344</t>
+  </si>
+  <si>
+    <t>21302239</t>
+  </si>
+  <si>
+    <t>'21302240</t>
+  </si>
+  <si>
+    <t>21309190</t>
+  </si>
+  <si>
+    <t>20256318</t>
+  </si>
+  <si>
+    <t>'21302239</t>
+  </si>
+  <si>
+    <t>21309189</t>
   </si>
   <si>
     <t>21422079</t>
   </si>
   <si>
-    <t>21417344</t>
-  </si>
-  <si>
-    <t>90966400</t>
-  </si>
-  <si>
     <t>90947730</t>
   </si>
   <si>
-    <t>21302239</t>
-  </si>
-  <si>
-    <t>21302240</t>
-  </si>
-  <si>
-    <t>'21302240</t>
-  </si>
-  <si>
     <t>21090111</t>
   </si>
   <si>
-    <t>21090112</t>
-  </si>
-  <si>
     <t>UNKNOWN</t>
   </si>
   <si>
@@ -548,502 +479,406 @@
     <t>1.25T</t>
   </si>
   <si>
-    <t>2026-01-13 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 16:00</t>
-  </si>
-  <si>
-    <t>B020: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+    <t>2026-01-06 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 22:00</t>
+  </si>
+  <si>
+    <t>B010: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B001: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
@@ -1052,127 +887,103 @@
     <t>B002: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B012: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+    <t>B011: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B003: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
+    <t>B012: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B004: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
     <t>B013: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
-    <t>B004: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B014: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
     <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B015: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
     <t>B006: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
+    <t>B026: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
     <t>B007: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B024: H&amp;S SHM 340ML X30 CM IN GST</t>
+    <t>B027: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B014: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B008: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B018: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B028: PNTN SHM 340MLX30 HS HFC IN GST</t>
+    <t>B029: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B015: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B009: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B019: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B010: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B037: PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>B038: PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>B039: PNTN COND 200MLX 24 HS HF IN PC25</t>
+    <t>B032: PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>B033: PNTN COND 200MLX 24 HS HF IN PC25</t>
   </si>
   <si>
     <t>WASHOUT</t>
   </si>
   <si>
-    <t>B011: H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
-  </si>
-  <si>
-    <t>B040: PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>B021: H&amp;S SHM 180ML X 56 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B022: H&amp;S SHM 180ML X 56 LF IN GST</t>
-  </si>
-  <si>
-    <t>B016: H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>B023: H&amp;S SHM 300ML X30 CM IN DM GST</t>
-  </si>
-  <si>
-    <t>B041: PNTN COND 200MLX 24 HS SS IN PC25</t>
-  </si>
-  <si>
-    <t>B017: H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>B042: PNTN COND 100MLX 24 HS HF IN AMJ25</t>
-  </si>
-  <si>
-    <t>B025: H&amp;S SHM 340ML X30 CM IN GST</t>
-  </si>
-  <si>
-    <t>B026: H&amp;S SHM 340ML X30 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B027: H&amp;S SHM 340ML X30 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B029: PNTN SHM 340ML X 30 HS LT IN GST</t>
-  </si>
-  <si>
-    <t>B030: PNTN SHM 180ML X 56 HS LT IN GST</t>
-  </si>
-  <si>
-    <t>B031: PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>B032: PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
-    <t>B043: PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
-  </si>
-  <si>
-    <t>B033: PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
-    <t>B034: PNTN SHM 650ML X 12 SSC IN GST</t>
-  </si>
-  <si>
-    <t>B035: H&amp;S SHM 650ML X12 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B036: H&amp;S SHM 650ML X12 CM IN GST</t>
+    <t>B016: H&amp;S SHM 72ML X 48 AHF IN GST</t>
+  </si>
+  <si>
+    <t>B034: PNTN 3MM BIOTIN COND 200MLX24 IN</t>
+  </si>
+  <si>
+    <t>B024: PNTN SHM 75 ML X 48 HS DR IN GST</t>
+  </si>
+  <si>
+    <t>B017: PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>B035: PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
+  </si>
+  <si>
+    <t>B018: PNTN SHM 650ML X 12 SSC IN GST</t>
+  </si>
+  <si>
+    <t>B019: PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B020: PNTN SHM 180MLX56 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B021: PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B025: PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B028: H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>B030: H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B022: PNTN SHM 400MLX30 HS LC IN GST</t>
+  </si>
+  <si>
+    <t>B031: H&amp;S SHM 72 ML X 48 CM IN GST</t>
+  </si>
+  <si>
+    <t>B023: PNTN SHM 340MLX30 HS HFC IN GST</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16" width="20.7109375" customWidth="1"/>
@@ -1598,46 +1409,46 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H2">
         <v>4.4185</v>
       </c>
       <c r="I2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="K2" s="2">
-        <v>46036.22291666667</v>
+        <v>46029.11388888889</v>
       </c>
       <c r="L2">
         <v>90</v>
       </c>
       <c r="M2" s="2">
-        <v>46036.28541666667</v>
+        <v>46029.17638888889</v>
       </c>
       <c r="N2">
         <v>120</v>
       </c>
       <c r="O2" s="2">
-        <v>46036.36875</v>
+        <v>46029.25972222222</v>
       </c>
       <c r="P2" s="2">
-        <v>46036.55208333334</v>
+        <v>46029.44305555556</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1648,46 +1459,46 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H3">
         <v>4.4185</v>
       </c>
       <c r="I3" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J3" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="K3" s="2">
-        <v>46036.35902777778</v>
+        <v>46029.28333333333</v>
       </c>
       <c r="L3">
         <v>90</v>
       </c>
       <c r="M3" s="2">
-        <v>46036.42152777778</v>
+        <v>46029.34583333333</v>
       </c>
       <c r="N3">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="O3" s="2">
-        <v>46036.55208333334</v>
+        <v>46029.44305555556</v>
       </c>
       <c r="P3" s="2">
-        <v>46036.73611111111</v>
+        <v>46029.62708333333</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1698,46 +1509,46 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H4">
         <v>4.4185</v>
       </c>
       <c r="I4" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J4" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K4" s="2">
-        <v>46036.59027777778</v>
+        <v>46029.48125</v>
       </c>
       <c r="L4">
         <v>90</v>
       </c>
       <c r="M4" s="2">
-        <v>46036.65277777778</v>
+        <v>46029.54375</v>
       </c>
       <c r="N4">
         <v>120</v>
       </c>
       <c r="O4" s="2">
-        <v>46036.73611111111</v>
+        <v>46029.62708333333</v>
       </c>
       <c r="P4" s="2">
-        <v>46036.91944444444</v>
+        <v>46029.81041666667</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1748,46 +1559,46 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H5">
         <v>4.4185</v>
       </c>
       <c r="I5" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J5" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="K5" s="2">
-        <v>46036.77361111111</v>
+        <v>46029.66458333333</v>
       </c>
       <c r="L5">
         <v>90</v>
       </c>
       <c r="M5" s="2">
-        <v>46036.83611111111</v>
+        <v>46029.72708333333</v>
       </c>
       <c r="N5">
         <v>120</v>
       </c>
       <c r="O5" s="2">
-        <v>46036.91944444444</v>
+        <v>46029.81041666667</v>
       </c>
       <c r="P5" s="2">
-        <v>46037.10347222222</v>
+        <v>46029.99444444444</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1798,46 +1609,46 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="F6" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G6" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H6">
         <v>4.4185</v>
       </c>
       <c r="I6" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J6" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="K6" s="2">
-        <v>46036.95763888889</v>
+        <v>46029.84861111111</v>
       </c>
       <c r="L6">
         <v>90</v>
       </c>
       <c r="M6" s="2">
-        <v>46037.02013888889</v>
+        <v>46029.91111111111</v>
       </c>
       <c r="N6">
         <v>120</v>
       </c>
       <c r="O6" s="2">
-        <v>46037.10347222222</v>
+        <v>46029.99444444444</v>
       </c>
       <c r="P6" s="2">
-        <v>46037.28680555556</v>
+        <v>46030.17847222222</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1848,46 +1659,46 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H7">
         <v>4.4185</v>
       </c>
       <c r="I7" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J7" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="K7" s="2">
-        <v>46037.14097222222</v>
+        <v>46030.03263888889</v>
       </c>
       <c r="L7">
         <v>90</v>
       </c>
       <c r="M7" s="2">
-        <v>46037.20347222222</v>
+        <v>46030.09513888889</v>
       </c>
       <c r="N7">
         <v>120</v>
       </c>
       <c r="O7" s="2">
-        <v>46037.28680555556</v>
+        <v>46030.17847222222</v>
       </c>
       <c r="P7" s="2">
-        <v>46037.47083333333</v>
+        <v>46030.36180555556</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1898,46 +1709,46 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G8" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H8">
         <v>4.4185</v>
       </c>
       <c r="I8" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J8" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="K8" s="2">
-        <v>46037.325</v>
+        <v>46030.20833333334</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8" s="2">
-        <v>46037.3875</v>
+        <v>46030.27083333334</v>
       </c>
       <c r="N8">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2">
-        <v>46037.47083333333</v>
+        <v>46030.36180555556</v>
       </c>
       <c r="P8" s="2">
-        <v>46037.65486111111</v>
+        <v>46030.54583333333</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1948,46 +1759,46 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="F9" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H9">
         <v>4.4185</v>
       </c>
       <c r="I9" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K9" s="2">
-        <v>46037.46875</v>
+        <v>46030.39583333334</v>
       </c>
       <c r="L9">
         <v>90</v>
       </c>
       <c r="M9" s="2">
-        <v>46037.53125</v>
+        <v>46030.45833333334</v>
       </c>
       <c r="N9">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="O9" s="2">
-        <v>46037.65486111111</v>
+        <v>46030.54583333333</v>
       </c>
       <c r="P9" s="2">
-        <v>46037.83819444444</v>
+        <v>46030.72916666666</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1998,96 +1809,96 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F10" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H10">
         <v>4.4185</v>
       </c>
       <c r="I10" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J10" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="K10" s="2">
-        <v>46037.68194444444</v>
+        <v>46030.58333333334</v>
       </c>
       <c r="L10">
         <v>90</v>
       </c>
       <c r="M10" s="2">
-        <v>46037.74444444444</v>
+        <v>46030.64583333334</v>
       </c>
       <c r="N10">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="O10" s="2">
-        <v>46037.83819444444</v>
+        <v>46030.72916666666</v>
       </c>
       <c r="P10" s="2">
-        <v>46038.02222222222</v>
+        <v>46030.91319444445</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H11">
         <v>4.4185</v>
       </c>
       <c r="I11" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J11" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="K11" s="2">
-        <v>46037.87638888889</v>
+        <v>46028.79861111111</v>
       </c>
       <c r="L11">
         <v>90</v>
       </c>
       <c r="M11" s="2">
-        <v>46037.93888888889</v>
+        <v>46028.86111111111</v>
       </c>
       <c r="N11">
         <v>120</v>
       </c>
       <c r="O11" s="2">
-        <v>46038.02222222222</v>
+        <v>46028.94444444445</v>
       </c>
       <c r="P11" s="2">
-        <v>46038.20555555556</v>
+        <v>46029.49166666667</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2098,46 +1909,46 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F12" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="G12" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H12">
-        <v>2.2082</v>
+        <v>4.4185</v>
       </c>
       <c r="I12" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J12" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="K12" s="2">
-        <v>46036.30208333334</v>
+        <v>46029.34583333333</v>
       </c>
       <c r="L12">
         <v>90</v>
       </c>
       <c r="M12" s="2">
-        <v>46036.36458333334</v>
+        <v>46029.40833333333</v>
       </c>
       <c r="N12">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="O12" s="2">
-        <v>46036.46111111111</v>
+        <v>46029.49166666667</v>
       </c>
       <c r="P12" s="2">
-        <v>46036.56736111111</v>
+        <v>46029.73541666667</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2148,46 +1959,46 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="F13" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H13">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I13" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J13" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K13" s="2">
-        <v>46036.42152777778</v>
+        <v>46029.58958333333</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13" s="2">
-        <v>46036.48402777778</v>
+        <v>46029.65208333333</v>
       </c>
       <c r="N13">
         <v>120</v>
       </c>
       <c r="O13" s="2">
-        <v>46036.56736111111</v>
+        <v>46029.73541666667</v>
       </c>
       <c r="P13" s="2">
-        <v>46036.78125</v>
+        <v>46029.94930555556</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2198,46 +2009,46 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H14">
         <v>4.4163</v>
       </c>
       <c r="I14" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="K14" s="2">
-        <v>46036.67708333334</v>
+        <v>46029.78611111111</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14" s="2">
-        <v>46036.73958333334</v>
+        <v>46029.84861111111</v>
       </c>
       <c r="N14">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="O14" s="2">
-        <v>46036.82291666666</v>
+        <v>46029.94930555556</v>
       </c>
       <c r="P14" s="2">
-        <v>46037.03611111111</v>
+        <v>46030.49583333333</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2248,46 +2059,46 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H15">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I15" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J15" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="K15" s="2">
-        <v>46036.89027777778</v>
+        <v>46030.33333333334</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15" s="2">
-        <v>46036.95277777778</v>
+        <v>46030.39583333334</v>
       </c>
       <c r="N15">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="O15" s="2">
-        <v>46037.03611111111</v>
+        <v>46030.49583333333</v>
       </c>
       <c r="P15" s="2">
-        <v>46037.25</v>
+        <v>46030.70972222222</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2298,246 +2109,246 @@
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G16" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H16">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I16" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="K16" s="2">
-        <v>46037.07847222222</v>
+        <v>46030.52083333334</v>
       </c>
       <c r="L16">
         <v>90</v>
       </c>
       <c r="M16" s="2">
-        <v>46037.14097222222</v>
+        <v>46030.58333333334</v>
       </c>
       <c r="N16">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="O16" s="2">
-        <v>46037.25</v>
+        <v>46030.70972222222</v>
       </c>
       <c r="P16" s="2">
-        <v>46037.46319444444</v>
+        <v>46030.92291666667</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F17" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="G17" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H17">
-        <v>2.2082</v>
+        <v>2.2314</v>
       </c>
       <c r="I17" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="K17" s="2">
-        <v>46037.03611111111</v>
+        <v>46029.09027777778</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17" s="2">
-        <v>46037.09861111111</v>
+        <v>46029.15277777778</v>
       </c>
       <c r="N17">
-        <v>525</v>
+        <v>350</v>
       </c>
       <c r="O17" s="2">
-        <v>46037.46319444444</v>
+        <v>46029.39583333334</v>
       </c>
       <c r="P17" s="2">
-        <v>46037.57013888889</v>
+        <v>46029.62916666667</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F18" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="G18" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H18">
-        <v>2.2082</v>
+        <v>2.2511</v>
       </c>
       <c r="I18" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="J18" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K18" s="2">
-        <v>46037.26180555556</v>
+        <v>46029.31944444445</v>
       </c>
       <c r="L18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M18" s="2">
-        <v>46037.32430555556</v>
+        <v>46029.37847222222</v>
       </c>
       <c r="N18">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="O18" s="2">
-        <v>46037.57013888889</v>
+        <v>46029.62916666667</v>
       </c>
       <c r="P18" s="2">
-        <v>46037.67708333334</v>
+        <v>46029.68958333333</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H19">
-        <v>4.4163</v>
+        <v>2.2511</v>
       </c>
       <c r="I19" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J19" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K19" s="2">
-        <v>46037.53125</v>
+        <v>46029.46875</v>
       </c>
       <c r="L19">
         <v>90</v>
       </c>
       <c r="M19" s="2">
-        <v>46037.59375</v>
+        <v>46029.53125</v>
       </c>
       <c r="N19">
-        <v>120</v>
+        <v>228</v>
       </c>
       <c r="O19" s="2">
-        <v>46037.67708333334</v>
+        <v>46029.68958333333</v>
       </c>
       <c r="P19" s="2">
-        <v>46037.89027777778</v>
+        <v>46029.75</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="G20" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H20">
-        <v>4.4163</v>
+        <v>1.1225</v>
       </c>
       <c r="I20" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J20" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="K20" s="2">
-        <v>46037.74444444444</v>
+        <v>46029.54513888889</v>
       </c>
       <c r="L20">
         <v>90</v>
       </c>
       <c r="M20" s="2">
-        <v>46037.80694444444</v>
+        <v>46029.60763888889</v>
       </c>
       <c r="N20">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="O20" s="2">
-        <v>46037.89027777778</v>
+        <v>46029.75</v>
       </c>
       <c r="P20" s="2">
-        <v>46038.10416666666</v>
+        <v>46029.77986111111</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2548,46 +2359,46 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="G21" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H21">
-        <v>4.5088</v>
+        <v>1.1174</v>
       </c>
       <c r="I21" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J21" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="K21" s="2">
-        <v>46036.16041666667</v>
+        <v>46029.60763888889</v>
       </c>
       <c r="L21">
         <v>90</v>
       </c>
       <c r="M21" s="2">
-        <v>46036.22291666667</v>
+        <v>46029.67013888889</v>
       </c>
       <c r="N21">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="O21" s="2">
-        <v>46036.36111111111</v>
+        <v>46029.77986111111</v>
       </c>
       <c r="P21" s="2">
-        <v>46036.55</v>
+        <v>46029.82638888889</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2598,46 +2409,46 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F22" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="G22" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H22">
         <v>2.2544</v>
       </c>
       <c r="I22" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="J22" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="K22" s="2">
-        <v>46036.88333333333</v>
+        <v>46029.68402777778</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M22" s="2">
-        <v>46036.94583333333</v>
+        <v>46029.74305555555</v>
       </c>
       <c r="N22">
-        <v>528</v>
+        <v>120</v>
       </c>
       <c r="O22" s="2">
-        <v>46037.3125</v>
+        <v>46029.82638888889</v>
       </c>
       <c r="P22" s="2">
-        <v>46037.40625</v>
+        <v>46029.92083333333</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2648,46 +2459,46 @@
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F23" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G23" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H23">
-        <v>2.2544</v>
+        <v>2.1937</v>
       </c>
       <c r="I23" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="K23" s="2">
-        <v>46036.95972222222</v>
+        <v>46030.67708333334</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M23" s="2">
-        <v>46037.02222222222</v>
+        <v>46030.73611111111</v>
       </c>
       <c r="N23">
-        <v>553</v>
+        <v>266</v>
       </c>
       <c r="O23" s="2">
-        <v>46037.40625</v>
+        <v>46030.92083333333</v>
       </c>
       <c r="P23" s="2">
-        <v>46037.50069444445</v>
+        <v>46030.96527777778</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2698,46 +2509,46 @@
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="G24" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H24">
-        <v>1.4702</v>
+        <v>2.2614</v>
       </c>
       <c r="I24" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="J24" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="K24" s="2">
-        <v>46037.1125</v>
+        <v>46030.82291666666</v>
       </c>
       <c r="L24">
         <v>85</v>
       </c>
       <c r="M24" s="2">
-        <v>46037.17152777778</v>
+        <v>46030.88194444445</v>
       </c>
       <c r="N24">
-        <v>474</v>
+        <v>120</v>
       </c>
       <c r="O24" s="2">
-        <v>46037.50069444445</v>
+        <v>46030.96527777778</v>
       </c>
       <c r="P24" s="2">
-        <v>46037.55833333333</v>
+        <v>46030.53472222222</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2748,46 +2559,46 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F25" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H25">
-        <v>2.9755</v>
+        <v>2.19</v>
       </c>
       <c r="I25" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J25" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K25" s="2">
-        <v>46037.40277777778</v>
+        <v>46029.24305555555</v>
       </c>
       <c r="L25">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M25" s="2">
-        <v>46037.46875</v>
+        <v>46029.30555555555</v>
       </c>
       <c r="N25">
-        <v>129</v>
+        <v>330</v>
       </c>
       <c r="O25" s="2">
-        <v>46037.55833333333</v>
+        <v>46029.53472222222</v>
       </c>
       <c r="P25" s="2">
-        <v>46037.6375</v>
+        <v>46030.25</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2798,46 +2609,46 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="F26" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="G26" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H26">
         <v>2.2614</v>
       </c>
       <c r="I26" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J26" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="K26" s="2">
-        <v>46037.47708333333</v>
+        <v>46030.10486111111</v>
       </c>
       <c r="L26">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M26" s="2">
-        <v>46037.53611111111</v>
+        <v>46030.16736111111</v>
       </c>
       <c r="N26">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="O26" s="2">
-        <v>46037.6375</v>
+        <v>46030.25069444445</v>
       </c>
       <c r="P26" s="2">
-        <v>46037.69791666666</v>
+        <v>46030.31111111111</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2848,46 +2659,46 @@
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G27" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H27">
-        <v>2.2614</v>
+        <v>4.5022</v>
       </c>
       <c r="I27" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J27" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="K27" s="2">
-        <v>46037.55</v>
+        <v>46030.14583333334</v>
       </c>
       <c r="L27">
         <v>90</v>
       </c>
       <c r="M27" s="2">
-        <v>46037.6125</v>
+        <v>46030.20833333334</v>
       </c>
       <c r="N27">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="O27" s="2">
-        <v>46037.69791666666</v>
+        <v>46030.31111111111</v>
       </c>
       <c r="P27" s="2">
-        <v>46037.75833333333</v>
+        <v>46030.43125</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2898,46 +2709,46 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F28" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G28" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H28">
-        <v>2.2614</v>
+        <v>4.5022</v>
       </c>
       <c r="I28" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J28" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="K28" s="2">
-        <v>46037.6125</v>
+        <v>46030.27083333334</v>
       </c>
       <c r="L28">
         <v>90</v>
       </c>
       <c r="M28" s="2">
-        <v>46037.675</v>
+        <v>46030.33333333334</v>
       </c>
       <c r="N28">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="O28" s="2">
-        <v>46037.75833333333</v>
+        <v>46030.43125</v>
       </c>
       <c r="P28" s="2">
-        <v>46037.81805555556</v>
+        <v>46030.55138888889</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2948,46 +2759,46 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="G29" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H29">
-        <v>4.5228</v>
+        <v>2.2614</v>
       </c>
       <c r="I29" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="J29" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="K29" s="2">
-        <v>46037.61597222222</v>
+        <v>46030.40555555555</v>
       </c>
       <c r="L29">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M29" s="2">
-        <v>46037.68194444444</v>
+        <v>46030.46805555555</v>
       </c>
       <c r="N29">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="O29" s="2">
-        <v>46037.81805555556</v>
+        <v>46030.55138888889</v>
       </c>
       <c r="P29" s="2">
-        <v>46037.93819444445</v>
+        <v>46030.61180555556</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2998,46 +2809,46 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G30" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H30">
-        <v>1.1307</v>
+        <v>4.5228</v>
       </c>
       <c r="I30" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J30" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="K30" s="2">
-        <v>46037.79236111111</v>
+        <v>46030.45833333334</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30" s="2">
-        <v>46037.85486111111</v>
+        <v>46030.52083333334</v>
       </c>
       <c r="N30">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="O30" s="2">
-        <v>46037.93819444445</v>
+        <v>46030.61180555556</v>
       </c>
       <c r="P30" s="2">
-        <v>46037.96875</v>
+        <v>46030.73194444444</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3048,46 +2859,46 @@
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="G31" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H31">
-        <v>1.1291</v>
+        <v>2.2314</v>
       </c>
       <c r="I31" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J31" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="K31" s="2">
-        <v>46038.0625</v>
+        <v>46030.58611111111</v>
       </c>
       <c r="L31">
         <v>90</v>
       </c>
       <c r="M31" s="2">
-        <v>46038.125</v>
+        <v>46030.64861111111</v>
       </c>
       <c r="N31">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="O31" s="2">
-        <v>46038.33333333334</v>
+        <v>46030.73194444444</v>
       </c>
       <c r="P31" s="2">
-        <v>46038.38055555556</v>
+        <v>46030.96527777778</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3098,646 +2909,246 @@
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="F32" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="G32" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H32">
-        <v>2.2544</v>
+        <v>2.2314</v>
       </c>
       <c r="I32" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="K32" s="2">
-        <v>46038.13888888889</v>
+        <v>46030.75</v>
       </c>
       <c r="L32">
         <v>85</v>
       </c>
       <c r="M32" s="2">
-        <v>46038.19791666666</v>
+        <v>46030.80902777778</v>
       </c>
       <c r="N32">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="O32" s="2">
-        <v>46038.38055555556</v>
+        <v>46030.96527777778</v>
       </c>
       <c r="P32" s="2">
-        <v>46038.47430555556</v>
+        <v>46031.19930555556</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
         <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H33">
-        <v>2.2511</v>
+        <v>0.5601</v>
       </c>
       <c r="I33" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="J33" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="K33" s="2">
-        <v>46038.19791666666</v>
+        <v>46028.1875</v>
       </c>
       <c r="L33">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="M33" s="2">
-        <v>46038.25694444445</v>
+        <v>46028.3125</v>
       </c>
       <c r="N33">
-        <v>313</v>
+        <v>1440</v>
       </c>
       <c r="O33" s="2">
-        <v>46038.47430555556</v>
+        <v>46029.3125</v>
       </c>
       <c r="P33" s="2">
-        <v>46038.53472222222</v>
+        <v>46029.48125</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" t="s">
         <v>143</v>
       </c>
-      <c r="F34" t="s">
-        <v>162</v>
-      </c>
       <c r="G34" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H34">
-        <v>2.2511</v>
+        <v>0.5601</v>
       </c>
       <c r="I34" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="J34" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K34" s="2">
-        <v>46038.34722222222</v>
+        <v>46028.45625</v>
       </c>
       <c r="L34">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="M34" s="2">
-        <v>46038.40625</v>
+        <v>46028.58125</v>
       </c>
       <c r="N34">
-        <v>185</v>
+        <v>1440</v>
       </c>
       <c r="O34" s="2">
-        <v>46038.53472222222</v>
+        <v>46029.58125</v>
       </c>
       <c r="P34" s="2">
-        <v>46038.59513888889</v>
+        <v>46030.41666666666</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E35" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" t="s">
         <v>144</v>
       </c>
-      <c r="F35" t="s">
-        <v>164</v>
-      </c>
       <c r="G35" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H35">
-        <v>2.2511</v>
+        <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J35" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K35" s="2">
-        <v>46038.42013888889</v>
+        <v>46029.16666666666</v>
       </c>
       <c r="L35">
         <v>90</v>
       </c>
       <c r="M35" s="2">
-        <v>46038.48263888889</v>
+        <v>46029.22916666666</v>
       </c>
       <c r="N35">
-        <v>162</v>
+        <v>1710</v>
       </c>
       <c r="O35" s="2">
-        <v>46038.59513888889</v>
+        <v>46030.41666666666</v>
       </c>
       <c r="P35" s="2">
-        <v>46038.65555555555</v>
+        <v>46030.59652777778</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="G36" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H36">
-        <v>2.2511</v>
+        <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="J36" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="K36" s="2">
-        <v>46038.49652777778</v>
+        <v>46029.39236111111</v>
       </c>
       <c r="L36">
         <v>90</v>
       </c>
       <c r="M36" s="2">
-        <v>46038.55902777778</v>
+        <v>46029.45486111111</v>
       </c>
       <c r="N36">
-        <v>139</v>
+        <v>1644</v>
       </c>
       <c r="O36" s="2">
-        <v>46038.65555555555</v>
+        <v>46030.59652777778</v>
       </c>
       <c r="P36" s="2">
-        <v>46038.71527777778</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F37" t="s">
-        <v>161</v>
-      </c>
-      <c r="G37" t="s">
-        <v>169</v>
-      </c>
-      <c r="H37">
-        <v>2.2511</v>
-      </c>
-      <c r="I37" t="s">
-        <v>170</v>
-      </c>
-      <c r="J37" t="s">
-        <v>173</v>
-      </c>
-      <c r="K37" s="2">
-        <v>46038.57291666666</v>
-      </c>
-      <c r="L37">
-        <v>85</v>
-      </c>
-      <c r="M37" s="2">
-        <v>46038.63194444445</v>
-      </c>
-      <c r="N37">
-        <v>120</v>
-      </c>
-      <c r="O37" s="2">
-        <v>46038.71527777778</v>
-      </c>
-      <c r="P37" s="2">
-        <v>46038.77569444444</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" t="s">
-        <v>107</v>
-      </c>
-      <c r="E38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F38" t="s">
-        <v>165</v>
-      </c>
-      <c r="G38" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38">
-        <v>0.5601</v>
-      </c>
-      <c r="I38" t="s">
-        <v>170</v>
-      </c>
-      <c r="J38" t="s">
-        <v>172</v>
-      </c>
-      <c r="K38" s="2">
-        <v>46035.27083333334</v>
-      </c>
-      <c r="L38">
-        <v>180</v>
-      </c>
-      <c r="M38" s="2">
-        <v>46035.39583333334</v>
-      </c>
-      <c r="N38">
-        <v>1440</v>
-      </c>
-      <c r="O38" s="2">
-        <v>46036.39583333334</v>
-      </c>
-      <c r="P38" s="2">
-        <v>46036.575</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" t="s">
-        <v>165</v>
-      </c>
-      <c r="G39" t="s">
-        <v>169</v>
-      </c>
-      <c r="H39">
-        <v>0.5601</v>
-      </c>
-      <c r="I39" t="s">
-        <v>170</v>
-      </c>
-      <c r="J39" t="s">
-        <v>173</v>
-      </c>
-      <c r="K39" s="2">
-        <v>46035.45</v>
-      </c>
-      <c r="L39">
-        <v>180</v>
-      </c>
-      <c r="M39" s="2">
-        <v>46035.575</v>
-      </c>
-      <c r="N39">
-        <v>1440</v>
-      </c>
-      <c r="O39" s="2">
-        <v>46036.575</v>
-      </c>
-      <c r="P39" s="2">
-        <v>46037.41041666667</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" t="s">
-        <v>149</v>
-      </c>
-      <c r="F40" t="s">
-        <v>165</v>
-      </c>
-      <c r="G40" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40">
-        <v>0.5601</v>
-      </c>
-      <c r="I40" t="s">
-        <v>170</v>
-      </c>
-      <c r="J40" t="s">
-        <v>172</v>
-      </c>
-      <c r="K40" s="2">
-        <v>46036.16319444445</v>
-      </c>
-      <c r="L40">
-        <v>180</v>
-      </c>
-      <c r="M40" s="2">
-        <v>46036.28819444445</v>
-      </c>
-      <c r="N40">
-        <v>1616</v>
-      </c>
-      <c r="O40" s="2">
-        <v>46037.41041666667</v>
-      </c>
-      <c r="P40" s="2">
-        <v>46037.59027777778</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="A41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" t="s">
-        <v>107</v>
-      </c>
-      <c r="E41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F41" t="s">
-        <v>165</v>
-      </c>
-      <c r="G41" t="s">
-        <v>169</v>
-      </c>
-      <c r="H41">
-        <v>0.5601</v>
-      </c>
-      <c r="I41" t="s">
-        <v>170</v>
-      </c>
-      <c r="J41" t="s">
-        <v>173</v>
-      </c>
-      <c r="K41" s="2">
-        <v>46036.46527777778</v>
-      </c>
-      <c r="L41">
-        <v>180</v>
-      </c>
-      <c r="M41" s="2">
-        <v>46036.59027777778</v>
-      </c>
-      <c r="N41">
-        <v>1440</v>
-      </c>
-      <c r="O41" s="2">
-        <v>46037.59027777778</v>
-      </c>
-      <c r="P41" s="2">
-        <v>46038.42569444444</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" t="s">
-        <v>108</v>
-      </c>
-      <c r="E42" t="s">
-        <v>151</v>
-      </c>
-      <c r="F42" t="s">
-        <v>166</v>
-      </c>
-      <c r="G42" t="s">
-        <v>169</v>
-      </c>
-      <c r="H42">
-        <v>0.5601</v>
-      </c>
-      <c r="I42" t="s">
-        <v>170</v>
-      </c>
-      <c r="J42" t="s">
-        <v>173</v>
-      </c>
-      <c r="K42" s="2">
-        <v>46037.18541666667</v>
-      </c>
-      <c r="L42">
-        <v>90</v>
-      </c>
-      <c r="M42" s="2">
-        <v>46037.24791666667</v>
-      </c>
-      <c r="N42">
-        <v>1696</v>
-      </c>
-      <c r="O42" s="2">
-        <v>46038.42569444444</v>
-      </c>
-      <c r="P42" s="2">
-        <v>46038.60486111111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" t="s">
-        <v>109</v>
-      </c>
-      <c r="E43" t="s">
-        <v>152</v>
-      </c>
-      <c r="F43" t="s">
-        <v>165</v>
-      </c>
-      <c r="G43" t="s">
-        <v>169</v>
-      </c>
-      <c r="H43">
-        <v>0.28</v>
-      </c>
-      <c r="I43" t="s">
-        <v>170</v>
-      </c>
-      <c r="J43" t="s">
-        <v>173</v>
-      </c>
-      <c r="K43" s="2">
-        <v>46037.33819444444</v>
-      </c>
-      <c r="L43">
-        <v>180</v>
-      </c>
-      <c r="M43" s="2">
-        <v>46037.46319444444</v>
-      </c>
-      <c r="N43">
-        <v>1644</v>
-      </c>
-      <c r="O43" s="2">
-        <v>46038.60486111111</v>
-      </c>
-      <c r="P43" s="2">
-        <v>46039.42569444444</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" t="s">
-        <v>86</v>
-      </c>
-      <c r="D44" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" t="s">
-        <v>153</v>
-      </c>
-      <c r="F44" t="s">
-        <v>167</v>
-      </c>
-      <c r="G44" t="s">
-        <v>169</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44" t="s">
-        <v>170</v>
-      </c>
-      <c r="J44" t="s">
-        <v>173</v>
-      </c>
-      <c r="K44" s="2">
-        <v>46038.27083333334</v>
-      </c>
-      <c r="L44">
-        <v>90</v>
-      </c>
-      <c r="M44" s="2">
-        <v>46038.33333333334</v>
-      </c>
-      <c r="N44">
-        <v>1573</v>
-      </c>
-      <c r="O44" s="2">
-        <v>46039.42569444444</v>
-      </c>
-      <c r="P44" s="2">
-        <v>46039.59027777778</v>
+        <v>46031.41736111111</v>
       </c>
     </row>
   </sheetData>
@@ -3747,7 +3158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -3757,1807 +3168,1440 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D12" t="s">
-        <v>362</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" t="s">
-        <v>362</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" t="s">
-        <v>362</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" t="s">
-        <v>362</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>362</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>362</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>150</v>
+      </c>
+      <c r="D18" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
-        <v>173</v>
+        <v>150</v>
+      </c>
+      <c r="D19" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>150</v>
+      </c>
+      <c r="D20" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>150</v>
+      </c>
+      <c r="D21" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
-        <v>174</v>
+        <v>150</v>
+      </c>
+      <c r="D22" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="C33" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="C34" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="C35" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="B45" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
-      </c>
-      <c r="C46" t="s">
-        <v>342</v>
-      </c>
-      <c r="D46" t="s">
-        <v>363</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
-      </c>
-      <c r="C47" t="s">
-        <v>342</v>
+        <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>363</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C48" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="D48" t="s">
-        <v>363</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C49" t="s">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="D49" t="s">
-        <v>363</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="D50" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" t="s">
-        <v>343</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="B52" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D52" t="s">
-        <v>364</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D53" t="s">
-        <v>365</v>
+        <v>307</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="B54" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D54" t="s">
-        <v>365</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D55" t="s">
-        <v>365</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>344</v>
+        <v>289</v>
       </c>
       <c r="D56" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>344</v>
+        <v>289</v>
+      </c>
+      <c r="D57" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C58" t="s">
-        <v>344</v>
+        <v>289</v>
+      </c>
+      <c r="D58" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="B59" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C59" t="s">
-        <v>345</v>
+        <v>290</v>
+      </c>
+      <c r="D59" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="B60" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C60" t="s">
-        <v>345</v>
+        <v>290</v>
+      </c>
+      <c r="D60" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B61" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C61" t="s">
-        <v>345</v>
+        <v>290</v>
       </c>
       <c r="D61" t="s">
-        <v>366</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="B62" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D62" t="s">
-        <v>366</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="B63" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D63" t="s">
-        <v>366</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B64" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D64" t="s">
-        <v>366</v>
+        <v>307</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>366</v>
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>150</v>
+      </c>
+      <c r="C66" t="s">
+        <v>291</v>
       </c>
       <c r="D66" t="s">
-        <v>366</v>
+        <v>313</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
-        <v>346</v>
+        <v>291</v>
+      </c>
+      <c r="D67" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B68" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C68" t="s">
-        <v>346</v>
+        <v>291</v>
+      </c>
+      <c r="D68" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
-      </c>
-      <c r="C69" t="s">
-        <v>346</v>
+        <v>150</v>
+      </c>
+      <c r="D69" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="B70" t="s">
-        <v>174</v>
+        <v>150</v>
+      </c>
+      <c r="D70" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="B71" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>347</v>
+        <v>292</v>
+      </c>
+      <c r="D71" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="B72" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C72" t="s">
-        <v>347</v>
+        <v>292</v>
+      </c>
+      <c r="D72" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="B73" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C73" t="s">
-        <v>347</v>
+        <v>292</v>
+      </c>
+      <c r="D73" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="B74" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="C74" t="s">
+        <v>293</v>
+      </c>
+      <c r="D74" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="C75" t="s">
+        <v>293</v>
+      </c>
+      <c r="D75" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="B76" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C76" t="s">
-        <v>348</v>
+        <v>293</v>
+      </c>
+      <c r="D76" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
-      </c>
-      <c r="C77" t="s">
-        <v>348</v>
+        <v>151</v>
+      </c>
+      <c r="D77" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="B78" t="s">
-        <v>174</v>
-      </c>
-      <c r="C78" t="s">
-        <v>348</v>
+        <v>151</v>
+      </c>
+      <c r="D78" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="C80" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C81" t="s">
-        <v>349</v>
-      </c>
-      <c r="D81" t="s">
-        <v>367</v>
+        <v>294</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C82" t="s">
-        <v>349</v>
-      </c>
-      <c r="D82" t="s">
-        <v>367</v>
+        <v>294</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="B83" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C83" t="s">
-        <v>349</v>
-      </c>
-      <c r="D83" t="s">
-        <v>367</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="B84" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C84" t="s">
-        <v>350</v>
-      </c>
-      <c r="D84" t="s">
-        <v>364</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
-        <v>350</v>
-      </c>
-      <c r="D85" t="s">
-        <v>368</v>
+        <v>295</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
-      </c>
-      <c r="C86" t="s">
-        <v>350</v>
-      </c>
-      <c r="D86" t="s">
-        <v>368</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="B87" t="s">
-        <v>172</v>
-      </c>
-      <c r="D87" t="s">
-        <v>368</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="B88" t="s">
-        <v>172</v>
-      </c>
-      <c r="D88" t="s">
-        <v>369</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="B89" t="s">
-        <v>172</v>
-      </c>
-      <c r="D89" t="s">
-        <v>369</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="B90" t="s">
-        <v>172</v>
-      </c>
-      <c r="C90" t="s">
-        <v>351</v>
-      </c>
-      <c r="D90" t="s">
-        <v>369</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="B91" t="s">
-        <v>172</v>
-      </c>
-      <c r="C91" t="s">
-        <v>351</v>
-      </c>
-      <c r="D91" t="s">
-        <v>364</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="B92" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C92" t="s">
-        <v>351</v>
-      </c>
-      <c r="D92" t="s">
-        <v>370</v>
+        <v>296</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="B93" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C93" t="s">
-        <v>352</v>
-      </c>
-      <c r="D93" t="s">
-        <v>370</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="B94" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C94" t="s">
-        <v>352</v>
-      </c>
-      <c r="D94" t="s">
-        <v>370</v>
+        <v>296</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
-      </c>
-      <c r="C95" t="s">
-        <v>352</v>
-      </c>
-      <c r="D95" t="s">
-        <v>371</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D96" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="B97" t="s">
-        <v>172</v>
+        <v>149</v>
+      </c>
+      <c r="C97" t="s">
+        <v>297</v>
       </c>
       <c r="D97" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="B98" t="s">
-        <v>172</v>
+        <v>149</v>
+      </c>
+      <c r="C98" t="s">
+        <v>297</v>
       </c>
       <c r="D98" t="s">
-        <v>364</v>
+        <v>317</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="B99" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" t="s">
-        <v>372</v>
+        <v>149</v>
+      </c>
+      <c r="C99" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="B100" t="s">
-        <v>172</v>
-      </c>
-      <c r="D100" t="s">
-        <v>372</v>
+        <v>149</v>
+      </c>
+      <c r="C100" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
-      </c>
-      <c r="D101" t="s">
-        <v>372</v>
+        <v>149</v>
+      </c>
+      <c r="C101" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C102" t="s">
-        <v>353</v>
-      </c>
-      <c r="D102" t="s">
-        <v>364</v>
+        <v>298</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="B103" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C103" t="s">
-        <v>353</v>
-      </c>
-      <c r="D103" t="s">
-        <v>373</v>
+        <v>299</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="B104" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C104" t="s">
-        <v>353</v>
-      </c>
-      <c r="D104" t="s">
-        <v>373</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="B105" t="s">
-        <v>173</v>
-      </c>
-      <c r="D105" t="s">
-        <v>373</v>
+        <v>150</v>
+      </c>
+      <c r="C105" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="B106" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C106" t="s">
-        <v>354</v>
-      </c>
-      <c r="D106" t="s">
-        <v>373</v>
+        <v>300</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="B107" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C107" t="s">
-        <v>354</v>
-      </c>
-      <c r="D107" t="s">
-        <v>373</v>
+        <v>300</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="B108" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C108" t="s">
-        <v>354</v>
-      </c>
-      <c r="D108" t="s">
-        <v>373</v>
+        <v>300</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="B109" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C109" t="s">
-        <v>355</v>
-      </c>
-      <c r="D109" t="s">
-        <v>374</v>
+        <v>301</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="B110" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C110" t="s">
-        <v>355</v>
+        <v>301</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="B111" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C111" t="s">
-        <v>355</v>
+        <v>301</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="B112" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C112" t="s">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="B113" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C113" t="s">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="B114" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C114" t="s">
-        <v>356</v>
-      </c>
-      <c r="D114" t="s">
-        <v>375</v>
+        <v>302</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="B115" t="s">
-        <v>173</v>
-      </c>
-      <c r="D115" t="s">
-        <v>375</v>
+        <v>150</v>
+      </c>
+      <c r="C115" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="B116" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="C116" t="s">
-        <v>357</v>
-      </c>
-      <c r="D116" t="s">
-        <v>376</v>
+        <v>303</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="B117" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C117" t="s">
-        <v>357</v>
-      </c>
-      <c r="D117" t="s">
-        <v>376</v>
+        <v>303</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="B118" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C118" t="s">
-        <v>357</v>
-      </c>
-      <c r="D118" t="s">
-        <v>376</v>
+        <v>304</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B119" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C119" t="s">
-        <v>358</v>
+        <v>304</v>
       </c>
       <c r="D119" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="B120" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C120" t="s">
-        <v>358</v>
+        <v>304</v>
+      </c>
+      <c r="D120" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="B121" t="s">
-        <v>174</v>
-      </c>
-      <c r="C121" t="s">
-        <v>358</v>
+        <v>151</v>
+      </c>
+      <c r="D121" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="B122" t="s">
-        <v>174</v>
-      </c>
-      <c r="C122" t="s">
-        <v>359</v>
+        <v>151</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="B123" t="s">
-        <v>174</v>
-      </c>
-      <c r="C123" t="s">
-        <v>359</v>
+        <v>151</v>
+      </c>
+      <c r="D123" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="B124" t="s">
-        <v>174</v>
-      </c>
-      <c r="C124" t="s">
-        <v>359</v>
+        <v>151</v>
+      </c>
+      <c r="D124" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B125" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>320</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="B126" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>321</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="B127" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>321</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="B128" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="D128" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="B129" t="s">
-        <v>174</v>
-      </c>
-      <c r="C129" t="s">
-        <v>360</v>
+        <v>151</v>
+      </c>
+      <c r="D129" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="B130" t="s">
-        <v>174</v>
-      </c>
-      <c r="C130" t="s">
-        <v>360</v>
+        <v>151</v>
+      </c>
+      <c r="D130" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="B131" t="s">
-        <v>174</v>
-      </c>
-      <c r="C131" t="s">
-        <v>360</v>
+        <v>151</v>
+      </c>
+      <c r="D131" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="B132" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="D132" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="B133" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="B134" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" t="s">
-        <v>310</v>
-      </c>
-      <c r="B135" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" t="s">
-        <v>311</v>
-      </c>
-      <c r="B136" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" t="s">
-        <v>312</v>
-      </c>
-      <c r="B137" t="s">
-        <v>172</v>
-      </c>
-      <c r="D137" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="A138" t="s">
-        <v>313</v>
-      </c>
-      <c r="B138" t="s">
-        <v>172</v>
-      </c>
-      <c r="D138" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" t="s">
-        <v>314</v>
-      </c>
-      <c r="B139" t="s">
-        <v>172</v>
-      </c>
-      <c r="D139" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" t="s">
-        <v>315</v>
-      </c>
-      <c r="B140" t="s">
-        <v>172</v>
-      </c>
-      <c r="D140" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" t="s">
-        <v>316</v>
-      </c>
-      <c r="B141" t="s">
-        <v>172</v>
-      </c>
-      <c r="D141" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" t="s">
-        <v>317</v>
-      </c>
-      <c r="B142" t="s">
-        <v>172</v>
-      </c>
-      <c r="D142" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" t="s">
-        <v>318</v>
-      </c>
-      <c r="B143" t="s">
-        <v>172</v>
-      </c>
-      <c r="D143" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" t="s">
-        <v>319</v>
-      </c>
-      <c r="B144" t="s">
-        <v>172</v>
-      </c>
-      <c r="D144" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="A145" t="s">
-        <v>320</v>
-      </c>
-      <c r="B145" t="s">
-        <v>172</v>
-      </c>
-      <c r="D145" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" t="s">
-        <v>321</v>
-      </c>
-      <c r="B146" t="s">
-        <v>172</v>
-      </c>
-      <c r="D146" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" t="s">
-        <v>322</v>
-      </c>
-      <c r="B147" t="s">
-        <v>172</v>
-      </c>
-      <c r="D147" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" t="s">
-        <v>323</v>
-      </c>
-      <c r="B148" t="s">
-        <v>172</v>
-      </c>
-      <c r="D148" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" t="s">
-        <v>324</v>
-      </c>
-      <c r="B149" t="s">
-        <v>173</v>
-      </c>
-      <c r="D149" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" t="s">
-        <v>325</v>
-      </c>
-      <c r="B150" t="s">
-        <v>173</v>
-      </c>
-      <c r="D150" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" t="s">
-        <v>326</v>
-      </c>
-      <c r="B151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D151" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" t="s">
-        <v>327</v>
-      </c>
-      <c r="B152" t="s">
-        <v>173</v>
-      </c>
-      <c r="D152" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" t="s">
-        <v>328</v>
-      </c>
-      <c r="B153" t="s">
-        <v>173</v>
-      </c>
-      <c r="D153" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" t="s">
-        <v>329</v>
-      </c>
-      <c r="B154" t="s">
-        <v>173</v>
-      </c>
-      <c r="D154" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" t="s">
-        <v>330</v>
-      </c>
-      <c r="B155" t="s">
-        <v>173</v>
-      </c>
-      <c r="D155" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
-      <c r="A156" t="s">
-        <v>331</v>
-      </c>
-      <c r="B156" t="s">
-        <v>173</v>
-      </c>
-      <c r="D156" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
-      <c r="A157" t="s">
-        <v>332</v>
-      </c>
-      <c r="B157" t="s">
-        <v>173</v>
-      </c>
-      <c r="D157" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" t="s">
-        <v>333</v>
-      </c>
-      <c r="B158" t="s">
-        <v>173</v>
-      </c>
-      <c r="D158" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
-      <c r="A159" t="s">
-        <v>334</v>
-      </c>
-      <c r="B159" t="s">
-        <v>173</v>
-      </c>
-      <c r="D159" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
-      <c r="A160" t="s">
-        <v>335</v>
-      </c>
-      <c r="B160" t="s">
-        <v>173</v>
-      </c>
-      <c r="D160" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" t="s">
-        <v>336</v>
-      </c>
-      <c r="B161" t="s">
-        <v>173</v>
-      </c>
-      <c r="D161" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
-      <c r="A162" t="s">
-        <v>337</v>
-      </c>
-      <c r="B162" t="s">
-        <v>173</v>
-      </c>
-      <c r="D162" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
-      <c r="A163" t="s">
-        <v>338</v>
-      </c>
-      <c r="B163" t="s">
-        <v>173</v>
-      </c>
-      <c r="D163" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
-      <c r="A164" t="s">
-        <v>339</v>
-      </c>
-      <c r="B164" t="s">
-        <v>173</v>
-      </c>
-      <c r="D164" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
-      <c r="A165" t="s">
-        <v>340</v>
-      </c>
-      <c r="B165" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="A166" t="s">
-        <v>341</v>
-      </c>
-      <c r="B166" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -7,14 +7,15 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Schedule" sheetId="1" r:id="rId1"/>
+    <sheet name="Tank Timeline" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="275">
   <si>
     <t>Production Line</t>
   </si>
@@ -70,432 +71,348 @@
     <t>MRP Status</t>
   </si>
   <si>
+    <t>INT2</t>
+  </si>
+  <si>
+    <t>INC1</t>
+  </si>
+  <si>
     <t>INC4</t>
   </si>
   <si>
-    <t>INC1</t>
-  </si>
-  <si>
-    <t>INT2</t>
-  </si>
-  <si>
-    <t>INT3</t>
+    <t>INC2</t>
   </si>
   <si>
     <t>INTERNAL</t>
   </si>
   <si>
-    <t>910715043</t>
-  </si>
-  <si>
-    <t>910712428</t>
-  </si>
-  <si>
-    <t>910712578</t>
-  </si>
-  <si>
-    <t>910714990</t>
-  </si>
-  <si>
-    <t>910712440</t>
-  </si>
-  <si>
-    <t>910717240</t>
-  </si>
-  <si>
-    <t>910717114</t>
-  </si>
-  <si>
-    <t>910717241</t>
-  </si>
-  <si>
-    <t>910717201</t>
-  </si>
-  <si>
-    <t>910717256</t>
-  </si>
-  <si>
-    <t>910717300</t>
-  </si>
-  <si>
-    <t>910717224</t>
-  </si>
-  <si>
-    <t>910717257</t>
-  </si>
-  <si>
-    <t>910717202</t>
-  </si>
-  <si>
-    <t>910717296</t>
-  </si>
-  <si>
-    <t>910717377</t>
-  </si>
-  <si>
-    <t>910717225</t>
-  </si>
-  <si>
-    <t>910717276</t>
-  </si>
-  <si>
-    <t>910714830</t>
-  </si>
-  <si>
-    <t>910714891</t>
-  </si>
-  <si>
-    <t>910715191</t>
-  </si>
-  <si>
-    <t>910717129</t>
-  </si>
-  <si>
-    <t>910715192</t>
+    <t>910741796</t>
+  </si>
+  <si>
+    <t>910741853</t>
+  </si>
+  <si>
+    <t>910741877</t>
+  </si>
+  <si>
+    <t>910741876</t>
+  </si>
+  <si>
+    <t>910741953</t>
+  </si>
+  <si>
+    <t>910741779</t>
+  </si>
+  <si>
+    <t>910741865</t>
+  </si>
+  <si>
+    <t>910744377</t>
+  </si>
+  <si>
+    <t>910744323</t>
+  </si>
+  <si>
+    <t>910744285</t>
+  </si>
+  <si>
+    <t>910744343</t>
+  </si>
+  <si>
+    <t>910744367</t>
+  </si>
+  <si>
+    <t>910744273</t>
+  </si>
+  <si>
+    <t>910744375</t>
+  </si>
+  <si>
+    <t>910744370</t>
+  </si>
+  <si>
+    <t>910744371</t>
+  </si>
+  <si>
+    <t>910744407</t>
+  </si>
+  <si>
+    <t>910744406</t>
+  </si>
+  <si>
+    <t>910739741</t>
+  </si>
+  <si>
+    <t>910741725</t>
   </si>
   <si>
     <t>AUTO_1</t>
   </si>
   <si>
-    <t>910715241</t>
-  </si>
-  <si>
-    <t>910717198</t>
-  </si>
-  <si>
-    <t>910715257</t>
-  </si>
-  <si>
-    <t>910715048</t>
-  </si>
-  <si>
-    <t>910715049</t>
+    <t>910741769</t>
+  </si>
+  <si>
+    <t>910741836</t>
+  </si>
+  <si>
+    <t>910739800</t>
+  </si>
+  <si>
+    <t>910741819</t>
   </si>
   <si>
     <t>AUTO_2</t>
   </si>
   <si>
-    <t>910715240</t>
+    <t>910744010</t>
   </si>
   <si>
     <t>AUTO_3</t>
   </si>
   <si>
-    <t>910717302</t>
+    <t>910744097</t>
   </si>
   <si>
     <t>AUTO_4</t>
   </si>
   <si>
+    <t>910744413</t>
+  </si>
+  <si>
+    <t>910744378</t>
+  </si>
+  <si>
     <t>AUTO_5</t>
   </si>
   <si>
-    <t>910717251</t>
-  </si>
-  <si>
-    <t>910717299</t>
-  </si>
-  <si>
-    <t>910717359</t>
-  </si>
-  <si>
-    <t>910717417</t>
-  </si>
-  <si>
-    <t>910717252</t>
-  </si>
-  <si>
-    <t>83900260</t>
+    <t>910744344</t>
+  </si>
+  <si>
+    <t>80880903</t>
   </si>
   <si>
     <t>83900263</t>
   </si>
   <si>
+    <t>83900259</t>
+  </si>
+  <si>
+    <t>80880904</t>
+  </si>
+  <si>
+    <t>80880902</t>
+  </si>
+  <si>
+    <t>83900261</t>
+  </si>
+  <si>
     <t>83900262</t>
   </si>
   <si>
     <t>80880898</t>
   </si>
   <si>
-    <t>80880902</t>
-  </si>
-  <si>
-    <t>80841061</t>
-  </si>
-  <si>
-    <t>80880885</t>
-  </si>
-  <si>
-    <t>80830098</t>
-  </si>
-  <si>
-    <t>80879282</t>
+    <t>80750817</t>
+  </si>
+  <si>
+    <t>80880895</t>
   </si>
   <si>
     <t>95619314</t>
   </si>
   <si>
-    <t>80879287</t>
-  </si>
-  <si>
-    <t>80878378</t>
-  </si>
-  <si>
-    <t>80879283</t>
-  </si>
-  <si>
-    <t>80889640</t>
-  </si>
-  <si>
-    <t>80889635</t>
-  </si>
-  <si>
-    <t>80879278</t>
-  </si>
-  <si>
-    <t>80896348</t>
-  </si>
-  <si>
-    <t>80880904</t>
+    <t>80880920</t>
+  </si>
+  <si>
+    <t>80896867</t>
   </si>
   <si>
     <t>80880883</t>
   </si>
   <si>
-    <t>80879268</t>
-  </si>
-  <si>
-    <t>80880881</t>
-  </si>
-  <si>
-    <t>80879274</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
+    <t>80880909</t>
+  </si>
+  <si>
+    <t>80896354</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
   </si>
   <si>
     <t>H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
+    <t>H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
     <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
   </si>
   <si>
-    <t>H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 72ML X 48 AHF IN GST</t>
-  </si>
-  <si>
-    <t>PNTN 3MM BIOTIN COND 200MLX24 IN</t>
-  </si>
-  <si>
-    <t>PNTN SHM 75 ML X 48 HS DR IN GST</t>
+    <t>H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 180ML X 56 CM IN GST</t>
   </si>
   <si>
     <t>Auto-Replenishment HC Base</t>
   </si>
   <si>
-    <t>PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
-    <t>PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 650ML X 12 SSC IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 180MLX56 SSC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
+    <t>H&amp;S SHM 180ML X 56 AP 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X 30 AP 2IN1 IN GST</t>
   </si>
   <si>
     <t>H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
   </si>
   <si>
-    <t>PNTN SHM 400MLX30 HS LC IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 72 ML X 48 CM IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
+    <t>H&amp;S SHM 72MLX48 S&amp;S 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X 30 S&amp;S 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B017</t>
+  </si>
+  <si>
+    <t>B001</t>
+  </si>
+  <si>
+    <t>B011</t>
+  </si>
+  <si>
+    <t>B002</t>
+  </si>
+  <si>
+    <t>B012</t>
+  </si>
+  <si>
+    <t>B021</t>
+  </si>
+  <si>
+    <t>B003</t>
+  </si>
+  <si>
+    <t>B013</t>
+  </si>
+  <si>
+    <t>B004</t>
+  </si>
+  <si>
+    <t>B025</t>
+  </si>
+  <si>
+    <t>B014</t>
+  </si>
+  <si>
+    <t>B027</t>
+  </si>
+  <si>
+    <t>B005</t>
+  </si>
+  <si>
+    <t>B028</t>
+  </si>
+  <si>
+    <t>B015</t>
+  </si>
+  <si>
+    <t>B006</t>
+  </si>
+  <si>
+    <t>B029</t>
+  </si>
+  <si>
+    <t>B016</t>
+  </si>
+  <si>
+    <t>B007</t>
+  </si>
+  <si>
+    <t>B018</t>
+  </si>
+  <si>
+    <t>REP30</t>
+  </si>
+  <si>
+    <t>B019</t>
+  </si>
+  <si>
+    <t>B020</t>
+  </si>
+  <si>
+    <t>B008</t>
+  </si>
+  <si>
+    <t>B022</t>
+  </si>
+  <si>
+    <t>REP31</t>
+  </si>
+  <si>
+    <t>B023</t>
+  </si>
+  <si>
+    <t>REP32</t>
+  </si>
+  <si>
+    <t>B024</t>
+  </si>
+  <si>
+    <t>REP33</t>
+  </si>
+  <si>
+    <t>B026</t>
+  </si>
+  <si>
+    <t>B009</t>
+  </si>
+  <si>
+    <t>REP34</t>
   </si>
   <si>
     <t>B010</t>
   </si>
   <si>
-    <t>B001</t>
-  </si>
-  <si>
-    <t>B002</t>
-  </si>
-  <si>
-    <t>B011</t>
-  </si>
-  <si>
-    <t>B003</t>
-  </si>
-  <si>
-    <t>B012</t>
-  </si>
-  <si>
-    <t>B004</t>
-  </si>
-  <si>
-    <t>B013</t>
-  </si>
-  <si>
-    <t>B005</t>
-  </si>
-  <si>
-    <t>B006</t>
-  </si>
-  <si>
-    <t>B026</t>
-  </si>
-  <si>
-    <t>B007</t>
-  </si>
-  <si>
-    <t>B027</t>
-  </si>
-  <si>
-    <t>B014</t>
-  </si>
-  <si>
-    <t>B008</t>
-  </si>
-  <si>
-    <t>B029</t>
-  </si>
-  <si>
-    <t>B015</t>
-  </si>
-  <si>
-    <t>B009</t>
-  </si>
-  <si>
-    <t>B032</t>
-  </si>
-  <si>
-    <t>B033</t>
-  </si>
-  <si>
-    <t>B016</t>
-  </si>
-  <si>
-    <t>B034</t>
-  </si>
-  <si>
-    <t>B024</t>
-  </si>
-  <si>
-    <t>REP36</t>
-  </si>
-  <si>
-    <t>B017</t>
-  </si>
-  <si>
-    <t>B035</t>
-  </si>
-  <si>
-    <t>B018</t>
-  </si>
-  <si>
-    <t>B019</t>
-  </si>
-  <si>
-    <t>B020</t>
-  </si>
-  <si>
-    <t>REP37</t>
-  </si>
-  <si>
-    <t>B021</t>
-  </si>
-  <si>
-    <t>REP38</t>
-  </si>
-  <si>
-    <t>B025</t>
-  </si>
-  <si>
-    <t>REP39</t>
-  </si>
-  <si>
-    <t>REP40</t>
-  </si>
-  <si>
-    <t>B028</t>
-  </si>
-  <si>
-    <t>B030</t>
-  </si>
-  <si>
-    <t>B022</t>
-  </si>
-  <si>
-    <t>B031</t>
-  </si>
-  <si>
-    <t>B023</t>
+    <t>21422079</t>
+  </si>
+  <si>
+    <t>21470269</t>
+  </si>
+  <si>
+    <t>21417344</t>
+  </si>
+  <si>
+    <t>21470270</t>
   </si>
   <si>
     <t>21453170</t>
   </si>
   <si>
-    <t>21470269</t>
-  </si>
-  <si>
-    <t>21422079</t>
-  </si>
-  <si>
-    <t>21090111</t>
-  </si>
-  <si>
-    <t>21417344</t>
-  </si>
-  <si>
-    <t>UNKNOWN</t>
-  </si>
-  <si>
-    <t>'21302239</t>
-  </si>
-  <si>
-    <t>21302239</t>
-  </si>
-  <si>
-    <t>'21302240</t>
-  </si>
-  <si>
-    <t>21309190</t>
-  </si>
-  <si>
-    <t>21309189</t>
-  </si>
-  <si>
-    <t>20256318</t>
+    <t>90275009</t>
   </si>
   <si>
     <t>90947730</t>
   </si>
   <si>
+    <t>91005113</t>
+  </si>
+  <si>
+    <t>21432817</t>
+  </si>
+  <si>
     <t>12T</t>
   </si>
   <si>
@@ -508,61 +425,421 @@
     <t>Dual</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>TK#_9_#</t>
+  </si>
+  <si>
+    <t>TK#_24_#</t>
+  </si>
+  <si>
+    <t>TK#_14_#</t>
+  </si>
+  <si>
+    <t>TK#_15_#</t>
+  </si>
+  <si>
+    <t>TK#_57_#</t>
+  </si>
+  <si>
+    <t>TK#_12_#</t>
+  </si>
+  <si>
+    <t>TK#_58_#</t>
+  </si>
+  <si>
+    <t>TK#_56_#</t>
+  </si>
+  <si>
+    <t>TK#_23_#</t>
   </si>
   <si>
     <t>TK#_53_#</t>
   </si>
   <si>
-    <t>TK#_14_#</t>
-  </si>
-  <si>
-    <t>TK#_12_#</t>
-  </si>
-  <si>
-    <t>NO_TANK</t>
-  </si>
-  <si>
-    <t>TK#_9_#</t>
-  </si>
-  <si>
-    <t>TK#_23_#</t>
-  </si>
-  <si>
-    <t>TK#_57_#</t>
-  </si>
-  <si>
-    <t>TK#_24_#</t>
-  </si>
-  <si>
-    <t>TK#_58_#</t>
-  </si>
-  <si>
-    <t>TK#_56_#</t>
-  </si>
-  <si>
-    <t>TK#_15_#</t>
-  </si>
-  <si>
     <t>TK#_16_#</t>
   </si>
   <si>
+    <t>LOW: SLE3S</t>
+  </si>
+  <si>
     <t>LOW: DM5500</t>
   </si>
   <si>
-    <t>LOW: SLE3S</t>
-  </si>
-  <si>
-    <t>UNKNOWN_SKU</t>
-  </si>
-  <si>
     <t>LOW: SLS</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>1.25T</t>
+  </si>
+  <si>
+    <t>2026-01-21 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-21 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-21 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-22 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-22 18:00</t>
+  </si>
+  <si>
+    <t>B017: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B001: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B011: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B002: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B012: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B021: H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>WASHOUT</t>
+  </si>
+  <si>
+    <t>B003: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B013: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B004: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B025: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B014: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B027: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B028: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B015: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B006: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B029: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B016: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B007: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
+  </si>
+  <si>
+    <t>B018: H&amp;S SHM 180ML X 56 CM IN GST</t>
+  </si>
+  <si>
+    <t>REP30: Auto-Replenishment HC Base</t>
+  </si>
+  <si>
+    <t>B019: H&amp;S SHM 180ML X 56 AP 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B020: H&amp;S SHM 340ML X 30 AP 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B008: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
+  </si>
+  <si>
+    <t>B022: H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>REP31: Auto-Replenishment HC Base</t>
+  </si>
+  <si>
+    <t>B023: H&amp;S SHM 72MLX48 S&amp;S 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>REP32: Auto-Replenishment HC Base</t>
+  </si>
+  <si>
+    <t>B024: H&amp;S SHM 340ML X 30 S&amp;S 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>REP33: Auto-Replenishment HC Base</t>
+  </si>
+  <si>
+    <t>B026: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B009: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
+  </si>
+  <si>
+    <t>REP34: Auto-Replenishment HC Base</t>
+  </si>
+  <si>
+    <t>B010: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
   </si>
 </sst>
 </file>
@@ -624,12 +901,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -924,8 +1204,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="21" width="15.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
@@ -991,52 +1274,52 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="G2" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H2">
-        <v>4.4185</v>
+        <v>4.5088</v>
       </c>
       <c r="I2" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J2" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="K2" s="2">
-        <v>46028.79861111111</v>
+        <v>46043.10625</v>
       </c>
       <c r="L2">
         <v>90</v>
       </c>
       <c r="M2" s="2">
-        <v>46028.86111111111</v>
+        <v>46043.16875</v>
       </c>
       <c r="N2">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="O2" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="P2" s="2">
-        <v>46028.94444444445</v>
+        <v>46043.3125</v>
       </c>
       <c r="Q2" s="2">
-        <v>46029.49166666667</v>
+        <v>46043.50069444445</v>
       </c>
       <c r="R2" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1047,220 +1330,220 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F3" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G3" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H3">
         <v>4.4185</v>
       </c>
       <c r="I3" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J3" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K3" s="2">
-        <v>46029.11388888889</v>
+        <v>46043.16875</v>
       </c>
       <c r="L3">
         <v>90</v>
       </c>
       <c r="M3" s="2">
-        <v>46029.17638888889</v>
+        <v>46043.23125</v>
       </c>
       <c r="N3">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="O3" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="P3" s="2">
-        <v>46029.25972222222</v>
+        <v>46043.36319444444</v>
       </c>
       <c r="Q3" s="2">
-        <v>46029.44305555556</v>
+        <v>46043.54722222222</v>
       </c>
       <c r="R3" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G4" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H4">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I4" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J4" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K4" s="2">
-        <v>46029.28333333333</v>
+        <v>46043.23125</v>
       </c>
       <c r="L4">
         <v>90</v>
       </c>
       <c r="M4" s="2">
-        <v>46029.34583333333</v>
+        <v>46043.29375</v>
       </c>
       <c r="N4">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="O4" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="P4" s="2">
-        <v>46029.44305555556</v>
+        <v>46043.37708333333</v>
       </c>
       <c r="Q4" s="2">
-        <v>46029.62708333333</v>
+        <v>46043.59027777778</v>
       </c>
       <c r="R4" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="G5" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H5">
         <v>4.4185</v>
       </c>
       <c r="I5" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J5" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K5" s="2">
-        <v>46029.34583333333</v>
+        <v>46043.38194444445</v>
       </c>
       <c r="L5">
         <v>90</v>
       </c>
       <c r="M5" s="2">
-        <v>46029.40833333333</v>
+        <v>46043.44444444445</v>
       </c>
       <c r="N5">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="O5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="P5" s="2">
-        <v>46029.49166666667</v>
+        <v>46043.54722222222</v>
       </c>
       <c r="Q5" s="2">
-        <v>46029.73541666667</v>
+        <v>46043.73055555556</v>
       </c>
       <c r="R5" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F6" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G6" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H6">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I6" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J6" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K6" s="2">
-        <v>46029.48125</v>
+        <v>46043.44444444445</v>
       </c>
       <c r="L6">
         <v>90</v>
       </c>
       <c r="M6" s="2">
-        <v>46029.54375</v>
+        <v>46043.50694444445</v>
       </c>
       <c r="N6">
         <v>120</v>
       </c>
       <c r="O6" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="P6" s="2">
-        <v>46029.62708333333</v>
+        <v>46043.59027777778</v>
       </c>
       <c r="Q6" s="2">
-        <v>46029.81041666667</v>
+        <v>46043.80416666667</v>
       </c>
       <c r="R6" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1271,52 +1554,52 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="G7" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H7">
-        <v>4.4185</v>
+        <v>4.5228</v>
       </c>
       <c r="I7" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J7" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K7" s="2">
-        <v>46029.58958333333</v>
+        <v>46043.50833333333</v>
       </c>
       <c r="L7">
         <v>90</v>
       </c>
       <c r="M7" s="2">
-        <v>46029.65208333333</v>
+        <v>46043.57083333333</v>
       </c>
       <c r="N7">
-        <v>120</v>
+        <v>203</v>
       </c>
       <c r="O7" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="P7" s="2">
-        <v>46029.73541666667</v>
+        <v>46043.71180555555</v>
       </c>
       <c r="Q7" s="2">
-        <v>46029.94930555556</v>
+        <v>46043.83194444444</v>
       </c>
       <c r="R7" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1327,108 +1610,108 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G8" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H8">
         <v>4.4185</v>
       </c>
       <c r="I8" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J8" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="K8" s="2">
-        <v>46029.66458333333</v>
+        <v>46043.58472222222</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8" s="2">
-        <v>46029.72708333333</v>
+        <v>46043.64722222222</v>
       </c>
       <c r="N8">
         <v>120</v>
       </c>
       <c r="O8" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="P8" s="2">
-        <v>46029.81041666667</v>
+        <v>46043.73055555556</v>
       </c>
       <c r="Q8" s="2">
-        <v>46029.99444444444</v>
+        <v>46043.91458333333</v>
       </c>
       <c r="R8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="G9" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H9">
         <v>4.4163</v>
       </c>
       <c r="I9" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J9" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="K9" s="2">
-        <v>46029.78611111111</v>
+        <v>46043.65833333333</v>
       </c>
       <c r="L9">
         <v>90</v>
       </c>
       <c r="M9" s="2">
-        <v>46029.84861111111</v>
+        <v>46043.72083333333</v>
       </c>
       <c r="N9">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="O9" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="P9" s="2">
-        <v>46029.94930555556</v>
+        <v>46043.80416666667</v>
       </c>
       <c r="Q9" s="2">
-        <v>46030.49583333333</v>
+        <v>46044.35069444445</v>
       </c>
       <c r="R9" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1439,108 +1722,108 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H10">
         <v>4.4185</v>
       </c>
       <c r="I10" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="K10" s="2">
-        <v>46029.84861111111</v>
+        <v>46043.76875</v>
       </c>
       <c r="L10">
         <v>90</v>
       </c>
       <c r="M10" s="2">
-        <v>46029.91111111111</v>
+        <v>46043.83125</v>
       </c>
       <c r="N10">
         <v>120</v>
       </c>
       <c r="O10" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="P10" s="2">
-        <v>46029.99444444444</v>
+        <v>46043.91458333333</v>
       </c>
       <c r="Q10" s="2">
-        <v>46030.17847222222</v>
+        <v>46044.43125</v>
       </c>
       <c r="R10" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H11">
-        <v>4.4185</v>
+        <v>4.5228</v>
       </c>
       <c r="I11" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J11" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K11" s="2">
-        <v>46030.03263888889</v>
+        <v>46044.06666666667</v>
       </c>
       <c r="L11">
         <v>90</v>
       </c>
       <c r="M11" s="2">
-        <v>46030.09513888889</v>
+        <v>46044.12916666667</v>
       </c>
       <c r="N11">
         <v>120</v>
       </c>
       <c r="O11" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="P11" s="2">
-        <v>46030.17847222222</v>
+        <v>46044.2125</v>
       </c>
       <c r="Q11" s="2">
-        <v>46030.36180555556</v>
+        <v>46044.33263888889</v>
       </c>
       <c r="R11" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1551,164 +1834,164 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="G12" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H12">
-        <v>4.5022</v>
+        <v>4.4185</v>
       </c>
       <c r="I12" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J12" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K12" s="2">
-        <v>46030.14583333334</v>
+        <v>46044.14583333334</v>
       </c>
       <c r="L12">
         <v>90</v>
       </c>
       <c r="M12" s="2">
-        <v>46030.20833333334</v>
+        <v>46044.20833333334</v>
       </c>
       <c r="N12">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="O12" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="P12" s="2">
-        <v>46030.31111111111</v>
+        <v>46044.35069444445</v>
       </c>
       <c r="Q12" s="2">
-        <v>46030.43125</v>
+        <v>46044.56458333333</v>
       </c>
       <c r="R12" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="G13" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H13">
-        <v>4.4185</v>
+        <v>4.5088</v>
       </c>
       <c r="I13" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J13" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K13" s="2">
-        <v>46030.20833333334</v>
+        <v>46044.20833333334</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13" s="2">
-        <v>46030.27083333334</v>
+        <v>46044.27083333334</v>
       </c>
       <c r="N13">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="O13" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="P13" s="2">
-        <v>46030.36180555556</v>
+        <v>46044.35416666666</v>
       </c>
       <c r="Q13" s="2">
-        <v>46030.54583333333</v>
+        <v>46044.54236111111</v>
       </c>
       <c r="R13" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="G14" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H14">
-        <v>4.5022</v>
+        <v>4.4185</v>
       </c>
       <c r="I14" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J14" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K14" s="2">
-        <v>46030.27083333334</v>
+        <v>46044.28194444445</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14" s="2">
-        <v>46030.33333333334</v>
+        <v>46044.34444444445</v>
       </c>
       <c r="N14">
+        <v>125</v>
+      </c>
+      <c r="O14" t="s">
         <v>141</v>
       </c>
-      <c r="O14" t="s">
-        <v>171</v>
-      </c>
       <c r="P14" s="2">
-        <v>46030.43125</v>
+        <v>46044.43125</v>
       </c>
       <c r="Q14" s="2">
-        <v>46030.55138888889</v>
+        <v>46044.61527777778</v>
       </c>
       <c r="R14" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1719,164 +2002,164 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="G15" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H15">
-        <v>4.4163</v>
+        <v>4.5088</v>
       </c>
       <c r="I15" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J15" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K15" s="2">
-        <v>46030.33333333334</v>
+        <v>46044.34444444445</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15" s="2">
-        <v>46030.39583333334</v>
+        <v>46044.40694444445</v>
       </c>
       <c r="N15">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="P15" s="2">
-        <v>46030.49583333333</v>
+        <v>46044.54236111111</v>
       </c>
       <c r="Q15" s="2">
-        <v>46030.70972222222</v>
+        <v>46044.73125</v>
       </c>
       <c r="R15" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="G16" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H16">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I16" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J16" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K16" s="2">
-        <v>46030.39583333334</v>
+        <v>46044.40694444445</v>
       </c>
       <c r="L16">
         <v>90</v>
       </c>
       <c r="M16" s="2">
-        <v>46030.45833333334</v>
+        <v>46044.46944444445</v>
       </c>
       <c r="N16">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="O16" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="P16" s="2">
-        <v>46030.54583333333</v>
+        <v>46044.56458333333</v>
       </c>
       <c r="Q16" s="2">
-        <v>46030.72916666666</v>
+        <v>46044.77777777778</v>
       </c>
       <c r="R16" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="G17" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H17">
-        <v>4.5228</v>
+        <v>4.4185</v>
       </c>
       <c r="I17" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J17" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K17" s="2">
-        <v>46030.45833333334</v>
+        <v>46044.46944444445</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17" s="2">
-        <v>46030.52083333334</v>
+        <v>46044.53194444445</v>
       </c>
       <c r="N17">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="O17" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="P17" s="2">
-        <v>46030.61180555556</v>
+        <v>46044.61527777778</v>
       </c>
       <c r="Q17" s="2">
-        <v>46030.73194444444</v>
+        <v>46044.79861111111</v>
       </c>
       <c r="R17" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1887,108 +2170,108 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
         <v>123</v>
       </c>
-      <c r="F18" t="s">
-        <v>147</v>
-      </c>
       <c r="G18" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H18">
-        <v>4.4163</v>
+        <v>4.5022</v>
       </c>
       <c r="I18" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J18" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K18" s="2">
-        <v>46030.52083333334</v>
+        <v>46044.56944444445</v>
       </c>
       <c r="L18">
         <v>90</v>
       </c>
       <c r="M18" s="2">
-        <v>46030.58333333334</v>
+        <v>46044.63194444445</v>
       </c>
       <c r="N18">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="O18" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="P18" s="2">
-        <v>46030.70972222222</v>
+        <v>46044.73125</v>
       </c>
       <c r="Q18" s="2">
-        <v>46030.92291666667</v>
+        <v>46046.33055555556</v>
       </c>
       <c r="R18" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="G19" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H19">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I19" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J19" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K19" s="2">
-        <v>46030.58333333334</v>
+        <v>46044.63194444445</v>
       </c>
       <c r="L19">
         <v>90</v>
       </c>
       <c r="M19" s="2">
-        <v>46030.64583333334</v>
+        <v>46044.69444444445</v>
       </c>
       <c r="N19">
         <v>120</v>
       </c>
       <c r="O19" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="P19" s="2">
-        <v>46030.72916666666</v>
+        <v>46044.77777777778</v>
       </c>
       <c r="Q19" s="2">
-        <v>46030.91319444445</v>
+        <v>46046.47083333333</v>
       </c>
       <c r="R19" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1999,612 +2282,612 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20">
+        <v>2.2511</v>
+      </c>
+      <c r="I20" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" t="s">
+        <v>136</v>
+      </c>
+      <c r="K20" s="2">
+        <v>46043</v>
+      </c>
+      <c r="L20">
+        <v>65</v>
+      </c>
+      <c r="M20" s="2">
+        <v>46043.04513888889</v>
+      </c>
+      <c r="N20">
+        <v>505</v>
+      </c>
+      <c r="O20" t="s">
+        <v>143</v>
+      </c>
+      <c r="P20" s="2">
+        <v>46043.39583333334</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>46043.69097222222</v>
+      </c>
+      <c r="R20" t="s">
         <v>150</v>
-      </c>
-      <c r="G20" t="s">
-        <v>161</v>
-      </c>
-      <c r="H20">
-        <v>0.5601</v>
-      </c>
-      <c r="I20" t="s">
-        <v>162</v>
-      </c>
-      <c r="J20" t="s">
-        <v>165</v>
-      </c>
-      <c r="K20" s="2">
-        <v>46028.1875</v>
-      </c>
-      <c r="L20">
-        <v>180</v>
-      </c>
-      <c r="M20" s="2">
-        <v>46028.3125</v>
-      </c>
-      <c r="N20">
-        <v>1440</v>
-      </c>
-      <c r="O20" t="s">
-        <v>173</v>
-      </c>
-      <c r="P20" s="2">
-        <v>46029.3125</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>46029.48125</v>
-      </c>
-      <c r="R20" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21">
+        <v>2.2544</v>
+      </c>
+      <c r="I21" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" t="s">
+        <v>137</v>
+      </c>
+      <c r="K21" s="2">
+        <v>46043.05902777778</v>
+      </c>
+      <c r="L21">
+        <v>85</v>
+      </c>
+      <c r="M21" s="2">
+        <v>46043.11805555555</v>
+      </c>
+      <c r="N21">
+        <v>551</v>
+      </c>
+      <c r="O21" t="s">
+        <v>145</v>
+      </c>
+      <c r="P21" s="2">
+        <v>46043.50069444445</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>46043.59513888889</v>
+      </c>
+      <c r="R21" t="s">
         <v>150</v>
-      </c>
-      <c r="G21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21">
-        <v>0.5601</v>
-      </c>
-      <c r="I21" t="s">
-        <v>162</v>
-      </c>
-      <c r="J21" t="s">
-        <v>166</v>
-      </c>
-      <c r="K21" s="2">
-        <v>46028.45625</v>
-      </c>
-      <c r="L21">
-        <v>180</v>
-      </c>
-      <c r="M21" s="2">
-        <v>46028.58125</v>
-      </c>
-      <c r="N21">
-        <v>1440</v>
-      </c>
-      <c r="O21" t="s">
-        <v>175</v>
-      </c>
-      <c r="P21" s="2">
-        <v>46029.58125</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>46030.41666666666</v>
-      </c>
-      <c r="R21" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H22">
-        <v>2.2314</v>
+        <v>1.128</v>
       </c>
       <c r="I22" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J22" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="K22" s="2">
-        <v>46028.71527777778</v>
+        <v>46043.13194444445</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M22" s="2">
-        <v>46028.77777777778</v>
+        <v>46043.25694444445</v>
       </c>
       <c r="N22">
-        <v>890</v>
+        <v>472</v>
       </c>
       <c r="O22" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="P22" s="2">
-        <v>46029.39583333334</v>
+        <v>46043.58472222222</v>
       </c>
       <c r="Q22" s="2">
-        <v>46029.62916666667</v>
+        <v>46043.62638888889</v>
       </c>
       <c r="R22" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="G23" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1.8035</v>
       </c>
       <c r="I23" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J23" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K23" s="2">
-        <v>46028.8125</v>
+        <v>46043.27083333334</v>
       </c>
       <c r="L23">
         <v>90</v>
       </c>
       <c r="M23" s="2">
-        <v>46028.875</v>
+        <v>46043.33333333334</v>
       </c>
       <c r="N23">
-        <v>2220</v>
+        <v>420</v>
       </c>
       <c r="O23" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="P23" s="2">
-        <v>46030.41666666666</v>
+        <v>46043.625</v>
       </c>
       <c r="Q23" s="2">
-        <v>46030.59652777778</v>
+        <v>46043.7</v>
       </c>
       <c r="R23" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H24">
-        <v>2.19</v>
+        <v>0.4364</v>
       </c>
       <c r="I24" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K24" s="2">
-        <v>46028.91666666666</v>
+        <v>46043.33333333334</v>
       </c>
       <c r="L24">
         <v>90</v>
       </c>
       <c r="M24" s="2">
-        <v>46028.97916666666</v>
+        <v>46043.39583333334</v>
       </c>
       <c r="N24">
-        <v>800</v>
+        <v>438</v>
       </c>
       <c r="O24" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="P24" s="2">
-        <v>46029.53472222222</v>
+        <v>46043.7</v>
       </c>
       <c r="Q24" s="2">
-        <v>46030.25</v>
+        <v>46043.71180555555</v>
       </c>
       <c r="R24" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="G25" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H25">
-        <v>1.128</v>
+        <v>2.2511</v>
       </c>
       <c r="I25" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="J25" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="K25" s="2">
-        <v>46028.99305555555</v>
+        <v>46043.40972222222</v>
       </c>
       <c r="L25">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="M25" s="2">
-        <v>46029.11805555555</v>
+        <v>46043.45486111111</v>
       </c>
       <c r="N25">
-        <v>787</v>
+        <v>340</v>
       </c>
       <c r="O25" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="P25" s="2">
-        <v>46029.66458333333</v>
+        <v>46043.69097222222</v>
       </c>
       <c r="Q25" s="2">
-        <v>46029.70625</v>
+        <v>46044.31944444445</v>
       </c>
       <c r="R25" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H26">
-        <v>2.2511</v>
+        <v>2.2314</v>
       </c>
       <c r="I26" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="J26" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="K26" s="2">
-        <v>46029.13194444445</v>
+        <v>46043.46875</v>
       </c>
       <c r="L26">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M26" s="2">
-        <v>46029.19097222222</v>
+        <v>46043.53125</v>
       </c>
       <c r="N26">
-        <v>631</v>
+        <v>433</v>
       </c>
       <c r="O26" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="P26" s="2">
-        <v>46029.62916666667</v>
+        <v>46043.83194444444</v>
       </c>
       <c r="Q26" s="2">
-        <v>46029.68958333333</v>
+        <v>46044.06527777778</v>
       </c>
       <c r="R26" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27">
+        <v>1.128</v>
+      </c>
+      <c r="I27" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" t="s">
+        <v>138</v>
+      </c>
+      <c r="K27" s="2">
+        <v>46043.54513888889</v>
+      </c>
+      <c r="L27">
+        <v>180</v>
+      </c>
+      <c r="M27" s="2">
+        <v>46043.67013888889</v>
+      </c>
+      <c r="N27">
+        <v>359</v>
+      </c>
+      <c r="O27" t="s">
+        <v>148</v>
+      </c>
+      <c r="P27" s="2">
+        <v>46043.91944444444</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>46043.96111111111</v>
+      </c>
+      <c r="R27" t="s">
         <v>152</v>
-      </c>
-      <c r="G27" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" t="s">
-        <v>162</v>
-      </c>
-      <c r="J27" t="s">
-        <v>166</v>
-      </c>
-      <c r="K27" s="2">
-        <v>46029.22569444445</v>
-      </c>
-      <c r="L27">
-        <v>90</v>
-      </c>
-      <c r="M27" s="2">
-        <v>46029.28819444445</v>
-      </c>
-      <c r="N27">
-        <v>1884</v>
-      </c>
-      <c r="O27" t="s">
-        <v>178</v>
-      </c>
-      <c r="P27" s="2">
-        <v>46030.59652777778</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>46031.41736111111</v>
-      </c>
-      <c r="R27" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" t="s">
         <v>133</v>
       </c>
-      <c r="F28" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" t="s">
-        <v>161</v>
-      </c>
       <c r="H28">
-        <v>2.2511</v>
+        <v>1.1157</v>
       </c>
       <c r="I28" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J28" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="K28" s="2">
-        <v>46029.32986111111</v>
+        <v>46043.68402777778</v>
       </c>
       <c r="L28">
         <v>90</v>
       </c>
       <c r="M28" s="2">
-        <v>46029.39236111111</v>
+        <v>46043.74652777778</v>
       </c>
       <c r="N28">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="O28" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="P28" s="2">
-        <v>46029.68958333333</v>
+        <v>46044.06527777778</v>
       </c>
       <c r="Q28" s="2">
-        <v>46029.75</v>
+        <v>46044.18194444444</v>
       </c>
       <c r="R28" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" t="s">
+        <v>133</v>
+      </c>
+      <c r="H29">
+        <v>1.128</v>
+      </c>
+      <c r="I29" t="s">
         <v>134</v>
       </c>
-      <c r="F29" t="s">
-        <v>156</v>
-      </c>
-      <c r="G29" t="s">
-        <v>161</v>
-      </c>
-      <c r="H29">
-        <v>1.1225</v>
-      </c>
-      <c r="I29" t="s">
-        <v>162</v>
-      </c>
       <c r="J29" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="K29" s="2">
-        <v>46029.40625</v>
+        <v>46043.76041666666</v>
       </c>
       <c r="L29">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M29" s="2">
-        <v>46029.46875</v>
+        <v>46043.88541666666</v>
       </c>
       <c r="N29">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="O29" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="P29" s="2">
-        <v>46029.75</v>
+        <v>46044.14583333334</v>
       </c>
       <c r="Q29" s="2">
-        <v>46029.77986111111</v>
+        <v>46044.1875</v>
       </c>
       <c r="R29" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F30" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="G30" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H30">
-        <v>1.1174</v>
+        <v>1.1307</v>
       </c>
       <c r="I30" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J30" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="K30" s="2">
-        <v>46029.46875</v>
+        <v>46043.89930555555</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30" s="2">
-        <v>46029.53125</v>
+        <v>46043.96180555555</v>
       </c>
       <c r="N30">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="O30" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="P30" s="2">
-        <v>46029.77986111111</v>
+        <v>46044.18194444444</v>
       </c>
       <c r="Q30" s="2">
-        <v>46029.82638888889</v>
+        <v>46044.2125</v>
       </c>
       <c r="R30" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2615,612 +2898,1360 @@
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H31">
         <v>1.128</v>
       </c>
       <c r="I31" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J31" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="K31" s="2">
-        <v>46029.54513888889</v>
+        <v>46043.97569444445</v>
       </c>
       <c r="L31">
         <v>180</v>
       </c>
       <c r="M31" s="2">
-        <v>46029.67013888889</v>
+        <v>46044.10069444445</v>
       </c>
       <c r="N31">
-        <v>257</v>
+        <v>351</v>
       </c>
       <c r="O31" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="P31" s="2">
-        <v>46029.84861111111</v>
+        <v>46044.34444444445</v>
       </c>
       <c r="Q31" s="2">
-        <v>46029.89027777778</v>
+        <v>46044.38611111111</v>
       </c>
       <c r="R31" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="G32" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H32">
-        <v>2.2544</v>
+        <v>0.9522</v>
       </c>
       <c r="I32" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="J32" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="K32" s="2">
-        <v>46029.68402777778</v>
+        <v>46044.11458333334</v>
       </c>
       <c r="L32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M32" s="2">
-        <v>46029.74305555555</v>
+        <v>46044.17708333334</v>
       </c>
       <c r="N32">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="O32" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="P32" s="2">
-        <v>46029.82638888889</v>
+        <v>46044.33263888889</v>
       </c>
       <c r="Q32" s="2">
-        <v>46029.92083333333</v>
+        <v>46044.35763888889</v>
       </c>
       <c r="R32" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="G33" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="H33">
-        <v>1.128</v>
+        <v>2.2511</v>
       </c>
       <c r="I33" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="J33" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="K33" s="2">
-        <v>46029.92638888889</v>
+        <v>46044.19097222222</v>
       </c>
       <c r="L33">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="M33" s="2">
-        <v>46030.05138888889</v>
+        <v>46044.23611111111</v>
       </c>
       <c r="N33">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="O33" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="P33" s="2">
-        <v>46030.20833333334</v>
+        <v>46044.31944444445</v>
       </c>
       <c r="Q33" s="2">
-        <v>46030.25</v>
+        <v>46044.61527777778</v>
       </c>
       <c r="R33" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" t="s">
+        <v>67</v>
+      </c>
+      <c r="G34" t="s">
+        <v>133</v>
+      </c>
+      <c r="H34">
+        <v>1.128</v>
+      </c>
+      <c r="I34" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" t="s">
+        <v>137</v>
+      </c>
+      <c r="K34" s="2">
+        <v>46044.34791666667</v>
+      </c>
+      <c r="L34">
+        <v>180</v>
+      </c>
+      <c r="M34" s="2">
+        <v>46044.47291666667</v>
+      </c>
+      <c r="N34">
         <v>139</v>
       </c>
-      <c r="F34" t="s">
-        <v>157</v>
-      </c>
-      <c r="G34" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34">
-        <v>2.2614</v>
-      </c>
-      <c r="I34" t="s">
-        <v>162</v>
-      </c>
-      <c r="J34" t="s">
-        <v>165</v>
-      </c>
-      <c r="K34" s="2">
-        <v>46030.06527777778</v>
-      </c>
-      <c r="L34">
-        <v>90</v>
-      </c>
-      <c r="M34" s="2">
-        <v>46030.12777777778</v>
-      </c>
-      <c r="N34">
-        <v>177</v>
-      </c>
       <c r="O34" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="P34" s="2">
-        <v>46030.25069444445</v>
+        <v>46044.56944444445</v>
       </c>
       <c r="Q34" s="2">
-        <v>46030.31111111111</v>
+        <v>46044.61111111111</v>
       </c>
       <c r="R34" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
         <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F35" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="G35" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35">
+        <v>2.2511</v>
+      </c>
+      <c r="I35" t="s">
+        <v>135</v>
+      </c>
+      <c r="J35" t="s">
+        <v>137</v>
+      </c>
+      <c r="K35" s="2">
+        <v>46044.48680555556</v>
+      </c>
+      <c r="L35">
+        <v>65</v>
+      </c>
+      <c r="M35" s="2">
+        <v>46044.53194444445</v>
+      </c>
+      <c r="N35">
+        <v>120</v>
+      </c>
+      <c r="O35" t="s">
+        <v>149</v>
+      </c>
+      <c r="P35" s="2">
+        <v>46044.61527777778</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>46046.38958333333</v>
+      </c>
+      <c r="R35" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E86"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="5" width="40.7109375" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>161</v>
       </c>
-      <c r="H35">
-        <v>1.128</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="B8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>162</v>
       </c>
-      <c r="J35" t="s">
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>165</v>
       </c>
-      <c r="K35" s="2">
-        <v>46030.14166666667</v>
-      </c>
-      <c r="L35">
+      <c r="B12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
         <v>180</v>
       </c>
-      <c r="M35" s="2">
-        <v>46030.26666666667</v>
-      </c>
-      <c r="N35">
+      <c r="B27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
         <v>186</v>
       </c>
-      <c r="O35" t="s">
-        <v>169</v>
-      </c>
-      <c r="P35" s="2">
-        <v>46030.39583333334</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>46030.4375</v>
-      </c>
-      <c r="R35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="B33" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>187</v>
+      </c>
+      <c r="B34" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" t="s">
-        <v>161</v>
-      </c>
-      <c r="H36">
-        <v>1.128</v>
-      </c>
-      <c r="I36" t="s">
-        <v>162</v>
-      </c>
-      <c r="J36" t="s">
-        <v>166</v>
-      </c>
-      <c r="K36" s="2">
-        <v>46030.26666666667</v>
-      </c>
-      <c r="L36">
-        <v>180</v>
-      </c>
-      <c r="M36" s="2">
-        <v>46030.39166666667</v>
-      </c>
-      <c r="N36">
-        <v>276</v>
-      </c>
-      <c r="O36" t="s">
-        <v>172</v>
-      </c>
-      <c r="P36" s="2">
-        <v>46030.58333333334</v>
-      </c>
-      <c r="Q36" s="2">
-        <v>46030.625</v>
-      </c>
-      <c r="R36" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
+        <v>138</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" t="s">
-        <v>142</v>
-      </c>
-      <c r="F37" t="s">
-        <v>151</v>
-      </c>
-      <c r="G37" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37">
-        <v>2.2614</v>
-      </c>
-      <c r="I37" t="s">
-        <v>162</v>
-      </c>
-      <c r="J37" t="s">
-        <v>166</v>
-      </c>
-      <c r="K37" s="2">
-        <v>46030.40555555555</v>
-      </c>
-      <c r="L37">
-        <v>90</v>
-      </c>
-      <c r="M37" s="2">
-        <v>46030.46805555555</v>
-      </c>
-      <c r="N37">
-        <v>120</v>
-      </c>
-      <c r="O37" t="s">
-        <v>167</v>
-      </c>
-      <c r="P37" s="2">
-        <v>46030.55138888889</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>46030.61180555556</v>
-      </c>
-      <c r="R37" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
+        <v>138</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" t="s">
-        <v>143</v>
-      </c>
-      <c r="F38" t="s">
-        <v>149</v>
-      </c>
-      <c r="G38" t="s">
-        <v>161</v>
-      </c>
-      <c r="H38">
-        <v>2.2314</v>
-      </c>
-      <c r="I38" t="s">
-        <v>162</v>
-      </c>
-      <c r="J38" t="s">
-        <v>166</v>
-      </c>
-      <c r="K38" s="2">
-        <v>46030.58611111111</v>
-      </c>
-      <c r="L38">
-        <v>90</v>
-      </c>
-      <c r="M38" s="2">
-        <v>46030.64861111111</v>
-      </c>
-      <c r="N38">
-        <v>120</v>
-      </c>
-      <c r="O38" t="s">
-        <v>167</v>
-      </c>
-      <c r="P38" s="2">
-        <v>46030.73194444444</v>
-      </c>
-      <c r="Q38" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="R38" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
+        <v>138</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>104</v>
-      </c>
-      <c r="E39" t="s">
-        <v>144</v>
-      </c>
-      <c r="F39" t="s">
-        <v>158</v>
-      </c>
-      <c r="G39" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39">
-        <v>2.1937</v>
-      </c>
-      <c r="I39" t="s">
-        <v>162</v>
-      </c>
-      <c r="J39" t="s">
-        <v>164</v>
-      </c>
-      <c r="K39" s="2">
-        <v>46030.67708333334</v>
-      </c>
-      <c r="L39">
-        <v>85</v>
-      </c>
-      <c r="M39" s="2">
-        <v>46030.73611111111</v>
-      </c>
-      <c r="N39">
-        <v>266</v>
-      </c>
-      <c r="O39" t="s">
-        <v>173</v>
-      </c>
-      <c r="P39" s="2">
-        <v>46030.92083333333</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="R39" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
+        <v>138</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E40" t="s">
-        <v>145</v>
-      </c>
-      <c r="F40" t="s">
-        <v>159</v>
-      </c>
-      <c r="G40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H40">
-        <v>2.2314</v>
-      </c>
-      <c r="I40" t="s">
-        <v>162</v>
-      </c>
-      <c r="J40" t="s">
-        <v>164</v>
-      </c>
-      <c r="K40" s="2">
-        <v>46030.75</v>
-      </c>
-      <c r="L40">
-        <v>85</v>
-      </c>
-      <c r="M40" s="2">
-        <v>46030.80902777778</v>
-      </c>
-      <c r="N40">
+        <v>138</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>196</v>
+      </c>
+      <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>197</v>
+      </c>
+      <c r="B44" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>200</v>
+      </c>
+      <c r="B47" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>201</v>
+      </c>
+      <c r="B48" t="s">
+        <v>138</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>203</v>
+      </c>
+      <c r="B50" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>204</v>
+      </c>
+      <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>208</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>209</v>
+      </c>
+      <c r="B56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>210</v>
+      </c>
+      <c r="B57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>211</v>
+      </c>
+      <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>212</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>213</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>214</v>
+      </c>
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>215</v>
+      </c>
+      <c r="B62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>217</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>218</v>
+      </c>
+      <c r="B65" t="s">
+        <v>137</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>219</v>
+      </c>
+      <c r="B66" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>220</v>
+      </c>
+      <c r="B67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>221</v>
+      </c>
+      <c r="B68" t="s">
+        <v>137</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>222</v>
+      </c>
+      <c r="B69" t="s">
+        <v>137</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>223</v>
+      </c>
+      <c r="B70" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>224</v>
+      </c>
+      <c r="B71" t="s">
+        <v>137</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
         <v>225</v>
       </c>
-      <c r="O40" t="s">
-        <v>175</v>
-      </c>
-      <c r="P40" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="Q40" s="2">
-        <v>46031.19930555556</v>
-      </c>
-      <c r="R40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" t="s">
-        <v>146</v>
-      </c>
-      <c r="F41" t="s">
-        <v>154</v>
-      </c>
-      <c r="G41" t="s">
-        <v>161</v>
-      </c>
-      <c r="H41">
-        <v>2.2614</v>
-      </c>
-      <c r="I41" t="s">
-        <v>163</v>
-      </c>
-      <c r="J41" t="s">
-        <v>164</v>
-      </c>
-      <c r="K41" s="2">
-        <v>46030.82291666666</v>
-      </c>
-      <c r="L41">
-        <v>85</v>
-      </c>
-      <c r="M41" s="2">
-        <v>46030.88194444445</v>
-      </c>
-      <c r="N41">
-        <v>120</v>
-      </c>
-      <c r="O41" t="s">
-        <v>177</v>
-      </c>
-      <c r="P41" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="Q41" s="2">
-        <v>46030.53472222222</v>
-      </c>
-      <c r="R41" t="s">
-        <v>179</v>
+      <c r="B72" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>226</v>
+      </c>
+      <c r="B73" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>227</v>
+      </c>
+      <c r="B74" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" t="s">
+        <v>137</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>229</v>
+      </c>
+      <c r="B76" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>230</v>
+      </c>
+      <c r="B77" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>231</v>
+      </c>
+      <c r="B78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" t="s">
+        <v>137</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>233</v>
+      </c>
+      <c r="B80" t="s">
+        <v>137</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>234</v>
+      </c>
+      <c r="B81" t="s">
+        <v>138</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>236</v>
+      </c>
+      <c r="B83" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>237</v>
+      </c>
+      <c r="B84" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>238</v>
+      </c>
+      <c r="B85" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>239</v>
+      </c>
+      <c r="B86" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="352">
   <si>
     <t>Production Line</t>
   </si>
@@ -71,348 +71,420 @@
     <t>MRP Status</t>
   </si>
   <si>
+    <t>INC4</t>
+  </si>
+  <si>
+    <t>INC1</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
     <t>INT2</t>
   </si>
   <si>
-    <t>INC1</t>
-  </si>
-  <si>
-    <t>INC4</t>
-  </si>
-  <si>
-    <t>INC2</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>910741796</t>
-  </si>
-  <si>
-    <t>910741853</t>
-  </si>
-  <si>
-    <t>910741877</t>
-  </si>
-  <si>
-    <t>910741876</t>
-  </si>
-  <si>
-    <t>910741953</t>
-  </si>
-  <si>
-    <t>910741779</t>
-  </si>
-  <si>
-    <t>910741865</t>
-  </si>
-  <si>
-    <t>910744377</t>
-  </si>
-  <si>
-    <t>910744323</t>
-  </si>
-  <si>
-    <t>910744285</t>
-  </si>
-  <si>
-    <t>910744343</t>
-  </si>
-  <si>
-    <t>910744367</t>
-  </si>
-  <si>
-    <t>910744273</t>
-  </si>
-  <si>
-    <t>910744375</t>
-  </si>
-  <si>
-    <t>910744370</t>
-  </si>
-  <si>
-    <t>910744371</t>
-  </si>
-  <si>
-    <t>910744407</t>
-  </si>
-  <si>
-    <t>910744406</t>
-  </si>
-  <si>
-    <t>910739741</t>
-  </si>
-  <si>
-    <t>910741725</t>
+    <t>INT3</t>
+  </si>
+  <si>
+    <t>910715043</t>
+  </si>
+  <si>
+    <t>910712428</t>
+  </si>
+  <si>
+    <t>910712578</t>
+  </si>
+  <si>
+    <t>910714990</t>
   </si>
   <si>
     <t>AUTO_1</t>
   </si>
   <si>
-    <t>910741769</t>
-  </si>
-  <si>
-    <t>910741836</t>
-  </si>
-  <si>
-    <t>910739800</t>
-  </si>
-  <si>
-    <t>910741819</t>
+    <t>910712440</t>
+  </si>
+  <si>
+    <t>910717240</t>
+  </si>
+  <si>
+    <t>910717114</t>
+  </si>
+  <si>
+    <t>910717241</t>
+  </si>
+  <si>
+    <t>910717201</t>
   </si>
   <si>
     <t>AUTO_2</t>
   </si>
   <si>
-    <t>910744010</t>
+    <t>910717256</t>
+  </si>
+  <si>
+    <t>910717300</t>
+  </si>
+  <si>
+    <t>910717224</t>
+  </si>
+  <si>
+    <t>910717257</t>
+  </si>
+  <si>
+    <t>910717202</t>
   </si>
   <si>
     <t>AUTO_3</t>
   </si>
   <si>
-    <t>910744097</t>
-  </si>
-  <si>
-    <t>AUTO_4</t>
-  </si>
-  <si>
-    <t>910744413</t>
-  </si>
-  <si>
-    <t>910744378</t>
-  </si>
-  <si>
-    <t>AUTO_5</t>
-  </si>
-  <si>
-    <t>910744344</t>
-  </si>
-  <si>
-    <t>80880903</t>
+    <t>910717296</t>
+  </si>
+  <si>
+    <t>910717377</t>
+  </si>
+  <si>
+    <t>910717225</t>
+  </si>
+  <si>
+    <t>910717276</t>
+  </si>
+  <si>
+    <t>910714830</t>
+  </si>
+  <si>
+    <t>910714891</t>
+  </si>
+  <si>
+    <t>910715191</t>
+  </si>
+  <si>
+    <t>910717129</t>
+  </si>
+  <si>
+    <t>910715192</t>
+  </si>
+  <si>
+    <t>910715241</t>
+  </si>
+  <si>
+    <t>910717198</t>
+  </si>
+  <si>
+    <t>910715257</t>
+  </si>
+  <si>
+    <t>910715048</t>
+  </si>
+  <si>
+    <t>910715049</t>
+  </si>
+  <si>
+    <t>910715240</t>
+  </si>
+  <si>
+    <t>910717302</t>
+  </si>
+  <si>
+    <t>910717251</t>
+  </si>
+  <si>
+    <t>910717299</t>
+  </si>
+  <si>
+    <t>910717359</t>
+  </si>
+  <si>
+    <t>910717417</t>
+  </si>
+  <si>
+    <t>910717252</t>
+  </si>
+  <si>
+    <t>83900260</t>
   </si>
   <si>
     <t>83900263</t>
   </si>
   <si>
-    <t>83900259</t>
+    <t>95619314</t>
+  </si>
+  <si>
+    <t>83900262</t>
+  </si>
+  <si>
+    <t>80880898</t>
+  </si>
+  <si>
+    <t>80880902</t>
+  </si>
+  <si>
+    <t>80841061</t>
+  </si>
+  <si>
+    <t>80880885</t>
+  </si>
+  <si>
+    <t>80830098</t>
+  </si>
+  <si>
+    <t>80879282</t>
+  </si>
+  <si>
+    <t>80879287</t>
+  </si>
+  <si>
+    <t>80878378</t>
+  </si>
+  <si>
+    <t>80879283</t>
+  </si>
+  <si>
+    <t>80889640</t>
+  </si>
+  <si>
+    <t>80889635</t>
+  </si>
+  <si>
+    <t>80879278</t>
+  </si>
+  <si>
+    <t>80896348</t>
   </si>
   <si>
     <t>80880904</t>
   </si>
   <si>
-    <t>80880902</t>
-  </si>
-  <si>
-    <t>83900261</t>
-  </si>
-  <si>
-    <t>83900262</t>
-  </si>
-  <si>
-    <t>80880898</t>
-  </si>
-  <si>
-    <t>80750817</t>
-  </si>
-  <si>
-    <t>80880895</t>
-  </si>
-  <si>
-    <t>95619314</t>
-  </si>
-  <si>
-    <t>80880920</t>
-  </si>
-  <si>
-    <t>80896867</t>
-  </si>
-  <si>
     <t>80880883</t>
   </si>
   <si>
-    <t>80880909</t>
-  </si>
-  <si>
-    <t>80896354</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+    <t>80879268</t>
+  </si>
+  <si>
+    <t>80880881</t>
+  </si>
+  <si>
+    <t>80879274</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+    <t>Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 72ML X 48 AHF IN GST</t>
+  </si>
+  <si>
+    <t>PNTN 3MM BIOTIN COND 200MLX24 IN</t>
+  </si>
+  <si>
+    <t>PNTN SHM 75 ML X 48 HS DR IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650ML X 12 SSC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 180MLX56 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
   </si>
   <si>
     <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
   </si>
   <si>
-    <t>H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 180ML X 56 CM IN GST</t>
-  </si>
-  <si>
-    <t>Auto-Replenishment HC Base</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 180ML X 56 AP 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 340ML X 30 AP 2IN1 IN GST</t>
-  </si>
-  <si>
     <t>H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
   </si>
   <si>
-    <t>H&amp;S SHM 72MLX48 S&amp;S 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 340ML X 30 S&amp;S 2IN1 IN GST</t>
+    <t>PNTN SHM 400MLX30 HS LC IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 72 ML X 48 CM IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B010</t>
+  </si>
+  <si>
+    <t>B001</t>
+  </si>
+  <si>
+    <t>B002</t>
+  </si>
+  <si>
+    <t>B011</t>
+  </si>
+  <si>
+    <t>REP36</t>
+  </si>
+  <si>
+    <t>B003</t>
+  </si>
+  <si>
+    <t>B012</t>
+  </si>
+  <si>
+    <t>B004</t>
+  </si>
+  <si>
+    <t>B013</t>
+  </si>
+  <si>
+    <t>B005</t>
+  </si>
+  <si>
+    <t>REP37</t>
+  </si>
+  <si>
+    <t>B006</t>
+  </si>
+  <si>
+    <t>B026</t>
+  </si>
+  <si>
+    <t>B007</t>
+  </si>
+  <si>
+    <t>B027</t>
+  </si>
+  <si>
+    <t>B014</t>
+  </si>
+  <si>
+    <t>REP38</t>
+  </si>
+  <si>
+    <t>B008</t>
+  </si>
+  <si>
+    <t>B029</t>
+  </si>
+  <si>
+    <t>B015</t>
+  </si>
+  <si>
+    <t>B009</t>
+  </si>
+  <si>
+    <t>B032</t>
+  </si>
+  <si>
+    <t>B033</t>
+  </si>
+  <si>
+    <t>B016</t>
+  </si>
+  <si>
+    <t>B034</t>
+  </si>
+  <si>
+    <t>B024</t>
   </si>
   <si>
     <t>B017</t>
   </si>
   <si>
-    <t>B001</t>
-  </si>
-  <si>
-    <t>B011</t>
-  </si>
-  <si>
-    <t>B002</t>
-  </si>
-  <si>
-    <t>B012</t>
+    <t>B035</t>
+  </si>
+  <si>
+    <t>B018</t>
+  </si>
+  <si>
+    <t>B019</t>
+  </si>
+  <si>
+    <t>B020</t>
   </si>
   <si>
     <t>B021</t>
   </si>
   <si>
-    <t>B003</t>
-  </si>
-  <si>
-    <t>B013</t>
-  </si>
-  <si>
-    <t>B004</t>
-  </si>
-  <si>
     <t>B025</t>
   </si>
   <si>
-    <t>B014</t>
-  </si>
-  <si>
-    <t>B027</t>
-  </si>
-  <si>
-    <t>B005</t>
-  </si>
-  <si>
     <t>B028</t>
   </si>
   <si>
-    <t>B015</t>
-  </si>
-  <si>
-    <t>B006</t>
-  </si>
-  <si>
-    <t>B029</t>
-  </si>
-  <si>
-    <t>B016</t>
-  </si>
-  <si>
-    <t>B007</t>
-  </si>
-  <si>
-    <t>B018</t>
-  </si>
-  <si>
-    <t>REP30</t>
-  </si>
-  <si>
-    <t>B019</t>
-  </si>
-  <si>
-    <t>B020</t>
-  </si>
-  <si>
-    <t>B008</t>
+    <t>B030</t>
   </si>
   <si>
     <t>B022</t>
   </si>
   <si>
-    <t>REP31</t>
+    <t>B031</t>
   </si>
   <si>
     <t>B023</t>
   </si>
   <si>
-    <t>REP32</t>
-  </si>
-  <si>
-    <t>B024</t>
-  </si>
-  <si>
-    <t>REP33</t>
-  </si>
-  <si>
-    <t>B026</t>
-  </si>
-  <si>
-    <t>B009</t>
-  </si>
-  <si>
-    <t>REP34</t>
-  </si>
-  <si>
-    <t>B010</t>
+    <t>21453170</t>
+  </si>
+  <si>
+    <t>21470269</t>
   </si>
   <si>
     <t>21422079</t>
   </si>
   <si>
-    <t>21470269</t>
+    <t>21090111</t>
   </si>
   <si>
     <t>21417344</t>
   </si>
   <si>
-    <t>21470270</t>
-  </si>
-  <si>
-    <t>21453170</t>
-  </si>
-  <si>
-    <t>90275009</t>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>'21302239</t>
+  </si>
+  <si>
+    <t>21302239</t>
+  </si>
+  <si>
+    <t>'21302240</t>
+  </si>
+  <si>
+    <t>21309190</t>
+  </si>
+  <si>
+    <t>21309189</t>
+  </si>
+  <si>
+    <t>20256318</t>
   </si>
   <si>
     <t>90947730</t>
   </si>
   <si>
-    <t>91005113</t>
-  </si>
-  <si>
-    <t>21432817</t>
-  </si>
-  <si>
     <t>12T</t>
   </si>
   <si>
@@ -425,55 +497,49 @@
     <t>Dual</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>B</t>
+    <t>TK#_24_#</t>
+  </si>
+  <si>
+    <t>TK#_14_#</t>
+  </si>
+  <si>
+    <t>TK#_15_#</t>
+  </si>
+  <si>
+    <t>NO_TANK_AVAILABLE</t>
   </si>
   <si>
     <t>TK#_9_#</t>
   </si>
   <si>
-    <t>TK#_24_#</t>
-  </si>
-  <si>
-    <t>TK#_14_#</t>
-  </si>
-  <si>
-    <t>TK#_15_#</t>
-  </si>
-  <si>
-    <t>TK#_57_#</t>
+    <t>TK#_23_#</t>
+  </si>
+  <si>
+    <t>TK#_53_#</t>
+  </si>
+  <si>
+    <t>TK#_16_#</t>
   </si>
   <si>
     <t>TK#_12_#</t>
   </si>
   <si>
-    <t>TK#_58_#</t>
-  </si>
-  <si>
-    <t>TK#_56_#</t>
-  </si>
-  <si>
-    <t>TK#_23_#</t>
-  </si>
-  <si>
-    <t>TK#_53_#</t>
-  </si>
-  <si>
-    <t>TK#_16_#</t>
-  </si>
-  <si>
-    <t>LOW: SLE3S</t>
+    <t>LOW: SLS</t>
   </si>
   <si>
     <t>LOW: DM5500</t>
   </si>
   <si>
-    <t>LOW: SLS</t>
+    <t>UNKNOWN_SKU</t>
   </si>
   <si>
     <t>Time</t>
@@ -482,364 +548,529 @@
     <t>1.25T</t>
   </si>
   <si>
-    <t>2026-01-21 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-21 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-21 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-22 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-22 18:00</t>
-  </si>
-  <si>
-    <t>B017: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+    <t>2026-01-06 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-06 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-06 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-07 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-07 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-08 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-08 23:00</t>
+  </si>
+  <si>
+    <t>B010: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B001: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B011: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
     <t>B002: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B012: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B021: H&amp;S SHM 340ML X30 AHF IN GST</t>
+    <t>B011: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>WASHOUT</t>
   </si>
   <si>
+    <t>REP36: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
     <t>B003: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B013: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+    <t>B012: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B004: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B025: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B014: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>B027: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+    <t>B013: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B028: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+    <t>REP37: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>B006: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B026: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B007: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B027: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B014: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>REP38: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>B008: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B029: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
   </si>
   <si>
     <t>B015: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
-    <t>B006: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B029: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B016: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B007: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
-  </si>
-  <si>
-    <t>B018: H&amp;S SHM 180ML X 56 CM IN GST</t>
-  </si>
-  <si>
-    <t>REP30: Auto-Replenishment HC Base</t>
-  </si>
-  <si>
-    <t>B019: H&amp;S SHM 180ML X 56 AP 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>B020: H&amp;S SHM 340ML X 30 AP 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>B008: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
-  </si>
-  <si>
-    <t>B022: H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>REP31: Auto-Replenishment HC Base</t>
-  </si>
-  <si>
-    <t>B023: H&amp;S SHM 72MLX48 S&amp;S 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>REP32: Auto-Replenishment HC Base</t>
-  </si>
-  <si>
-    <t>B024: H&amp;S SHM 340ML X 30 S&amp;S 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>REP33: Auto-Replenishment HC Base</t>
-  </si>
-  <si>
-    <t>B026: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B009: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
-  </si>
-  <si>
-    <t>REP34: Auto-Replenishment HC Base</t>
-  </si>
-  <si>
-    <t>B010: H&amp;S SHM 9.1 ML X 800 MF 2in1 IN CL DF</t>
+    <t>B009: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B032: PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>COND WASH (60m)</t>
+  </si>
+  <si>
+    <t>B033: PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>B016: H&amp;S SHM 72ML X 48 AHF IN GST</t>
+  </si>
+  <si>
+    <t>B034: PNTN 3MM BIOTIN COND 200MLX24 IN</t>
+  </si>
+  <si>
+    <t>B024: PNTN SHM 75 ML X 48 HS DR IN GST</t>
+  </si>
+  <si>
+    <t>B017: PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>B035: PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
+  </si>
+  <si>
+    <t>B018: PNTN SHM 650ML X 12 SSC IN GST</t>
+  </si>
+  <si>
+    <t>B019: PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B020: PNTN SHM 180MLX56 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B021: PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B025: PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B028: H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>B030: H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B022: PNTN SHM 400MLX30 HS LC IN GST</t>
+  </si>
+  <si>
+    <t>B031: H&amp;S SHM 72 ML X 48 CM IN GST</t>
+  </si>
+  <si>
+    <t>B023: PNTN SHM 340MLX30 HS HFC IN GST</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="21" width="15.7109375" customWidth="1"/>
@@ -1274,52 +1505,52 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H2">
-        <v>4.5088</v>
+        <v>4.4185</v>
       </c>
       <c r="I2" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J2" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="K2" s="2">
-        <v>46043.10625</v>
+        <v>46028.79861111111</v>
       </c>
       <c r="L2">
         <v>90</v>
       </c>
       <c r="M2" s="2">
-        <v>46043.16875</v>
+        <v>46028.86111111111</v>
       </c>
       <c r="N2">
-        <v>207</v>
+        <v>120</v>
       </c>
       <c r="O2" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="P2" s="2">
-        <v>46043.3125</v>
+        <v>46028.94444444445</v>
       </c>
       <c r="Q2" s="2">
-        <v>46043.50069444445</v>
+        <v>46029.49166666667</v>
       </c>
       <c r="R2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1330,164 +1561,164 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H3">
         <v>4.4185</v>
       </c>
       <c r="I3" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J3" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="K3" s="2">
-        <v>46043.16875</v>
+        <v>46029.11388888889</v>
       </c>
       <c r="L3">
         <v>90</v>
       </c>
       <c r="M3" s="2">
-        <v>46043.23125</v>
+        <v>46029.17638888889</v>
       </c>
       <c r="N3">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="O3" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="P3" s="2">
-        <v>46043.36319444444</v>
+        <v>46029.25972222222</v>
       </c>
       <c r="Q3" s="2">
-        <v>46043.54722222222</v>
+        <v>46029.44305555556</v>
       </c>
       <c r="R3" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H4">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I4" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J4" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="K4" s="2">
-        <v>46043.23125</v>
+        <v>46029.1875</v>
       </c>
       <c r="L4">
         <v>90</v>
       </c>
       <c r="M4" s="2">
-        <v>46043.29375</v>
+        <v>46029.25</v>
       </c>
       <c r="N4">
-        <v>120</v>
+        <v>278</v>
       </c>
       <c r="O4" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="P4" s="2">
-        <v>46043.37708333333</v>
+        <v>46029.44305555556</v>
       </c>
       <c r="Q4" s="2">
-        <v>46043.59027777778</v>
+        <v>46029.62708333333</v>
       </c>
       <c r="R4" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H5">
         <v>4.4185</v>
       </c>
       <c r="I5" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J5" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K5" s="2">
-        <v>46043.38194444445</v>
+        <v>46029.25</v>
       </c>
       <c r="L5">
         <v>90</v>
       </c>
       <c r="M5" s="2">
-        <v>46043.44444444445</v>
+        <v>46029.3125</v>
       </c>
       <c r="N5">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="O5" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="P5" s="2">
-        <v>46043.54722222222</v>
+        <v>46029.49166666667</v>
       </c>
       <c r="Q5" s="2">
-        <v>46043.73055555556</v>
+        <v>46029.73541666667</v>
       </c>
       <c r="R5" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1498,332 +1729,332 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H6">
-        <v>4.4163</v>
+        <v>2.2948</v>
       </c>
       <c r="I6" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J6" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K6" s="2">
-        <v>46043.44444444445</v>
+        <v>46029.32638888889</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M6" s="2">
-        <v>46043.50694444445</v>
+        <v>46029.45138888889</v>
       </c>
       <c r="N6">
-        <v>120</v>
+        <v>277</v>
       </c>
       <c r="O6" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="P6" s="2">
-        <v>46043.59027777778</v>
+        <v>46029.64375</v>
       </c>
       <c r="Q6" s="2">
-        <v>46043.80416666667</v>
+        <v>46029.68541666667</v>
       </c>
       <c r="R6" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F7" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H7">
-        <v>4.5228</v>
+        <v>4.4185</v>
       </c>
       <c r="I7" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J7" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K7" s="2">
-        <v>46043.50833333333</v>
+        <v>46029.46527777778</v>
       </c>
       <c r="L7">
         <v>90</v>
       </c>
       <c r="M7" s="2">
-        <v>46043.57083333333</v>
+        <v>46029.52777777778</v>
       </c>
       <c r="N7">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="O7" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="P7" s="2">
-        <v>46043.71180555555</v>
+        <v>46029.62708333333</v>
       </c>
       <c r="Q7" s="2">
-        <v>46043.83194444444</v>
+        <v>46029.81041666667</v>
       </c>
       <c r="R7" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="F8" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="G8" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H8">
         <v>4.4185</v>
       </c>
       <c r="I8" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J8" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K8" s="2">
-        <v>46043.58472222222</v>
+        <v>46029.52777777778</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8" s="2">
-        <v>46043.64722222222</v>
+        <v>46029.59027777778</v>
       </c>
       <c r="N8">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="O8" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="P8" s="2">
-        <v>46043.73055555556</v>
+        <v>46029.73541666667</v>
       </c>
       <c r="Q8" s="2">
-        <v>46043.91458333333</v>
+        <v>46029.94930555556</v>
       </c>
       <c r="R8" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="G9" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H9">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I9" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J9" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="K9" s="2">
-        <v>46043.65833333333</v>
+        <v>46029.59027777778</v>
       </c>
       <c r="L9">
         <v>90</v>
       </c>
       <c r="M9" s="2">
-        <v>46043.72083333333</v>
+        <v>46029.65277777778</v>
       </c>
       <c r="N9">
-        <v>120</v>
+        <v>227</v>
       </c>
       <c r="O9" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="P9" s="2">
-        <v>46043.80416666667</v>
+        <v>46029.81041666667</v>
       </c>
       <c r="Q9" s="2">
-        <v>46044.35069444445</v>
+        <v>46029.99444444444</v>
       </c>
       <c r="R9" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H10">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I10" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J10" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="K10" s="2">
-        <v>46043.76875</v>
+        <v>46029.65277777778</v>
       </c>
       <c r="L10">
         <v>90</v>
       </c>
       <c r="M10" s="2">
-        <v>46043.83125</v>
+        <v>46029.71527777778</v>
       </c>
       <c r="N10">
-        <v>120</v>
+        <v>337</v>
       </c>
       <c r="O10" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="P10" s="2">
-        <v>46043.91458333333</v>
+        <v>46029.94930555556</v>
       </c>
       <c r="Q10" s="2">
-        <v>46044.43125</v>
+        <v>46030.49583333333</v>
       </c>
       <c r="R10" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="G11" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>4.5228</v>
+        <v>4.4185</v>
       </c>
       <c r="I11" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J11" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="K11" s="2">
-        <v>46044.06666666667</v>
+        <v>46029.71527777778</v>
       </c>
       <c r="L11">
         <v>90</v>
       </c>
       <c r="M11" s="2">
-        <v>46044.12916666667</v>
+        <v>46029.77777777778</v>
       </c>
       <c r="N11">
-        <v>120</v>
+        <v>312</v>
       </c>
       <c r="O11" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="P11" s="2">
-        <v>46044.2125</v>
+        <v>46029.99444444444</v>
       </c>
       <c r="Q11" s="2">
-        <v>46044.33263888889</v>
+        <v>46030.17847222222</v>
       </c>
       <c r="R11" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1834,444 +2065,444 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H12">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="I12" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J12" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="K12" s="2">
-        <v>46044.14583333334</v>
+        <v>46029.79166666666</v>
       </c>
       <c r="L12">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M12" s="2">
-        <v>46044.20833333334</v>
+        <v>46029.91666666666</v>
       </c>
       <c r="N12">
-        <v>205</v>
+        <v>390</v>
       </c>
       <c r="O12" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="P12" s="2">
-        <v>46044.35069444445</v>
+        <v>46030.1875</v>
       </c>
       <c r="Q12" s="2">
-        <v>46044.56458333333</v>
+        <v>46030.22916666666</v>
       </c>
       <c r="R12" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="G13" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H13">
-        <v>4.5088</v>
+        <v>4.4185</v>
       </c>
       <c r="I13" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J13" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="K13" s="2">
-        <v>46044.20833333334</v>
+        <v>46029.93055555555</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13" s="2">
-        <v>46044.27083333334</v>
+        <v>46029.99305555555</v>
       </c>
       <c r="N13">
-        <v>120</v>
+        <v>267</v>
       </c>
       <c r="O13" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="P13" s="2">
-        <v>46044.35416666666</v>
+        <v>46030.17847222222</v>
       </c>
       <c r="Q13" s="2">
-        <v>46044.54236111111</v>
+        <v>46030.36180555556</v>
       </c>
       <c r="R13" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="G14" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H14">
-        <v>4.4185</v>
+        <v>4.5022</v>
       </c>
       <c r="I14" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J14" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="K14" s="2">
-        <v>46044.28194444445</v>
+        <v>46029.99305555555</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14" s="2">
-        <v>46044.34444444445</v>
+        <v>46030.05555555555</v>
       </c>
       <c r="N14">
-        <v>125</v>
+        <v>368</v>
       </c>
       <c r="O14" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="P14" s="2">
-        <v>46044.43125</v>
+        <v>46030.31111111111</v>
       </c>
       <c r="Q14" s="2">
-        <v>46044.61527777778</v>
+        <v>46030.43125</v>
       </c>
       <c r="R14" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F15" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="G15" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H15">
-        <v>4.5088</v>
+        <v>4.4185</v>
       </c>
       <c r="I15" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J15" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="K15" s="2">
-        <v>46044.34444444445</v>
+        <v>46030.05555555555</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15" s="2">
-        <v>46044.40694444445</v>
+        <v>46030.11805555555</v>
       </c>
       <c r="N15">
-        <v>195</v>
+        <v>351</v>
       </c>
       <c r="O15" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="P15" s="2">
-        <v>46044.54236111111</v>
+        <v>46030.36180555556</v>
       </c>
       <c r="Q15" s="2">
-        <v>46044.73125</v>
+        <v>46030.54583333333</v>
       </c>
       <c r="R15" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="F16" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="G16" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H16">
-        <v>4.4163</v>
+        <v>4.5022</v>
       </c>
       <c r="I16" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J16" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="K16" s="2">
-        <v>46044.40694444445</v>
+        <v>46030.11805555555</v>
       </c>
       <c r="L16">
         <v>90</v>
       </c>
       <c r="M16" s="2">
-        <v>46044.46944444445</v>
+        <v>46030.18055555555</v>
       </c>
       <c r="N16">
-        <v>137</v>
+        <v>361</v>
       </c>
       <c r="O16" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="P16" s="2">
-        <v>46044.56458333333</v>
+        <v>46030.43125</v>
       </c>
       <c r="Q16" s="2">
-        <v>46044.77777777778</v>
+        <v>46030.55138888889</v>
       </c>
       <c r="R16" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="G17" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H17">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I17" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J17" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K17" s="2">
-        <v>46044.46944444445</v>
+        <v>46030.18055555555</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17" s="2">
-        <v>46044.53194444445</v>
+        <v>46030.24305555555</v>
       </c>
       <c r="N17">
-        <v>120</v>
+        <v>364</v>
       </c>
       <c r="O17" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="P17" s="2">
-        <v>46044.61527777778</v>
+        <v>46030.49583333333</v>
       </c>
       <c r="Q17" s="2">
-        <v>46044.79861111111</v>
+        <v>46030.70972222222</v>
       </c>
       <c r="R17" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H18">
-        <v>4.5022</v>
+        <v>2.2948</v>
       </c>
       <c r="I18" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J18" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K18" s="2">
-        <v>46044.56944444445</v>
+        <v>46030.25694444445</v>
       </c>
       <c r="L18">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M18" s="2">
-        <v>46044.63194444445</v>
+        <v>46030.38194444445</v>
       </c>
       <c r="N18">
-        <v>143</v>
+        <v>260</v>
       </c>
       <c r="O18" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="P18" s="2">
-        <v>46044.73125</v>
+        <v>46030.5625</v>
       </c>
       <c r="Q18" s="2">
-        <v>46046.33055555556</v>
+        <v>46030.60416666666</v>
       </c>
       <c r="R18" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H19">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I19" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J19" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K19" s="2">
-        <v>46044.63194444445</v>
+        <v>46030.39583333334</v>
       </c>
       <c r="L19">
         <v>90</v>
       </c>
       <c r="M19" s="2">
-        <v>46044.69444444445</v>
+        <v>46030.45833333334</v>
       </c>
       <c r="N19">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O19" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="P19" s="2">
-        <v>46044.77777777778</v>
+        <v>46030.54583333333</v>
       </c>
       <c r="Q19" s="2">
-        <v>46046.47083333333</v>
+        <v>46030.72916666666</v>
       </c>
       <c r="R19" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2282,52 +2513,52 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F20" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G20" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="H20">
-        <v>2.2511</v>
+        <v>4.5228</v>
       </c>
       <c r="I20" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="J20" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="K20" s="2">
-        <v>46043</v>
+        <v>46030.45833333334</v>
       </c>
       <c r="L20">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="M20" s="2">
-        <v>46043.04513888889</v>
+        <v>46030.52083333334</v>
       </c>
       <c r="N20">
-        <v>505</v>
+        <v>131</v>
       </c>
       <c r="O20" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="P20" s="2">
-        <v>46043.39583333334</v>
+        <v>46030.61180555556</v>
       </c>
       <c r="Q20" s="2">
-        <v>46043.69097222222</v>
+        <v>46030.73194444444</v>
       </c>
       <c r="R20" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2338,220 +2569,220 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G21" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="H21">
-        <v>2.2544</v>
+        <v>4.4163</v>
       </c>
       <c r="I21" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J21" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K21" s="2">
-        <v>46043.05902777778</v>
+        <v>46030.52083333334</v>
       </c>
       <c r="L21">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M21" s="2">
-        <v>46043.11805555555</v>
+        <v>46030.58333333334</v>
       </c>
       <c r="N21">
-        <v>551</v>
+        <v>182</v>
       </c>
       <c r="O21" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="P21" s="2">
-        <v>46043.50069444445</v>
+        <v>46030.70972222222</v>
       </c>
       <c r="Q21" s="2">
-        <v>46043.59513888889</v>
+        <v>46030.92291666667</v>
       </c>
       <c r="R21" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="G22" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="H22">
-        <v>1.128</v>
+        <v>4.4185</v>
       </c>
       <c r="I22" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J22" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K22" s="2">
-        <v>46043.13194444445</v>
+        <v>46030.58333333334</v>
       </c>
       <c r="L22">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M22" s="2">
-        <v>46043.25694444445</v>
+        <v>46030.64583333334</v>
       </c>
       <c r="N22">
-        <v>472</v>
+        <v>120</v>
       </c>
       <c r="O22" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="P22" s="2">
-        <v>46043.58472222222</v>
+        <v>46030.72916666666</v>
       </c>
       <c r="Q22" s="2">
-        <v>46043.62638888889</v>
+        <v>46030.91319444445</v>
       </c>
       <c r="R22" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="G23" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H23">
-        <v>1.8035</v>
+        <v>0.5601</v>
       </c>
       <c r="I23" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J23" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="K23" s="2">
-        <v>46043.27083333334</v>
+        <v>46028.1875</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M23" s="2">
-        <v>46043.33333333334</v>
+        <v>46028.3125</v>
       </c>
       <c r="N23">
-        <v>420</v>
+        <v>1440</v>
       </c>
       <c r="O23" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="P23" s="2">
-        <v>46043.625</v>
+        <v>46029.3125</v>
       </c>
       <c r="Q23" s="2">
-        <v>46043.7</v>
+        <v>46029.48125</v>
       </c>
       <c r="R23" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="G24" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H24">
-        <v>0.4364</v>
+        <v>0.5601</v>
       </c>
       <c r="I24" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J24" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K24" s="2">
-        <v>46043.33333333334</v>
+        <v>46028.45625</v>
       </c>
       <c r="L24">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M24" s="2">
-        <v>46043.39583333334</v>
+        <v>46028.58125</v>
       </c>
       <c r="N24">
-        <v>438</v>
+        <v>1440</v>
       </c>
       <c r="O24" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="P24" s="2">
-        <v>46043.7</v>
+        <v>46029.58125</v>
       </c>
       <c r="Q24" s="2">
-        <v>46043.71180555555</v>
+        <v>46030.41666666666</v>
       </c>
       <c r="R24" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2562,169 +2793,169 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F25" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="G25" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H25">
-        <v>2.2511</v>
+        <v>2.2314</v>
       </c>
       <c r="I25" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="J25" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="K25" s="2">
-        <v>46043.40972222222</v>
+        <v>46028.99305555555</v>
       </c>
       <c r="L25">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="M25" s="2">
-        <v>46043.45486111111</v>
+        <v>46029.05555555555</v>
       </c>
       <c r="N25">
-        <v>340</v>
+        <v>490</v>
       </c>
       <c r="O25" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="P25" s="2">
-        <v>46043.69097222222</v>
+        <v>46029.39583333334</v>
       </c>
       <c r="Q25" s="2">
-        <v>46044.31944444445</v>
+        <v>46029.62916666667</v>
       </c>
       <c r="R25" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="G26" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H26">
-        <v>2.2314</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J26" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="K26" s="2">
-        <v>46043.46875</v>
+        <v>46029.09027777778</v>
       </c>
       <c r="L26">
         <v>90</v>
       </c>
       <c r="M26" s="2">
-        <v>46043.53125</v>
+        <v>46029.15277777778</v>
       </c>
       <c r="N26">
-        <v>433</v>
+        <v>1820</v>
       </c>
       <c r="O26" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="P26" s="2">
-        <v>46043.83194444444</v>
+        <v>46030.41666666666</v>
       </c>
       <c r="Q26" s="2">
-        <v>46044.06527777778</v>
+        <v>46030.59652777778</v>
       </c>
       <c r="R26" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="G27" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H27">
-        <v>1.128</v>
+        <v>2.19</v>
       </c>
       <c r="I27" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J27" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="K27" s="2">
-        <v>46043.54513888889</v>
+        <v>46029.19444444445</v>
       </c>
       <c r="L27">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M27" s="2">
-        <v>46043.67013888889</v>
+        <v>46029.25694444445</v>
       </c>
       <c r="N27">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="O27" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="P27" s="2">
-        <v>46043.91944444444</v>
+        <v>46029.53472222222</v>
       </c>
       <c r="Q27" s="2">
-        <v>46043.96111111111</v>
+        <v>46030.25</v>
       </c>
       <c r="R27" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
@@ -2733,49 +2964,49 @@
         <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="G28" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H28">
-        <v>1.1157</v>
+        <v>2.2511</v>
       </c>
       <c r="I28" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="J28" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="K28" s="2">
-        <v>46043.68402777778</v>
+        <v>46029.27083333334</v>
       </c>
       <c r="L28">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M28" s="2">
-        <v>46043.74652777778</v>
+        <v>46029.32986111111</v>
       </c>
       <c r="N28">
-        <v>459</v>
+        <v>431</v>
       </c>
       <c r="O28" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="P28" s="2">
-        <v>46044.06527777778</v>
+        <v>46029.62916666667</v>
       </c>
       <c r="Q28" s="2">
-        <v>46044.18194444444</v>
+        <v>46029.68958333333</v>
       </c>
       <c r="R28" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2786,220 +3017,220 @@
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>148</v>
       </c>
       <c r="G29" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H29">
-        <v>1.128</v>
+        <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J29" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="K29" s="2">
-        <v>46043.76041666666</v>
+        <v>46029.36458333334</v>
       </c>
       <c r="L29">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M29" s="2">
-        <v>46043.88541666666</v>
+        <v>46029.42708333334</v>
       </c>
       <c r="N29">
-        <v>375</v>
+        <v>1684</v>
       </c>
       <c r="O29" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="P29" s="2">
-        <v>46044.14583333334</v>
+        <v>46030.59652777778</v>
       </c>
       <c r="Q29" s="2">
-        <v>46044.1875</v>
+        <v>46031.41736111111</v>
       </c>
       <c r="R29" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="G30" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H30">
-        <v>1.1307</v>
+        <v>2.2511</v>
       </c>
       <c r="I30" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J30" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="K30" s="2">
-        <v>46043.89930555555</v>
+        <v>46029.46875</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30" s="2">
-        <v>46043.96180555555</v>
+        <v>46029.53125</v>
       </c>
       <c r="N30">
-        <v>317</v>
+        <v>228</v>
       </c>
       <c r="O30" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="P30" s="2">
-        <v>46044.18194444444</v>
+        <v>46029.68958333333</v>
       </c>
       <c r="Q30" s="2">
-        <v>46044.2125</v>
+        <v>46029.75</v>
       </c>
       <c r="R30" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="G31" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H31">
-        <v>1.128</v>
+        <v>1.1225</v>
       </c>
       <c r="I31" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J31" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="K31" s="2">
-        <v>46043.97569444445</v>
+        <v>46029.54513888889</v>
       </c>
       <c r="L31">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M31" s="2">
-        <v>46044.10069444445</v>
+        <v>46029.60763888889</v>
       </c>
       <c r="N31">
-        <v>351</v>
+        <v>205</v>
       </c>
       <c r="O31" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="P31" s="2">
-        <v>46044.34444444445</v>
+        <v>46029.75</v>
       </c>
       <c r="Q31" s="2">
-        <v>46044.38611111111</v>
+        <v>46029.77986111111</v>
       </c>
       <c r="R31" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E32" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="G32" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H32">
-        <v>0.9522</v>
+        <v>1.1174</v>
       </c>
       <c r="I32" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J32" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="K32" s="2">
-        <v>46044.11458333334</v>
+        <v>46029.60763888889</v>
       </c>
       <c r="L32">
         <v>90</v>
       </c>
       <c r="M32" s="2">
-        <v>46044.17708333334</v>
+        <v>46029.67013888889</v>
       </c>
       <c r="N32">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="O32" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="P32" s="2">
-        <v>46044.33263888889</v>
+        <v>46029.77986111111</v>
       </c>
       <c r="Q32" s="2">
-        <v>46044.35763888889</v>
+        <v>46029.82638888889</v>
       </c>
       <c r="R32" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -3010,108 +3241,108 @@
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E33" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F33" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="G33" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H33">
-        <v>2.2511</v>
+        <v>2.2544</v>
       </c>
       <c r="I33" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J33" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="K33" s="2">
-        <v>46044.19097222222</v>
+        <v>46029.68402777778</v>
       </c>
       <c r="L33">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="M33" s="2">
-        <v>46044.23611111111</v>
+        <v>46029.74305555555</v>
       </c>
       <c r="N33">
         <v>120</v>
       </c>
       <c r="O33" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="P33" s="2">
-        <v>46044.31944444445</v>
+        <v>46029.82638888889</v>
       </c>
       <c r="Q33" s="2">
-        <v>46044.61527777778</v>
+        <v>46029.92083333333</v>
       </c>
       <c r="R33" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="G34" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H34">
-        <v>1.128</v>
+        <v>2.2614</v>
       </c>
       <c r="I34" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J34" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="K34" s="2">
-        <v>46044.34791666667</v>
+        <v>46030.10486111111</v>
       </c>
       <c r="L34">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M34" s="2">
-        <v>46044.47291666667</v>
+        <v>46030.16736111111</v>
       </c>
       <c r="N34">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="O34" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="P34" s="2">
-        <v>46044.56944444445</v>
+        <v>46030.25069444445</v>
       </c>
       <c r="Q34" s="2">
-        <v>46044.61111111111</v>
+        <v>46030.31111111111</v>
       </c>
       <c r="R34" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -3122,52 +3353,276 @@
         <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E35" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="G35" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="H35">
-        <v>2.2511</v>
+        <v>2.2614</v>
       </c>
       <c r="I35" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="J35" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K35" s="2">
-        <v>46044.48680555556</v>
+        <v>46030.40555555555</v>
       </c>
       <c r="L35">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="M35" s="2">
-        <v>46044.53194444445</v>
+        <v>46030.46805555555</v>
       </c>
       <c r="N35">
         <v>120</v>
       </c>
       <c r="O35" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="P35" s="2">
-        <v>46044.61527777778</v>
+        <v>46030.55138888889</v>
       </c>
       <c r="Q35" s="2">
-        <v>46046.38958333333</v>
+        <v>46030.61180555556</v>
       </c>
       <c r="R35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" t="s">
+        <v>139</v>
+      </c>
+      <c r="F36" t="s">
+        <v>145</v>
+      </c>
+      <c r="G36" t="s">
+        <v>157</v>
+      </c>
+      <c r="H36">
+        <v>2.2314</v>
+      </c>
+      <c r="I36" t="s">
+        <v>158</v>
+      </c>
+      <c r="J36" t="s">
+        <v>162</v>
+      </c>
+      <c r="K36" s="2">
+        <v>46030.58611111111</v>
+      </c>
+      <c r="L36">
+        <v>90</v>
+      </c>
+      <c r="M36" s="2">
+        <v>46030.64861111111</v>
+      </c>
+      <c r="N36">
+        <v>120</v>
+      </c>
+      <c r="O36" t="s">
+        <v>163</v>
+      </c>
+      <c r="P36" s="2">
+        <v>46030.73194444444</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>46030.96527777778</v>
+      </c>
+      <c r="R36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" t="s">
+        <v>154</v>
+      </c>
+      <c r="G37" t="s">
+        <v>157</v>
+      </c>
+      <c r="H37">
+        <v>2.1937</v>
+      </c>
+      <c r="I37" t="s">
+        <v>158</v>
+      </c>
+      <c r="J37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K37" s="2">
+        <v>46030.67708333334</v>
+      </c>
+      <c r="L37">
+        <v>85</v>
+      </c>
+      <c r="M37" s="2">
+        <v>46030.73611111111</v>
+      </c>
+      <c r="N37">
+        <v>266</v>
+      </c>
+      <c r="O37" t="s">
+        <v>164</v>
+      </c>
+      <c r="P37" s="2">
+        <v>46030.92083333333</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>46030.96527777778</v>
+      </c>
+      <c r="R37" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" t="s">
+        <v>155</v>
+      </c>
+      <c r="G38" t="s">
+        <v>157</v>
+      </c>
+      <c r="H38">
+        <v>2.2314</v>
+      </c>
+      <c r="I38" t="s">
+        <v>158</v>
+      </c>
+      <c r="J38" t="s">
+        <v>160</v>
+      </c>
+      <c r="K38" s="2">
+        <v>46030.75</v>
+      </c>
+      <c r="L38">
+        <v>85</v>
+      </c>
+      <c r="M38" s="2">
+        <v>46030.80902777778</v>
+      </c>
+      <c r="N38">
+        <v>225</v>
+      </c>
+      <c r="O38" t="s">
+        <v>165</v>
+      </c>
+      <c r="P38" s="2">
+        <v>46030.96527777778</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>46031.19930555556</v>
+      </c>
+      <c r="R38" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" t="s">
         <v>150</v>
+      </c>
+      <c r="G39" t="s">
+        <v>157</v>
+      </c>
+      <c r="H39">
+        <v>2.2614</v>
+      </c>
+      <c r="I39" t="s">
+        <v>159</v>
+      </c>
+      <c r="J39" t="s">
+        <v>160</v>
+      </c>
+      <c r="K39" s="2">
+        <v>46030.82291666666</v>
+      </c>
+      <c r="L39">
+        <v>85</v>
+      </c>
+      <c r="M39" s="2">
+        <v>46030.88194444445</v>
+      </c>
+      <c r="N39">
+        <v>120</v>
+      </c>
+      <c r="O39" t="s">
+        <v>168</v>
+      </c>
+      <c r="P39" s="2">
+        <v>46030.96527777778</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>46030.53472222222</v>
+      </c>
+      <c r="R39" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3177,7 +3632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3187,1071 +3642,1540 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>259</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>259</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>259</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>260</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>260</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>260</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" t="s">
         <v>161</v>
       </c>
-      <c r="B8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>262</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>262</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>262</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>263</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>263</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>263</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>246</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>264</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>264</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>246</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>266</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>266</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>266</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>266</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="B33" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>267</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>267</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>246</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>268</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>268</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>268</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>268</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>246</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>269</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>269</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>161</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>269</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>161</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>270</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>161</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>161</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>161</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>270</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>161</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>270</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>270</v>
+        <v>339</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="B55" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>246</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>271</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>271</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>246</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>272</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>272</v>
+        <v>341</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>252</v>
+        <v>317</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B63" t="s">
-        <v>136</v>
+        <v>162</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>253</v>
+        <v>316</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>253</v>
+        <v>318</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>253</v>
+        <v>318</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>273</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>273</v>
+        <v>343</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>273</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="B71" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>273</v>
+        <v>343</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>246</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>256</v>
+        <v>321</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>274</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="B75" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>256</v>
+        <v>321</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>274</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="B76" t="s">
-        <v>137</v>
+        <v>160</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>160</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>257</v>
+        <v>322</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>257</v>
+        <v>322</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>256</v>
+      </c>
+      <c r="B81" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>234</v>
-      </c>
-      <c r="B81" t="s">
-        <v>138</v>
-      </c>
-      <c r="C81" s="3" t="s">
+      <c r="B82" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
-        <v>235</v>
-      </c>
-      <c r="B82" t="s">
-        <v>138</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" t="s">
-        <v>236</v>
-      </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="B84" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+        <v>160</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="B85" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>160</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="B86" t="s">
-        <v>138</v>
+        <v>160</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>262</v>
+      </c>
+      <c r="B87" t="s">
+        <v>160</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>263</v>
+      </c>
+      <c r="B88" t="s">
+        <v>160</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>264</v>
+      </c>
+      <c r="B89" t="s">
+        <v>161</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>265</v>
+      </c>
+      <c r="B90" t="s">
+        <v>161</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>266</v>
+      </c>
+      <c r="B91" t="s">
+        <v>161</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>267</v>
+      </c>
+      <c r="B92" t="s">
+        <v>161</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>268</v>
+      </c>
+      <c r="B93" t="s">
+        <v>161</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>269</v>
+      </c>
+      <c r="B94" t="s">
+        <v>161</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>270</v>
+      </c>
+      <c r="B95" t="s">
+        <v>161</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>271</v>
+      </c>
+      <c r="B96" t="s">
+        <v>161</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>272</v>
+      </c>
+      <c r="B97" t="s">
+        <v>161</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>273</v>
+      </c>
+      <c r="B98" t="s">
+        <v>161</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>274</v>
+      </c>
+      <c r="B99" t="s">
+        <v>161</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>275</v>
+      </c>
+      <c r="B100" t="s">
+        <v>161</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>276</v>
+      </c>
+      <c r="B101" t="s">
+        <v>161</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>277</v>
+      </c>
+      <c r="B102" t="s">
+        <v>161</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>278</v>
+      </c>
+      <c r="B103" t="s">
+        <v>161</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>279</v>
+      </c>
+      <c r="B104" t="s">
+        <v>161</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>280</v>
+      </c>
+      <c r="B105" t="s">
+        <v>162</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>281</v>
+      </c>
+      <c r="B106" t="s">
+        <v>162</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>282</v>
+      </c>
+      <c r="B107" t="s">
+        <v>162</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>283</v>
+      </c>
+      <c r="B108" t="s">
+        <v>162</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>284</v>
+      </c>
+      <c r="B109" t="s">
+        <v>162</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>285</v>
+      </c>
+      <c r="B110" t="s">
+        <v>162</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>286</v>
+      </c>
+      <c r="B111" t="s">
+        <v>162</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>287</v>
+      </c>
+      <c r="B112" t="s">
+        <v>162</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>288</v>
+      </c>
+      <c r="B113" t="s">
+        <v>162</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>289</v>
+      </c>
+      <c r="B114" t="s">
+        <v>162</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>290</v>
+      </c>
+      <c r="B115" t="s">
+        <v>162</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>291</v>
+      </c>
+      <c r="B116" t="s">
+        <v>162</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>292</v>
+      </c>
+      <c r="B117" t="s">
+        <v>162</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>293</v>
+      </c>
+      <c r="B118" t="s">
+        <v>162</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>294</v>
+      </c>
+      <c r="B119" t="s">
+        <v>162</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>295</v>
+      </c>
+      <c r="B120" t="s">
+        <v>162</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>296</v>
+      </c>
+      <c r="B121" t="s">
+        <v>160</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>297</v>
+      </c>
+      <c r="B122" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>298</v>
+      </c>
+      <c r="B123" t="s">
+        <v>160</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>299</v>
+      </c>
+      <c r="B124" t="s">
+        <v>160</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>300</v>
+      </c>
+      <c r="B125" t="s">
+        <v>160</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>301</v>
+      </c>
+      <c r="B126" t="s">
+        <v>160</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>302</v>
+      </c>
+      <c r="B127" t="s">
+        <v>160</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>303</v>
+      </c>
+      <c r="B128" t="s">
+        <v>160</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>304</v>
+      </c>
+      <c r="B129" t="s">
+        <v>160</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>305</v>
+      </c>
+      <c r="B130" t="s">
+        <v>160</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>306</v>
+      </c>
+      <c r="B131" t="s">
+        <v>160</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>307</v>
+      </c>
+      <c r="B132" t="s">
+        <v>160</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>308</v>
+      </c>
+      <c r="B133" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>309</v>
+      </c>
+      <c r="B134" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>310</v>
+      </c>
+      <c r="B135" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>311</v>
+      </c>
+      <c r="B136" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="316">
   <si>
     <t>Production Line</t>
   </si>
@@ -74,12 +74,12 @@
     <t>INC4</t>
   </si>
   <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
     <t>INC1</t>
   </si>
   <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
     <t>INT2</t>
   </si>
   <si>
@@ -89,21 +89,33 @@
     <t>910715043</t>
   </si>
   <si>
+    <t>AUTO_1</t>
+  </si>
+  <si>
     <t>910712428</t>
   </si>
   <si>
+    <t>AUTO_2</t>
+  </si>
+  <si>
+    <t>910715191 + 910717251</t>
+  </si>
+  <si>
     <t>910712578</t>
   </si>
   <si>
     <t>910714990</t>
   </si>
   <si>
-    <t>AUTO_1</t>
+    <t>910715241 + 910715240</t>
   </si>
   <si>
     <t>910712440</t>
   </si>
   <si>
+    <t>AUTO_3</t>
+  </si>
+  <si>
     <t>910717240</t>
   </si>
   <si>
@@ -116,9 +128,6 @@
     <t>910717201</t>
   </si>
   <si>
-    <t>AUTO_2</t>
-  </si>
-  <si>
     <t>910717256</t>
   </si>
   <si>
@@ -134,9 +143,6 @@
     <t>910717202</t>
   </si>
   <si>
-    <t>AUTO_3</t>
-  </si>
-  <si>
     <t>910717296</t>
   </si>
   <si>
@@ -149,13 +155,7 @@
     <t>910717276</t>
   </si>
   <si>
-    <t>910714830</t>
-  </si>
-  <si>
-    <t>910714891</t>
-  </si>
-  <si>
-    <t>910715191</t>
+    <t>910714830 + 910714891</t>
   </si>
   <si>
     <t>910717129</t>
@@ -164,49 +164,43 @@
     <t>910715192</t>
   </si>
   <si>
-    <t>910715241</t>
-  </si>
-  <si>
     <t>910717198</t>
   </si>
   <si>
     <t>910715257</t>
   </si>
   <si>
-    <t>910715048</t>
-  </si>
-  <si>
-    <t>910715049</t>
-  </si>
-  <si>
-    <t>910715240</t>
+    <t>910715048 + 910715049</t>
   </si>
   <si>
     <t>910717302</t>
   </si>
   <si>
-    <t>910717251</t>
-  </si>
-  <si>
     <t>910717299</t>
   </si>
   <si>
     <t>910717359</t>
   </si>
   <si>
+    <t>910717252</t>
+  </si>
+  <si>
     <t>910717417</t>
   </si>
   <si>
-    <t>910717252</t>
-  </si>
-  <si>
     <t>83900260</t>
   </si>
   <si>
+    <t>95619314</t>
+  </si>
+  <si>
     <t>83900263</t>
   </si>
   <si>
-    <t>95619314</t>
+    <t>80880885</t>
+  </si>
+  <si>
+    <t>80879287</t>
   </si>
   <si>
     <t>83900262</t>
@@ -221,18 +215,12 @@
     <t>80841061</t>
   </si>
   <si>
-    <t>80880885</t>
-  </si>
-  <si>
     <t>80830098</t>
   </si>
   <si>
     <t>80879282</t>
   </si>
   <si>
-    <t>80879287</t>
-  </si>
-  <si>
     <t>80878378</t>
   </si>
   <si>
@@ -242,37 +230,34 @@
     <t>80889640</t>
   </si>
   <si>
-    <t>80889635</t>
-  </si>
-  <si>
-    <t>80879278</t>
-  </si>
-  <si>
     <t>80896348</t>
   </si>
   <si>
-    <t>80880904</t>
-  </si>
-  <si>
     <t>80880883</t>
   </si>
   <si>
     <t>80879268</t>
   </si>
   <si>
+    <t>80879274</t>
+  </si>
+  <si>
     <t>80880881</t>
   </si>
   <si>
-    <t>80879274</t>
-  </si>
-  <si>
     <t>H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
   </si>
   <si>
+    <t>Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
     <t>H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>Auto-Replenishment HC Base (12T)</t>
+    <t>H&amp;S SHM 72ML X 48 AHF IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650ML X 12 HFC GST</t>
   </si>
   <si>
     <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
@@ -287,18 +272,12 @@
     <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
   </si>
   <si>
-    <t>H&amp;S SHM 72ML X 48 AHF IN GST</t>
-  </si>
-  <si>
     <t>PNTN 3MM BIOTIN COND 200MLX24 IN</t>
   </si>
   <si>
     <t>PNTN SHM 75 ML X 48 HS DR IN GST</t>
   </si>
   <si>
-    <t>PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
     <t>PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
   </si>
   <si>
@@ -308,91 +287,112 @@
     <t>PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
   </si>
   <si>
-    <t>PNTN SHM 180MLX56 SSC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
     <t>PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
   </si>
   <si>
-    <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
-  </si>
-  <si>
     <t>H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
   </si>
   <si>
     <t>PNTN SHM 400MLX30 HS LC IN GST</t>
   </si>
   <si>
+    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
     <t>H&amp;S SHM 72 ML X 48 CM IN GST</t>
   </si>
   <si>
-    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
+    <t>B001</t>
+  </si>
+  <si>
+    <t>REP02</t>
+  </si>
+  <si>
+    <t>B003</t>
+  </si>
+  <si>
+    <t>REP06</t>
+  </si>
+  <si>
+    <t>B005</t>
+  </si>
+  <si>
+    <t>B007</t>
+  </si>
+  <si>
+    <t>B008</t>
+  </si>
+  <si>
+    <t>B011</t>
   </si>
   <si>
     <t>B010</t>
   </si>
   <si>
-    <t>B001</t>
-  </si>
-  <si>
-    <t>B002</t>
-  </si>
-  <si>
-    <t>B011</t>
-  </si>
-  <si>
-    <t>REP36</t>
-  </si>
-  <si>
-    <t>B003</t>
+    <t>REP15</t>
+  </si>
+  <si>
+    <t>B013</t>
+  </si>
+  <si>
+    <t>B016</t>
+  </si>
+  <si>
+    <t>B017</t>
+  </si>
+  <si>
+    <t>B018</t>
+  </si>
+  <si>
+    <t>B019</t>
+  </si>
+  <si>
+    <t>B021</t>
+  </si>
+  <si>
+    <t>B022</t>
+  </si>
+  <si>
+    <t>B024</t>
+  </si>
+  <si>
+    <t>B025</t>
+  </si>
+  <si>
+    <t>B026</t>
+  </si>
+  <si>
+    <t>B028</t>
+  </si>
+  <si>
+    <t>B029</t>
+  </si>
+  <si>
+    <t>B030</t>
+  </si>
+  <si>
+    <t>B004</t>
+  </si>
+  <si>
+    <t>B023</t>
+  </si>
+  <si>
+    <t>B009</t>
+  </si>
+  <si>
+    <t>B027</t>
   </si>
   <si>
     <t>B012</t>
   </si>
   <si>
-    <t>B004</t>
-  </si>
-  <si>
-    <t>B013</t>
-  </si>
-  <si>
-    <t>B005</t>
-  </si>
-  <si>
-    <t>REP37</t>
-  </si>
-  <si>
-    <t>B006</t>
-  </si>
-  <si>
-    <t>B026</t>
-  </si>
-  <si>
-    <t>B007</t>
-  </si>
-  <si>
-    <t>B027</t>
-  </si>
-  <si>
     <t>B014</t>
   </si>
   <si>
-    <t>REP38</t>
-  </si>
-  <si>
-    <t>B008</t>
-  </si>
-  <si>
-    <t>B029</t>
-  </si>
-  <si>
-    <t>B015</t>
-  </si>
-  <si>
-    <t>B009</t>
+    <t>B020</t>
+  </si>
+  <si>
+    <t>B031</t>
   </si>
   <si>
     <t>B032</t>
@@ -401,75 +401,33 @@
     <t>B033</t>
   </si>
   <si>
-    <t>B016</t>
-  </si>
-  <si>
     <t>B034</t>
   </si>
   <si>
-    <t>B024</t>
-  </si>
-  <si>
-    <t>B017</t>
-  </si>
-  <si>
-    <t>B035</t>
-  </si>
-  <si>
-    <t>B018</t>
-  </si>
-  <si>
-    <t>B019</t>
-  </si>
-  <si>
-    <t>B020</t>
-  </si>
-  <si>
-    <t>B021</t>
-  </si>
-  <si>
-    <t>B025</t>
-  </si>
-  <si>
-    <t>B028</t>
-  </si>
-  <si>
-    <t>B030</t>
-  </si>
-  <si>
-    <t>B022</t>
-  </si>
-  <si>
-    <t>B031</t>
-  </si>
-  <si>
-    <t>B023</t>
-  </si>
-  <si>
     <t>21453170</t>
   </si>
   <si>
     <t>21470269</t>
   </si>
   <si>
+    <t>21417344</t>
+  </si>
+  <si>
+    <t>21302239</t>
+  </si>
+  <si>
     <t>21422079</t>
   </si>
   <si>
     <t>21090111</t>
   </si>
   <si>
-    <t>21417344</t>
-  </si>
-  <si>
     <t>UNKNOWN</t>
   </si>
   <si>
     <t>'21302239</t>
   </si>
   <si>
-    <t>21302239</t>
-  </si>
-  <si>
     <t>'21302240</t>
   </si>
   <si>
@@ -506,33 +464,33 @@
     <t>A</t>
   </si>
   <si>
+    <t>TK#_15_#</t>
+  </si>
+  <si>
+    <t>NO_TANK_AVAILABLE</t>
+  </si>
+  <si>
+    <t>TK#_16_#</t>
+  </si>
+  <si>
+    <t>TK#_14_#</t>
+  </si>
+  <si>
     <t>TK#_24_#</t>
   </si>
   <si>
-    <t>TK#_14_#</t>
-  </si>
-  <si>
-    <t>TK#_15_#</t>
-  </si>
-  <si>
-    <t>NO_TANK_AVAILABLE</t>
+    <t>TK#_12_#</t>
   </si>
   <si>
     <t>TK#_9_#</t>
   </si>
   <si>
+    <t>TK#_53_#</t>
+  </si>
+  <si>
     <t>TK#_23_#</t>
   </si>
   <si>
-    <t>TK#_53_#</t>
-  </si>
-  <si>
-    <t>TK#_16_#</t>
-  </si>
-  <si>
-    <t>TK#_12_#</t>
-  </si>
-  <si>
     <t>LOW: SLS</t>
   </si>
   <si>
@@ -899,178 +857,112 @@
     <t>2026-01-08 14:00</t>
   </si>
   <si>
-    <t>2026-01-08 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 23:00</t>
-  </si>
-  <si>
-    <t>B010: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B001: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B002: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B011: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
+    <t>B001: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>REP02: Auto-Replenishment HC Base (12T)</t>
   </si>
   <si>
     <t>WASHOUT</t>
   </si>
   <si>
-    <t>REP36: Auto-Replenishment HC Base (12T)</t>
-  </si>
-  <si>
     <t>B003: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B012: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B004: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B013: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>REP37: Auto-Replenishment HC Base (12T)</t>
-  </si>
-  <si>
-    <t>B006: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B026: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+    <t>REP06: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>B005: H&amp;S SHM 72ML X 48 AHF IN GST</t>
   </si>
   <si>
     <t>B007: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B027: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B014: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>REP38: Auto-Replenishment HC Base (12T)</t>
-  </si>
-  <si>
-    <t>B008: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B029: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B015: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B009: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B032: PNTN COND 200MLX 24 HS HF IN PC25</t>
+    <t>B008: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B011: PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>B010: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>REP15: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>B013: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B016: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B017: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B018: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B019: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B021: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B022: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B024: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B025: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B026: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B028: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B029: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B030: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B004: PNTN COND 200MLX 24 HS HF IN PC25</t>
   </si>
   <si>
     <t>COND WASH (60m)</t>
   </si>
   <si>
-    <t>B033: PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>B016: H&amp;S SHM 72ML X 48 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B034: PNTN 3MM BIOTIN COND 200MLX24 IN</t>
-  </si>
-  <si>
-    <t>B024: PNTN SHM 75 ML X 48 HS DR IN GST</t>
-  </si>
-  <si>
-    <t>B017: PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
-    <t>B035: PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
-  </si>
-  <si>
-    <t>B018: PNTN SHM 650ML X 12 SSC IN GST</t>
-  </si>
-  <si>
-    <t>B019: PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>B020: PNTN SHM 180MLX56 SSC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>B021: PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>B025: PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>B028: H&amp;S SHM 340ML X30 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B030: H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B022: PNTN SHM 400MLX30 HS LC IN GST</t>
-  </si>
-  <si>
-    <t>B031: H&amp;S SHM 72 ML X 48 CM IN GST</t>
-  </si>
-  <si>
-    <t>B023: PNTN SHM 340MLX30 HS HFC IN GST</t>
+    <t>B023: PNTN 3MM BIOTIN COND 200MLX24 IN</t>
+  </si>
+  <si>
+    <t>B009: PNTN SHM 75 ML X 48 HS DR IN GST</t>
+  </si>
+  <si>
+    <t>B027: PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
+  </si>
+  <si>
+    <t>B012: PNTN SHM 650ML X 12 SSC IN GST</t>
+  </si>
+  <si>
+    <t>B014: PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B020: PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
+  </si>
+  <si>
+    <t>B031: H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B032: PNTN SHM 400MLX30 HS LC IN GST</t>
+  </si>
+  <si>
+    <t>B033: PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B034: H&amp;S SHM 72 ML X 48 CM IN GST</t>
   </si>
 </sst>
 </file>
@@ -1435,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="21" width="15.7109375" customWidth="1"/>
@@ -1505,28 +1397,28 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="G2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H2">
         <v>4.4185</v>
       </c>
       <c r="I2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="K2" s="2">
         <v>46028.79861111111</v>
@@ -1541,7 +1433,7 @@
         <v>120</v>
       </c>
       <c r="O2" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="P2" s="2">
         <v>46028.94444444445</v>
@@ -1550,7 +1442,7 @@
         <v>46029.49166666667</v>
       </c>
       <c r="R2" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1561,276 +1453,276 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H3">
+        <v>2.2948</v>
+      </c>
+      <c r="I3" t="s">
         <v>144</v>
       </c>
-      <c r="G3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3">
-        <v>4.4185</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K3" s="2">
+        <v>46028.875</v>
+      </c>
+      <c r="L3">
+        <v>180</v>
+      </c>
+      <c r="M3" s="2">
+        <v>46029</v>
+      </c>
+      <c r="N3">
+        <v>60</v>
+      </c>
+      <c r="O3" t="s">
+        <v>150</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46029.04166666666</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>46029.08333333334</v>
+      </c>
+      <c r="R3" t="s">
         <v>158</v>
-      </c>
-      <c r="J3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K3" s="2">
-        <v>46029.11388888889</v>
-      </c>
-      <c r="L3">
-        <v>90</v>
-      </c>
-      <c r="M3" s="2">
-        <v>46029.17638888889</v>
-      </c>
-      <c r="N3">
-        <v>120</v>
-      </c>
-      <c r="O3" t="s">
-        <v>164</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46029.25972222222</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>46029.44305555556</v>
-      </c>
-      <c r="R3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G4" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H4">
         <v>4.4185</v>
       </c>
       <c r="I4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="K4" s="2">
-        <v>46029.1875</v>
+        <v>46029.01388888889</v>
       </c>
       <c r="L4">
         <v>90</v>
       </c>
       <c r="M4" s="2">
-        <v>46029.25</v>
+        <v>46029.07638888889</v>
       </c>
       <c r="N4">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="O4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="P4" s="2">
+        <v>46029.25972222222</v>
+      </c>
+      <c r="Q4" s="2">
         <v>46029.44305555556</v>
       </c>
-      <c r="Q4" s="2">
-        <v>46029.62708333333</v>
-      </c>
       <c r="R4" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H5">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="I5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J5" t="s">
+        <v>147</v>
+      </c>
+      <c r="K5" s="2">
+        <v>46029.09027777778</v>
+      </c>
+      <c r="L5">
+        <v>180</v>
+      </c>
+      <c r="M5" s="2">
+        <v>46029.21527777778</v>
+      </c>
+      <c r="N5">
+        <v>295</v>
+      </c>
+      <c r="O5" t="s">
+        <v>150</v>
+      </c>
+      <c r="P5" s="2">
+        <v>46029.42013888889</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>46029.46180555555</v>
+      </c>
+      <c r="R5" t="s">
         <v>158</v>
-      </c>
-      <c r="J5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K5" s="2">
-        <v>46029.25</v>
-      </c>
-      <c r="L5">
-        <v>90</v>
-      </c>
-      <c r="M5" s="2">
-        <v>46029.3125</v>
-      </c>
-      <c r="N5">
-        <v>258</v>
-      </c>
-      <c r="O5" t="s">
-        <v>166</v>
-      </c>
-      <c r="P5" s="2">
-        <v>46029.49166666667</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>46029.73541666667</v>
-      </c>
-      <c r="R5" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H6">
-        <v>2.2948</v>
+        <v>2.9976</v>
       </c>
       <c r="I6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K6" s="2">
+        <v>46029.22916666666</v>
+      </c>
+      <c r="L6">
+        <v>90</v>
+      </c>
+      <c r="M6" s="2">
+        <v>46029.29166666666</v>
+      </c>
+      <c r="N6">
+        <v>150</v>
+      </c>
+      <c r="O6" t="s">
+        <v>150</v>
+      </c>
+      <c r="P6" s="2">
+        <v>46029.39583333334</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>46030.61180555556</v>
+      </c>
+      <c r="R6" t="s">
         <v>158</v>
-      </c>
-      <c r="J6" t="s">
-        <v>162</v>
-      </c>
-      <c r="K6" s="2">
-        <v>46029.32638888889</v>
-      </c>
-      <c r="L6">
-        <v>180</v>
-      </c>
-      <c r="M6" s="2">
-        <v>46029.45138888889</v>
-      </c>
-      <c r="N6">
-        <v>277</v>
-      </c>
-      <c r="O6" t="s">
-        <v>164</v>
-      </c>
-      <c r="P6" s="2">
-        <v>46029.64375</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>46029.68541666667</v>
-      </c>
-      <c r="R6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H7">
         <v>4.4185</v>
       </c>
       <c r="I7" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J7" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K7" s="2">
-        <v>46029.46527777778</v>
+        <v>46029.30555555555</v>
       </c>
       <c r="L7">
         <v>90</v>
       </c>
       <c r="M7" s="2">
-        <v>46029.52777777778</v>
+        <v>46029.36805555555</v>
       </c>
       <c r="N7">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="O7" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="P7" s="2">
+        <v>46029.44305555556</v>
+      </c>
+      <c r="Q7" s="2">
         <v>46029.62708333333</v>
       </c>
-      <c r="Q7" s="2">
-        <v>46029.81041666667</v>
-      </c>
       <c r="R7" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1841,164 +1733,164 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="G8" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H8">
         <v>4.4185</v>
       </c>
       <c r="I8" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J8" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K8" s="2">
-        <v>46029.52777777778</v>
+        <v>46029.36805555555</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8" s="2">
-        <v>46029.59027777778</v>
+        <v>46029.43055555555</v>
       </c>
       <c r="N8">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="O8" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="P8" s="2">
+        <v>46029.49166666667</v>
+      </c>
+      <c r="Q8" s="2">
         <v>46029.73541666667</v>
       </c>
-      <c r="Q8" s="2">
-        <v>46029.94930555556</v>
-      </c>
       <c r="R8" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H9">
-        <v>4.4185</v>
+        <v>3.9956</v>
       </c>
       <c r="I9" t="s">
+        <v>145</v>
+      </c>
+      <c r="J9" t="s">
+        <v>148</v>
+      </c>
+      <c r="K9" s="2">
+        <v>46029.43055555555</v>
+      </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
+      <c r="M9" s="2">
+        <v>46029.49652777778</v>
+      </c>
+      <c r="N9">
+        <v>191</v>
+      </c>
+      <c r="O9" t="s">
+        <v>149</v>
+      </c>
+      <c r="P9" s="2">
+        <v>46029.62916666667</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>46029.92083333333</v>
+      </c>
+      <c r="R9" t="s">
         <v>158</v>
-      </c>
-      <c r="J9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K9" s="2">
-        <v>46029.59027777778</v>
-      </c>
-      <c r="L9">
-        <v>90</v>
-      </c>
-      <c r="M9" s="2">
-        <v>46029.65277777778</v>
-      </c>
-      <c r="N9">
-        <v>227</v>
-      </c>
-      <c r="O9" t="s">
-        <v>165</v>
-      </c>
-      <c r="P9" s="2">
-        <v>46029.81041666667</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>46029.99444444444</v>
-      </c>
-      <c r="R9" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F10" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H10">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I10" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="K10" s="2">
-        <v>46029.65277777778</v>
+        <v>46029.49652777778</v>
       </c>
       <c r="L10">
         <v>90</v>
       </c>
       <c r="M10" s="2">
-        <v>46029.71527777778</v>
+        <v>46029.55902777778</v>
       </c>
       <c r="N10">
-        <v>337</v>
+        <v>98</v>
       </c>
       <c r="O10" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="P10" s="2">
-        <v>46029.94930555556</v>
+        <v>46029.62708333333</v>
       </c>
       <c r="Q10" s="2">
-        <v>46030.49583333333</v>
+        <v>46029.81041666667</v>
       </c>
       <c r="R10" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2009,388 +1901,388 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11">
+        <v>2.2948</v>
+      </c>
+      <c r="I11" t="s">
         <v>144</v>
       </c>
-      <c r="G11" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11">
-        <v>4.4185</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
+        <v>148</v>
+      </c>
+      <c r="K11" s="2">
+        <v>46029.57291666666</v>
+      </c>
+      <c r="L11">
+        <v>180</v>
+      </c>
+      <c r="M11" s="2">
+        <v>46029.69791666666</v>
+      </c>
+      <c r="N11">
+        <v>140</v>
+      </c>
+      <c r="O11" t="s">
+        <v>150</v>
+      </c>
+      <c r="P11" s="2">
+        <v>46029.79513888889</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>46029.83680555555</v>
+      </c>
+      <c r="R11" t="s">
         <v>158</v>
-      </c>
-      <c r="J11" t="s">
-        <v>160</v>
-      </c>
-      <c r="K11" s="2">
-        <v>46029.71527777778</v>
-      </c>
-      <c r="L11">
-        <v>90</v>
-      </c>
-      <c r="M11" s="2">
-        <v>46029.77777777778</v>
-      </c>
-      <c r="N11">
-        <v>312</v>
-      </c>
-      <c r="O11" t="s">
-        <v>167</v>
-      </c>
-      <c r="P11" s="2">
-        <v>46029.99444444444</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>46030.17847222222</v>
-      </c>
-      <c r="R11" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="G12" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H12">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="I12" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" t="s">
+        <v>148</v>
+      </c>
+      <c r="K12" s="2">
+        <v>46029.71180555555</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12" s="2">
+        <v>46029.77430555555</v>
+      </c>
+      <c r="N12">
+        <v>-56</v>
+      </c>
+      <c r="O12" t="s">
+        <v>151</v>
+      </c>
+      <c r="P12" s="2">
+        <v>46029.73541666667</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>46029.94930555556</v>
+      </c>
+      <c r="R12" t="s">
         <v>158</v>
-      </c>
-      <c r="J12" t="s">
-        <v>160</v>
-      </c>
-      <c r="K12" s="2">
-        <v>46029.79166666666</v>
-      </c>
-      <c r="L12">
-        <v>180</v>
-      </c>
-      <c r="M12" s="2">
-        <v>46029.91666666666</v>
-      </c>
-      <c r="N12">
-        <v>390</v>
-      </c>
-      <c r="O12" t="s">
-        <v>168</v>
-      </c>
-      <c r="P12" s="2">
-        <v>46030.1875</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>46030.22916666666</v>
-      </c>
-      <c r="R12" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H13">
         <v>4.4185</v>
       </c>
       <c r="I13" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J13" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="K13" s="2">
-        <v>46029.93055555555</v>
+        <v>46029.77430555555</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13" s="2">
-        <v>46029.99305555555</v>
+        <v>46029.83680555555</v>
       </c>
       <c r="N13">
-        <v>267</v>
+        <v>-38</v>
       </c>
       <c r="O13" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="P13" s="2">
-        <v>46030.17847222222</v>
+        <v>46029.81041666667</v>
       </c>
       <c r="Q13" s="2">
-        <v>46030.36180555556</v>
+        <v>46029.99444444444</v>
       </c>
       <c r="R13" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F14" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H14">
-        <v>4.5022</v>
+        <v>4.4163</v>
       </c>
       <c r="I14" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J14" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="K14" s="2">
-        <v>46029.99305555555</v>
+        <v>46029.83680555555</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14" s="2">
-        <v>46030.05555555555</v>
+        <v>46029.89930555555</v>
       </c>
       <c r="N14">
-        <v>368</v>
+        <v>72</v>
       </c>
       <c r="O14" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="P14" s="2">
-        <v>46030.31111111111</v>
+        <v>46029.94930555556</v>
       </c>
       <c r="Q14" s="2">
-        <v>46030.43125</v>
+        <v>46030.49583333333</v>
       </c>
       <c r="R14" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H15">
         <v>4.4185</v>
       </c>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J15" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="K15" s="2">
-        <v>46030.05555555555</v>
+        <v>46029.89930555555</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15" s="2">
-        <v>46030.11805555555</v>
+        <v>46029.96180555555</v>
       </c>
       <c r="N15">
-        <v>351</v>
+        <v>47</v>
       </c>
       <c r="O15" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="P15" s="2">
-        <v>46030.36180555556</v>
+        <v>46029.99444444444</v>
       </c>
       <c r="Q15" s="2">
-        <v>46030.54583333333</v>
+        <v>46030.17847222222</v>
       </c>
       <c r="R15" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H16">
-        <v>4.5022</v>
+        <v>4.4185</v>
       </c>
       <c r="I16" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J16" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="K16" s="2">
-        <v>46030.11805555555</v>
+        <v>46029.96180555555</v>
       </c>
       <c r="L16">
         <v>90</v>
       </c>
       <c r="M16" s="2">
-        <v>46030.18055555555</v>
+        <v>46030.02430555555</v>
       </c>
       <c r="N16">
-        <v>361</v>
+        <v>222</v>
       </c>
       <c r="O16" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="P16" s="2">
-        <v>46030.43125</v>
+        <v>46030.17847222222</v>
       </c>
       <c r="Q16" s="2">
-        <v>46030.55138888889</v>
+        <v>46030.36180555556</v>
       </c>
       <c r="R16" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H17">
-        <v>4.4163</v>
+        <v>4.5022</v>
       </c>
       <c r="I17" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J17" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K17" s="2">
-        <v>46030.18055555555</v>
+        <v>46030.02430555555</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17" s="2">
-        <v>46030.24305555555</v>
+        <v>46030.08680555555</v>
       </c>
       <c r="N17">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="O17" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="P17" s="2">
-        <v>46030.49583333333</v>
+        <v>46030.31111111111</v>
       </c>
       <c r="Q17" s="2">
-        <v>46030.70972222222</v>
+        <v>46030.43125</v>
       </c>
       <c r="R17" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2401,444 +2293,444 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="G18" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H18">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="I18" t="s">
+        <v>144</v>
+      </c>
+      <c r="J18" t="s">
+        <v>147</v>
+      </c>
+      <c r="K18" s="2">
+        <v>46030.08680555555</v>
+      </c>
+      <c r="L18">
+        <v>90</v>
+      </c>
+      <c r="M18" s="2">
+        <v>46030.14930555555</v>
+      </c>
+      <c r="N18">
+        <v>306</v>
+      </c>
+      <c r="O18" t="s">
+        <v>150</v>
+      </c>
+      <c r="P18" s="2">
+        <v>46030.36180555556</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>46030.54583333333</v>
+      </c>
+      <c r="R18" t="s">
         <v>158</v>
-      </c>
-      <c r="J18" t="s">
-        <v>162</v>
-      </c>
-      <c r="K18" s="2">
-        <v>46030.25694444445</v>
-      </c>
-      <c r="L18">
-        <v>180</v>
-      </c>
-      <c r="M18" s="2">
-        <v>46030.38194444445</v>
-      </c>
-      <c r="N18">
-        <v>260</v>
-      </c>
-      <c r="O18" t="s">
-        <v>163</v>
-      </c>
-      <c r="P18" s="2">
-        <v>46030.5625</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>46030.60416666666</v>
-      </c>
-      <c r="R18" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" t="s">
+        <v>142</v>
+      </c>
+      <c r="H19">
+        <v>4.5022</v>
+      </c>
+      <c r="I19" t="s">
         <v>144</v>
       </c>
-      <c r="G19" t="s">
-        <v>156</v>
-      </c>
-      <c r="H19">
-        <v>4.4185</v>
-      </c>
-      <c r="I19" t="s">
-        <v>158</v>
-      </c>
       <c r="J19" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K19" s="2">
-        <v>46030.39583333334</v>
+        <v>46030.14930555555</v>
       </c>
       <c r="L19">
         <v>90</v>
       </c>
       <c r="M19" s="2">
-        <v>46030.45833333334</v>
+        <v>46030.21180555555</v>
       </c>
       <c r="N19">
-        <v>126</v>
+        <v>316</v>
       </c>
       <c r="O19" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P19" s="2">
-        <v>46030.54583333333</v>
+        <v>46030.43125</v>
       </c>
       <c r="Q19" s="2">
-        <v>46030.72916666666</v>
+        <v>46030.55138888889</v>
       </c>
       <c r="R19" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G20" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H20">
-        <v>4.5228</v>
+        <v>4.4163</v>
       </c>
       <c r="I20" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J20" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K20" s="2">
-        <v>46030.45833333334</v>
+        <v>46030.21180555555</v>
       </c>
       <c r="L20">
         <v>90</v>
       </c>
       <c r="M20" s="2">
-        <v>46030.52083333334</v>
+        <v>46030.27430555555</v>
       </c>
       <c r="N20">
-        <v>131</v>
+        <v>319</v>
       </c>
       <c r="O20" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="P20" s="2">
-        <v>46030.61180555556</v>
+        <v>46030.49583333333</v>
       </c>
       <c r="Q20" s="2">
-        <v>46030.73194444444</v>
+        <v>46030.70972222222</v>
       </c>
       <c r="R20" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F21" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="H21">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J21" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K21" s="2">
-        <v>46030.52083333334</v>
+        <v>46030.27430555555</v>
       </c>
       <c r="L21">
         <v>90</v>
       </c>
       <c r="M21" s="2">
-        <v>46030.58333333334</v>
+        <v>46030.33680555555</v>
       </c>
       <c r="N21">
-        <v>182</v>
+        <v>301</v>
       </c>
       <c r="O21" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="P21" s="2">
-        <v>46030.70972222222</v>
+        <v>46030.54583333333</v>
       </c>
       <c r="Q21" s="2">
-        <v>46030.92291666667</v>
+        <v>46030.72916666666</v>
       </c>
       <c r="R21" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22">
+        <v>4.5228</v>
+      </c>
+      <c r="I22" t="s">
         <v>144</v>
       </c>
-      <c r="G22" t="s">
-        <v>156</v>
-      </c>
-      <c r="H22">
-        <v>4.4185</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
       <c r="J22" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K22" s="2">
-        <v>46030.58333333334</v>
+        <v>46030.33680555555</v>
       </c>
       <c r="L22">
         <v>90</v>
       </c>
       <c r="M22" s="2">
-        <v>46030.64583333334</v>
+        <v>46030.39930555555</v>
       </c>
       <c r="N22">
-        <v>120</v>
+        <v>306</v>
       </c>
       <c r="O22" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="P22" s="2">
-        <v>46030.72916666666</v>
+        <v>46030.61180555556</v>
       </c>
       <c r="Q22" s="2">
-        <v>46030.91319444445</v>
+        <v>46030.73194444444</v>
       </c>
       <c r="R22" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G23" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="H23">
-        <v>0.5601</v>
+        <v>4.4163</v>
       </c>
       <c r="I23" t="s">
+        <v>144</v>
+      </c>
+      <c r="J23" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="2">
+        <v>46030.39930555555</v>
+      </c>
+      <c r="L23">
+        <v>90</v>
+      </c>
+      <c r="M23" s="2">
+        <v>46030.46180555555</v>
+      </c>
+      <c r="N23">
+        <v>357</v>
+      </c>
+      <c r="O23" t="s">
+        <v>149</v>
+      </c>
+      <c r="P23" s="2">
+        <v>46030.70972222222</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>46030.92291666667</v>
+      </c>
+      <c r="R23" t="s">
         <v>158</v>
-      </c>
-      <c r="J23" t="s">
-        <v>161</v>
-      </c>
-      <c r="K23" s="2">
-        <v>46028.1875</v>
-      </c>
-      <c r="L23">
-        <v>180</v>
-      </c>
-      <c r="M23" s="2">
-        <v>46028.3125</v>
-      </c>
-      <c r="N23">
-        <v>1440</v>
-      </c>
-      <c r="O23" t="s">
-        <v>167</v>
-      </c>
-      <c r="P23" s="2">
-        <v>46029.3125</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>46029.48125</v>
-      </c>
-      <c r="R23" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="H24">
-        <v>0.5601</v>
+        <v>4.4185</v>
       </c>
       <c r="I24" t="s">
+        <v>144</v>
+      </c>
+      <c r="J24" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="2">
+        <v>46030.46180555555</v>
+      </c>
+      <c r="L24">
+        <v>90</v>
+      </c>
+      <c r="M24" s="2">
+        <v>46030.52430555555</v>
+      </c>
+      <c r="N24">
+        <v>295</v>
+      </c>
+      <c r="O24" t="s">
+        <v>155</v>
+      </c>
+      <c r="P24" s="2">
+        <v>46030.72916666666</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>46030.91319444445</v>
+      </c>
+      <c r="R24" t="s">
         <v>158</v>
-      </c>
-      <c r="J24" t="s">
-        <v>162</v>
-      </c>
-      <c r="K24" s="2">
-        <v>46028.45625</v>
-      </c>
-      <c r="L24">
-        <v>180</v>
-      </c>
-      <c r="M24" s="2">
-        <v>46028.58125</v>
-      </c>
-      <c r="N24">
-        <v>1440</v>
-      </c>
-      <c r="O24" t="s">
-        <v>169</v>
-      </c>
-      <c r="P24" s="2">
-        <v>46029.58125</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>46030.41666666666</v>
-      </c>
-      <c r="R24" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="G25" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H25">
-        <v>2.2314</v>
+        <v>1.1202</v>
       </c>
       <c r="I25" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J25" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="K25" s="2">
-        <v>46028.99305555555</v>
+        <v>46028.1875</v>
       </c>
       <c r="L25">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M25" s="2">
-        <v>46029.05555555555</v>
+        <v>46028.3125</v>
       </c>
       <c r="N25">
-        <v>490</v>
+        <v>1440</v>
       </c>
       <c r="O25" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="P25" s="2">
-        <v>46029.39583333334</v>
+        <v>46029.3125</v>
       </c>
       <c r="Q25" s="2">
-        <v>46029.62916666667</v>
+        <v>46030.41666666666</v>
       </c>
       <c r="R25" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2849,43 +2741,43 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F26" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="G26" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J26" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K26" s="2">
-        <v>46029.09027777778</v>
+        <v>46028.375</v>
       </c>
       <c r="L26">
         <v>90</v>
       </c>
       <c r="M26" s="2">
-        <v>46029.15277777778</v>
+        <v>46028.4375</v>
       </c>
       <c r="N26">
-        <v>1820</v>
+        <v>2850</v>
       </c>
       <c r="O26" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="P26" s="2">
         <v>46030.41666666666</v>
@@ -2894,7 +2786,7 @@
         <v>46030.59652777778</v>
       </c>
       <c r="R26" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2905,43 +2797,43 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G27" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H27">
         <v>2.19</v>
       </c>
       <c r="I27" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J27" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K27" s="2">
-        <v>46029.19444444445</v>
+        <v>46028.47916666666</v>
       </c>
       <c r="L27">
         <v>90</v>
       </c>
       <c r="M27" s="2">
-        <v>46029.25694444445</v>
+        <v>46028.54166666666</v>
       </c>
       <c r="N27">
-        <v>400</v>
+        <v>1430</v>
       </c>
       <c r="O27" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="P27" s="2">
         <v>46029.53472222222</v>
@@ -2950,119 +2842,119 @@
         <v>46030.25</v>
       </c>
       <c r="R27" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F28" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="G28" t="s">
+        <v>143</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J28" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="2">
+        <v>46028.57638888889</v>
+      </c>
+      <c r="L28">
+        <v>90</v>
+      </c>
+      <c r="M28" s="2">
+        <v>46028.63888888889</v>
+      </c>
+      <c r="N28">
+        <v>2819</v>
+      </c>
+      <c r="O28" t="s">
         <v>157</v>
       </c>
-      <c r="H28">
-        <v>2.2511</v>
-      </c>
-      <c r="I28" t="s">
-        <v>159</v>
-      </c>
-      <c r="J28" t="s">
-        <v>162</v>
-      </c>
-      <c r="K28" s="2">
-        <v>46029.27083333334</v>
-      </c>
-      <c r="L28">
-        <v>85</v>
-      </c>
-      <c r="M28" s="2">
-        <v>46029.32986111111</v>
-      </c>
-      <c r="N28">
-        <v>431</v>
-      </c>
-      <c r="O28" t="s">
-        <v>166</v>
-      </c>
       <c r="P28" s="2">
-        <v>46029.62916666667</v>
+        <v>46030.59652777778</v>
       </c>
       <c r="Q28" s="2">
-        <v>46029.68958333333</v>
+        <v>46031.41736111111</v>
       </c>
       <c r="R28" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G29" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2.2511</v>
       </c>
       <c r="I29" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J29" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K29" s="2">
-        <v>46029.36458333334</v>
+        <v>46028.68055555555</v>
       </c>
       <c r="L29">
         <v>90</v>
       </c>
       <c r="M29" s="2">
-        <v>46029.42708333334</v>
+        <v>46028.74305555555</v>
       </c>
       <c r="N29">
-        <v>1684</v>
+        <v>1363</v>
       </c>
       <c r="O29" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="P29" s="2">
-        <v>46030.59652777778</v>
+        <v>46029.68958333333</v>
       </c>
       <c r="Q29" s="2">
-        <v>46031.41736111111</v>
+        <v>46029.75</v>
       </c>
       <c r="R29" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -3073,52 +2965,52 @@
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G30" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H30">
-        <v>2.2511</v>
+        <v>1.9872</v>
       </c>
       <c r="I30" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J30" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K30" s="2">
-        <v>46029.46875</v>
+        <v>46028.75694444445</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30" s="2">
-        <v>46029.53125</v>
+        <v>46028.81944444445</v>
       </c>
       <c r="N30">
-        <v>228</v>
+        <v>1340</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="P30" s="2">
-        <v>46029.68958333333</v>
+        <v>46029.75</v>
       </c>
       <c r="Q30" s="2">
-        <v>46029.75</v>
+        <v>46029.82638888889</v>
       </c>
       <c r="R30" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -3129,52 +3021,52 @@
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G31" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H31">
-        <v>1.1225</v>
+        <v>2.2614</v>
       </c>
       <c r="I31" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J31" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K31" s="2">
-        <v>46029.54513888889</v>
+        <v>46028.83333333334</v>
       </c>
       <c r="L31">
         <v>90</v>
       </c>
       <c r="M31" s="2">
-        <v>46029.60763888889</v>
+        <v>46028.89583333334</v>
       </c>
       <c r="N31">
-        <v>205</v>
+        <v>1951</v>
       </c>
       <c r="O31" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="P31" s="2">
-        <v>46029.75</v>
+        <v>46030.25069444445</v>
       </c>
       <c r="Q31" s="2">
-        <v>46029.77986111111</v>
+        <v>46030.31111111111</v>
       </c>
       <c r="R31" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -3185,52 +3077,52 @@
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="G32" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H32">
-        <v>1.1174</v>
+        <v>2.2314</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J32" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="K32" s="2">
-        <v>46029.60763888889</v>
+        <v>46028.90972222222</v>
       </c>
       <c r="L32">
         <v>90</v>
       </c>
       <c r="M32" s="2">
-        <v>46029.67013888889</v>
+        <v>46028.97222222222</v>
       </c>
       <c r="N32">
+        <v>2534</v>
+      </c>
+      <c r="O32" t="s">
+        <v>150</v>
+      </c>
+      <c r="P32" s="2">
+        <v>46030.73194444444</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>46030.96527777778</v>
+      </c>
+      <c r="R32" t="s">
         <v>158</v>
-      </c>
-      <c r="O32" t="s">
-        <v>168</v>
-      </c>
-      <c r="P32" s="2">
-        <v>46029.77986111111</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>46029.82638888889</v>
-      </c>
-      <c r="R32" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -3241,52 +3133,52 @@
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G33" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H33">
-        <v>2.2544</v>
+        <v>2.1937</v>
       </c>
       <c r="I33" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="J33" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="K33" s="2">
-        <v>46029.68402777778</v>
+        <v>46028.98611111111</v>
       </c>
       <c r="L33">
         <v>85</v>
       </c>
       <c r="M33" s="2">
-        <v>46029.74305555555</v>
+        <v>46029.04513888889</v>
       </c>
       <c r="N33">
-        <v>120</v>
+        <v>2701</v>
       </c>
       <c r="O33" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="P33" s="2">
-        <v>46029.82638888889</v>
+        <v>46030.92083333333</v>
       </c>
       <c r="Q33" s="2">
-        <v>46029.92083333333</v>
+        <v>46030.96527777778</v>
       </c>
       <c r="R33" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -3297,52 +3189,52 @@
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F34" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G34" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H34">
         <v>2.2614</v>
       </c>
       <c r="I34" t="s">
+        <v>145</v>
+      </c>
+      <c r="J34" t="s">
+        <v>146</v>
+      </c>
+      <c r="K34" s="2">
+        <v>46029.05902777778</v>
+      </c>
+      <c r="L34">
+        <v>85</v>
+      </c>
+      <c r="M34" s="2">
+        <v>46029.11805555555</v>
+      </c>
+      <c r="N34">
+        <v>2660</v>
+      </c>
+      <c r="O34" t="s">
+        <v>150</v>
+      </c>
+      <c r="P34" s="2">
+        <v>46030.96527777778</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>46030.53472222222</v>
+      </c>
+      <c r="R34" t="s">
         <v>158</v>
-      </c>
-      <c r="J34" t="s">
-        <v>161</v>
-      </c>
-      <c r="K34" s="2">
-        <v>46030.10486111111</v>
-      </c>
-      <c r="L34">
-        <v>90</v>
-      </c>
-      <c r="M34" s="2">
-        <v>46030.16736111111</v>
-      </c>
-      <c r="N34">
-        <v>120</v>
-      </c>
-      <c r="O34" t="s">
-        <v>166</v>
-      </c>
-      <c r="P34" s="2">
-        <v>46030.25069444445</v>
-      </c>
-      <c r="Q34" s="2">
-        <v>46030.31111111111</v>
-      </c>
-      <c r="R34" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -3353,276 +3245,52 @@
         <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G35" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="H35">
-        <v>2.2614</v>
+        <v>2.2314</v>
       </c>
       <c r="I35" t="s">
+        <v>144</v>
+      </c>
+      <c r="J35" t="s">
+        <v>146</v>
+      </c>
+      <c r="K35" s="2">
+        <v>46029.13194444445</v>
+      </c>
+      <c r="L35">
+        <v>85</v>
+      </c>
+      <c r="M35" s="2">
+        <v>46029.19097222222</v>
+      </c>
+      <c r="N35">
+        <v>2555</v>
+      </c>
+      <c r="O35" t="s">
+        <v>150</v>
+      </c>
+      <c r="P35" s="2">
+        <v>46030.96527777778</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>46031.19930555556</v>
+      </c>
+      <c r="R35" t="s">
         <v>158</v>
-      </c>
-      <c r="J35" t="s">
-        <v>162</v>
-      </c>
-      <c r="K35" s="2">
-        <v>46030.40555555555</v>
-      </c>
-      <c r="L35">
-        <v>90</v>
-      </c>
-      <c r="M35" s="2">
-        <v>46030.46805555555</v>
-      </c>
-      <c r="N35">
-        <v>120</v>
-      </c>
-      <c r="O35" t="s">
-        <v>169</v>
-      </c>
-      <c r="P35" s="2">
-        <v>46030.55138888889</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>46030.61180555556</v>
-      </c>
-      <c r="R35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
-      <c r="A36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" t="s">
-        <v>139</v>
-      </c>
-      <c r="F36" t="s">
-        <v>145</v>
-      </c>
-      <c r="G36" t="s">
-        <v>157</v>
-      </c>
-      <c r="H36">
-        <v>2.2314</v>
-      </c>
-      <c r="I36" t="s">
-        <v>158</v>
-      </c>
-      <c r="J36" t="s">
-        <v>162</v>
-      </c>
-      <c r="K36" s="2">
-        <v>46030.58611111111</v>
-      </c>
-      <c r="L36">
-        <v>90</v>
-      </c>
-      <c r="M36" s="2">
-        <v>46030.64861111111</v>
-      </c>
-      <c r="N36">
-        <v>120</v>
-      </c>
-      <c r="O36" t="s">
-        <v>163</v>
-      </c>
-      <c r="P36" s="2">
-        <v>46030.73194444444</v>
-      </c>
-      <c r="Q36" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="R36" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
-      <c r="A37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" t="s">
-        <v>154</v>
-      </c>
-      <c r="G37" t="s">
-        <v>157</v>
-      </c>
-      <c r="H37">
-        <v>2.1937</v>
-      </c>
-      <c r="I37" t="s">
-        <v>158</v>
-      </c>
-      <c r="J37" t="s">
-        <v>160</v>
-      </c>
-      <c r="K37" s="2">
-        <v>46030.67708333334</v>
-      </c>
-      <c r="L37">
-        <v>85</v>
-      </c>
-      <c r="M37" s="2">
-        <v>46030.73611111111</v>
-      </c>
-      <c r="N37">
-        <v>266</v>
-      </c>
-      <c r="O37" t="s">
-        <v>164</v>
-      </c>
-      <c r="P37" s="2">
-        <v>46030.92083333333</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="R37" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
-      <c r="A38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F38" t="s">
-        <v>155</v>
-      </c>
-      <c r="G38" t="s">
-        <v>157</v>
-      </c>
-      <c r="H38">
-        <v>2.2314</v>
-      </c>
-      <c r="I38" t="s">
-        <v>158</v>
-      </c>
-      <c r="J38" t="s">
-        <v>160</v>
-      </c>
-      <c r="K38" s="2">
-        <v>46030.75</v>
-      </c>
-      <c r="L38">
-        <v>85</v>
-      </c>
-      <c r="M38" s="2">
-        <v>46030.80902777778</v>
-      </c>
-      <c r="N38">
-        <v>225</v>
-      </c>
-      <c r="O38" t="s">
-        <v>165</v>
-      </c>
-      <c r="P38" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="Q38" s="2">
-        <v>46031.19930555556</v>
-      </c>
-      <c r="R38" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
-      <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>104</v>
-      </c>
-      <c r="E39" t="s">
-        <v>142</v>
-      </c>
-      <c r="F39" t="s">
-        <v>150</v>
-      </c>
-      <c r="G39" t="s">
-        <v>157</v>
-      </c>
-      <c r="H39">
-        <v>2.2614</v>
-      </c>
-      <c r="I39" t="s">
-        <v>159</v>
-      </c>
-      <c r="J39" t="s">
-        <v>160</v>
-      </c>
-      <c r="K39" s="2">
-        <v>46030.82291666666</v>
-      </c>
-      <c r="L39">
-        <v>85</v>
-      </c>
-      <c r="M39" s="2">
-        <v>46030.88194444445</v>
-      </c>
-      <c r="N39">
-        <v>120</v>
-      </c>
-      <c r="O39" t="s">
-        <v>168</v>
-      </c>
-      <c r="P39" s="2">
-        <v>46030.96527777778</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>46030.53472222222</v>
-      </c>
-      <c r="R39" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3632,7 +3300,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3642,1540 +3310,1345 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>335</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>335</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>148</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>148</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>148</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>148</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>336</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>336</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>148</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B27" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>312</v>
+        <v>280</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>312</v>
+        <v>280</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>312</v>
+        <v>280</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>282</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B47" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>284</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>338</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>339</v>
+        <v>284</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>340</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B56" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>340</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B57" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B58" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B59" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B61" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
+        <v>225</v>
+      </c>
+      <c r="B64" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>226</v>
+      </c>
+      <c r="B65" t="s">
+        <v>148</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>227</v>
+      </c>
+      <c r="B66" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>228</v>
+      </c>
+      <c r="B67" t="s">
+        <v>148</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>229</v>
+      </c>
+      <c r="B68" t="s">
+        <v>148</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>230</v>
+      </c>
+      <c r="B69" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>231</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>232</v>
+      </c>
+      <c r="B71" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>233</v>
+      </c>
+      <c r="B72" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>234</v>
+      </c>
+      <c r="B73" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>235</v>
+      </c>
+      <c r="B74" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>236</v>
+      </c>
+      <c r="B75" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>237</v>
+      </c>
+      <c r="B76" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77" t="s">
+        <v>146</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
         <v>239</v>
       </c>
-      <c r="B64" t="s">
-        <v>162</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
+      <c r="B78" t="s">
+        <v>146</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
         <v>240</v>
       </c>
-      <c r="B65" t="s">
-        <v>162</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
+      <c r="B79" t="s">
+        <v>146</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
         <v>241</v>
       </c>
-      <c r="B66" t="s">
-        <v>162</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
+      <c r="B80" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>242</v>
       </c>
-      <c r="B67" t="s">
-        <v>162</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
+      <c r="B81" t="s">
+        <v>146</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
         <v>243</v>
       </c>
-      <c r="B68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
+      <c r="B82" t="s">
+        <v>146</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
         <v>244</v>
       </c>
-      <c r="B69" t="s">
-        <v>162</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
+      <c r="B83" t="s">
+        <v>146</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
         <v>245</v>
       </c>
-      <c r="B70" t="s">
-        <v>162</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
+      <c r="B84" t="s">
+        <v>146</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
         <v>246</v>
       </c>
-      <c r="B71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
+      <c r="B85" t="s">
+        <v>146</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
         <v>247</v>
       </c>
-      <c r="B72" t="s">
-        <v>162</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
+      <c r="B86" t="s">
+        <v>146</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
         <v>248</v>
       </c>
-      <c r="B73" t="s">
-        <v>160</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
+      <c r="B87" t="s">
+        <v>146</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
         <v>249</v>
       </c>
-      <c r="B74" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
+      <c r="B88" t="s">
+        <v>146</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
         <v>250</v>
       </c>
-      <c r="B75" t="s">
-        <v>160</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
+      <c r="B89" t="s">
+        <v>147</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>251</v>
       </c>
-      <c r="B76" t="s">
-        <v>160</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
+      <c r="B90" t="s">
+        <v>147</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>252</v>
       </c>
-      <c r="B77" t="s">
-        <v>160</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
+      <c r="B91" t="s">
+        <v>147</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
         <v>253</v>
       </c>
-      <c r="B78" t="s">
-        <v>160</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
+      <c r="B92" t="s">
+        <v>147</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
         <v>254</v>
       </c>
-      <c r="B79" t="s">
-        <v>160</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
+      <c r="B93" t="s">
+        <v>147</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
         <v>255</v>
       </c>
-      <c r="B80" t="s">
-        <v>160</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
+      <c r="B94" t="s">
+        <v>147</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
         <v>256</v>
       </c>
-      <c r="B81" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
+      <c r="B95" t="s">
+        <v>147</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
         <v>257</v>
       </c>
-      <c r="B82" t="s">
-        <v>160</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
+      <c r="B96" t="s">
+        <v>147</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
         <v>258</v>
       </c>
-      <c r="B83" t="s">
-        <v>160</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
+      <c r="B97" t="s">
+        <v>147</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
         <v>259</v>
       </c>
-      <c r="B84" t="s">
-        <v>160</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
+      <c r="B98" t="s">
+        <v>147</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
         <v>260</v>
       </c>
-      <c r="B85" t="s">
-        <v>160</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
+      <c r="B99" t="s">
+        <v>147</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
         <v>261</v>
       </c>
-      <c r="B86" t="s">
-        <v>160</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
+      <c r="B100" t="s">
+        <v>147</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
         <v>262</v>
       </c>
-      <c r="B87" t="s">
-        <v>160</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
+      <c r="B101" t="s">
+        <v>147</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
         <v>263</v>
       </c>
-      <c r="B88" t="s">
-        <v>160</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
+      <c r="B102" t="s">
+        <v>147</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
         <v>264</v>
       </c>
-      <c r="B89" t="s">
-        <v>161</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
+      <c r="B103" t="s">
+        <v>147</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
         <v>265</v>
       </c>
-      <c r="B90" t="s">
-        <v>161</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
+      <c r="B104" t="s">
+        <v>147</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
         <v>266</v>
       </c>
-      <c r="B91" t="s">
-        <v>161</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
+      <c r="B105" t="s">
+        <v>148</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
         <v>267</v>
       </c>
-      <c r="B92" t="s">
-        <v>161</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
+      <c r="B106" t="s">
+        <v>148</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
         <v>268</v>
       </c>
-      <c r="B93" t="s">
-        <v>161</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
+      <c r="B107" t="s">
+        <v>148</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
         <v>269</v>
       </c>
-      <c r="B94" t="s">
-        <v>161</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
+      <c r="B108" t="s">
+        <v>148</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
         <v>270</v>
       </c>
-      <c r="B95" t="s">
-        <v>161</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
+      <c r="B109" t="s">
+        <v>148</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
         <v>271</v>
       </c>
-      <c r="B96" t="s">
-        <v>161</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
+      <c r="B110" t="s">
+        <v>148</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
         <v>272</v>
       </c>
-      <c r="B97" t="s">
-        <v>161</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" t="s">
+      <c r="B111" t="s">
+        <v>148</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
         <v>273</v>
       </c>
-      <c r="B98" t="s">
-        <v>161</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
+      <c r="B112" t="s">
+        <v>148</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
         <v>274</v>
       </c>
-      <c r="B99" t="s">
-        <v>161</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
+      <c r="B113" t="s">
+        <v>148</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
         <v>275</v>
       </c>
-      <c r="B100" t="s">
-        <v>161</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" t="s">
+      <c r="B114" t="s">
+        <v>148</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
         <v>276</v>
       </c>
-      <c r="B101" t="s">
-        <v>161</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" t="s">
+      <c r="B115" t="s">
+        <v>148</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
         <v>277</v>
       </c>
-      <c r="B102" t="s">
-        <v>161</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" t="s">
+      <c r="B116" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
         <v>278</v>
       </c>
-      <c r="B103" t="s">
-        <v>161</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" t="s">
+      <c r="B117" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
         <v>279</v>
       </c>
-      <c r="B104" t="s">
-        <v>161</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" t="s">
-        <v>280</v>
-      </c>
-      <c r="B105" t="s">
-        <v>162</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" t="s">
-        <v>281</v>
-      </c>
-      <c r="B106" t="s">
-        <v>162</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" t="s">
-        <v>282</v>
-      </c>
-      <c r="B107" t="s">
-        <v>162</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" t="s">
-        <v>283</v>
-      </c>
-      <c r="B108" t="s">
-        <v>162</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" t="s">
-        <v>284</v>
-      </c>
-      <c r="B109" t="s">
-        <v>162</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" t="s">
-        <v>285</v>
-      </c>
-      <c r="B110" t="s">
-        <v>162</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" t="s">
-        <v>286</v>
-      </c>
-      <c r="B111" t="s">
-        <v>162</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" t="s">
-        <v>287</v>
-      </c>
-      <c r="B112" t="s">
-        <v>162</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" t="s">
-        <v>288</v>
-      </c>
-      <c r="B113" t="s">
-        <v>162</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" t="s">
-        <v>289</v>
-      </c>
-      <c r="B114" t="s">
-        <v>162</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" t="s">
-        <v>290</v>
-      </c>
-      <c r="B115" t="s">
-        <v>162</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" t="s">
-        <v>291</v>
-      </c>
-      <c r="B116" t="s">
-        <v>162</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" t="s">
-        <v>292</v>
-      </c>
-      <c r="B117" t="s">
-        <v>162</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" t="s">
-        <v>293</v>
-      </c>
       <c r="B118" t="s">
-        <v>162</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" t="s">
-        <v>294</v>
-      </c>
-      <c r="B119" t="s">
-        <v>162</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" t="s">
-        <v>295</v>
-      </c>
-      <c r="B120" t="s">
-        <v>162</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" t="s">
-        <v>296</v>
-      </c>
-      <c r="B121" t="s">
-        <v>160</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" t="s">
-        <v>297</v>
-      </c>
-      <c r="B122" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" t="s">
-        <v>298</v>
-      </c>
-      <c r="B123" t="s">
-        <v>160</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124" t="s">
-        <v>299</v>
-      </c>
-      <c r="B124" t="s">
-        <v>160</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125" t="s">
-        <v>300</v>
-      </c>
-      <c r="B125" t="s">
-        <v>160</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126" t="s">
-        <v>301</v>
-      </c>
-      <c r="B126" t="s">
-        <v>160</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" t="s">
-        <v>302</v>
-      </c>
-      <c r="B127" t="s">
-        <v>160</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" t="s">
-        <v>303</v>
-      </c>
-      <c r="B128" t="s">
-        <v>160</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" t="s">
-        <v>304</v>
-      </c>
-      <c r="B129" t="s">
-        <v>160</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" t="s">
-        <v>305</v>
-      </c>
-      <c r="B130" t="s">
-        <v>160</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131" t="s">
-        <v>306</v>
-      </c>
-      <c r="B131" t="s">
-        <v>160</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" t="s">
-        <v>307</v>
-      </c>
-      <c r="B132" t="s">
-        <v>160</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" t="s">
-        <v>308</v>
-      </c>
-      <c r="B133" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" t="s">
-        <v>309</v>
-      </c>
-      <c r="B134" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" t="s">
-        <v>310</v>
-      </c>
-      <c r="B135" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" t="s">
-        <v>311</v>
-      </c>
-      <c r="B136" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="369">
   <si>
     <t>Production Line</t>
   </si>
@@ -71,378 +71,384 @@
     <t>MRP Status</t>
   </si>
   <si>
+    <t>INT2</t>
+  </si>
+  <si>
+    <t>INC1</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
     <t>INC4</t>
   </si>
   <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>INC1</t>
-  </si>
-  <si>
-    <t>INT2</t>
-  </si>
-  <si>
     <t>INT3</t>
   </si>
   <si>
-    <t>910715043</t>
+    <t>910728980</t>
+  </si>
+  <si>
+    <t>910728614</t>
   </si>
   <si>
     <t>AUTO_1</t>
   </si>
   <si>
-    <t>910712428</t>
+    <t>910728754</t>
+  </si>
+  <si>
+    <t>910728848</t>
+  </si>
+  <si>
+    <t>910728783</t>
+  </si>
+  <si>
+    <t>910728860</t>
+  </si>
+  <si>
+    <t>910730952</t>
   </si>
   <si>
     <t>AUTO_2</t>
   </si>
   <si>
-    <t>910715191 + 910717251</t>
-  </si>
-  <si>
-    <t>910712578</t>
-  </si>
-  <si>
-    <t>910714990</t>
-  </si>
-  <si>
-    <t>910715241 + 910715240</t>
-  </si>
-  <si>
-    <t>910712440</t>
+    <t>910731193</t>
+  </si>
+  <si>
+    <t>910731174</t>
+  </si>
+  <si>
+    <t>910731148</t>
+  </si>
+  <si>
+    <t>910731092</t>
+  </si>
+  <si>
+    <t>910731062 + 910731125</t>
   </si>
   <si>
     <t>AUTO_3</t>
   </si>
   <si>
-    <t>910717240</t>
-  </si>
-  <si>
-    <t>910717114</t>
-  </si>
-  <si>
-    <t>910717241</t>
-  </si>
-  <si>
-    <t>910717201</t>
-  </si>
-  <si>
-    <t>910717256</t>
-  </si>
-  <si>
-    <t>910717300</t>
-  </si>
-  <si>
-    <t>910717224</t>
-  </si>
-  <si>
-    <t>910717257</t>
-  </si>
-  <si>
-    <t>910717202</t>
-  </si>
-  <si>
-    <t>910717296</t>
-  </si>
-  <si>
-    <t>910717377</t>
-  </si>
-  <si>
-    <t>910717225</t>
-  </si>
-  <si>
-    <t>910717276</t>
-  </si>
-  <si>
-    <t>910714830 + 910714891</t>
-  </si>
-  <si>
-    <t>910717129</t>
-  </si>
-  <si>
-    <t>910715192</t>
-  </si>
-  <si>
-    <t>910717198</t>
-  </si>
-  <si>
-    <t>910715257</t>
-  </si>
-  <si>
-    <t>910715048 + 910715049</t>
-  </si>
-  <si>
-    <t>910717302</t>
-  </si>
-  <si>
-    <t>910717299</t>
-  </si>
-  <si>
-    <t>910717359</t>
-  </si>
-  <si>
-    <t>910717252</t>
-  </si>
-  <si>
-    <t>910717417</t>
-  </si>
-  <si>
-    <t>83900260</t>
+    <t>910730972 + 910730971</t>
+  </si>
+  <si>
+    <t>910730950</t>
+  </si>
+  <si>
+    <t>910731102 + 910730963</t>
+  </si>
+  <si>
+    <t>910730943 + 910731293</t>
+  </si>
+  <si>
+    <t>910731190</t>
+  </si>
+  <si>
+    <t>910731147</t>
+  </si>
+  <si>
+    <t>910731168 + 910731221</t>
+  </si>
+  <si>
+    <t>910731183</t>
+  </si>
+  <si>
+    <t>910731146</t>
+  </si>
+  <si>
+    <t>910731172</t>
+  </si>
+  <si>
+    <t>910730970</t>
+  </si>
+  <si>
+    <t>910731238 + 910731304</t>
+  </si>
+  <si>
+    <t>910728866 + 910728931 + 910728784 + 910728850 + 910730961</t>
+  </si>
+  <si>
+    <t>910728859</t>
+  </si>
+  <si>
+    <t>910731115</t>
+  </si>
+  <si>
+    <t>910731057</t>
+  </si>
+  <si>
+    <t>910731220 + 910731319</t>
+  </si>
+  <si>
+    <t>910731210</t>
+  </si>
+  <si>
+    <t>910731292</t>
+  </si>
+  <si>
+    <t>80880903</t>
+  </si>
+  <si>
+    <t>83900263</t>
   </si>
   <si>
     <t>95619314</t>
   </si>
   <si>
-    <t>83900263</t>
-  </si>
-  <si>
-    <t>80880885</t>
+    <t>83900262</t>
+  </si>
+  <si>
+    <t>83900261</t>
+  </si>
+  <si>
+    <t>80880893</t>
+  </si>
+  <si>
+    <t>83900207</t>
+  </si>
+  <si>
+    <t>80880900</t>
+  </si>
+  <si>
+    <t>80880914</t>
+  </si>
+  <si>
+    <t>83900259</t>
+  </si>
+  <si>
+    <t>80880904</t>
+  </si>
+  <si>
+    <t>80879274</t>
+  </si>
+  <si>
+    <t>80879278</t>
+  </si>
+  <si>
+    <t>80841061</t>
+  </si>
+  <si>
+    <t>83900258</t>
+  </si>
+  <si>
+    <t>80880901</t>
+  </si>
+  <si>
+    <t>80841060</t>
+  </si>
+  <si>
+    <t>80879275</t>
   </si>
   <si>
     <t>80879287</t>
   </si>
   <si>
-    <t>83900262</t>
-  </si>
-  <si>
-    <t>80880898</t>
-  </si>
-  <si>
-    <t>80880902</t>
-  </si>
-  <si>
-    <t>80841061</t>
-  </si>
-  <si>
-    <t>80830098</t>
-  </si>
-  <si>
-    <t>80879282</t>
-  </si>
-  <si>
-    <t>80878378</t>
-  </si>
-  <si>
     <t>80879283</t>
   </si>
   <si>
-    <t>80889640</t>
-  </si>
-  <si>
-    <t>80896348</t>
-  </si>
-  <si>
-    <t>80880883</t>
-  </si>
-  <si>
-    <t>80879268</t>
-  </si>
-  <si>
-    <t>80879274</t>
-  </si>
-  <si>
-    <t>80880881</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
+    <t>H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
     <t>Auto-Replenishment HC Base (12T)</t>
   </si>
   <si>
-    <t>H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 72ML X 48 AHF IN GST</t>
+    <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 180ML X 56 AHF IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 300ML X30 CM IN DM GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X30 CM IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 180ML X 56 LF IN GST</t>
+  </si>
+  <si>
+    <t>PNTN COND 200MLX 24 HS SS IN PC25</t>
+  </si>
+  <si>
+    <t>PNTN SHM 340ML X 30 HS LT IN GST</t>
   </si>
   <si>
     <t>PNTN SHM 650ML X 12 HFC GST</t>
   </si>
   <si>
-    <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>PNTN 3MM BIOTIN COND 200MLX24 IN</t>
-  </si>
-  <si>
-    <t>PNTN SHM 75 ML X 48 HS DR IN GST</t>
-  </si>
-  <si>
-    <t>PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
-  </si>
-  <si>
     <t>PNTN SHM 650ML X 12 SSC IN GST</t>
   </si>
   <si>
-    <t>PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 400MLX30 HS LC IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 72 ML X 48 CM IN GST</t>
-  </si>
-  <si>
     <t>B001</t>
   </si>
   <si>
-    <t>REP02</t>
+    <t>B002</t>
+  </si>
+  <si>
+    <t>REP07</t>
+  </si>
+  <si>
+    <t>B005</t>
+  </si>
+  <si>
+    <t>B006</t>
+  </si>
+  <si>
+    <t>B008</t>
+  </si>
+  <si>
+    <t>B009</t>
+  </si>
+  <si>
+    <t>B010</t>
+  </si>
+  <si>
+    <t>REP12</t>
+  </si>
+  <si>
+    <t>B011</t>
+  </si>
+  <si>
+    <t>B013</t>
+  </si>
+  <si>
+    <t>B014</t>
+  </si>
+  <si>
+    <t>B015</t>
+  </si>
+  <si>
+    <t>B016</t>
+  </si>
+  <si>
+    <t>REP18</t>
+  </si>
+  <si>
+    <t>B019</t>
+  </si>
+  <si>
+    <t>B020</t>
+  </si>
+  <si>
+    <t>B021</t>
+  </si>
+  <si>
+    <t>B022</t>
+  </si>
+  <si>
+    <t>B023</t>
+  </si>
+  <si>
+    <t>B024</t>
+  </si>
+  <si>
+    <t>B025</t>
+  </si>
+  <si>
+    <t>B026</t>
+  </si>
+  <si>
+    <t>B027</t>
+  </si>
+  <si>
+    <t>B028</t>
+  </si>
+  <si>
+    <t>B030</t>
+  </si>
+  <si>
+    <t>B031</t>
   </si>
   <si>
     <t>B003</t>
   </si>
   <si>
-    <t>REP06</t>
-  </si>
-  <si>
-    <t>B005</t>
-  </si>
-  <si>
-    <t>B007</t>
-  </si>
-  <si>
-    <t>B008</t>
-  </si>
-  <si>
-    <t>B011</t>
-  </si>
-  <si>
-    <t>B010</t>
-  </si>
-  <si>
-    <t>REP15</t>
-  </si>
-  <si>
-    <t>B013</t>
-  </si>
-  <si>
-    <t>B016</t>
+    <t>B004</t>
   </si>
   <si>
     <t>B017</t>
   </si>
   <si>
-    <t>B018</t>
-  </si>
-  <si>
-    <t>B019</t>
-  </si>
-  <si>
-    <t>B021</t>
-  </si>
-  <si>
-    <t>B022</t>
-  </si>
-  <si>
-    <t>B024</t>
-  </si>
-  <si>
-    <t>B025</t>
-  </si>
-  <si>
-    <t>B026</t>
-  </si>
-  <si>
-    <t>B028</t>
+    <t>B032</t>
   </si>
   <si>
     <t>B029</t>
   </si>
   <si>
-    <t>B030</t>
-  </si>
-  <si>
-    <t>B004</t>
-  </si>
-  <si>
-    <t>B023</t>
-  </si>
-  <si>
-    <t>B009</t>
-  </si>
-  <si>
-    <t>B027</t>
-  </si>
-  <si>
-    <t>B012</t>
-  </si>
-  <si>
-    <t>B014</t>
-  </si>
-  <si>
-    <t>B020</t>
-  </si>
-  <si>
-    <t>B031</t>
-  </si>
-  <si>
-    <t>B032</t>
-  </si>
-  <si>
     <t>B033</t>
   </si>
   <si>
     <t>B034</t>
   </si>
   <si>
+    <t>21422079</t>
+  </si>
+  <si>
+    <t>21470269</t>
+  </si>
+  <si>
     <t>21453170</t>
   </si>
   <si>
-    <t>21470269</t>
+    <t>21470270</t>
   </si>
   <si>
     <t>21417344</t>
   </si>
   <si>
+    <t>90947730</t>
+  </si>
+  <si>
     <t>21302239</t>
   </si>
   <si>
-    <t>21422079</t>
-  </si>
-  <si>
     <t>21090111</t>
   </si>
   <si>
-    <t>UNKNOWN</t>
-  </si>
-  <si>
-    <t>'21302239</t>
+    <t>21448509</t>
+  </si>
+  <si>
+    <t>90966400</t>
+  </si>
+  <si>
+    <t>21090112</t>
+  </si>
+  <si>
+    <t>21302240</t>
   </si>
   <si>
     <t>'21302240</t>
   </si>
   <si>
-    <t>21309190</t>
-  </si>
-  <si>
-    <t>21309189</t>
-  </si>
-  <si>
-    <t>20256318</t>
-  </si>
-  <si>
-    <t>90947730</t>
-  </si>
-  <si>
     <t>12T</t>
   </si>
   <si>
@@ -464,40 +470,31 @@
     <t>A</t>
   </si>
   <si>
-    <t>TK#_15_#</t>
+    <t>TK#_51_#</t>
   </si>
   <si>
     <t>NO_TANK_AVAILABLE</t>
   </si>
   <si>
+    <t>TK#_12_# + TK#_16_#</t>
+  </si>
+  <si>
+    <t>TK#_22_#</t>
+  </si>
+  <si>
     <t>TK#_16_#</t>
   </si>
   <si>
-    <t>TK#_14_#</t>
-  </si>
-  <si>
-    <t>TK#_24_#</t>
-  </si>
-  <si>
     <t>TK#_12_#</t>
   </si>
   <si>
-    <t>TK#_9_#</t>
-  </si>
-  <si>
-    <t>TK#_53_#</t>
-  </si>
-  <si>
-    <t>TK#_23_#</t>
-  </si>
-  <si>
     <t>LOW: SLS</t>
   </si>
   <si>
     <t>LOW: DM5500</t>
   </si>
   <si>
-    <t>UNKNOWN_SKU</t>
+    <t>OK</t>
   </si>
   <si>
     <t>Time</t>
@@ -506,463 +503,625 @@
     <t>1.25T</t>
   </si>
   <si>
-    <t>2026-01-06 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-06 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-06 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-07 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-07 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-08 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-08 14:00</t>
-  </si>
-  <si>
-    <t>B001: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>REP02: Auto-Replenishment HC Base (12T)</t>
+    <t>2026-01-12 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-12 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-12 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-12 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-12 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-12 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-12 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-12 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 09:00</t>
+  </si>
+  <si>
+    <t>B001: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B002: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
     <t>WASHOUT</t>
   </si>
   <si>
-    <t>B003: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>REP06: Auto-Replenishment HC Base (12T)</t>
-  </si>
-  <si>
-    <t>B005: H&amp;S SHM 72ML X 48 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B007: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B008: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B011: PNTN SHM 650ML X 12 HFC GST</t>
+    <t>REP07: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B006: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B008: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B009: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B010: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>REP15: Auto-Replenishment HC Base (12T)</t>
-  </si>
-  <si>
-    <t>B013: H&amp;S SHM 5.7MLX960 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B016: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B017: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B018: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B019: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B021: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B022: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B024: H&amp;S SHM 650ML X12 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B025: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B026: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B028: H&amp;S SHM 340ML X 30 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B029: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+    <t>REP12: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>B011: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B013: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B014: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B015: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B016: H&amp;S SHM 180ML X 56 AHF IN GST</t>
+  </si>
+  <si>
+    <t>REP18: Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>B019: H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B020: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B021: H&amp;S SHM 300ML X30 CM IN DM GST</t>
+  </si>
+  <si>
+    <t>B022: H&amp;S SHM 340ML X30 CM IN GST</t>
+  </si>
+  <si>
+    <t>B023: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B024: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B025: H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>B026: PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B027: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B028: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
     <t>B030: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B004: PNTN COND 200MLX 24 HS HF IN PC25</t>
+    <t>B031: PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B003: PNTN COND 200MLX 24 HS HF IN PC25</t>
   </si>
   <si>
     <t>COND WASH (60m)</t>
   </si>
   <si>
-    <t>B023: PNTN 3MM BIOTIN COND 200MLX24 IN</t>
-  </si>
-  <si>
-    <t>B009: PNTN SHM 75 ML X 48 HS DR IN GST</t>
-  </si>
-  <si>
-    <t>B027: PNTN 3MM COLLAGEN CONDI 80MLX24 IN GST</t>
-  </si>
-  <si>
-    <t>B012: PNTN SHM 650ML X 12 SSC IN GST</t>
-  </si>
-  <si>
-    <t>B014: PNTN SHM 650MLX12 SSC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>B020: PNTN SHM 340MLX30 HS HFC 2IN1 IN GST</t>
-  </si>
-  <si>
-    <t>B031: H&amp;S SHM 72ML X 48 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B032: PNTN SHM 400MLX30 HS LC IN GST</t>
-  </si>
-  <si>
-    <t>B033: PNTN SHM 340MLX30 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>B034: H&amp;S SHM 72 ML X 48 CM IN GST</t>
+    <t>B004: H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
+  </si>
+  <si>
+    <t>B017: H&amp;S SHM 180ML X 56 LF IN GST</t>
+  </si>
+  <si>
+    <t>B032: PNTN COND 200MLX 24 HS SS IN PC25</t>
+  </si>
+  <si>
+    <t>B029: PNTN SHM 340ML X 30 HS LT IN GST</t>
+  </si>
+  <si>
+    <t>B033: PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>B034: PNTN SHM 650ML X 12 SSC IN GST</t>
   </si>
 </sst>
 </file>
@@ -1400,49 +1559,49 @@
         <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H2">
-        <v>4.4185</v>
+        <v>4.5088</v>
       </c>
       <c r="I2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K2" s="2">
-        <v>46028.79861111111</v>
+        <v>46035.94930555556</v>
       </c>
       <c r="L2">
         <v>90</v>
       </c>
       <c r="M2" s="2">
-        <v>46028.86111111111</v>
+        <v>46036.01180555556</v>
       </c>
       <c r="N2">
-        <v>120</v>
+        <v>503</v>
       </c>
       <c r="O2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P2" s="2">
-        <v>46028.94444444445</v>
+        <v>46036.36111111111</v>
       </c>
       <c r="Q2" s="2">
-        <v>46029.49166666667</v>
+        <v>46036.55</v>
       </c>
       <c r="R2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1456,49 +1615,49 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H3">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="I3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K3" s="2">
-        <v>46028.875</v>
+        <v>46036.01180555556</v>
       </c>
       <c r="L3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M3" s="2">
-        <v>46029</v>
+        <v>46036.07430555556</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>424</v>
       </c>
       <c r="O3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P3" s="2">
-        <v>46029.04166666666</v>
+        <v>46036.36875</v>
       </c>
       <c r="Q3" s="2">
-        <v>46029.08333333334</v>
+        <v>46036.55208333334</v>
       </c>
       <c r="R3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1512,49 +1671,49 @@
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H4">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="I4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K4" s="2">
-        <v>46029.01388888889</v>
+        <v>46036.08819444444</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M4" s="2">
-        <v>46029.07638888889</v>
+        <v>46036.21319444444</v>
       </c>
       <c r="N4">
-        <v>264</v>
+        <v>513</v>
       </c>
       <c r="O4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P4" s="2">
-        <v>46029.25972222222</v>
+        <v>46036.56944444445</v>
       </c>
       <c r="Q4" s="2">
-        <v>46029.44305555556</v>
+        <v>46036.61111111111</v>
       </c>
       <c r="R4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1568,49 +1727,49 @@
         <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H5">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="I5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K5" s="2">
-        <v>46029.09027777778</v>
+        <v>46036.22708333333</v>
       </c>
       <c r="L5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M5" s="2">
-        <v>46029.21527777778</v>
+        <v>46036.28958333333</v>
       </c>
       <c r="N5">
-        <v>295</v>
+        <v>378</v>
       </c>
       <c r="O5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P5" s="2">
-        <v>46029.42013888889</v>
+        <v>46036.55208333334</v>
       </c>
       <c r="Q5" s="2">
-        <v>46029.46180555555</v>
+        <v>46036.73611111111</v>
       </c>
       <c r="R5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1624,217 +1783,217 @@
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H6">
-        <v>2.9976</v>
+        <v>4.4163</v>
       </c>
       <c r="I6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K6" s="2">
-        <v>46029.22916666666</v>
+        <v>46036.28958333333</v>
       </c>
       <c r="L6">
         <v>90</v>
       </c>
       <c r="M6" s="2">
-        <v>46029.29166666666</v>
+        <v>46036.35208333333</v>
       </c>
       <c r="N6">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="O6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P6" s="2">
-        <v>46029.39583333334</v>
+        <v>46036.56736111111</v>
       </c>
       <c r="Q6" s="2">
-        <v>46030.61180555556</v>
+        <v>46036.78125</v>
       </c>
       <c r="R6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
         <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H7">
         <v>4.4185</v>
       </c>
       <c r="I7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K7" s="2">
-        <v>46029.30555555555</v>
+        <v>46036.35208333333</v>
       </c>
       <c r="L7">
         <v>90</v>
       </c>
       <c r="M7" s="2">
-        <v>46029.36805555555</v>
+        <v>46036.41458333333</v>
       </c>
       <c r="N7">
-        <v>108</v>
+        <v>463</v>
       </c>
       <c r="O7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P7" s="2">
-        <v>46029.44305555556</v>
+        <v>46036.73611111111</v>
       </c>
       <c r="Q7" s="2">
-        <v>46029.62708333333</v>
+        <v>46036.91944444444</v>
       </c>
       <c r="R7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H8">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K8" s="2">
-        <v>46029.36805555555</v>
+        <v>46036.41458333333</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8" s="2">
-        <v>46029.43055555555</v>
+        <v>46036.47708333333</v>
       </c>
       <c r="N8">
-        <v>88</v>
+        <v>498</v>
       </c>
       <c r="O8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P8" s="2">
-        <v>46029.49166666667</v>
+        <v>46036.82291666666</v>
       </c>
       <c r="Q8" s="2">
-        <v>46029.73541666667</v>
+        <v>46037.03611111111</v>
       </c>
       <c r="R8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F9" t="s">
         <v>132</v>
       </c>
       <c r="G9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H9">
-        <v>3.9956</v>
+        <v>4.4185</v>
       </c>
       <c r="I9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K9" s="2">
-        <v>46029.43055555555</v>
+        <v>46036.47708333333</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M9" s="2">
-        <v>46029.49652777778</v>
+        <v>46036.53958333333</v>
       </c>
       <c r="N9">
-        <v>191</v>
+        <v>547</v>
       </c>
       <c r="O9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P9" s="2">
-        <v>46029.62916666667</v>
+        <v>46036.91944444444</v>
       </c>
       <c r="Q9" s="2">
-        <v>46029.92083333333</v>
+        <v>46037.10347222222</v>
       </c>
       <c r="R9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1848,329 +2007,329 @@
         <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F10" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H10">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="I10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K10" s="2">
-        <v>46029.49652777778</v>
+        <v>46036.55347222222</v>
       </c>
       <c r="L10">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M10" s="2">
-        <v>46029.55902777778</v>
+        <v>46036.67847222222</v>
       </c>
       <c r="N10">
-        <v>98</v>
+        <v>550</v>
       </c>
       <c r="O10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P10" s="2">
-        <v>46029.62708333333</v>
+        <v>46037.06041666667</v>
       </c>
       <c r="Q10" s="2">
-        <v>46029.81041666667</v>
+        <v>46037.10208333333</v>
       </c>
       <c r="R10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="G11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H11">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="I11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J11" t="s">
         <v>148</v>
       </c>
       <c r="K11" s="2">
-        <v>46029.57291666666</v>
+        <v>46036.69236111111</v>
       </c>
       <c r="L11">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M11" s="2">
-        <v>46029.69791666666</v>
+        <v>46036.75486111111</v>
       </c>
       <c r="N11">
-        <v>140</v>
+        <v>405</v>
       </c>
       <c r="O11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" s="2">
-        <v>46029.79513888889</v>
+        <v>46037.03611111111</v>
       </c>
       <c r="Q11" s="2">
-        <v>46029.83680555555</v>
+        <v>46037.25</v>
       </c>
       <c r="R11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H12">
         <v>4.4185</v>
       </c>
       <c r="I12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J12" t="s">
         <v>148</v>
       </c>
       <c r="K12" s="2">
-        <v>46029.71180555555</v>
+        <v>46036.75486111111</v>
       </c>
       <c r="L12">
         <v>90</v>
       </c>
       <c r="M12" s="2">
-        <v>46029.77430555555</v>
+        <v>46036.81736111111</v>
       </c>
       <c r="N12">
-        <v>-56</v>
+        <v>412</v>
       </c>
       <c r="O12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P12" s="2">
-        <v>46029.73541666667</v>
+        <v>46037.10347222222</v>
       </c>
       <c r="Q12" s="2">
-        <v>46029.94930555556</v>
+        <v>46037.28680555556</v>
       </c>
       <c r="R12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H13">
         <v>4.4185</v>
       </c>
       <c r="I13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K13" s="2">
-        <v>46029.77430555555</v>
+        <v>46036.81736111111</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13" s="2">
-        <v>46029.83680555555</v>
+        <v>46036.87986111111</v>
       </c>
       <c r="N13">
-        <v>-38</v>
+        <v>533</v>
       </c>
       <c r="O13" t="s">
         <v>152</v>
       </c>
       <c r="P13" s="2">
-        <v>46029.81041666667</v>
+        <v>46037.25</v>
       </c>
       <c r="Q13" s="2">
-        <v>46029.99444444444</v>
+        <v>46037.46319444444</v>
       </c>
       <c r="R13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H14">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K14" s="2">
-        <v>46029.83680555555</v>
+        <v>46036.87986111111</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14" s="2">
-        <v>46029.89930555555</v>
+        <v>46036.94236111111</v>
       </c>
       <c r="N14">
-        <v>72</v>
+        <v>496</v>
       </c>
       <c r="O14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P14" s="2">
-        <v>46029.94930555556</v>
+        <v>46037.28680555556</v>
       </c>
       <c r="Q14" s="2">
-        <v>46030.49583333333</v>
+        <v>46037.47083333333</v>
       </c>
       <c r="R14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H15">
-        <v>4.4185</v>
+        <v>4.4891</v>
       </c>
       <c r="I15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K15" s="2">
-        <v>46029.89930555555</v>
+        <v>46036.94236111111</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15" s="2">
-        <v>46029.96180555555</v>
+        <v>46037.00486111111</v>
       </c>
       <c r="N15">
-        <v>47</v>
+        <v>443</v>
       </c>
       <c r="O15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P15" s="2">
-        <v>46029.99444444444</v>
+        <v>46037.3125</v>
       </c>
       <c r="Q15" s="2">
-        <v>46030.17847222222</v>
+        <v>46037.75833333333</v>
       </c>
       <c r="R15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2184,49 +2343,49 @@
         <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H16">
-        <v>4.4185</v>
+        <v>2.2948</v>
       </c>
       <c r="I16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K16" s="2">
-        <v>46029.96180555555</v>
+        <v>46037.01875</v>
       </c>
       <c r="L16">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M16" s="2">
-        <v>46030.02430555555</v>
+        <v>46037.14375</v>
       </c>
       <c r="N16">
-        <v>222</v>
+        <v>450</v>
       </c>
       <c r="O16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P16" s="2">
-        <v>46030.17847222222</v>
+        <v>46037.45625</v>
       </c>
       <c r="Q16" s="2">
-        <v>46030.36180555556</v>
+        <v>46037.49791666667</v>
       </c>
       <c r="R16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2240,161 +2399,161 @@
         <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H17">
-        <v>4.5022</v>
+        <v>4.4163</v>
       </c>
       <c r="I17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K17" s="2">
-        <v>46030.02430555555</v>
+        <v>46037.15763888889</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17" s="2">
-        <v>46030.08680555555</v>
+        <v>46037.22013888889</v>
       </c>
       <c r="N17">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="O17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P17" s="2">
-        <v>46030.31111111111</v>
+        <v>46037.46319444444</v>
       </c>
       <c r="Q17" s="2">
-        <v>46030.43125</v>
+        <v>46037.67708333334</v>
       </c>
       <c r="R17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
         <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G18" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H18">
         <v>4.4185</v>
       </c>
       <c r="I18" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K18" s="2">
-        <v>46030.08680555555</v>
+        <v>46037.22013888889</v>
       </c>
       <c r="L18">
         <v>90</v>
       </c>
       <c r="M18" s="2">
-        <v>46030.14930555555</v>
+        <v>46037.28263888889</v>
       </c>
       <c r="N18">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="O18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P18" s="2">
-        <v>46030.36180555556</v>
+        <v>46037.47083333333</v>
       </c>
       <c r="Q18" s="2">
-        <v>46030.54583333333</v>
+        <v>46037.65486111111</v>
       </c>
       <c r="R18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H19">
-        <v>4.5022</v>
+        <v>4.0957</v>
       </c>
       <c r="I19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K19" s="2">
-        <v>46030.14930555555</v>
+        <v>46037.28263888889</v>
       </c>
       <c r="L19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M19" s="2">
-        <v>46030.21180555555</v>
+        <v>46037.34861111111</v>
       </c>
       <c r="N19">
-        <v>316</v>
+        <v>219</v>
       </c>
       <c r="O19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P19" s="2">
-        <v>46030.43125</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="Q19" s="2">
-        <v>46030.55138888889</v>
+        <v>46037.6375</v>
       </c>
       <c r="R19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2405,108 +2564,108 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G20" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H20">
-        <v>4.4163</v>
+        <v>5.2051</v>
       </c>
       <c r="I20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K20" s="2">
-        <v>46030.21180555555</v>
+        <v>46037.34861111111</v>
       </c>
       <c r="L20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M20" s="2">
-        <v>46030.27430555555</v>
+        <v>46037.41458333333</v>
       </c>
       <c r="N20">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P20" s="2">
-        <v>46030.49583333333</v>
+        <v>46037.6375</v>
       </c>
       <c r="Q20" s="2">
-        <v>46030.70972222222</v>
+        <v>46038.77569444444</v>
       </c>
       <c r="R20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
         <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H21">
         <v>4.4185</v>
       </c>
       <c r="I21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K21" s="2">
-        <v>46030.27430555555</v>
+        <v>46037.41458333333</v>
       </c>
       <c r="L21">
         <v>90</v>
       </c>
       <c r="M21" s="2">
-        <v>46030.33680555555</v>
+        <v>46037.47708333333</v>
       </c>
       <c r="N21">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="O21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P21" s="2">
-        <v>46030.54583333333</v>
+        <v>46037.65486111111</v>
       </c>
       <c r="Q21" s="2">
-        <v>46030.72916666666</v>
+        <v>46037.83819444444</v>
       </c>
       <c r="R21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2517,52 +2676,52 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H22">
-        <v>4.5228</v>
+        <v>4.4163</v>
       </c>
       <c r="I22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K22" s="2">
-        <v>46030.33680555555</v>
+        <v>46037.47708333333</v>
       </c>
       <c r="L22">
         <v>90</v>
       </c>
       <c r="M22" s="2">
-        <v>46030.39930555555</v>
+        <v>46037.53958333333</v>
       </c>
       <c r="N22">
-        <v>306</v>
+        <v>198</v>
       </c>
       <c r="O22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P22" s="2">
-        <v>46030.61180555556</v>
+        <v>46037.67708333334</v>
       </c>
       <c r="Q22" s="2">
-        <v>46030.73194444444</v>
+        <v>46037.89027777778</v>
       </c>
       <c r="R22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2573,169 +2732,169 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H23">
-        <v>4.4163</v>
+        <v>5.2051</v>
       </c>
       <c r="I23" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K23" s="2">
-        <v>46030.39930555555</v>
+        <v>46037.53958333333</v>
       </c>
       <c r="L23">
         <v>90</v>
       </c>
       <c r="M23" s="2">
-        <v>46030.46180555555</v>
+        <v>46037.60208333333</v>
       </c>
       <c r="N23">
-        <v>357</v>
+        <v>225</v>
       </c>
       <c r="O23" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P23" s="2">
-        <v>46030.70972222222</v>
+        <v>46037.75833333333</v>
       </c>
       <c r="Q23" s="2">
-        <v>46030.92291666667</v>
+        <v>46038.71527777778</v>
       </c>
       <c r="R23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H24">
-        <v>4.4185</v>
+        <v>4.5228</v>
       </c>
       <c r="I24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K24" s="2">
-        <v>46030.46180555555</v>
+        <v>46037.61597222222</v>
       </c>
       <c r="L24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M24" s="2">
-        <v>46030.52430555555</v>
+        <v>46037.68194444444</v>
       </c>
       <c r="N24">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="O24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P24" s="2">
-        <v>46030.72916666666</v>
+        <v>46037.81805555556</v>
       </c>
       <c r="Q24" s="2">
-        <v>46030.91319444445</v>
+        <v>46037.93819444445</v>
       </c>
       <c r="R24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H25">
-        <v>1.1202</v>
+        <v>4.4185</v>
       </c>
       <c r="I25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K25" s="2">
-        <v>46028.1875</v>
+        <v>46037.68194444444</v>
       </c>
       <c r="L25">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M25" s="2">
-        <v>46028.3125</v>
+        <v>46037.74444444444</v>
       </c>
       <c r="N25">
-        <v>1440</v>
+        <v>135</v>
       </c>
       <c r="O25" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P25" s="2">
-        <v>46029.3125</v>
+        <v>46037.83819444444</v>
       </c>
       <c r="Q25" s="2">
-        <v>46030.41666666666</v>
+        <v>46038.02222222222</v>
       </c>
       <c r="R25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -2744,214 +2903,214 @@
         <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F26" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>4.4163</v>
       </c>
       <c r="I26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J26" t="s">
         <v>148</v>
       </c>
       <c r="K26" s="2">
-        <v>46028.375</v>
+        <v>46037.74444444444</v>
       </c>
       <c r="L26">
         <v>90</v>
       </c>
       <c r="M26" s="2">
-        <v>46028.4375</v>
+        <v>46037.80694444444</v>
       </c>
       <c r="N26">
-        <v>2850</v>
+        <v>120</v>
       </c>
       <c r="O26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="P26" s="2">
-        <v>46030.41666666666</v>
+        <v>46037.89027777778</v>
       </c>
       <c r="Q26" s="2">
-        <v>46030.59652777778</v>
+        <v>46038.10416666666</v>
       </c>
       <c r="R26" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H27">
-        <v>2.19</v>
+        <v>4.4185</v>
       </c>
       <c r="I27" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J27" t="s">
         <v>148</v>
       </c>
       <c r="K27" s="2">
-        <v>46028.47916666666</v>
+        <v>46037.87638888889</v>
       </c>
       <c r="L27">
         <v>90</v>
       </c>
       <c r="M27" s="2">
-        <v>46028.54166666666</v>
+        <v>46037.93888888889</v>
       </c>
       <c r="N27">
-        <v>1430</v>
+        <v>120</v>
       </c>
       <c r="O27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P27" s="2">
-        <v>46029.53472222222</v>
+        <v>46038.02222222222</v>
       </c>
       <c r="Q27" s="2">
-        <v>46030.25</v>
+        <v>46038.20555555556</v>
       </c>
       <c r="R27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>5.1635</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K28" s="2">
-        <v>46028.57638888889</v>
+        <v>46038.23125</v>
       </c>
       <c r="L28">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M28" s="2">
-        <v>46028.63888888889</v>
+        <v>46038.29722222222</v>
       </c>
       <c r="N28">
-        <v>2819</v>
+        <v>120</v>
       </c>
       <c r="O28" t="s">
+        <v>151</v>
+      </c>
+      <c r="P28" s="2">
+        <v>46038.38055555556</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>46038.53472222222</v>
+      </c>
+      <c r="R28" t="s">
         <v>157</v>
-      </c>
-      <c r="P28" s="2">
-        <v>46030.59652777778</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>46031.41736111111</v>
-      </c>
-      <c r="R28" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G29" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H29">
-        <v>2.2511</v>
+        <v>2.8005</v>
       </c>
       <c r="I29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J29" t="s">
         <v>148</v>
       </c>
       <c r="K29" s="2">
-        <v>46028.68055555555</v>
+        <v>46034.85416666666</v>
       </c>
       <c r="L29">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M29" s="2">
-        <v>46028.74305555555</v>
+        <v>46034.97916666666</v>
       </c>
       <c r="N29">
-        <v>1363</v>
+        <v>2040</v>
       </c>
       <c r="O29" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P29" s="2">
-        <v>46029.68958333333</v>
+        <v>46036.39583333334</v>
       </c>
       <c r="Q29" s="2">
-        <v>46029.75</v>
+        <v>46039.42569444444</v>
       </c>
       <c r="R29" t="s">
         <v>158</v>
@@ -2965,332 +3124,332 @@
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H30">
-        <v>1.9872</v>
+        <v>2.2082</v>
       </c>
       <c r="I30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K30" s="2">
-        <v>46028.75694444445</v>
+        <v>46035.3125</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30" s="2">
-        <v>46028.81944444445</v>
+        <v>46035.375</v>
       </c>
       <c r="N30">
-        <v>1340</v>
+        <v>1564</v>
       </c>
       <c r="O30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P30" s="2">
-        <v>46029.75</v>
+        <v>46036.46111111111</v>
       </c>
       <c r="Q30" s="2">
-        <v>46029.82638888889</v>
+        <v>46036.56736111111</v>
       </c>
       <c r="R30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H31">
-        <v>2.2614</v>
+        <v>2.2544</v>
       </c>
       <c r="I31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J31" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K31" s="2">
-        <v>46028.83333333334</v>
+        <v>46035.38888888889</v>
       </c>
       <c r="L31">
         <v>90</v>
       </c>
       <c r="M31" s="2">
-        <v>46028.89583333334</v>
+        <v>46035.45138888889</v>
       </c>
       <c r="N31">
-        <v>1951</v>
+        <v>2815</v>
       </c>
       <c r="O31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P31" s="2">
-        <v>46030.25069444445</v>
+        <v>46037.40625</v>
       </c>
       <c r="Q31" s="2">
-        <v>46030.31111111111</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="R31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H32">
-        <v>2.2314</v>
+        <v>0.5601</v>
       </c>
       <c r="I32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K32" s="2">
-        <v>46028.90972222222</v>
+        <v>46035.48611111111</v>
       </c>
       <c r="L32">
         <v>90</v>
       </c>
       <c r="M32" s="2">
-        <v>46028.97222222222</v>
+        <v>46035.54861111111</v>
       </c>
       <c r="N32">
-        <v>2534</v>
+        <v>4143</v>
       </c>
       <c r="O32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P32" s="2">
-        <v>46030.73194444444</v>
+        <v>46038.42569444444</v>
       </c>
       <c r="Q32" s="2">
-        <v>46030.96527777778</v>
+        <v>46038.60486111111</v>
       </c>
       <c r="R32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G33" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H33">
-        <v>2.1937</v>
+        <v>2.2733</v>
       </c>
       <c r="I33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J33" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K33" s="2">
-        <v>46028.98611111111</v>
+        <v>46035.59027777778</v>
       </c>
       <c r="L33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M33" s="2">
-        <v>46029.04513888889</v>
+        <v>46035.65277777778</v>
       </c>
       <c r="N33">
-        <v>2701</v>
+        <v>3291</v>
       </c>
       <c r="O33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P33" s="2">
-        <v>46030.92083333333</v>
+        <v>46037.93819444445</v>
       </c>
       <c r="Q33" s="2">
-        <v>46030.96527777778</v>
+        <v>46038.38055555556</v>
       </c>
       <c r="R33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F34" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H34">
-        <v>2.2614</v>
+        <v>2.2511</v>
       </c>
       <c r="I34" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J34" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K34" s="2">
-        <v>46029.05902777778</v>
+        <v>46035.66666666666</v>
       </c>
       <c r="L34">
         <v>85</v>
       </c>
       <c r="M34" s="2">
-        <v>46029.11805555555</v>
+        <v>46035.72569444445</v>
       </c>
       <c r="N34">
-        <v>2660</v>
+        <v>4045</v>
       </c>
       <c r="O34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P34" s="2">
-        <v>46030.96527777778</v>
+        <v>46038.53472222222</v>
       </c>
       <c r="Q34" s="2">
-        <v>46030.53472222222</v>
+        <v>46038.59513888889</v>
       </c>
       <c r="R34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
         <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G35" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H35">
-        <v>2.2314</v>
+        <v>2.2511</v>
       </c>
       <c r="I35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J35" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K35" s="2">
-        <v>46029.13194444445</v>
+        <v>46035.73958333334</v>
       </c>
       <c r="L35">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M35" s="2">
-        <v>46029.19097222222</v>
+        <v>46035.80208333334</v>
       </c>
       <c r="N35">
-        <v>2555</v>
+        <v>4022</v>
       </c>
       <c r="O35" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P35" s="2">
-        <v>46030.96527777778</v>
+        <v>46038.59513888889</v>
       </c>
       <c r="Q35" s="2">
-        <v>46031.19930555556</v>
+        <v>46038.65555555555</v>
       </c>
       <c r="R35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -3300,7 +3459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3310,1345 +3469,1765 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>305</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>306</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>306</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>306</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>305</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>305</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>307</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>307</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>307</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>282</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>305</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>305</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>309</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>282</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>310</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>282</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>281</v>
+        <v>148</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>282</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>282</v>
+        <v>148</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>283</v>
+        <v>148</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>283</v>
+        <v>148</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>283</v>
+        <v>148</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>282</v>
+        <v>148</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>314</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>284</v>
+        <v>148</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>314</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" t="s">
+        <v>148</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>209</v>
       </c>
-      <c r="B48" t="s">
-        <v>147</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>210</v>
       </c>
-      <c r="B49" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>211</v>
       </c>
-      <c r="B50" t="s">
-        <v>147</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>212</v>
       </c>
-      <c r="B51" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>213</v>
       </c>
-      <c r="B52" t="s">
-        <v>147</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>214</v>
       </c>
-      <c r="B53" t="s">
-        <v>147</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>215</v>
       </c>
-      <c r="B54" t="s">
-        <v>147</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>216</v>
       </c>
-      <c r="B55" t="s">
-        <v>147</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>217</v>
       </c>
-      <c r="B56" t="s">
-        <v>147</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>218</v>
       </c>
-      <c r="B57" t="s">
-        <v>148</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>219</v>
       </c>
-      <c r="B58" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
         <v>220</v>
       </c>
-      <c r="B59" t="s">
-        <v>148</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>221</v>
       </c>
-      <c r="B60" t="s">
-        <v>148</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
         <v>222</v>
       </c>
-      <c r="B61" t="s">
-        <v>148</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>223</v>
       </c>
-      <c r="B62" t="s">
-        <v>148</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
         <v>224</v>
       </c>
-      <c r="B63" t="s">
-        <v>148</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>225</v>
-      </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>288</v>
+        <v>336</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>288</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>289</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>290</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>282</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B77" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B79" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B80" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B81" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>292</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>292</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>293</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>293</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>295</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>295</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>295</v>
+        <v>335</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B92" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>296</v>
+        <v>343</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B93" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>296</v>
+        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B94" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>296</v>
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B96" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B97" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B99" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B101" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B102" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B103" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B104" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B105" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B106" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B107" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B108" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B109" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B110" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B111" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B112" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B113" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>303</v>
+        <v>349</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B115" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>303</v>
+        <v>349</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B116" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B117" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
+        <v>278</v>
+      </c>
+      <c r="B118" t="s">
+        <v>149</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
         <v>279</v>
       </c>
-      <c r="B118" t="s">
-        <v>148</v>
+      <c r="B119" t="s">
+        <v>149</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>280</v>
+      </c>
+      <c r="B120" t="s">
+        <v>149</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>281</v>
+      </c>
+      <c r="B121" t="s">
+        <v>150</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>282</v>
+      </c>
+      <c r="B122" t="s">
+        <v>150</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>283</v>
+      </c>
+      <c r="B123" t="s">
+        <v>150</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>284</v>
+      </c>
+      <c r="B124" t="s">
+        <v>150</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>285</v>
+      </c>
+      <c r="B125" t="s">
+        <v>150</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>286</v>
+      </c>
+      <c r="B126" t="s">
+        <v>150</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>287</v>
+      </c>
+      <c r="B127" t="s">
+        <v>150</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>288</v>
+      </c>
+      <c r="B128" t="s">
+        <v>150</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>289</v>
+      </c>
+      <c r="B129" t="s">
+        <v>150</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>290</v>
+      </c>
+      <c r="B130" t="s">
+        <v>150</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" t="s">
+        <v>150</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" t="s">
+        <v>150</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>293</v>
+      </c>
+      <c r="B133" t="s">
+        <v>150</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>294</v>
+      </c>
+      <c r="B134" t="s">
+        <v>150</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>295</v>
+      </c>
+      <c r="B135" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>296</v>
+      </c>
+      <c r="B136" t="s">
+        <v>150</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>297</v>
+      </c>
+      <c r="B137" t="s">
+        <v>148</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>298</v>
+      </c>
+      <c r="B138" t="s">
+        <v>148</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" t="s">
+        <v>148</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>300</v>
+      </c>
+      <c r="B140" t="s">
+        <v>148</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>301</v>
+      </c>
+      <c r="B141" t="s">
+        <v>148</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>302</v>
+      </c>
+      <c r="B142" t="s">
+        <v>148</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>303</v>
+      </c>
+      <c r="B143" t="s">
+        <v>148</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>304</v>
+      </c>
+      <c r="B144" t="s">
+        <v>148</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>305</v>
+      </c>
+      <c r="B145" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>306</v>
+      </c>
+      <c r="B146" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>307</v>
+      </c>
+      <c r="B147" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>308</v>
+      </c>
+      <c r="B148" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>309</v>
+      </c>
+      <c r="B149" t="s">
+        <v>148</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>310</v>
+      </c>
+      <c r="B150" t="s">
+        <v>148</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>311</v>
+      </c>
+      <c r="B151" t="s">
+        <v>148</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>312</v>
+      </c>
+      <c r="B152" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>313</v>
+      </c>
+      <c r="B153" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>314</v>
+      </c>
+      <c r="B154" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
+        <v>315</v>
+      </c>
+      <c r="B155" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>316</v>
+      </c>
+      <c r="B156" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
+        <v>317</v>
+      </c>
+      <c r="B157" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
+        <v>318</v>
+      </c>
+      <c r="B158" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
+        <v>319</v>
+      </c>
+      <c r="B159" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
+        <v>320</v>
+      </c>
+      <c r="B160" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>321</v>
+      </c>
+      <c r="B161" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>322</v>
+      </c>
+      <c r="B162" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
+        <v>323</v>
+      </c>
+      <c r="B163" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
+        <v>324</v>
+      </c>
+      <c r="B164" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
+        <v>325</v>
+      </c>
+      <c r="B165" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
+        <v>326</v>
+      </c>
+      <c r="B166" t="s">
+        <v>149</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
+        <v>327</v>
+      </c>
+      <c r="B167" t="s">
+        <v>149</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
+        <v>328</v>
+      </c>
+      <c r="B168" t="s">
+        <v>149</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
+        <v>329</v>
+      </c>
+      <c r="B169" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
+        <v>330</v>
+      </c>
+      <c r="B170" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
+        <v>331</v>
+      </c>
+      <c r="B171" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
+        <v>332</v>
+      </c>
+      <c r="B172" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="345">
   <si>
     <t>Production Line</t>
   </si>
@@ -77,108 +77,111 @@
     <t>INC1</t>
   </si>
   <si>
+    <t>INC4</t>
+  </si>
+  <si>
+    <t>INT3</t>
+  </si>
+  <si>
     <t>INTERNAL</t>
   </si>
   <si>
-    <t>INC4</t>
-  </si>
-  <si>
-    <t>INT3</t>
-  </si>
-  <si>
     <t>910728980</t>
   </si>
   <si>
     <t>910728614</t>
   </si>
   <si>
+    <t>910728754</t>
+  </si>
+  <si>
+    <t>910728848</t>
+  </si>
+  <si>
+    <t>910728783</t>
+  </si>
+  <si>
+    <t>910728860</t>
+  </si>
+  <si>
+    <t>910730952</t>
+  </si>
+  <si>
+    <t>910731193</t>
+  </si>
+  <si>
+    <t>910731174</t>
+  </si>
+  <si>
+    <t>910731148</t>
+  </si>
+  <si>
+    <t>910731092</t>
+  </si>
+  <si>
+    <t>910731062 + 910731125</t>
+  </si>
+  <si>
+    <t>910730972 + 910730971</t>
+  </si>
+  <si>
+    <t>910730950</t>
+  </si>
+  <si>
+    <t>910731102 + 910730963</t>
+  </si>
+  <si>
+    <t>910730943 + 910731293</t>
+  </si>
+  <si>
+    <t>910731190</t>
+  </si>
+  <si>
+    <t>910731147</t>
+  </si>
+  <si>
+    <t>910731168 + 910731221</t>
+  </si>
+  <si>
+    <t>910731183</t>
+  </si>
+  <si>
+    <t>910731146</t>
+  </si>
+  <si>
+    <t>910731172</t>
+  </si>
+  <si>
+    <t>910730970</t>
+  </si>
+  <si>
+    <t>910731238 + 910731304</t>
+  </si>
+  <si>
+    <t>910728866 + 910728931 + 910728784 + 910728850</t>
+  </si>
+  <si>
+    <t>910728859</t>
+  </si>
+  <si>
     <t>AUTO_1</t>
   </si>
   <si>
-    <t>910728754</t>
-  </si>
-  <si>
-    <t>910728848</t>
-  </si>
-  <si>
-    <t>910728783</t>
-  </si>
-  <si>
-    <t>910728860</t>
-  </si>
-  <si>
-    <t>910730952</t>
-  </si>
-  <si>
     <t>AUTO_2</t>
   </si>
   <si>
-    <t>910731193</t>
-  </si>
-  <si>
-    <t>910731174</t>
-  </si>
-  <si>
-    <t>910731148</t>
-  </si>
-  <si>
-    <t>910731092</t>
-  </si>
-  <si>
-    <t>910731062 + 910731125</t>
+    <t>910731115</t>
   </si>
   <si>
     <t>AUTO_3</t>
   </si>
   <si>
-    <t>910730972 + 910730971</t>
-  </si>
-  <si>
-    <t>910730950</t>
-  </si>
-  <si>
-    <t>910731102 + 910730963</t>
-  </si>
-  <si>
-    <t>910730943 + 910731293</t>
-  </si>
-  <si>
-    <t>910731190</t>
-  </si>
-  <si>
-    <t>910731147</t>
-  </si>
-  <si>
-    <t>910731168 + 910731221</t>
-  </si>
-  <si>
-    <t>910731183</t>
-  </si>
-  <si>
-    <t>910731146</t>
-  </si>
-  <si>
-    <t>910731172</t>
-  </si>
-  <si>
-    <t>910730970</t>
-  </si>
-  <si>
-    <t>910731238 + 910731304</t>
-  </si>
-  <si>
-    <t>910728866 + 910728931 + 910728784 + 910728850 + 910730961</t>
-  </si>
-  <si>
-    <t>910728859</t>
-  </si>
-  <si>
-    <t>910731115</t>
-  </si>
-  <si>
     <t>910731057</t>
   </si>
   <si>
+    <t>910730961</t>
+  </si>
+  <si>
     <t>910731220 + 910731319</t>
   </si>
   <si>
@@ -194,51 +197,54 @@
     <t>83900263</t>
   </si>
   <si>
+    <t>83900262</t>
+  </si>
+  <si>
+    <t>83900261</t>
+  </si>
+  <si>
+    <t>80880893</t>
+  </si>
+  <si>
+    <t>83900207</t>
+  </si>
+  <si>
+    <t>80880900</t>
+  </si>
+  <si>
+    <t>80880914</t>
+  </si>
+  <si>
+    <t>83900259</t>
+  </si>
+  <si>
+    <t>80880904</t>
+  </si>
+  <si>
+    <t>80879274</t>
+  </si>
+  <si>
+    <t>80879278</t>
+  </si>
+  <si>
+    <t>80841061</t>
+  </si>
+  <si>
+    <t>83900258</t>
+  </si>
+  <si>
     <t>95619314</t>
   </si>
   <si>
-    <t>83900262</t>
-  </si>
-  <si>
-    <t>83900261</t>
-  </si>
-  <si>
-    <t>80880893</t>
-  </si>
-  <si>
-    <t>83900207</t>
-  </si>
-  <si>
-    <t>80880900</t>
-  </si>
-  <si>
-    <t>80880914</t>
-  </si>
-  <si>
-    <t>83900259</t>
-  </si>
-  <si>
-    <t>80880904</t>
-  </si>
-  <si>
-    <t>80879274</t>
-  </si>
-  <si>
-    <t>80879278</t>
-  </si>
-  <si>
-    <t>80841061</t>
-  </si>
-  <si>
-    <t>83900258</t>
-  </si>
-  <si>
     <t>80880901</t>
   </si>
   <si>
     <t>80841060</t>
   </si>
   <si>
+    <t>80851522</t>
+  </si>
+  <si>
     <t>80879275</t>
   </si>
   <si>
@@ -254,51 +260,54 @@
     <t>H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
+    <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 180ML X 56 AHF IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 300ML X30 CM IN DM GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X30 CM IN GST</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
+  </si>
+  <si>
     <t>Auto-Replenishment HC Base (12T)</t>
   </si>
   <si>
-    <t>H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 180ML X 56 AHF IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 300ML X30 CM IN DM GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 340ML X30 CM IN GST</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 340ML X30 AHF IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 340MLX30 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
-  </si>
-  <si>
     <t>H&amp;S SHM 180ML X 56 LF IN GST</t>
   </si>
   <si>
     <t>PNTN COND 200MLX 24 HS SS IN PC25</t>
   </si>
   <si>
+    <t>PNTN COND 100MLX 24 HS HF IN AMJ25</t>
+  </si>
+  <si>
     <t>PNTN SHM 340ML X 30 HS LT IN GST</t>
   </si>
   <si>
@@ -314,93 +323,96 @@
     <t>B002</t>
   </si>
   <si>
+    <t>B005</t>
+  </si>
+  <si>
+    <t>B006</t>
+  </si>
+  <si>
+    <t>B008</t>
+  </si>
+  <si>
+    <t>B009</t>
+  </si>
+  <si>
+    <t>B010</t>
+  </si>
+  <si>
+    <t>B011</t>
+  </si>
+  <si>
+    <t>B013</t>
+  </si>
+  <si>
+    <t>B014</t>
+  </si>
+  <si>
+    <t>B015</t>
+  </si>
+  <si>
+    <t>B016</t>
+  </si>
+  <si>
+    <t>B019</t>
+  </si>
+  <si>
+    <t>B020</t>
+  </si>
+  <si>
+    <t>B021</t>
+  </si>
+  <si>
+    <t>B022</t>
+  </si>
+  <si>
+    <t>B023</t>
+  </si>
+  <si>
+    <t>B024</t>
+  </si>
+  <si>
+    <t>B025</t>
+  </si>
+  <si>
+    <t>B026</t>
+  </si>
+  <si>
+    <t>B027</t>
+  </si>
+  <si>
+    <t>B028</t>
+  </si>
+  <si>
+    <t>B030</t>
+  </si>
+  <si>
+    <t>B031</t>
+  </si>
+  <si>
+    <t>B003</t>
+  </si>
+  <si>
+    <t>B004</t>
+  </si>
+  <si>
     <t>REP07</t>
   </si>
   <si>
-    <t>B005</t>
-  </si>
-  <si>
-    <t>B006</t>
-  </si>
-  <si>
-    <t>B008</t>
-  </si>
-  <si>
-    <t>B009</t>
-  </si>
-  <si>
-    <t>B010</t>
-  </si>
-  <si>
     <t>REP12</t>
   </si>
   <si>
-    <t>B011</t>
-  </si>
-  <si>
-    <t>B013</t>
-  </si>
-  <si>
-    <t>B014</t>
-  </si>
-  <si>
-    <t>B015</t>
-  </si>
-  <si>
-    <t>B016</t>
+    <t>B017</t>
   </si>
   <si>
     <t>REP18</t>
   </si>
   <si>
-    <t>B019</t>
-  </si>
-  <si>
-    <t>B020</t>
-  </si>
-  <si>
-    <t>B021</t>
-  </si>
-  <si>
-    <t>B022</t>
-  </si>
-  <si>
-    <t>B023</t>
-  </si>
-  <si>
-    <t>B024</t>
-  </si>
-  <si>
-    <t>B025</t>
-  </si>
-  <si>
-    <t>B026</t>
-  </si>
-  <si>
-    <t>B027</t>
-  </si>
-  <si>
-    <t>B028</t>
-  </si>
-  <si>
-    <t>B030</t>
-  </si>
-  <si>
-    <t>B031</t>
-  </si>
-  <si>
-    <t>B003</t>
-  </si>
-  <si>
-    <t>B004</t>
-  </si>
-  <si>
-    <t>B017</t>
-  </si>
-  <si>
     <t>B032</t>
   </si>
   <si>
+    <t>B035</t>
+  </si>
+  <si>
     <t>B029</t>
   </si>
   <si>
@@ -461,24 +473,21 @@
     <t>Dual</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>TK#_51_#</t>
   </si>
   <si>
     <t>NO_TANK_AVAILABLE</t>
   </si>
   <si>
-    <t>TK#_12_# + TK#_16_#</t>
-  </si>
-  <si>
     <t>TK#_22_#</t>
   </si>
   <si>
@@ -503,78 +512,6 @@
     <t>1.25T</t>
   </si>
   <si>
-    <t>2026-01-12 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-12 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-12 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-12 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-12 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-12 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-12 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-12 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 07:30</t>
-  </si>
-  <si>
     <t>2026-01-13 08:00</t>
   </si>
   <si>
@@ -1004,115 +941,106 @@
     <t>2026-01-16 07:00</t>
   </si>
   <si>
-    <t>2026-01-16 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 09:00</t>
-  </si>
-  <si>
     <t>B001: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
   </si>
   <si>
     <t>B002: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
+    <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B006: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B008: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B009: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B010: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B011: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B013: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B014: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B015: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B016: H&amp;S SHM 180ML X 56 AHF IN GST</t>
+  </si>
+  <si>
     <t>WASHOUT</t>
   </si>
   <si>
+    <t>B019: H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B020: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B021: H&amp;S SHM 300ML X30 CM IN DM GST</t>
+  </si>
+  <si>
+    <t>B022: H&amp;S SHM 340ML X30 CM IN GST</t>
+  </si>
+  <si>
+    <t>B023: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B024: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B025: H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>B026: PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B027: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B028: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B030: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B031: PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B003: PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>COND WASH (60m)</t>
+  </si>
+  <si>
+    <t>B004: H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
+  </si>
+  <si>
     <t>REP07: Auto-Replenishment HC Base (12T)</t>
   </si>
   <si>
-    <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B006: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B008: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B009: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B010: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
     <t>REP12: Auto-Replenishment HC Base (12T)</t>
   </si>
   <si>
-    <t>B011: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>B013: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B014: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>B015: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B016: H&amp;S SHM 180ML X 56 AHF IN GST</t>
+    <t>B017: H&amp;S SHM 180ML X 56 LF IN GST</t>
   </si>
   <si>
     <t>REP18: Auto-Replenishment HC Base (12T)</t>
   </si>
   <si>
-    <t>B019: H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>B020: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B021: H&amp;S SHM 300ML X30 CM IN DM GST</t>
-  </si>
-  <si>
-    <t>B022: H&amp;S SHM 340ML X30 CM IN GST</t>
-  </si>
-  <si>
-    <t>B023: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B024: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B025: H&amp;S SHM 340ML X30 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B026: PNTN SHM 340MLX30 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>B027: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B028: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B030: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B031: PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>B003: PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>COND WASH (60m)</t>
-  </si>
-  <si>
-    <t>B004: H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
-  </si>
-  <si>
-    <t>B017: H&amp;S SHM 180ML X 56 LF IN GST</t>
-  </si>
-  <si>
     <t>B032: PNTN COND 200MLX 24 HS SS IN PC25</t>
+  </si>
+  <si>
+    <t>B035: PNTN COND 100MLX 24 HS HF IN AMJ25</t>
   </si>
   <si>
     <t>B029: PNTN SHM 340ML X 30 HS LT IN GST</t>
@@ -1183,15 +1111,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1486,10 +1411,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="21" width="15.7109375" customWidth="1"/>
+    <col min="1" max="18" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1556,43 +1481,43 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H2">
         <v>4.5088</v>
       </c>
       <c r="I2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K2" s="2">
-        <v>46035.94930555556</v>
+        <v>46036.16041666667</v>
       </c>
       <c r="L2">
         <v>90</v>
       </c>
       <c r="M2" s="2">
-        <v>46036.01180555556</v>
+        <v>46036.22291666667</v>
       </c>
       <c r="N2">
-        <v>503</v>
+        <v>199</v>
       </c>
       <c r="O2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="P2" s="2">
         <v>46036.36111111111</v>
@@ -1601,7 +1526,7 @@
         <v>46036.55</v>
       </c>
       <c r="R2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1612,43 +1537,43 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H3">
         <v>4.4185</v>
       </c>
       <c r="I3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K3" s="2">
-        <v>46036.01180555556</v>
+        <v>46036.22291666667</v>
       </c>
       <c r="L3">
         <v>90</v>
       </c>
       <c r="M3" s="2">
-        <v>46036.07430555556</v>
+        <v>46036.28541666667</v>
       </c>
       <c r="N3">
-        <v>424</v>
+        <v>120</v>
       </c>
       <c r="O3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P3" s="2">
         <v>46036.36875</v>
@@ -1657,12 +1582,12 @@
         <v>46036.55208333334</v>
       </c>
       <c r="R3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
@@ -1671,334 +1596,334 @@
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H4">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="I4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K4" s="2">
-        <v>46036.08819444444</v>
+        <v>46036.35902777778</v>
       </c>
       <c r="L4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M4" s="2">
-        <v>46036.21319444444</v>
+        <v>46036.42152777778</v>
       </c>
       <c r="N4">
-        <v>513</v>
+        <v>188</v>
       </c>
       <c r="O4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P4" s="2">
-        <v>46036.56944444445</v>
+        <v>46036.55208333334</v>
       </c>
       <c r="Q4" s="2">
-        <v>46036.61111111111</v>
+        <v>46036.73611111111</v>
       </c>
       <c r="R4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H5">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K5" s="2">
-        <v>46036.22708333333</v>
+        <v>46036.42152777778</v>
       </c>
       <c r="L5">
         <v>90</v>
       </c>
       <c r="M5" s="2">
-        <v>46036.28958333333</v>
+        <v>46036.48402777778</v>
       </c>
       <c r="N5">
-        <v>378</v>
+        <v>120</v>
       </c>
       <c r="O5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P5" s="2">
-        <v>46036.55208333334</v>
+        <v>46036.56736111111</v>
       </c>
       <c r="Q5" s="2">
-        <v>46036.73611111111</v>
+        <v>46036.78125</v>
       </c>
       <c r="R5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
         <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H6">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K6" s="2">
-        <v>46036.28958333333</v>
+        <v>46036.59027777778</v>
       </c>
       <c r="L6">
         <v>90</v>
       </c>
       <c r="M6" s="2">
-        <v>46036.35208333333</v>
+        <v>46036.65277777778</v>
       </c>
       <c r="N6">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="O6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P6" s="2">
-        <v>46036.56736111111</v>
+        <v>46036.73611111111</v>
       </c>
       <c r="Q6" s="2">
-        <v>46036.78125</v>
+        <v>46036.91944444444</v>
       </c>
       <c r="R6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H7">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K7" s="2">
-        <v>46036.35208333333</v>
+        <v>46036.67708333334</v>
       </c>
       <c r="L7">
         <v>90</v>
       </c>
       <c r="M7" s="2">
-        <v>46036.41458333333</v>
+        <v>46036.73958333334</v>
       </c>
       <c r="N7">
-        <v>463</v>
+        <v>120</v>
       </c>
       <c r="O7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P7" s="2">
-        <v>46036.73611111111</v>
+        <v>46036.82291666666</v>
       </c>
       <c r="Q7" s="2">
-        <v>46036.91944444444</v>
+        <v>46037.03611111111</v>
       </c>
       <c r="R7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
         <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H8">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K8" s="2">
-        <v>46036.41458333333</v>
+        <v>46036.77361111111</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8" s="2">
-        <v>46036.47708333333</v>
+        <v>46036.83611111111</v>
       </c>
       <c r="N8">
-        <v>498</v>
+        <v>120</v>
       </c>
       <c r="O8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P8" s="2">
-        <v>46036.82291666666</v>
+        <v>46036.91944444444</v>
       </c>
       <c r="Q8" s="2">
-        <v>46037.03611111111</v>
+        <v>46037.10347222222</v>
       </c>
       <c r="R8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F9" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H9">
         <v>4.4185</v>
       </c>
       <c r="I9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K9" s="2">
-        <v>46036.47708333333</v>
+        <v>46036.84166666667</v>
       </c>
       <c r="L9">
         <v>90</v>
       </c>
       <c r="M9" s="2">
-        <v>46036.53958333333</v>
+        <v>46036.90416666667</v>
       </c>
       <c r="N9">
-        <v>547</v>
+        <v>190</v>
       </c>
       <c r="O9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P9" s="2">
-        <v>46036.91944444444</v>
+        <v>46037.03611111111</v>
       </c>
       <c r="Q9" s="2">
-        <v>46037.10347222222</v>
+        <v>46037.25</v>
       </c>
       <c r="R9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -2007,54 +1932,54 @@
         <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="G10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H10">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="I10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K10" s="2">
-        <v>46036.55347222222</v>
+        <v>46036.90416666667</v>
       </c>
       <c r="L10">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M10" s="2">
-        <v>46036.67847222222</v>
+        <v>46036.96666666667</v>
       </c>
       <c r="N10">
-        <v>550</v>
+        <v>197</v>
       </c>
       <c r="O10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="P10" s="2">
-        <v>46037.06041666667</v>
+        <v>46037.10347222222</v>
       </c>
       <c r="Q10" s="2">
-        <v>46037.10208333333</v>
+        <v>46037.28680555556</v>
       </c>
       <c r="R10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
@@ -2063,49 +1988,49 @@
         <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H11">
         <v>4.4185</v>
       </c>
       <c r="I11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J11" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K11" s="2">
-        <v>46036.69236111111</v>
+        <v>46036.96666666667</v>
       </c>
       <c r="L11">
         <v>90</v>
       </c>
       <c r="M11" s="2">
-        <v>46036.75486111111</v>
+        <v>46037.02916666667</v>
       </c>
       <c r="N11">
-        <v>405</v>
+        <v>318</v>
       </c>
       <c r="O11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P11" s="2">
-        <v>46037.03611111111</v>
+        <v>46037.25</v>
       </c>
       <c r="Q11" s="2">
-        <v>46037.25</v>
+        <v>46037.46319444444</v>
       </c>
       <c r="R11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2116,332 +2041,332 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G12" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H12">
         <v>4.4185</v>
       </c>
       <c r="I12" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K12" s="2">
-        <v>46036.75486111111</v>
+        <v>46037.02916666667</v>
       </c>
       <c r="L12">
         <v>90</v>
       </c>
       <c r="M12" s="2">
-        <v>46036.81736111111</v>
+        <v>46037.09166666667</v>
       </c>
       <c r="N12">
-        <v>412</v>
+        <v>281</v>
       </c>
       <c r="O12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P12" s="2">
-        <v>46037.10347222222</v>
+        <v>46037.28680555556</v>
       </c>
       <c r="Q12" s="2">
-        <v>46037.28680555556</v>
+        <v>46037.47083333333</v>
       </c>
       <c r="R12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F13" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H13">
-        <v>4.4185</v>
+        <v>4.4891</v>
       </c>
       <c r="I13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K13" s="2">
-        <v>46036.81736111111</v>
+        <v>46037.09166666667</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13" s="2">
-        <v>46036.87986111111</v>
+        <v>46037.15416666667</v>
       </c>
       <c r="N13">
-        <v>533</v>
+        <v>228</v>
       </c>
       <c r="O13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P13" s="2">
-        <v>46037.25</v>
+        <v>46037.3125</v>
       </c>
       <c r="Q13" s="2">
-        <v>46037.46319444444</v>
+        <v>46037.75833333333</v>
       </c>
       <c r="R13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H14">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="I14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K14" s="2">
-        <v>46036.87986111111</v>
+        <v>46037.16805555556</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14" s="2">
-        <v>46036.94236111111</v>
+        <v>46037.23055555556</v>
       </c>
       <c r="N14">
-        <v>496</v>
+        <v>335</v>
       </c>
       <c r="O14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P14" s="2">
-        <v>46037.28680555556</v>
+        <v>46037.46319444444</v>
       </c>
       <c r="Q14" s="2">
-        <v>46037.47083333333</v>
+        <v>46037.67708333334</v>
       </c>
       <c r="R14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G15" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H15">
-        <v>4.4891</v>
+        <v>4.4185</v>
       </c>
       <c r="I15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K15" s="2">
-        <v>46036.94236111111</v>
+        <v>46037.23055555556</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15" s="2">
-        <v>46037.00486111111</v>
+        <v>46037.29305555556</v>
       </c>
       <c r="N15">
-        <v>443</v>
+        <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P15" s="2">
-        <v>46037.3125</v>
+        <v>46037.47083333333</v>
       </c>
       <c r="Q15" s="2">
-        <v>46037.75833333333</v>
+        <v>46037.65486111111</v>
       </c>
       <c r="R15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="G16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H16">
-        <v>2.2948</v>
+        <v>4.0957</v>
       </c>
       <c r="I16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K16" s="2">
-        <v>46037.01875</v>
+        <v>46037.29305555556</v>
       </c>
       <c r="L16">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M16" s="2">
-        <v>46037.14375</v>
+        <v>46037.35555555556</v>
       </c>
       <c r="N16">
-        <v>450</v>
+        <v>209</v>
       </c>
       <c r="O16" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="P16" s="2">
-        <v>46037.45625</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="Q16" s="2">
-        <v>46037.49791666667</v>
+        <v>46037.6375</v>
       </c>
       <c r="R16" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F17" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H17">
-        <v>4.4163</v>
+        <v>5.2051</v>
       </c>
       <c r="I17" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J17" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K17" s="2">
-        <v>46037.15763888889</v>
+        <v>46037.35555555556</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17" s="2">
-        <v>46037.22013888889</v>
+        <v>46037.41805555556</v>
       </c>
       <c r="N17">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="O17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P17" s="2">
-        <v>46037.46319444444</v>
+        <v>46037.6375</v>
       </c>
       <c r="Q17" s="2">
-        <v>46037.67708333334</v>
+        <v>46038.77569444444</v>
       </c>
       <c r="R17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2452,108 +2377,108 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G18" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H18">
         <v>4.4185</v>
       </c>
       <c r="I18" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J18" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K18" s="2">
-        <v>46037.22013888889</v>
+        <v>46037.41805555556</v>
       </c>
       <c r="L18">
         <v>90</v>
       </c>
       <c r="M18" s="2">
-        <v>46037.28263888889</v>
+        <v>46037.48055555556</v>
       </c>
       <c r="N18">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="O18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P18" s="2">
-        <v>46037.47083333333</v>
+        <v>46037.65486111111</v>
       </c>
       <c r="Q18" s="2">
-        <v>46037.65486111111</v>
+        <v>46037.83819444444</v>
       </c>
       <c r="R18" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s">
         <v>136</v>
       </c>
       <c r="G19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H19">
-        <v>4.0957</v>
+        <v>4.4163</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K19" s="2">
-        <v>46037.28263888889</v>
+        <v>46037.48055555556</v>
       </c>
       <c r="L19">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M19" s="2">
-        <v>46037.34861111111</v>
+        <v>46037.54305555556</v>
       </c>
       <c r="N19">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="O19" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P19" s="2">
-        <v>46037.50069444445</v>
+        <v>46037.67708333334</v>
       </c>
       <c r="Q19" s="2">
-        <v>46037.6375</v>
+        <v>46037.89027777778</v>
       </c>
       <c r="R19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2564,332 +2489,332 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H20">
         <v>5.2051</v>
       </c>
       <c r="I20" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K20" s="2">
-        <v>46037.34861111111</v>
+        <v>46037.54305555556</v>
       </c>
       <c r="L20">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M20" s="2">
-        <v>46037.41458333333</v>
+        <v>46037.60555555556</v>
       </c>
       <c r="N20">
-        <v>321</v>
+        <v>220</v>
       </c>
       <c r="O20" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P20" s="2">
-        <v>46037.6375</v>
+        <v>46037.75833333333</v>
       </c>
       <c r="Q20" s="2">
-        <v>46038.77569444444</v>
+        <v>46038.71527777778</v>
       </c>
       <c r="R20" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G21" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H21">
-        <v>4.4185</v>
+        <v>4.5228</v>
       </c>
       <c r="I21" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K21" s="2">
-        <v>46037.41458333333</v>
+        <v>46037.61944444444</v>
       </c>
       <c r="L21">
         <v>90</v>
       </c>
       <c r="M21" s="2">
-        <v>46037.47708333333</v>
+        <v>46037.68194444444</v>
       </c>
       <c r="N21">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="O21" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P21" s="2">
-        <v>46037.65486111111</v>
+        <v>46037.81805555556</v>
       </c>
       <c r="Q21" s="2">
-        <v>46037.83819444444</v>
+        <v>46037.93819444445</v>
       </c>
       <c r="R21" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G22" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H22">
-        <v>4.4163</v>
+        <v>4.4185</v>
       </c>
       <c r="I22" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K22" s="2">
-        <v>46037.47708333333</v>
+        <v>46037.68194444444</v>
       </c>
       <c r="L22">
         <v>90</v>
       </c>
       <c r="M22" s="2">
-        <v>46037.53958333333</v>
+        <v>46037.74444444444</v>
       </c>
       <c r="N22">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="O22" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="P22" s="2">
-        <v>46037.67708333334</v>
+        <v>46037.83819444444</v>
       </c>
       <c r="Q22" s="2">
-        <v>46037.89027777778</v>
+        <v>46038.02222222222</v>
       </c>
       <c r="R22" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
         <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G23" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H23">
-        <v>5.2051</v>
+        <v>4.4163</v>
       </c>
       <c r="I23" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K23" s="2">
-        <v>46037.53958333333</v>
+        <v>46037.74444444444</v>
       </c>
       <c r="L23">
         <v>90</v>
       </c>
       <c r="M23" s="2">
-        <v>46037.60208333333</v>
+        <v>46037.80694444444</v>
       </c>
       <c r="N23">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="O23" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P23" s="2">
-        <v>46037.75833333333</v>
+        <v>46037.89027777778</v>
       </c>
       <c r="Q23" s="2">
-        <v>46038.71527777778</v>
+        <v>46038.10416666666</v>
       </c>
       <c r="R23" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H24">
-        <v>4.5228</v>
+        <v>4.4185</v>
       </c>
       <c r="I24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J24" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K24" s="2">
-        <v>46037.61597222222</v>
+        <v>46037.87638888889</v>
       </c>
       <c r="L24">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M24" s="2">
-        <v>46037.68194444444</v>
+        <v>46037.93888888889</v>
       </c>
       <c r="N24">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="O24" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P24" s="2">
-        <v>46037.81805555556</v>
+        <v>46038.02222222222</v>
       </c>
       <c r="Q24" s="2">
-        <v>46037.93819444445</v>
+        <v>46038.20555555556</v>
       </c>
       <c r="R24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H25">
-        <v>4.4185</v>
+        <v>5.1635</v>
       </c>
       <c r="I25" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J25" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K25" s="2">
-        <v>46037.68194444444</v>
+        <v>46038.23472222222</v>
       </c>
       <c r="L25">
         <v>90</v>
       </c>
       <c r="M25" s="2">
-        <v>46037.74444444444</v>
+        <v>46038.29722222222</v>
       </c>
       <c r="N25">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="O25" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P25" s="2">
-        <v>46037.83819444444</v>
+        <v>46038.38055555556</v>
       </c>
       <c r="Q25" s="2">
-        <v>46038.02222222222</v>
+        <v>46038.53472222222</v>
       </c>
       <c r="R25" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2900,164 +2825,164 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F26" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G26" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H26">
-        <v>4.4163</v>
+        <v>2.2404</v>
       </c>
       <c r="I26" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K26" s="2">
-        <v>46037.74444444444</v>
+        <v>46035.33333333334</v>
       </c>
       <c r="L26">
         <v>90</v>
       </c>
       <c r="M26" s="2">
-        <v>46037.80694444444</v>
+        <v>46035.39583333334</v>
       </c>
       <c r="N26">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="O26" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="P26" s="2">
-        <v>46037.89027777778</v>
+        <v>46036.39583333334</v>
       </c>
       <c r="Q26" s="2">
-        <v>46038.10416666666</v>
+        <v>46038.42569444444</v>
       </c>
       <c r="R26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F27" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H27">
-        <v>4.4185</v>
+        <v>2.2082</v>
       </c>
       <c r="I27" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J27" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K27" s="2">
-        <v>46037.87638888889</v>
+        <v>46035.4375</v>
       </c>
       <c r="L27">
         <v>90</v>
       </c>
       <c r="M27" s="2">
-        <v>46037.93888888889</v>
+        <v>46035.5</v>
       </c>
       <c r="N27">
-        <v>120</v>
+        <v>1384</v>
       </c>
       <c r="O27" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="P27" s="2">
-        <v>46038.02222222222</v>
+        <v>46036.46111111111</v>
       </c>
       <c r="Q27" s="2">
-        <v>46038.20555555556</v>
+        <v>46036.56736111111</v>
       </c>
       <c r="R27" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H28">
-        <v>5.1635</v>
+        <v>2.2948</v>
       </c>
       <c r="I28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J28" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K28" s="2">
-        <v>46038.23125</v>
+        <v>46035.51388888889</v>
       </c>
       <c r="L28">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M28" s="2">
-        <v>46038.29722222222</v>
+        <v>46035.57638888889</v>
       </c>
       <c r="N28">
-        <v>120</v>
+        <v>1430</v>
       </c>
       <c r="O28" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="P28" s="2">
-        <v>46038.38055555556</v>
+        <v>46036.56944444445</v>
       </c>
       <c r="Q28" s="2">
-        <v>46038.53472222222</v>
+        <v>46036.61111111111</v>
       </c>
       <c r="R28" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -3068,113 +2993,113 @@
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29">
+        <v>2.2948</v>
+      </c>
+      <c r="I29" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29" t="s">
+        <v>153</v>
+      </c>
+      <c r="K29" s="2">
+        <v>46035.57638888889</v>
+      </c>
+      <c r="L29">
         <v>90</v>
       </c>
-      <c r="E29" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" t="s">
-        <v>145</v>
-      </c>
-      <c r="H29">
-        <v>2.8005</v>
-      </c>
-      <c r="I29" t="s">
-        <v>146</v>
-      </c>
-      <c r="J29" t="s">
-        <v>148</v>
-      </c>
-      <c r="K29" s="2">
-        <v>46034.85416666666</v>
-      </c>
-      <c r="L29">
-        <v>180</v>
-      </c>
       <c r="M29" s="2">
-        <v>46034.97916666666</v>
+        <v>46035.63888888889</v>
       </c>
       <c r="N29">
-        <v>2040</v>
+        <v>2062</v>
       </c>
       <c r="O29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P29" s="2">
-        <v>46036.39583333334</v>
+        <v>46037.07083333333</v>
       </c>
       <c r="Q29" s="2">
-        <v>46039.42569444444</v>
+        <v>46037.1125</v>
       </c>
       <c r="R29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F30" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H30">
-        <v>2.2082</v>
+        <v>2.2544</v>
       </c>
       <c r="I30" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J30" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K30" s="2">
-        <v>46035.3125</v>
+        <v>46035.65277777778</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30" s="2">
-        <v>46035.375</v>
+        <v>46035.71527777778</v>
       </c>
       <c r="N30">
-        <v>1564</v>
+        <v>2435</v>
       </c>
       <c r="O30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P30" s="2">
-        <v>46036.46111111111</v>
+        <v>46037.40625</v>
       </c>
       <c r="Q30" s="2">
-        <v>46036.56736111111</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="R30" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
         <v>52</v>
@@ -3183,96 +3108,96 @@
         <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F31" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H31">
-        <v>2.2544</v>
+        <v>2.2948</v>
       </c>
       <c r="I31" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J31" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K31" s="2">
-        <v>46035.38888888889</v>
+        <v>46035.72916666666</v>
       </c>
       <c r="L31">
         <v>90</v>
       </c>
       <c r="M31" s="2">
-        <v>46035.45138888889</v>
+        <v>46035.79166666666</v>
       </c>
       <c r="N31">
-        <v>2815</v>
+        <v>2402</v>
       </c>
       <c r="O31" t="s">
         <v>156</v>
       </c>
       <c r="P31" s="2">
-        <v>46037.40625</v>
+        <v>46037.45972222222</v>
       </c>
       <c r="Q31" s="2">
-        <v>46037.50069444445</v>
+        <v>46037.50138888889</v>
       </c>
       <c r="R31" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G32" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H32">
         <v>0.5601</v>
       </c>
       <c r="I32" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J32" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K32" s="2">
-        <v>46035.48611111111</v>
+        <v>46035.82638888889</v>
       </c>
       <c r="L32">
         <v>90</v>
       </c>
       <c r="M32" s="2">
-        <v>46035.54861111111</v>
+        <v>46035.88888888889</v>
       </c>
       <c r="N32">
-        <v>4143</v>
+        <v>3653</v>
       </c>
       <c r="O32" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P32" s="2">
         <v>46038.42569444444</v>
@@ -3281,63 +3206,63 @@
         <v>46038.60486111111</v>
       </c>
       <c r="R32" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F33" t="s">
         <v>142</v>
       </c>
       <c r="G33" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H33">
-        <v>2.2733</v>
+        <v>0.28</v>
       </c>
       <c r="I33" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J33" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K33" s="2">
-        <v>46035.59027777778</v>
+        <v>46036.3125</v>
       </c>
       <c r="L33">
         <v>90</v>
       </c>
       <c r="M33" s="2">
-        <v>46035.65277777778</v>
+        <v>46036.375</v>
       </c>
       <c r="N33">
-        <v>3291</v>
+        <v>3211</v>
       </c>
       <c r="O33" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P33" s="2">
-        <v>46037.93819444445</v>
+        <v>46038.60486111111</v>
       </c>
       <c r="Q33" s="2">
-        <v>46038.38055555556</v>
+        <v>46039.42569444444</v>
       </c>
       <c r="R33" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -3348,52 +3273,52 @@
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F34" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G34" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H34">
-        <v>2.2511</v>
+        <v>2.2733</v>
       </c>
       <c r="I34" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J34" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K34" s="2">
-        <v>46035.66666666666</v>
+        <v>46036.41666666666</v>
       </c>
       <c r="L34">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M34" s="2">
-        <v>46035.72569444445</v>
+        <v>46036.47916666666</v>
       </c>
       <c r="N34">
-        <v>4045</v>
+        <v>2101</v>
       </c>
       <c r="O34" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P34" s="2">
-        <v>46038.53472222222</v>
+        <v>46037.93819444445</v>
       </c>
       <c r="Q34" s="2">
-        <v>46038.59513888889</v>
+        <v>46038.38055555556</v>
       </c>
       <c r="R34" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -3404,52 +3329,108 @@
         <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G35" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H35">
         <v>2.2511</v>
       </c>
       <c r="I35" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J35" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K35" s="2">
-        <v>46035.73958333334</v>
+        <v>46036.49305555555</v>
       </c>
       <c r="L35">
         <v>90</v>
       </c>
       <c r="M35" s="2">
-        <v>46035.80208333334</v>
+        <v>46036.55555555555</v>
       </c>
       <c r="N35">
-        <v>4022</v>
+        <v>2850</v>
       </c>
       <c r="O35" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="P35" s="2">
+        <v>46038.53472222222</v>
+      </c>
+      <c r="Q35" s="2">
         <v>46038.59513888889</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" t="s">
+        <v>147</v>
+      </c>
+      <c r="G36" t="s">
+        <v>149</v>
+      </c>
+      <c r="H36">
+        <v>2.2511</v>
+      </c>
+      <c r="I36" t="s">
+        <v>150</v>
+      </c>
+      <c r="J36" t="s">
+        <v>153</v>
+      </c>
+      <c r="K36" s="2">
+        <v>46036.56944444445</v>
+      </c>
+      <c r="L36">
+        <v>90</v>
+      </c>
+      <c r="M36" s="2">
+        <v>46036.63194444445</v>
+      </c>
+      <c r="N36">
+        <v>2827</v>
+      </c>
+      <c r="O36" t="s">
+        <v>159</v>
+      </c>
+      <c r="P36" s="2">
+        <v>46038.59513888889</v>
+      </c>
+      <c r="Q36" s="2">
         <v>46038.65555555555</v>
       </c>
-      <c r="R35" t="s">
-        <v>157</v>
+      <c r="R36" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3459,1775 +3440,1519 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="5" width="40.7109375" style="3" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>153</v>
+      </c>
+      <c r="D2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>361</v>
+        <v>153</v>
+      </c>
+      <c r="D3" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>361</v>
+        <v>153</v>
+      </c>
+      <c r="D4" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>361</v>
+        <v>153</v>
+      </c>
+      <c r="D5" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>361</v>
+        <v>153</v>
+      </c>
+      <c r="D6" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>361</v>
+        <v>153</v>
+      </c>
+      <c r="D7" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>361</v>
+        <v>153</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>362</v>
+        <v>153</v>
+      </c>
+      <c r="D9" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>362</v>
+        <v>153</v>
+      </c>
+      <c r="D10" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="D11" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="D12" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="D13" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="D14" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="D15" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="D16" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D17" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D18" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D19" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D20" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D21" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D22" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D23" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="D24" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B25" t="s">
-        <v>150</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>363</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>363</v>
+        <v>154</v>
+      </c>
+      <c r="D26" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B27" t="s">
-        <v>150</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>363</v>
+        <v>154</v>
+      </c>
+      <c r="D27" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>335</v>
+        <v>154</v>
+      </c>
+      <c r="D28" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>364</v>
+        <v>154</v>
+      </c>
+      <c r="D29" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B30" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>364</v>
+        <v>154</v>
+      </c>
+      <c r="D30" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>364</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s">
-        <v>150</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B39" t="s">
-        <v>150</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>152</v>
+      </c>
+      <c r="C42" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>152</v>
+      </c>
+      <c r="C43" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>152</v>
+      </c>
+      <c r="C44" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>152</v>
+      </c>
+      <c r="C45" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>152</v>
+      </c>
+      <c r="C46" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>152</v>
+      </c>
+      <c r="C47" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D49" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D50" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D51" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="C52" t="s">
+        <v>310</v>
+      </c>
+      <c r="D52" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="C53" t="s">
+        <v>310</v>
+      </c>
+      <c r="D53" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="C54" t="s">
+        <v>310</v>
+      </c>
+      <c r="D54" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="C55" t="s">
+        <v>311</v>
+      </c>
+      <c r="D55" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="C56" t="s">
+        <v>311</v>
+      </c>
+      <c r="D56" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="C57" t="s">
+        <v>311</v>
+      </c>
+      <c r="D57" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D58" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D59" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D60" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D61" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="D62" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="C63" t="s">
+        <v>312</v>
+      </c>
+      <c r="D63" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>336</v>
+        <v>153</v>
+      </c>
+      <c r="C64" t="s">
+        <v>312</v>
+      </c>
+      <c r="D64" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>336</v>
+        <v>154</v>
+      </c>
+      <c r="C65" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B66" t="s">
-        <v>149</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>336</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B67" t="s">
-        <v>149</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>336</v>
+        <v>154</v>
+      </c>
+      <c r="C67" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>336</v>
+        <v>154</v>
+      </c>
+      <c r="C68" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>337</v>
+        <v>154</v>
+      </c>
+      <c r="C69" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B70" t="s">
-        <v>149</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>337</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>337</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>338</v>
+        <v>154</v>
+      </c>
+      <c r="C72" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B73" t="s">
-        <v>150</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>338</v>
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B74" t="s">
-        <v>150</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>338</v>
+        <v>154</v>
+      </c>
+      <c r="C74" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>339</v>
+        <v>154</v>
+      </c>
+      <c r="C75" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B76" t="s">
-        <v>150</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>339</v>
+        <v>154</v>
+      </c>
+      <c r="C76" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>339</v>
+        <v>154</v>
+      </c>
+      <c r="C77" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>340</v>
+        <v>154</v>
+      </c>
+      <c r="C78" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>340</v>
+        <v>154</v>
+      </c>
+      <c r="C79" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B80" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>340</v>
+        <v>154</v>
+      </c>
+      <c r="C80" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>341</v>
+        <v>152</v>
+      </c>
+      <c r="C81" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B82" t="s">
-        <v>150</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>341</v>
+        <v>152</v>
+      </c>
+      <c r="C82" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>341</v>
+        <v>152</v>
+      </c>
+      <c r="C83" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>335</v>
+        <v>152</v>
+      </c>
+      <c r="C84" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>342</v>
+        <v>152</v>
+      </c>
+      <c r="C85" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B86" t="s">
-        <v>150</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>342</v>
+        <v>152</v>
+      </c>
+      <c r="C86" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B87" t="s">
-        <v>150</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>342</v>
+        <v>152</v>
+      </c>
+      <c r="C87" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B88" t="s">
-        <v>150</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>342</v>
+        <v>152</v>
+      </c>
+      <c r="C88" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B89" t="s">
-        <v>148</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>342</v>
+        <v>152</v>
+      </c>
+      <c r="C89" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B90" t="s">
-        <v>148</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>342</v>
+        <v>152</v>
+      </c>
+      <c r="C90" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B91" t="s">
-        <v>148</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>335</v>
+        <v>152</v>
+      </c>
+      <c r="C91" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B92" t="s">
-        <v>148</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>343</v>
+        <v>152</v>
+      </c>
+      <c r="C92" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B93" t="s">
-        <v>148</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>343</v>
+        <v>152</v>
+      </c>
+      <c r="C93" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B94" t="s">
-        <v>148</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>343</v>
+        <v>152</v>
+      </c>
+      <c r="C94" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B95" t="s">
-        <v>148</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>344</v>
+        <v>152</v>
+      </c>
+      <c r="C95" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B96" t="s">
-        <v>148</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>344</v>
+        <v>152</v>
+      </c>
+      <c r="C96" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B97" t="s">
-        <v>148</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>344</v>
+        <v>153</v>
+      </c>
+      <c r="C97" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B98" t="s">
-        <v>148</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>345</v>
+        <v>153</v>
+      </c>
+      <c r="C98" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>345</v>
+        <v>153</v>
+      </c>
+      <c r="C99" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B100" t="s">
-        <v>148</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>345</v>
+        <v>153</v>
+      </c>
+      <c r="C100" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B101" t="s">
-        <v>148</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>346</v>
+        <v>153</v>
+      </c>
+      <c r="C101" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B102" t="s">
-        <v>148</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>346</v>
+        <v>153</v>
+      </c>
+      <c r="C102" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B103" t="s">
-        <v>148</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>346</v>
+        <v>153</v>
+      </c>
+      <c r="C103" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B104" t="s">
-        <v>148</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>347</v>
+        <v>153</v>
+      </c>
+      <c r="C104" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B105" t="s">
-        <v>149</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>347</v>
+        <v>153</v>
+      </c>
+      <c r="C105" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>347</v>
+        <v>153</v>
+      </c>
+      <c r="C106" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B107" t="s">
-        <v>149</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>348</v>
+        <v>153</v>
+      </c>
+      <c r="C107" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B108" t="s">
-        <v>149</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>348</v>
+        <v>153</v>
+      </c>
+      <c r="C108" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B109" t="s">
-        <v>149</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>348</v>
+        <v>153</v>
+      </c>
+      <c r="C109" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B110" t="s">
-        <v>149</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>348</v>
+        <v>153</v>
+      </c>
+      <c r="C110" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>348</v>
+        <v>153</v>
+      </c>
+      <c r="C111" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B112" t="s">
-        <v>149</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>348</v>
+        <v>153</v>
+      </c>
+      <c r="C112" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B113" t="s">
-        <v>149</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>335</v>
+        <v>154</v>
+      </c>
+      <c r="C113" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B114" t="s">
-        <v>149</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>349</v>
+        <v>154</v>
+      </c>
+      <c r="C114" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B115" t="s">
-        <v>149</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>349</v>
+        <v>154</v>
+      </c>
+      <c r="C115" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B116" t="s">
-        <v>149</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>349</v>
+        <v>154</v>
+      </c>
+      <c r="C116" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B117" t="s">
-        <v>149</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>350</v>
+        <v>154</v>
+      </c>
+      <c r="C117" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>350</v>
+        <v>154</v>
+      </c>
+      <c r="C118" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B119" t="s">
-        <v>149</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>350</v>
+        <v>154</v>
+      </c>
+      <c r="C119" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B120" t="s">
-        <v>149</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>351</v>
+        <v>154</v>
+      </c>
+      <c r="C120" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B121" t="s">
-        <v>150</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>351</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B122" t="s">
-        <v>150</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>351</v>
+        <v>154</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B123" t="s">
-        <v>150</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>352</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B124" t="s">
-        <v>150</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>352</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B125" t="s">
-        <v>150</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>352</v>
+        <v>154</v>
+      </c>
+      <c r="C125" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B126" t="s">
-        <v>150</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>353</v>
+        <v>154</v>
+      </c>
+      <c r="C126" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B127" t="s">
-        <v>150</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>353</v>
+        <v>154</v>
+      </c>
+      <c r="C127" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B128" t="s">
-        <v>150</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>353</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B129" t="s">
-        <v>150</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>354</v>
+        <v>152</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B130" t="s">
-        <v>150</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>354</v>
+        <v>152</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B131" t="s">
-        <v>150</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>354</v>
+        <v>152</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B132" t="s">
-        <v>150</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>355</v>
+        <v>152</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>355</v>
+        <v>152</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B134" t="s">
-        <v>150</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>355</v>
+        <v>152</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B135" t="s">
-        <v>150</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>335</v>
+        <v>152</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B136" t="s">
-        <v>150</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>356</v>
+        <v>152</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B137" t="s">
-        <v>148</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>356</v>
+        <v>152</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B138" t="s">
-        <v>148</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>356</v>
+        <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B139" t="s">
-        <v>148</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>357</v>
+        <v>152</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B140" t="s">
-        <v>148</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>357</v>
+        <v>152</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B141" t="s">
-        <v>148</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>357</v>
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B142" t="s">
-        <v>148</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>358</v>
+        <v>152</v>
+      </c>
+      <c r="C142" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B143" t="s">
-        <v>148</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>358</v>
+        <v>152</v>
+      </c>
+      <c r="C143" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B144" t="s">
-        <v>148</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" t="s">
-        <v>305</v>
-      </c>
-      <c r="B145" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" t="s">
-        <v>306</v>
-      </c>
-      <c r="B146" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" t="s">
-        <v>307</v>
-      </c>
-      <c r="B147" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" t="s">
-        <v>308</v>
-      </c>
-      <c r="B148" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" t="s">
-        <v>309</v>
-      </c>
-      <c r="B149" t="s">
-        <v>148</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" t="s">
-        <v>310</v>
-      </c>
-      <c r="B150" t="s">
-        <v>148</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
-        <v>311</v>
-      </c>
-      <c r="B151" t="s">
-        <v>148</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" t="s">
-        <v>312</v>
-      </c>
-      <c r="B152" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" t="s">
-        <v>313</v>
-      </c>
-      <c r="B153" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" t="s">
-        <v>314</v>
-      </c>
-      <c r="B154" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" t="s">
-        <v>315</v>
-      </c>
-      <c r="B155" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" t="s">
-        <v>316</v>
-      </c>
-      <c r="B156" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" t="s">
-        <v>317</v>
-      </c>
-      <c r="B157" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
-        <v>318</v>
-      </c>
-      <c r="B158" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" t="s">
-        <v>319</v>
-      </c>
-      <c r="B159" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
-        <v>320</v>
-      </c>
-      <c r="B160" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" t="s">
-        <v>321</v>
-      </c>
-      <c r="B161" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" t="s">
-        <v>322</v>
-      </c>
-      <c r="B162" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" t="s">
-        <v>323</v>
-      </c>
-      <c r="B163" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" t="s">
-        <v>324</v>
-      </c>
-      <c r="B164" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" t="s">
-        <v>325</v>
-      </c>
-      <c r="B165" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" t="s">
-        <v>326</v>
-      </c>
-      <c r="B166" t="s">
-        <v>149</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" t="s">
-        <v>327</v>
-      </c>
-      <c r="B167" t="s">
-        <v>149</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" t="s">
-        <v>328</v>
-      </c>
-      <c r="B168" t="s">
-        <v>149</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" t="s">
-        <v>329</v>
-      </c>
-      <c r="B169" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
-        <v>330</v>
-      </c>
-      <c r="B170" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" t="s">
-        <v>331</v>
-      </c>
-      <c r="B171" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" t="s">
+        <v>152</v>
+      </c>
+      <c r="C144" t="s">
         <v>332</v>
-      </c>
-      <c r="B172" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="371">
   <si>
     <t>Production Line</t>
   </si>
@@ -158,13 +158,31 @@
     <t>910731238 + 910731304</t>
   </si>
   <si>
-    <t>910728866 + 910728931 + 910728784 + 910728850</t>
+    <t>910731057</t>
+  </si>
+  <si>
+    <t>910728866 + 910728931</t>
+  </si>
+  <si>
+    <t>AUTO_1</t>
+  </si>
+  <si>
+    <t>910730961</t>
   </si>
   <si>
     <t>910728859</t>
   </si>
   <si>
-    <t>AUTO_1</t>
+    <t>910731220 + 910731319</t>
+  </si>
+  <si>
+    <t>910728784 + 910728850</t>
+  </si>
+  <si>
+    <t>910731210</t>
+  </si>
+  <si>
+    <t>910731292</t>
   </si>
   <si>
     <t>AUTO_2</t>
@@ -176,21 +194,6 @@
     <t>AUTO_3</t>
   </si>
   <si>
-    <t>910731057</t>
-  </si>
-  <si>
-    <t>910730961</t>
-  </si>
-  <si>
-    <t>910731220 + 910731319</t>
-  </si>
-  <si>
-    <t>910731210</t>
-  </si>
-  <si>
-    <t>910731292</t>
-  </si>
-  <si>
     <t>80880903</t>
   </si>
   <si>
@@ -227,33 +230,33 @@
     <t>80879278</t>
   </si>
   <si>
+    <t>80841060</t>
+  </si>
+  <si>
     <t>80841061</t>
   </si>
   <si>
+    <t>95619314</t>
+  </si>
+  <si>
+    <t>80851522</t>
+  </si>
+  <si>
     <t>83900258</t>
   </si>
   <si>
-    <t>95619314</t>
+    <t>80879275</t>
+  </si>
+  <si>
+    <t>80879287</t>
+  </si>
+  <si>
+    <t>80879283</t>
   </si>
   <si>
     <t>80880901</t>
   </si>
   <si>
-    <t>80841060</t>
-  </si>
-  <si>
-    <t>80851522</t>
-  </si>
-  <si>
-    <t>80879275</t>
-  </si>
-  <si>
-    <t>80879287</t>
-  </si>
-  <si>
-    <t>80879283</t>
-  </si>
-  <si>
     <t>H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
   </si>
   <si>
@@ -290,136 +293,139 @@
     <t>PNTN SHM 180MLX56 HS HFC IN GST</t>
   </si>
   <si>
+    <t>PNTN COND 200MLX 24 HS SS IN PC25</t>
+  </si>
+  <si>
     <t>PNTN COND 200MLX 24 HS HF IN PC25</t>
   </si>
   <si>
+    <t>Auto-Replenishment HC Base (12T)</t>
+  </si>
+  <si>
+    <t>PNTN COND 100MLX 24 HS HF IN AMJ25</t>
+  </si>
+  <si>
     <t>H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
   </si>
   <si>
-    <t>Auto-Replenishment HC Base (12T)</t>
+    <t>PNTN SHM 340ML X 30 HS LT IN GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>PNTN SHM 650ML X 12 SSC IN GST</t>
   </si>
   <si>
     <t>H&amp;S SHM 180ML X 56 LF IN GST</t>
   </si>
   <si>
-    <t>PNTN COND 200MLX 24 HS SS IN PC25</t>
-  </si>
-  <si>
-    <t>PNTN COND 100MLX 24 HS HF IN AMJ25</t>
-  </si>
-  <si>
-    <t>PNTN SHM 340ML X 30 HS LT IN GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
-    <t>PNTN SHM 650ML X 12 SSC IN GST</t>
-  </si>
-  <si>
-    <t>B001</t>
-  </si>
-  <si>
     <t>B002</t>
   </si>
   <si>
+    <t>B003</t>
+  </si>
+  <si>
+    <t>B006</t>
+  </si>
+  <si>
+    <t>B007</t>
+  </si>
+  <si>
+    <t>B008</t>
+  </si>
+  <si>
+    <t>B010</t>
+  </si>
+  <si>
+    <t>B011</t>
+  </si>
+  <si>
+    <t>B012</t>
+  </si>
+  <si>
+    <t>B013</t>
+  </si>
+  <si>
+    <t>B014</t>
+  </si>
+  <si>
+    <t>B015</t>
+  </si>
+  <si>
+    <t>B016</t>
+  </si>
+  <si>
+    <t>B020</t>
+  </si>
+  <si>
+    <t>B021</t>
+  </si>
+  <si>
+    <t>B022</t>
+  </si>
+  <si>
+    <t>B023</t>
+  </si>
+  <si>
+    <t>B024</t>
+  </si>
+  <si>
+    <t>B025</t>
+  </si>
+  <si>
+    <t>B026</t>
+  </si>
+  <si>
+    <t>B027</t>
+  </si>
+  <si>
+    <t>B028</t>
+  </si>
+  <si>
+    <t>B029</t>
+  </si>
+  <si>
+    <t>B031</t>
+  </si>
+  <si>
+    <t>B032</t>
+  </si>
+  <si>
+    <t>B033</t>
+  </si>
+  <si>
+    <t>B004</t>
+  </si>
+  <si>
+    <t>REP01</t>
+  </si>
+  <si>
+    <t>B036</t>
+  </si>
+  <si>
     <t>B005</t>
   </si>
   <si>
-    <t>B006</t>
-  </si>
-  <si>
-    <t>B008</t>
-  </si>
-  <si>
-    <t>B009</t>
-  </si>
-  <si>
-    <t>B010</t>
-  </si>
-  <si>
-    <t>B011</t>
-  </si>
-  <si>
-    <t>B013</t>
-  </si>
-  <si>
-    <t>B014</t>
-  </si>
-  <si>
-    <t>B015</t>
-  </si>
-  <si>
-    <t>B016</t>
-  </si>
-  <si>
-    <t>B019</t>
-  </si>
-  <si>
-    <t>B020</t>
-  </si>
-  <si>
-    <t>B021</t>
-  </si>
-  <si>
-    <t>B022</t>
-  </si>
-  <si>
-    <t>B023</t>
-  </si>
-  <si>
-    <t>B024</t>
-  </si>
-  <si>
-    <t>B025</t>
-  </si>
-  <si>
-    <t>B026</t>
-  </si>
-  <si>
-    <t>B027</t>
-  </si>
-  <si>
-    <t>B028</t>
-  </si>
-  <si>
     <t>B030</t>
   </si>
   <si>
-    <t>B031</t>
-  </si>
-  <si>
-    <t>B003</t>
-  </si>
-  <si>
-    <t>B004</t>
-  </si>
-  <si>
-    <t>REP07</t>
-  </si>
-  <si>
-    <t>REP12</t>
+    <t>B018</t>
+  </si>
+  <si>
+    <t>B034</t>
+  </si>
+  <si>
+    <t>B035</t>
+  </si>
+  <si>
+    <t>REP09</t>
   </si>
   <si>
     <t>B017</t>
   </si>
   <si>
-    <t>REP18</t>
-  </si>
-  <si>
-    <t>B032</t>
-  </si>
-  <si>
-    <t>B035</t>
-  </si>
-  <si>
-    <t>B029</t>
-  </si>
-  <si>
-    <t>B033</t>
-  </si>
-  <si>
-    <t>B034</t>
+    <t>REP19</t>
   </si>
   <si>
     <t>21422079</t>
@@ -443,24 +449,24 @@
     <t>21302239</t>
   </si>
   <si>
+    <t>21090112</t>
+  </si>
+  <si>
     <t>21090111</t>
   </si>
   <si>
     <t>21448509</t>
   </si>
   <si>
+    <t>21302240</t>
+  </si>
+  <si>
+    <t>'21302240</t>
+  </si>
+  <si>
     <t>90966400</t>
   </si>
   <si>
-    <t>21090112</t>
-  </si>
-  <si>
-    <t>21302240</t>
-  </si>
-  <si>
-    <t>'21302240</t>
-  </si>
-  <si>
     <t>12T</t>
   </si>
   <si>
@@ -473,45 +479,126 @@
     <t>Dual</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>TK#_51_#</t>
-  </si>
-  <si>
-    <t>NO_TANK_AVAILABLE</t>
-  </si>
-  <si>
-    <t>TK#_22_#</t>
-  </si>
-  <si>
-    <t>TK#_16_#</t>
-  </si>
-  <si>
-    <t>TK#_12_#</t>
+    <t>TK#_51_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_7_# [Wash 20m] + TK#_6_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_23_# [Wash 20m] + TK#_24_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_21_# [Wash 20m] + TK#_2_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_17_# [Wash 20m] + TK#_20_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_3_# [Wash 20m] + TK#_4_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_1_# [Wash 20m] + TK#_18_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_13_# [Wash 20m] + TK#_7_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_6_# + TK#_19_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_16_# [Wash 20m] + TK#_15_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_23_# + TK#_24_#</t>
+  </si>
+  <si>
+    <t>TK#_8_# [Wash 20m] + TK#_21_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_17_# + TK#_20_#</t>
+  </si>
+  <si>
+    <t>TK#_52_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_53_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_6_# + TK#_19_#</t>
+  </si>
+  <si>
+    <t>TK#_22_# [Wash 20m] + TK#_5_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_1_# + TK#_18_#</t>
+  </si>
+  <si>
+    <t>TK#_52_#</t>
+  </si>
+  <si>
+    <t>TK#_27_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_26_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_17_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_25_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_13_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_11_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_28_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_10_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_9_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_8_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_5_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_22_# [Wash 20m]</t>
   </si>
   <si>
     <t>LOW: SLS</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
     <t>LOW: DM5500</t>
   </si>
   <si>
-    <t>OK</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
     <t>1.25T</t>
   </si>
   <si>
+    <t>2026-01-13 07:30</t>
+  </si>
+  <si>
     <t>2026-01-13 08:00</t>
   </si>
   <si>
@@ -941,28 +1028,28 @@
     <t>2026-01-16 07:00</t>
   </si>
   <si>
-    <t>B001: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
-  </si>
-  <si>
-    <t>B002: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B005: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B006: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+    <t>B002: H&amp;S SHM 180ML X 56 S&amp;S IN GST</t>
+  </si>
+  <si>
+    <t>B003: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B006: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B007: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
   </si>
   <si>
     <t>B008: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
   </si>
   <si>
-    <t>B009: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
-  </si>
-  <si>
-    <t>B010: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B011: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
+    <t>B010: H&amp;S SHM 5.7MLX1200 DAILY COOL IN GST FC</t>
+  </si>
+  <si>
+    <t>B011: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B012: H&amp;S SHM 5.7MLX 960 DS IN GST FC</t>
   </si>
   <si>
     <t>B013: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
@@ -977,79 +1064,70 @@
     <t>B016: H&amp;S SHM 180ML X 56 AHF IN GST</t>
   </si>
   <si>
+    <t>B020: H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
+  </si>
+  <si>
+    <t>B021: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B022: H&amp;S SHM 300ML X30 CM IN DM GST</t>
+  </si>
+  <si>
+    <t>B023: H&amp;S SHM 340ML X30 CM IN GST</t>
+  </si>
+  <si>
+    <t>B024: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B025: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B026: H&amp;S SHM 340ML X30 AHF IN GST</t>
+  </si>
+  <si>
+    <t>B027: PNTN SHM 340MLX30 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B028: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B029: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B031: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
+  </si>
+  <si>
+    <t>B032: PNTN SHM 180MLX56 HS HFC IN GST</t>
+  </si>
+  <si>
+    <t>B033: PNTN COND 200MLX 24 HS SS IN PC25</t>
+  </si>
+  <si>
+    <t>B004: PNTN COND 200MLX 24 HS HF IN PC25</t>
+  </si>
+  <si>
+    <t>COND WASH (60m)</t>
+  </si>
+  <si>
+    <t>B036: PNTN COND 100MLX 24 HS HF IN AMJ25</t>
+  </si>
+  <si>
+    <t>B030: PNTN SHM 340ML X 30 HS LT IN GST</t>
+  </si>
+  <si>
     <t>WASHOUT</t>
   </si>
   <si>
-    <t>B019: H&amp;S SHM 5.7MLX1200 DS IN GST FC</t>
-  </si>
-  <si>
-    <t>B020: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B021: H&amp;S SHM 300ML X30 CM IN DM GST</t>
-  </si>
-  <si>
-    <t>B022: H&amp;S SHM 340ML X30 CM IN GST</t>
-  </si>
-  <si>
-    <t>B023: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B024: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B025: H&amp;S SHM 340ML X30 AHF IN GST</t>
-  </si>
-  <si>
-    <t>B026: PNTN SHM 340MLX30 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>B027: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B028: H&amp;S SHM 5.7MLX1200 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B030: H&amp;S SHM 5.7MLX960 DAILY CLEAN IN GST FC</t>
-  </si>
-  <si>
-    <t>B031: PNTN SHM 180MLX56 HS HFC IN GST</t>
-  </si>
-  <si>
-    <t>B003: PNTN COND 200MLX 24 HS HF IN PC25</t>
-  </si>
-  <si>
-    <t>COND WASH (60m)</t>
-  </si>
-  <si>
-    <t>B004: H&amp;S SHM 5.7MLX1200 NEEM IN GST FC</t>
-  </si>
-  <si>
-    <t>REP07: Auto-Replenishment HC Base (12T)</t>
-  </si>
-  <si>
-    <t>REP12: Auto-Replenishment HC Base (12T)</t>
+    <t>B034: PNTN SHM 650ML X 12 HFC GST</t>
+  </si>
+  <si>
+    <t>REP09: Auto-Replenishment HC Base (12T)</t>
   </si>
   <si>
     <t>B017: H&amp;S SHM 180ML X 56 LF IN GST</t>
   </si>
   <si>
-    <t>REP18: Auto-Replenishment HC Base (12T)</t>
-  </si>
-  <si>
-    <t>B032: PNTN COND 200MLX 24 HS SS IN PC25</t>
-  </si>
-  <si>
-    <t>B035: PNTN COND 100MLX 24 HS HF IN AMJ25</t>
-  </si>
-  <si>
-    <t>B029: PNTN SHM 340ML X 30 HS LT IN GST</t>
-  </si>
-  <si>
-    <t>B033: PNTN SHM 650ML X 12 HFC GST</t>
-  </si>
-  <si>
-    <t>B034: PNTN SHM 650ML X 12 SSC IN GST</t>
+    <t>REP19: Auto-Replenishment HC Base (12T)</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="15.7109375" customWidth="1"/>
@@ -1481,43 +1559,43 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H2">
         <v>4.5088</v>
       </c>
       <c r="I2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K2" s="2">
-        <v>46036.16041666667</v>
+        <v>46035.72916666666</v>
       </c>
       <c r="L2">
         <v>90</v>
       </c>
       <c r="M2" s="2">
-        <v>46036.22291666667</v>
+        <v>46035.79166666666</v>
       </c>
       <c r="N2">
-        <v>199</v>
+        <v>820</v>
       </c>
       <c r="O2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P2" s="2">
         <v>46036.36111111111</v>
@@ -1526,7 +1604,7 @@
         <v>46036.55</v>
       </c>
       <c r="R2" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1537,43 +1615,43 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H3">
         <v>4.4185</v>
       </c>
       <c r="I3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K3" s="2">
-        <v>46036.22291666667</v>
+        <v>46035.79166666666</v>
       </c>
       <c r="L3">
         <v>90</v>
       </c>
       <c r="M3" s="2">
-        <v>46036.28541666667</v>
+        <v>46035.85416666666</v>
       </c>
       <c r="N3">
-        <v>120</v>
+        <v>741</v>
       </c>
       <c r="O3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P3" s="2">
         <v>46036.36875</v>
@@ -1582,7 +1660,7 @@
         <v>46036.55208333334</v>
       </c>
       <c r="R3" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1593,43 +1671,43 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H4">
         <v>4.4185</v>
       </c>
       <c r="I4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K4" s="2">
-        <v>46036.35902777778</v>
+        <v>46035.85416666666</v>
       </c>
       <c r="L4">
         <v>90</v>
       </c>
       <c r="M4" s="2">
-        <v>46036.42152777778</v>
+        <v>46035.91666666666</v>
       </c>
       <c r="N4">
-        <v>188</v>
+        <v>915</v>
       </c>
       <c r="O4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="P4" s="2">
         <v>46036.55208333334</v>
@@ -1638,7 +1716,7 @@
         <v>46036.73611111111</v>
       </c>
       <c r="R4" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1649,43 +1727,43 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H5">
         <v>4.4163</v>
       </c>
       <c r="I5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K5" s="2">
-        <v>46036.42152777778</v>
+        <v>46035.91666666666</v>
       </c>
       <c r="L5">
         <v>90</v>
       </c>
       <c r="M5" s="2">
-        <v>46036.48402777778</v>
+        <v>46035.97916666666</v>
       </c>
       <c r="N5">
-        <v>120</v>
+        <v>847</v>
       </c>
       <c r="O5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="P5" s="2">
         <v>46036.56736111111</v>
@@ -1694,7 +1772,7 @@
         <v>46036.78125</v>
       </c>
       <c r="R5" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1705,43 +1783,43 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H6">
         <v>4.4185</v>
       </c>
       <c r="I6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K6" s="2">
-        <v>46036.59027777778</v>
+        <v>46036.34027777778</v>
       </c>
       <c r="L6">
         <v>90</v>
       </c>
       <c r="M6" s="2">
-        <v>46036.65277777778</v>
+        <v>46036.40277777778</v>
       </c>
       <c r="N6">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="O6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="P6" s="2">
         <v>46036.73611111111</v>
@@ -1750,7 +1828,7 @@
         <v>46036.91944444444</v>
       </c>
       <c r="R6" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1761,43 +1839,43 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H7">
         <v>4.4163</v>
       </c>
       <c r="I7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K7" s="2">
-        <v>46036.67708333334</v>
+        <v>46036.40277777778</v>
       </c>
       <c r="L7">
         <v>90</v>
       </c>
       <c r="M7" s="2">
-        <v>46036.73958333334</v>
+        <v>46036.46527777778</v>
       </c>
       <c r="N7">
-        <v>120</v>
+        <v>515</v>
       </c>
       <c r="O7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="P7" s="2">
         <v>46036.82291666666</v>
@@ -1806,7 +1884,7 @@
         <v>46037.03611111111</v>
       </c>
       <c r="R7" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1817,43 +1895,43 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H8">
         <v>4.4185</v>
       </c>
       <c r="I8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K8" s="2">
-        <v>46036.77361111111</v>
+        <v>46036.46527777778</v>
       </c>
       <c r="L8">
         <v>90</v>
       </c>
       <c r="M8" s="2">
-        <v>46036.83611111111</v>
+        <v>46036.52777777778</v>
       </c>
       <c r="N8">
-        <v>120</v>
+        <v>564</v>
       </c>
       <c r="O8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="P8" s="2">
         <v>46036.91944444444</v>
@@ -1862,7 +1940,7 @@
         <v>46037.10347222222</v>
       </c>
       <c r="R8" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1873,43 +1951,43 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H9">
         <v>4.4185</v>
       </c>
       <c r="I9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K9" s="2">
-        <v>46036.84166666667</v>
+        <v>46036.52777777778</v>
       </c>
       <c r="L9">
         <v>90</v>
       </c>
       <c r="M9" s="2">
-        <v>46036.90416666667</v>
+        <v>46036.59027777778</v>
       </c>
       <c r="N9">
-        <v>190</v>
+        <v>642</v>
       </c>
       <c r="O9" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="P9" s="2">
         <v>46037.03611111111</v>
@@ -1918,7 +1996,7 @@
         <v>46037.25</v>
       </c>
       <c r="R9" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1929,43 +2007,43 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H10">
         <v>4.4185</v>
       </c>
       <c r="I10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K10" s="2">
-        <v>46036.90416666667</v>
+        <v>46036.59027777778</v>
       </c>
       <c r="L10">
         <v>90</v>
       </c>
       <c r="M10" s="2">
-        <v>46036.96666666667</v>
+        <v>46036.65277777778</v>
       </c>
       <c r="N10">
-        <v>197</v>
+        <v>649</v>
       </c>
       <c r="O10" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P10" s="2">
         <v>46037.10347222222</v>
@@ -1974,7 +2052,7 @@
         <v>46037.28680555556</v>
       </c>
       <c r="R10" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1985,43 +2063,43 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H11">
         <v>4.4185</v>
       </c>
       <c r="I11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J11" t="s">
         <v>154</v>
       </c>
       <c r="K11" s="2">
-        <v>46036.96666666667</v>
+        <v>46036.65277777778</v>
       </c>
       <c r="L11">
         <v>90</v>
       </c>
       <c r="M11" s="2">
-        <v>46037.02916666667</v>
+        <v>46036.71527777778</v>
       </c>
       <c r="N11">
-        <v>318</v>
+        <v>770</v>
       </c>
       <c r="O11" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="P11" s="2">
         <v>46037.25</v>
@@ -2030,7 +2108,7 @@
         <v>46037.46319444444</v>
       </c>
       <c r="R11" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2041,43 +2119,43 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H12">
         <v>4.4185</v>
       </c>
       <c r="I12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K12" s="2">
-        <v>46037.02916666667</v>
+        <v>46036.71527777778</v>
       </c>
       <c r="L12">
         <v>90</v>
       </c>
       <c r="M12" s="2">
-        <v>46037.09166666667</v>
+        <v>46036.77777777778</v>
       </c>
       <c r="N12">
-        <v>281</v>
+        <v>733</v>
       </c>
       <c r="O12" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="P12" s="2">
         <v>46037.28680555556</v>
@@ -2086,7 +2164,7 @@
         <v>46037.47083333333</v>
       </c>
       <c r="R12" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2097,43 +2175,43 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H13">
         <v>4.4891</v>
       </c>
       <c r="I13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K13" s="2">
-        <v>46037.09166666667</v>
+        <v>46036.77777777778</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13" s="2">
-        <v>46037.15416666667</v>
+        <v>46036.84027777778</v>
       </c>
       <c r="N13">
-        <v>228</v>
+        <v>680</v>
       </c>
       <c r="O13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P13" s="2">
         <v>46037.3125</v>
@@ -2142,7 +2220,7 @@
         <v>46037.75833333333</v>
       </c>
       <c r="R13" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2153,43 +2231,43 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H14">
         <v>4.4163</v>
       </c>
       <c r="I14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K14" s="2">
-        <v>46037.16805555556</v>
+        <v>46036.85416666666</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14" s="2">
-        <v>46037.23055555556</v>
+        <v>46036.91666666666</v>
       </c>
       <c r="N14">
-        <v>335</v>
+        <v>787</v>
       </c>
       <c r="O14" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="P14" s="2">
         <v>46037.46319444444</v>
@@ -2198,7 +2276,7 @@
         <v>46037.67708333334</v>
       </c>
       <c r="R14" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2209,43 +2287,43 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H15">
         <v>4.4185</v>
       </c>
       <c r="I15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K15" s="2">
-        <v>46037.23055555556</v>
+        <v>46036.91666666666</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15" s="2">
-        <v>46037.29305555556</v>
+        <v>46036.97916666666</v>
       </c>
       <c r="N15">
-        <v>256</v>
+        <v>708</v>
       </c>
       <c r="O15" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="P15" s="2">
         <v>46037.47083333333</v>
@@ -2254,7 +2332,7 @@
         <v>46037.65486111111</v>
       </c>
       <c r="R15" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2265,28 +2343,28 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H16">
         <v>4.0957</v>
       </c>
       <c r="I16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K16" s="2">
         <v>46037.29305555556</v>
@@ -2301,7 +2379,7 @@
         <v>209</v>
       </c>
       <c r="O16" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="P16" s="2">
         <v>46037.50069444445</v>
@@ -2310,7 +2388,7 @@
         <v>46037.6375</v>
       </c>
       <c r="R16" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2321,28 +2399,28 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H17">
         <v>5.2051</v>
       </c>
       <c r="I17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K17" s="2">
         <v>46037.35555555556</v>
@@ -2357,7 +2435,7 @@
         <v>316</v>
       </c>
       <c r="O17" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="P17" s="2">
         <v>46037.6375</v>
@@ -2366,7 +2444,7 @@
         <v>46038.77569444444</v>
       </c>
       <c r="R17" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2377,28 +2455,28 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H18">
         <v>4.4185</v>
       </c>
       <c r="I18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K18" s="2">
         <v>46037.41805555556</v>
@@ -2413,7 +2491,7 @@
         <v>251</v>
       </c>
       <c r="O18" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="P18" s="2">
         <v>46037.65486111111</v>
@@ -2422,7 +2500,7 @@
         <v>46037.83819444444</v>
       </c>
       <c r="R18" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2433,28 +2511,28 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H19">
         <v>4.4163</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K19" s="2">
         <v>46037.48055555556</v>
@@ -2469,7 +2547,7 @@
         <v>193</v>
       </c>
       <c r="O19" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="P19" s="2">
         <v>46037.67708333334</v>
@@ -2478,7 +2556,7 @@
         <v>46037.89027777778</v>
       </c>
       <c r="R19" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2489,28 +2567,28 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H20">
         <v>5.2051</v>
       </c>
       <c r="I20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K20" s="2">
         <v>46037.54305555556</v>
@@ -2525,7 +2603,7 @@
         <v>220</v>
       </c>
       <c r="O20" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="P20" s="2">
         <v>46037.75833333333</v>
@@ -2534,7 +2612,7 @@
         <v>46038.71527777778</v>
       </c>
       <c r="R20" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2545,28 +2623,28 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F21" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H21">
         <v>4.5228</v>
       </c>
       <c r="I21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K21" s="2">
         <v>46037.61944444444</v>
@@ -2581,7 +2659,7 @@
         <v>196</v>
       </c>
       <c r="O21" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="P21" s="2">
         <v>46037.81805555556</v>
@@ -2590,7 +2668,7 @@
         <v>46037.93819444445</v>
       </c>
       <c r="R21" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2601,25 +2679,25 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H22">
         <v>4.4185</v>
       </c>
       <c r="I22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" t="s">
         <v>154</v>
@@ -2637,7 +2715,7 @@
         <v>135</v>
       </c>
       <c r="O22" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="P22" s="2">
         <v>46037.83819444444</v>
@@ -2646,7 +2724,7 @@
         <v>46038.02222222222</v>
       </c>
       <c r="R22" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2657,25 +2735,25 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H23">
         <v>4.4163</v>
       </c>
       <c r="I23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J23" t="s">
         <v>154</v>
@@ -2693,7 +2771,7 @@
         <v>120</v>
       </c>
       <c r="O23" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="P23" s="2">
         <v>46037.89027777778</v>
@@ -2702,7 +2780,7 @@
         <v>46038.10416666666</v>
       </c>
       <c r="R23" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2713,25 +2791,25 @@
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H24">
         <v>4.4185</v>
       </c>
       <c r="I24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J24" t="s">
         <v>154</v>
@@ -2749,7 +2827,7 @@
         <v>120</v>
       </c>
       <c r="O24" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="P24" s="2">
         <v>46038.02222222222</v>
@@ -2758,7 +2836,7 @@
         <v>46038.20555555556</v>
       </c>
       <c r="R24" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2769,28 +2847,28 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G25" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H25">
         <v>5.1635</v>
       </c>
       <c r="I25" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J25" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K25" s="2">
         <v>46038.23472222222</v>
@@ -2805,7 +2883,7 @@
         <v>120</v>
       </c>
       <c r="O25" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="P25" s="2">
         <v>46038.38055555556</v>
@@ -2814,7 +2892,7 @@
         <v>46038.53472222222</v>
       </c>
       <c r="R25" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2825,108 +2903,108 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H26">
-        <v>2.2404</v>
+        <v>0.5601</v>
       </c>
       <c r="I26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K26" s="2">
-        <v>46035.33333333334</v>
+        <v>46035.3125</v>
       </c>
       <c r="L26">
         <v>90</v>
       </c>
       <c r="M26" s="2">
-        <v>46035.39583333334</v>
+        <v>46035.375</v>
       </c>
       <c r="N26">
-        <v>1440</v>
+        <v>4393</v>
       </c>
       <c r="O26" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="P26" s="2">
-        <v>46036.39583333334</v>
+        <v>46038.42569444444</v>
       </c>
       <c r="Q26" s="2">
-        <v>46038.42569444444</v>
+        <v>46038.60486111111</v>
       </c>
       <c r="R26" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F27" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G27" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H27">
-        <v>2.2082</v>
+        <v>1.1202</v>
       </c>
       <c r="I27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K27" s="2">
-        <v>46035.4375</v>
+        <v>46035.33333333334</v>
       </c>
       <c r="L27">
         <v>90</v>
       </c>
       <c r="M27" s="2">
-        <v>46035.5</v>
+        <v>46035.39583333334</v>
       </c>
       <c r="N27">
-        <v>1384</v>
+        <v>1440</v>
       </c>
       <c r="O27" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="P27" s="2">
-        <v>46036.46111111111</v>
+        <v>46036.39583333334</v>
       </c>
       <c r="Q27" s="2">
-        <v>46036.56736111111</v>
+        <v>46037.41041666667</v>
       </c>
       <c r="R27" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2937,220 +3015,220 @@
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H28">
         <v>2.2948</v>
       </c>
       <c r="I28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K28" s="2">
-        <v>46035.51388888889</v>
+        <v>46035.4375</v>
       </c>
       <c r="L28">
         <v>90</v>
       </c>
       <c r="M28" s="2">
-        <v>46035.57638888889</v>
+        <v>46035.5</v>
       </c>
       <c r="N28">
-        <v>1430</v>
+        <v>1180</v>
       </c>
       <c r="O28" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="P28" s="2">
-        <v>46036.56944444445</v>
+        <v>46036.31944444445</v>
       </c>
       <c r="Q28" s="2">
-        <v>46036.61111111111</v>
+        <v>46036.36111111111</v>
       </c>
       <c r="R28" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H29">
-        <v>2.2948</v>
+        <v>0.28</v>
       </c>
       <c r="I29" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J29" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K29" s="2">
-        <v>46035.57638888889</v>
+        <v>46035.4375</v>
       </c>
       <c r="L29">
         <v>90</v>
       </c>
       <c r="M29" s="2">
-        <v>46035.63888888889</v>
+        <v>46035.5</v>
       </c>
       <c r="N29">
-        <v>2062</v>
+        <v>4471</v>
       </c>
       <c r="O29" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="P29" s="2">
-        <v>46037.07083333333</v>
+        <v>46038.60486111111</v>
       </c>
       <c r="Q29" s="2">
-        <v>46037.1125</v>
+        <v>46039.42569444444</v>
       </c>
       <c r="R29" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H30">
-        <v>2.2544</v>
+        <v>2.2082</v>
       </c>
       <c r="I30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K30" s="2">
-        <v>46035.65277777778</v>
+        <v>46035.51388888889</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30" s="2">
-        <v>46035.71527777778</v>
+        <v>46035.57638888889</v>
       </c>
       <c r="N30">
-        <v>2435</v>
+        <v>1274</v>
       </c>
       <c r="O30" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="P30" s="2">
-        <v>46037.40625</v>
+        <v>46036.46111111111</v>
       </c>
       <c r="Q30" s="2">
-        <v>46037.50069444445</v>
+        <v>46036.56736111111</v>
       </c>
       <c r="R30" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="G31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H31">
-        <v>2.2948</v>
+        <v>2.2733</v>
       </c>
       <c r="I31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K31" s="2">
-        <v>46035.72916666666</v>
+        <v>46035.54166666666</v>
       </c>
       <c r="L31">
         <v>90</v>
       </c>
       <c r="M31" s="2">
-        <v>46035.79166666666</v>
+        <v>46035.60416666666</v>
       </c>
       <c r="N31">
-        <v>2402</v>
+        <v>3361</v>
       </c>
       <c r="O31" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="P31" s="2">
-        <v>46037.45972222222</v>
+        <v>46037.93819444445</v>
       </c>
       <c r="Q31" s="2">
-        <v>46037.50138888889</v>
+        <v>46038.38055555556</v>
       </c>
       <c r="R31" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -3161,108 +3239,108 @@
         <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" t="s">
         <v>145</v>
       </c>
       <c r="G32" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H32">
-        <v>0.5601</v>
+        <v>1.1202</v>
       </c>
       <c r="I32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K32" s="2">
-        <v>46035.82638888889</v>
+        <v>46035.61111111111</v>
       </c>
       <c r="L32">
         <v>90</v>
       </c>
       <c r="M32" s="2">
-        <v>46035.88888888889</v>
+        <v>46035.67361111111</v>
       </c>
       <c r="N32">
-        <v>3653</v>
+        <v>2501</v>
       </c>
       <c r="O32" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="P32" s="2">
+        <v>46037.41041666667</v>
+      </c>
+      <c r="Q32" s="2">
         <v>46038.42569444444</v>
       </c>
-      <c r="Q32" s="2">
-        <v>46038.60486111111</v>
-      </c>
       <c r="R32" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H33">
-        <v>0.28</v>
+        <v>2.2511</v>
       </c>
       <c r="I33" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K33" s="2">
-        <v>46036.3125</v>
+        <v>46035.61805555555</v>
       </c>
       <c r="L33">
         <v>90</v>
       </c>
       <c r="M33" s="2">
-        <v>46036.375</v>
+        <v>46035.68055555555</v>
       </c>
       <c r="N33">
-        <v>3211</v>
+        <v>4110</v>
       </c>
       <c r="O33" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="P33" s="2">
-        <v>46038.60486111111</v>
+        <v>46038.53472222222</v>
       </c>
       <c r="Q33" s="2">
-        <v>46039.42569444444</v>
+        <v>46038.59513888889</v>
       </c>
       <c r="R33" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -3273,108 +3351,108 @@
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H34">
-        <v>2.2733</v>
+        <v>2.2511</v>
       </c>
       <c r="I34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K34" s="2">
-        <v>46036.41666666666</v>
+        <v>46035.69444444445</v>
       </c>
       <c r="L34">
         <v>90</v>
       </c>
       <c r="M34" s="2">
-        <v>46036.47916666666</v>
+        <v>46035.75694444445</v>
       </c>
       <c r="N34">
-        <v>2101</v>
+        <v>4087</v>
       </c>
       <c r="O34" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="P34" s="2">
-        <v>46037.93819444445</v>
+        <v>46038.59513888889</v>
       </c>
       <c r="Q34" s="2">
-        <v>46038.38055555556</v>
+        <v>46038.65555555555</v>
       </c>
       <c r="R34" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
         <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="G35" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H35">
-        <v>2.2511</v>
+        <v>2.2948</v>
       </c>
       <c r="I35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K35" s="2">
-        <v>46036.49305555555</v>
+        <v>46035.71527777778</v>
       </c>
       <c r="L35">
         <v>90</v>
       </c>
       <c r="M35" s="2">
-        <v>46036.55555555555</v>
+        <v>46035.77777777778</v>
       </c>
       <c r="N35">
-        <v>2850</v>
+        <v>1410</v>
       </c>
       <c r="O35" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="P35" s="2">
-        <v>46038.53472222222</v>
+        <v>46036.75694444445</v>
       </c>
       <c r="Q35" s="2">
-        <v>46038.59513888889</v>
+        <v>46036.79861111111</v>
       </c>
       <c r="R35" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -3385,52 +3463,108 @@
         <v>57</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G36" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H36">
-        <v>2.2511</v>
+        <v>2.2544</v>
       </c>
       <c r="I36" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K36" s="2">
-        <v>46036.56944444445</v>
+        <v>46035.79166666666</v>
       </c>
       <c r="L36">
         <v>90</v>
       </c>
       <c r="M36" s="2">
-        <v>46036.63194444445</v>
+        <v>46035.85416666666</v>
       </c>
       <c r="N36">
-        <v>2827</v>
+        <v>2235</v>
       </c>
       <c r="O36" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="P36" s="2">
-        <v>46038.59513888889</v>
+        <v>46037.40625</v>
       </c>
       <c r="Q36" s="2">
-        <v>46038.65555555555</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="R36" t="s">
-        <v>160</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H37">
+        <v>2.2948</v>
+      </c>
+      <c r="I37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J37" t="s">
+        <v>154</v>
+      </c>
+      <c r="K37" s="2">
+        <v>46035.86805555555</v>
+      </c>
+      <c r="L37">
+        <v>90</v>
+      </c>
+      <c r="M37" s="2">
+        <v>46035.93055555555</v>
+      </c>
+      <c r="N37">
+        <v>2202</v>
+      </c>
+      <c r="O37" t="s">
+        <v>187</v>
+      </c>
+      <c r="P37" s="2">
+        <v>46037.45972222222</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>46037.50138888889</v>
+      </c>
+      <c r="R37" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -3440,1322 +3574,1280 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
-        <v>320</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s">
         <v>154</v>
       </c>
       <c r="D18" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s">
         <v>154</v>
       </c>
       <c r="D19" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s">
         <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s">
         <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s">
         <v>154</v>
       </c>
+      <c r="C22" t="s">
+        <v>337</v>
+      </c>
       <c r="D22" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s">
         <v>154</v>
       </c>
+      <c r="C23" t="s">
+        <v>337</v>
+      </c>
       <c r="D23" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s">
         <v>154</v>
       </c>
+      <c r="C24" t="s">
+        <v>337</v>
+      </c>
       <c r="D24" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
         <v>154</v>
+      </c>
+      <c r="C25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s">
         <v>154</v>
       </c>
+      <c r="C26" t="s">
+        <v>338</v>
+      </c>
       <c r="D26" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="B27" t="s">
         <v>154</v>
       </c>
+      <c r="C27" t="s">
+        <v>338</v>
+      </c>
       <c r="D27" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s">
         <v>154</v>
       </c>
+      <c r="C28" t="s">
+        <v>339</v>
+      </c>
       <c r="D28" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s">
         <v>154</v>
       </c>
+      <c r="C29" t="s">
+        <v>339</v>
+      </c>
       <c r="D29" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s">
         <v>154</v>
       </c>
+      <c r="C30" t="s">
+        <v>339</v>
+      </c>
       <c r="D30" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="B31" t="s">
         <v>154</v>
+      </c>
+      <c r="C31" t="s">
+        <v>340</v>
+      </c>
+      <c r="D31" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="B32" t="s">
         <v>154</v>
+      </c>
+      <c r="C32" t="s">
+        <v>340</v>
+      </c>
+      <c r="D32" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>154</v>
+      </c>
+      <c r="C33" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
-      </c>
-      <c r="C42" t="s">
-        <v>308</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
-      </c>
-      <c r="C43" t="s">
-        <v>308</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" t="s">
-        <v>308</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="B45" t="s">
-        <v>152</v>
-      </c>
-      <c r="C45" t="s">
-        <v>309</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
-      </c>
-      <c r="C46" t="s">
-        <v>309</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
-      </c>
-      <c r="C47" t="s">
-        <v>309</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
-      </c>
-      <c r="D49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>241</v>
+      </c>
+      <c r="B50" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>242</v>
+      </c>
+      <c r="B51" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>243</v>
+      </c>
+      <c r="B52" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>213</v>
-      </c>
-      <c r="B50" t="s">
-        <v>153</v>
-      </c>
-      <c r="D50" t="s">
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>244</v>
+      </c>
+      <c r="B53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>214</v>
-      </c>
-      <c r="B51" t="s">
-        <v>153</v>
-      </c>
-      <c r="D51" t="s">
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>245</v>
+      </c>
+      <c r="B54" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>215</v>
-      </c>
-      <c r="B52" t="s">
-        <v>153</v>
-      </c>
-      <c r="C52" t="s">
-        <v>310</v>
-      </c>
-      <c r="D52" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>216</v>
-      </c>
-      <c r="B53" t="s">
-        <v>153</v>
-      </c>
-      <c r="C53" t="s">
-        <v>310</v>
-      </c>
-      <c r="D53" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>217</v>
-      </c>
-      <c r="B54" t="s">
-        <v>153</v>
-      </c>
-      <c r="C54" t="s">
-        <v>310</v>
-      </c>
-      <c r="D54" t="s">
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>246</v>
+      </c>
+      <c r="B55" t="s">
+        <v>155</v>
+      </c>
+      <c r="C55" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>218</v>
-      </c>
-      <c r="B55" t="s">
-        <v>153</v>
-      </c>
-      <c r="C55" t="s">
-        <v>311</v>
-      </c>
-      <c r="D55" t="s">
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>247</v>
+      </c>
+      <c r="B56" t="s">
+        <v>155</v>
+      </c>
+      <c r="C56" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B56" t="s">
-        <v>153</v>
-      </c>
-      <c r="C56" t="s">
-        <v>311</v>
-      </c>
-      <c r="D56" t="s">
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>248</v>
+      </c>
+      <c r="B57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C57" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>220</v>
-      </c>
-      <c r="B57" t="s">
-        <v>153</v>
-      </c>
-      <c r="C57" t="s">
-        <v>311</v>
-      </c>
-      <c r="D57" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
-      </c>
-      <c r="D58" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
-      </c>
-      <c r="D59" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
-      </c>
-      <c r="D60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s">
-        <v>153</v>
-      </c>
-      <c r="D61" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+        <v>155</v>
+      </c>
+      <c r="C61" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
-      </c>
-      <c r="D62" t="s">
+        <v>155</v>
+      </c>
+      <c r="C62" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="B63" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>312</v>
-      </c>
-      <c r="D63" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>312</v>
-      </c>
-      <c r="D64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C65" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s">
         <v>154</v>
+      </c>
+      <c r="C66" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s">
         <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="B68" t="s">
         <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="B69" t="s">
         <v>154</v>
       </c>
       <c r="C69" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="B70" t="s">
         <v>154</v>
+      </c>
+      <c r="C70" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="B71" t="s">
         <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="B72" t="s">
         <v>154</v>
       </c>
       <c r="C72" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="B73" t="s">
         <v>154</v>
       </c>
       <c r="C73" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="B74" t="s">
         <v>154</v>
       </c>
       <c r="C74" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="B75" t="s">
         <v>154</v>
       </c>
       <c r="C75" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="B76" t="s">
         <v>154</v>
       </c>
       <c r="C76" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="B77" t="s">
         <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="B78" t="s">
         <v>154</v>
       </c>
       <c r="C78" t="s">
-        <v>316</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="B79" t="s">
         <v>154</v>
       </c>
       <c r="C79" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="B80" t="s">
         <v>154</v>
       </c>
       <c r="C80" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C81" t="s">
-        <v>317</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
-      </c>
-      <c r="C82" t="s">
-        <v>317</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="B83" t="s">
-        <v>152</v>
-      </c>
-      <c r="C83" t="s">
-        <v>317</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
-      </c>
-      <c r="C84" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
-      </c>
-      <c r="C85" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
-      </c>
-      <c r="C86" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="B87" t="s">
-        <v>152</v>
-      </c>
-      <c r="C87" t="s">
-        <v>319</v>
+        <v>156</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
-      </c>
-      <c r="C88" t="s">
-        <v>319</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
-      </c>
-      <c r="C89" t="s">
-        <v>319</v>
+        <v>156</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
-      </c>
-      <c r="C90" t="s">
-        <v>320</v>
+        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
-      </c>
-      <c r="C91" t="s">
-        <v>321</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
-      </c>
-      <c r="C92" t="s">
-        <v>321</v>
+        <v>156</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
-      </c>
-      <c r="C93" t="s">
-        <v>321</v>
+        <v>156</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="B94" t="s">
-        <v>152</v>
-      </c>
-      <c r="C94" t="s">
-        <v>322</v>
+        <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="B95" t="s">
-        <v>152</v>
-      </c>
-      <c r="C95" t="s">
-        <v>322</v>
+        <v>156</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="B96" t="s">
-        <v>152</v>
-      </c>
-      <c r="C96" t="s">
-        <v>322</v>
+        <v>156</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="B97" t="s">
-        <v>153</v>
-      </c>
-      <c r="C97" t="s">
-        <v>323</v>
+        <v>156</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="B98" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C98" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="B99" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C99" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="B100" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C100" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="B101" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C101" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="B102" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C102" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="B103" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C103" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="B104" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C104" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C105" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="B106" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C106" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="B107" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C107" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="B108" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C108" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C109" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="B110" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C110" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C111" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="B112" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C112" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="B113" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C113" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="B114" t="s">
         <v>154</v>
       </c>
       <c r="C114" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="B115" t="s">
         <v>154</v>
       </c>
       <c r="C115" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="B116" t="s">
         <v>154</v>
       </c>
       <c r="C116" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="B117" t="s">
         <v>154</v>
       </c>
       <c r="C117" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="B118" t="s">
         <v>154</v>
       </c>
       <c r="C118" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="B119" t="s">
         <v>154</v>
       </c>
       <c r="C119" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="B120" t="s">
         <v>154</v>
       </c>
       <c r="C120" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="B121" t="s">
         <v>154</v>
+      </c>
+      <c r="C121" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="B122" t="s">
         <v>154</v>
@@ -4763,7 +4855,7 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="B123" t="s">
         <v>154</v>
@@ -4771,7 +4863,7 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="B124" t="s">
         <v>154</v>
@@ -4779,180 +4871,188 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="B125" t="s">
         <v>154</v>
-      </c>
-      <c r="C125" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="B126" t="s">
         <v>154</v>
       </c>
       <c r="C126" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="B127" t="s">
         <v>154</v>
       </c>
       <c r="C127" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="B128" t="s">
         <v>154</v>
+      </c>
+      <c r="C128" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="B129" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="B130" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="B131" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="B132" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="B133" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="B134" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="B135" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="B136" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="B137" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="B138" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="B140" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="B141" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
-      </c>
-      <c r="C142" t="s">
-        <v>332</v>
+        <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C143" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C144" t="s">
-        <v>332</v>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>336</v>
+      </c>
+      <c r="B145" t="s">
+        <v>156</v>
+      </c>
+      <c r="C145" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/APPT/data/output/Final_Production_Plan.xlsx
+++ b/APPT/data/output/Final_Production_Plan.xlsx
@@ -495,705 +495,705 @@
     <t>C</t>
   </si>
   <si>
-    <t>TK#_53_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_21_# [Wash 20m] + TK#_1_# [Wash 20m]</t>
+    <t>TK#_51_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_19_# [Wash 20m] + TK#_20_# [Wash 20m]</t>
   </si>
   <si>
     <t>HC Base Tank</t>
   </si>
   <si>
-    <t>TK#_18_# [Wash 20m] + TK#_12_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_14_# [Wash 20m] + TK#_16_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_17_# [Wash 20m] + TK#_15_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_19_# [Wash 20m] + TK#_20_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_1_# + TK#_13_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_18_# + TK#_12_#</t>
-  </si>
-  <si>
-    <t>TK#_26_# [Wash 20m] + TK#_3_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_17_# + TK#_15_#</t>
-  </si>
-  <si>
-    <t>TK#_13_# + TK#_1_#</t>
-  </si>
-  <si>
-    <t>TK#_15_# + TK#_13_#</t>
-  </si>
-  <si>
-    <t>TK#_1_# + TK#_18_#</t>
-  </si>
-  <si>
-    <t>TK#_53_#</t>
-  </si>
-  <si>
-    <t>TK#_26_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_13_# [Wash 20m]</t>
+    <t>TK#_13_# [Wash 20m] + TK#_12_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_11_# [Wash 20m] + TK#_10_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_14_# [Wash 20m] + TK#_6_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_4_# [Wash 20m] + TK#_3_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_20_# + TK#_1_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_13_# + TK#_12_#</t>
+  </si>
+  <si>
+    <t>TK#_28_# [Wash 20m] + TK#_7_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_14_# + TK#_6_#</t>
+  </si>
+  <si>
+    <t>TK#_1_# + TK#_20_#</t>
+  </si>
+  <si>
+    <t>TK#_6_# + TK#_1_#</t>
+  </si>
+  <si>
+    <t>TK#_20_# + TK#_13_#</t>
+  </si>
+  <si>
+    <t>TK#_51_#</t>
+  </si>
+  <si>
+    <t>TK#_28_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_1_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_27_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_19_# [Wash 20m]</t>
   </si>
   <si>
     <t>TK#_25_# [Wash 20m]</t>
   </si>
   <si>
-    <t>TK#_21_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_27_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_11_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_19_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_20_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_17_# [Wash 20m]</t>
+    <t>TK#_5_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_4_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_3_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_14_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_4_#</t>
+  </si>
+  <si>
+    <t>TK#_5_#</t>
+  </si>
+  <si>
+    <t>LOW: SLS</t>
+  </si>
+  <si>
+    <t>LOW: SLS | WARN: MAX CAP (12T) EXCEEDED</t>
+  </si>
+  <si>
+    <t>LOW: DM5500</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>1.25T</t>
+  </si>
+  <si>
+    <t>2026-01-13 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-13 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-13 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-14 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-14 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 09:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 09:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 10:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 10:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 11:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 11:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 12:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 12:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 13:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 13:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 14:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 20:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 20:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 21:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 21:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 22:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 22:30</t>
+  </si>
+  <si>
+    <t>2026-01-15 23:00</t>
+  </si>
+  <si>
+    <t>2026-01-15 23:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 00:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 00:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 01:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 01:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 02:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 02:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 03:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 03:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 04:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 04:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 05:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 05:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 06:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 06:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 07:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 07:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 08:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 08:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 09:00</t>
+  </si>
+  <si>
+    <t>CI400: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI401: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>WASHOUT</t>
+  </si>
+  <si>
+    <t>REP01-0114: HC BASE</t>
+  </si>
+  <si>
+    <t>CI404: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI405: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI406: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI407: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>REP02-0114: HC BASE</t>
+  </si>
+  <si>
+    <t>CI408: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI409: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI410: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI411: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI412: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI413: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI416: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI417: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI418: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>REP03-0114: HC BASE</t>
+  </si>
+  <si>
+    <t>CI420: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI421: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI423: PTN  Hair Fall Control</t>
+  </si>
+  <si>
+    <t>CI424: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI425: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI427: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI428: PTN  Hair Fall Control</t>
+  </si>
+  <si>
+    <t>CI402: PTN HFC Conditioner</t>
+  </si>
+  <si>
+    <t>COND WASH (60m)</t>
+  </si>
+  <si>
+    <t>CI403: H&amp;S Neem Libra</t>
+  </si>
+  <si>
+    <t>CI415: PTN HFC Conditioner</t>
+  </si>
+  <si>
+    <t>CI414: H&amp;S LF</t>
+  </si>
+  <si>
+    <t>CI429: PTN SS Conditioner</t>
+  </si>
+  <si>
+    <t>CI419: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>CI432: PTN HFC Conditioner</t>
+  </si>
+  <si>
+    <t>CI422: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI426: PTN Healthy Shine</t>
+  </si>
+  <si>
+    <t>CI430: PTN  Hair Fall Control</t>
+  </si>
+  <si>
+    <t>CI431: PTN Silky Smooth Shampoo</t>
+  </si>
+  <si>
+    <t>CI433: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI434: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>TK#_1_#</t>
+  </si>
+  <si>
+    <t>TK#_3_#</t>
+  </si>
+  <si>
+    <t>TK#_6_#</t>
+  </si>
+  <si>
+    <t>TK#_7_#</t>
+  </si>
+  <si>
+    <t>TK#_10_#</t>
+  </si>
+  <si>
+    <t>TK#_11_#</t>
+  </si>
+  <si>
+    <t>TK#_12_#</t>
+  </si>
+  <si>
+    <t>TK#_13_#</t>
+  </si>
+  <si>
+    <t>TK#_14_#</t>
   </si>
   <si>
     <t>TK#_19_#</t>
   </si>
   <si>
-    <t>TK#_11_#</t>
-  </si>
-  <si>
-    <t>LOW: SLS</t>
-  </si>
-  <si>
-    <t>LOW: SLS | WARN: MAX CAP (12T) EXCEEDED</t>
-  </si>
-  <si>
-    <t>LOW: DM5500</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>1.25T</t>
-  </si>
-  <si>
-    <t>2026-01-13 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-13 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-13 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-14 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-14 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 09:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 09:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 10:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 10:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 11:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 11:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 12:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 12:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 13:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 13:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 14:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 14:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 15:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 15:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 16:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 16:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 17:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 17:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 18:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 18:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 19:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 19:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 20:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 20:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 21:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 21:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 22:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 22:30</t>
-  </si>
-  <si>
-    <t>2026-01-15 23:00</t>
-  </si>
-  <si>
-    <t>2026-01-15 23:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 00:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 00:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 01:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 01:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 02:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 02:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 03:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 03:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 04:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 04:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 05:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 05:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 06:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 06:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 07:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 07:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 08:00</t>
-  </si>
-  <si>
-    <t>2026-01-16 08:30</t>
-  </si>
-  <si>
-    <t>2026-01-16 09:00</t>
-  </si>
-  <si>
-    <t>CI400: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI401: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>WASHOUT</t>
-  </si>
-  <si>
-    <t>REP01-0114: HC BASE</t>
-  </si>
-  <si>
-    <t>CI404: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI405: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI406: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI407: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>REP02-0114: HC BASE</t>
-  </si>
-  <si>
-    <t>CI408: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI409: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI410: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI411: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI412: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI413: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI416: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI417: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI418: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>REP03-0114: HC BASE</t>
-  </si>
-  <si>
-    <t>CI420: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI421: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI423: PTN  Hair Fall Control</t>
-  </si>
-  <si>
-    <t>CI424: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI425: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI427: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI428: PTN  Hair Fall Control</t>
-  </si>
-  <si>
-    <t>CI402: PTN HFC Conditioner</t>
-  </si>
-  <si>
-    <t>COND WASH (60m)</t>
-  </si>
-  <si>
-    <t>CI403: H&amp;S Neem Libra</t>
-  </si>
-  <si>
-    <t>CI415: PTN HFC Conditioner</t>
-  </si>
-  <si>
-    <t>CI414: H&amp;S LF</t>
-  </si>
-  <si>
-    <t>CI429: PTN SS Conditioner</t>
-  </si>
-  <si>
-    <t>CI419: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>CI432: PTN HFC Conditioner</t>
-  </si>
-  <si>
-    <t>CI422: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI426: PTN Healthy Shine</t>
-  </si>
-  <si>
-    <t>CI430: PTN  Hair Fall Control</t>
-  </si>
-  <si>
-    <t>CI431: PTN Silky Smooth Shampoo</t>
-  </si>
-  <si>
-    <t>CI433: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI434: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>TK#_1_#</t>
-  </si>
-  <si>
-    <t>TK#_3_#</t>
-  </si>
-  <si>
-    <t>TK#_12_#</t>
-  </si>
-  <si>
-    <t>TK#_13_#</t>
-  </si>
-  <si>
-    <t>TK#_14_#</t>
-  </si>
-  <si>
-    <t>TK#_15_#</t>
-  </si>
-  <si>
-    <t>TK#_16_#</t>
-  </si>
-  <si>
-    <t>TK#_17_#</t>
-  </si>
-  <si>
-    <t>TK#_18_#</t>
-  </si>
-  <si>
     <t>TK#_20_#</t>
   </si>
   <si>
-    <t>TK#_21_#</t>
-  </si>
-  <si>
     <t>TK#_25_#</t>
   </si>
   <si>
-    <t>TK#_26_#</t>
-  </si>
-  <si>
     <t>TK#_27_#</t>
   </si>
   <si>
+    <t>TK#_28_#</t>
+  </si>
+  <si>
     <t>2026-01-16 09:30</t>
   </si>
   <si>
@@ -1356,70 +1356,70 @@
     <t>2026-01-17 12:00</t>
   </si>
   <si>
+    <t>WASHOUT (20m) | CI403: H&amp;S Neem Libra</t>
+  </si>
+  <si>
+    <t>CI408: H&amp;S Daily Clean Libra | CI403: H&amp;S Neem Libra</t>
+  </si>
+  <si>
+    <t>CI408: H&amp;S Daily Clean Libra | CI417: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI417: H&amp;S Daily Clean Libra | CI420: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI420: H&amp;S Daily Clean Libra | CI424: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI407: H&amp;S Daily Cool Libra | CI416: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI416: H&amp;S Daily Smooth Libra | WASHOUT (20m)</t>
+  </si>
+  <si>
+    <t>CI416: H&amp;S Daily Smooth Libra | CI426: PTN Healthy Shine</t>
+  </si>
+  <si>
+    <t>CI416: H&amp;S Daily Smooth Libra | CI422: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI422: H&amp;S AHF | CI433: H&amp;S AHF</t>
+  </si>
+  <si>
     <t>WASHOUT (20m)</t>
   </si>
   <si>
+    <t>CI406: H&amp;S Daily Clean Libra | CI412: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI421: H&amp;S Daily Clean Libra | CI424: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI405: H&amp;S Daily Cool Libra | WASHOUT (20m)</t>
+  </si>
+  <si>
+    <t>CI405: H&amp;S Daily Cool Libra | CI409: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI404: H&amp;S Daily Clean Libra | CI410: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI425: H&amp;S Daily Clean Libra | CI427: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI421: H&amp;S Daily Clean Libra | CI431: PTN Silky Smooth Shampoo</t>
+  </si>
+  <si>
+    <t>CI401: H&amp;S Daily Clean Libra | WASHOUT (20m)</t>
+  </si>
+  <si>
+    <t>CI401: H&amp;S Daily Clean Libra | CI414: H&amp;S LF</t>
+  </si>
+  <si>
     <t>CI401: H&amp;S Daily Clean Libra | CI408: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
-    <t>CI408: H&amp;S Daily Clean Libra | CI417: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI417: H&amp;S Daily Clean Libra | CI420: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
     <t>CI420: H&amp;S Daily Clean Libra | CI425: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI425: H&amp;S Daily Clean Libra | CI427: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI404: H&amp;S Daily Clean Libra | CI410: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>WASHOUT (20m) | CI403: H&amp;S Neem Libra</t>
-  </si>
-  <si>
-    <t>CI408: H&amp;S Daily Clean Libra | CI403: H&amp;S Neem Libra</t>
-  </si>
-  <si>
-    <t>CI420: H&amp;S Daily Clean Libra | CI424: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI405: H&amp;S Daily Cool Libra | WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI405: H&amp;S Daily Cool Libra | CI409: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI406: H&amp;S Daily Clean Libra | CI412: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI421: H&amp;S Daily Clean Libra | CI424: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI421: H&amp;S Daily Clean Libra | CI431: PTN Silky Smooth Shampoo</t>
-  </si>
-  <si>
-    <t>CI407: H&amp;S Daily Cool Libra | CI416: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI416: H&amp;S Daily Smooth Libra | CI422: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI422: H&amp;S AHF | CI433: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI416: H&amp;S Daily Smooth Libra | WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI416: H&amp;S Daily Smooth Libra | CI426: PTN Healthy Shine</t>
-  </si>
-  <si>
-    <t>CI401: H&amp;S Daily Clean Libra | WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI401: H&amp;S Daily Clean Libra | CI414: H&amp;S LF</t>
   </si>
   <si>
     <t>CI415: PTN HFC Conditioner | WASHOUT (20m)</t>
@@ -5754,31 +5754,31 @@
         <v>379</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>387</v>
@@ -5814,7 +5814,7 @@
       <c r="B3" t="s">
         <v>156</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
       <c r="B4" t="s">
         <v>156</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="B5" t="s">
         <v>156</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       <c r="B6" t="s">
         <v>156</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="R6" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       <c r="B7" t="s">
         <v>156</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="R7" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5869,10 +5869,10 @@
       <c r="B8" t="s">
         <v>156</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5883,10 +5883,10 @@
       <c r="B9" t="s">
         <v>156</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="R9" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5897,10 +5897,10 @@
       <c r="B10" t="s">
         <v>156</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5911,10 +5911,10 @@
       <c r="B11" t="s">
         <v>156</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q11" s="3" t="s">
+      <c r="R11" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5925,10 +5925,10 @@
       <c r="B12" t="s">
         <v>156</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="R12" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5939,10 +5939,10 @@
       <c r="B13" t="s">
         <v>156</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q13" s="3" t="s">
+      <c r="R13" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5953,14 +5953,14 @@
       <c r="B14" t="s">
         <v>156</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -5970,10 +5970,10 @@
       <c r="B15" t="s">
         <v>157</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S15" s="3" t="s">
@@ -5987,10 +5987,10 @@
       <c r="B16" t="s">
         <v>157</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="Q16" s="3" t="s">
+      <c r="R16" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S16" s="3" t="s">
@@ -6005,15 +6005,15 @@
         <v>157</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="G17" s="3" t="s">
         <v>366</v>
       </c>
+      <c r="N17" s="3" t="s">
+        <v>456</v>
+      </c>
       <c r="O17" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q17" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S17" s="3" t="s">
@@ -6028,15 +6028,15 @@
         <v>157</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q18" s="3" t="s">
+      <c r="R18" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S18" s="3" t="s">
@@ -6051,15 +6051,15 @@
         <v>157</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q19" s="3" t="s">
+      <c r="R19" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S19" s="3" t="s">
@@ -6074,15 +6074,15 @@
         <v>157</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q20" s="3" t="s">
+      <c r="R20" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S20" s="3" t="s">
@@ -6097,15 +6097,15 @@
         <v>157</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S21" s="3" t="s">
@@ -6120,15 +6120,15 @@
         <v>157</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S22" s="3" t="s">
@@ -6143,15 +6143,15 @@
         <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q23" s="3" t="s">
+      <c r="R23" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S23" s="3" t="s">
@@ -6166,15 +6166,15 @@
         <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="R24" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S24" s="3" t="s">
@@ -6189,21 +6189,21 @@
         <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F25" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="N25" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O25" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q25" s="3" t="s">
+      <c r="R25" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S25" s="3" t="s">
@@ -6218,21 +6218,21 @@
         <v>157</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F26" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="N26" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O26" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q26" s="3" t="s">
+      <c r="R26" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S26" s="3" t="s">
@@ -6247,21 +6247,21 @@
         <v>157</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F27" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="N27" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O27" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q27" s="3" t="s">
+      <c r="R27" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S27" s="3" t="s">
@@ -6276,30 +6276,30 @@
         <v>157</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G28" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>343</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>343</v>
       </c>
+      <c r="K28" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="L28" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="N28" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O28" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P28" s="3" t="s">
+      <c r="Q28" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q28" s="3" t="s">
+      <c r="R28" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S28" s="3" t="s">
@@ -6314,30 +6314,30 @@
         <v>157</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G29" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>343</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>343</v>
       </c>
+      <c r="K29" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="L29" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="N29" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O29" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="Q29" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S29" s="3" t="s">
@@ -6352,30 +6352,30 @@
         <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G30" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>343</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>343</v>
       </c>
+      <c r="K30" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="L30" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="N30" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O30" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P30" s="3" t="s">
+      <c r="Q30" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q30" s="3" t="s">
+      <c r="R30" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S30" s="3" t="s">
@@ -6390,36 +6390,36 @@
         <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H31" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M31" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O31" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P31" s="3" t="s">
+      <c r="Q31" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q31" s="3" t="s">
+      <c r="R31" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S31" s="3" t="s">
@@ -6434,36 +6434,36 @@
         <v>158</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H32" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M32" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O32" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P32" s="3" t="s">
+      <c r="Q32" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q32" s="3" t="s">
+      <c r="R32" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S32" s="3" t="s">
@@ -6478,36 +6478,36 @@
         <v>158</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H33" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M33" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O33" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P33" s="3" t="s">
+      <c r="Q33" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q33" s="3" t="s">
+      <c r="R33" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S33" s="3" t="s">
@@ -6522,36 +6522,36 @@
         <v>158</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H34" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M34" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O34" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P34" s="3" t="s">
+      <c r="Q34" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q34" s="3" t="s">
+      <c r="R34" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S34" s="3" t="s">
@@ -6566,36 +6566,36 @@
         <v>158</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H35" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M35" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O35" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P35" s="3" t="s">
+      <c r="Q35" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q35" s="3" t="s">
+      <c r="R35" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S35" s="3" t="s">
@@ -6610,36 +6610,36 @@
         <v>158</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H36" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M36" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O36" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P36" s="3" t="s">
+      <c r="Q36" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q36" s="3" t="s">
+      <c r="R36" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S36" s="3" t="s">
@@ -6654,36 +6654,36 @@
         <v>158</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H37" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M37" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O37" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P37" s="3" t="s">
+      <c r="Q37" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q37" s="3" t="s">
+      <c r="R37" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S37" s="3" t="s">
@@ -6698,36 +6698,36 @@
         <v>158</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H38" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M38" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O38" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P38" s="3" t="s">
+      <c r="Q38" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q38" s="3" t="s">
+      <c r="R38" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S38" s="3" t="s">
@@ -6742,36 +6742,36 @@
         <v>158</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H39" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M39" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O39" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P39" s="3" t="s">
+      <c r="Q39" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q39" s="3" t="s">
+      <c r="R39" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S39" s="3" t="s">
@@ -6786,36 +6786,36 @@
         <v>158</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H40" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M40" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O40" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P40" s="3" t="s">
+      <c r="Q40" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q40" s="3" t="s">
+      <c r="R40" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S40" s="3" t="s">
@@ -6830,36 +6830,36 @@
         <v>158</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H41" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M41" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O41" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P41" s="3" t="s">
+      <c r="Q41" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q41" s="3" t="s">
+      <c r="R41" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S41" s="3" t="s">
@@ -6874,36 +6874,36 @@
         <v>158</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H42" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M42" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O42" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P42" s="3" t="s">
+      <c r="Q42" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="R42" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S42" s="3" t="s">
@@ -6918,36 +6918,36 @@
         <v>158</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H43" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M43" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O43" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P43" s="3" t="s">
+      <c r="Q43" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q43" s="3" t="s">
+      <c r="R43" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S43" s="3" t="s">
@@ -6962,36 +6962,36 @@
         <v>158</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H44" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M44" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O44" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P44" s="3" t="s">
+      <c r="Q44" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q44" s="3" t="s">
+      <c r="R44" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S44" s="3" t="s">
@@ -7006,36 +7006,36 @@
         <v>158</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H45" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M45" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O45" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P45" s="3" t="s">
+      <c r="Q45" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q45" s="3" t="s">
+      <c r="R45" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S45" s="3" t="s">
@@ -7050,36 +7050,36 @@
         <v>158</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H46" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M46" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O46" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P46" s="3" t="s">
+      <c r="Q46" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q46" s="3" t="s">
+      <c r="R46" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S46" s="3" t="s">
@@ -7094,36 +7094,36 @@
         <v>156</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H47" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M47" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O47" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q47" s="3" t="s">
+      <c r="R47" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S47" s="3" t="s">
@@ -7138,36 +7138,36 @@
         <v>156</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H48" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M48" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O48" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P48" s="3" t="s">
+      <c r="Q48" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q48" s="3" t="s">
+      <c r="R48" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S48" s="3" t="s">
@@ -7182,36 +7182,36 @@
         <v>156</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H49" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>342</v>
       </c>
+      <c r="M49" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="O49" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P49" s="3" t="s">
+      <c r="Q49" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q49" s="3" t="s">
+      <c r="R49" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S49" s="3" t="s">
@@ -7226,42 +7226,42 @@
         <v>156</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H50" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P50" s="3" t="s">
+      <c r="Q50" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q50" s="3" t="s">
+      <c r="R50" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S50" s="3" t="s">
@@ -7276,42 +7276,42 @@
         <v>156</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H51" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>345</v>
+        <v>464</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="P51" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q51" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q51" s="3" t="s">
+      <c r="R51" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S51" s="3" t="s">
@@ -7326,42 +7326,42 @@
         <v>156</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H52" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P52" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q52" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q52" s="3" t="s">
+      <c r="R52" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S52" s="3" t="s">
@@ -7376,42 +7376,42 @@
         <v>156</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H53" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P53" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q53" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q53" s="3" t="s">
+      <c r="R53" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S53" s="3" t="s">
@@ -7426,42 +7426,42 @@
         <v>156</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H54" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P54" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q54" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q54" s="3" t="s">
+      <c r="R54" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S54" s="3" t="s">
@@ -7476,42 +7476,42 @@
         <v>156</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H55" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P55" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q55" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q55" s="3" t="s">
+      <c r="R55" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S55" s="3" t="s">
@@ -7526,42 +7526,42 @@
         <v>156</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H56" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P56" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q56" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q56" s="3" t="s">
+      <c r="R56" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S56" s="3" t="s">
@@ -7576,42 +7576,42 @@
         <v>156</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>342</v>
+        <v>446</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="H57" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P57" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q57" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q57" s="3" t="s">
+      <c r="R57" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S57" s="3" t="s">
@@ -7628,40 +7628,40 @@
       <c r="C58" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>342</v>
+      <c r="D58" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="H58" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>345</v>
+        <v>465</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="P58" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q58" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q58" s="3" t="s">
+      <c r="R58" s="3" t="s">
         <v>364</v>
       </c>
       <c r="S58" s="3" t="s">
@@ -7676,42 +7676,42 @@
         <v>156</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>342</v>
+        <v>447</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="H59" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>343</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P59" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q59" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q59" s="3" t="s">
+      <c r="R59" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -7725,40 +7725,40 @@
       <c r="C60" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="D60" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P60" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q60" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q60" s="3" t="s">
+      <c r="R60" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -7772,40 +7772,40 @@
       <c r="C61" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="D61" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P61" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q61" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q61" s="3" t="s">
+      <c r="R61" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -7819,40 +7819,40 @@
       <c r="C62" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="D62" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P62" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q62" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q62" s="3" t="s">
+      <c r="R62" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -7866,40 +7866,40 @@
       <c r="C63" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="D63" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>342</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P63" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q63" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q63" s="3" t="s">
+      <c r="R63" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -7913,40 +7913,40 @@
       <c r="C64" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>452</v>
+      <c r="D64" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G64" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O64" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P64" s="3" t="s">
+      <c r="Q64" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q64" s="3" t="s">
+      <c r="R64" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -7960,40 +7960,40 @@
       <c r="C65" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>452</v>
+      <c r="D65" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G65" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O65" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P65" s="3" t="s">
+      <c r="Q65" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q65" s="3" t="s">
+      <c r="R65" s="3" t="s">
         <v>364</v>
       </c>
     </row>
@@ -8008,42 +8008,42 @@
         <v>347</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>452</v>
+        <v>345</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="G66" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O66" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q66" s="3" t="s">
+      <c r="R66" s="3" t="s">
         <v>470</v>
       </c>
     </row>
@@ -8058,42 +8058,42 @@
         <v>347</v>
       </c>
       <c r="D67" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="H67" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="G67" s="3" t="s">
+      <c r="I67" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O67" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P67" s="3" t="s">
+      <c r="Q67" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q67" s="3" t="s">
+      <c r="R67" s="3" t="s">
         <v>471</v>
       </c>
     </row>
@@ -8108,42 +8108,42 @@
         <v>347</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="I68" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P68" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q68" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q68" s="3" t="s">
+      <c r="R68" s="3" t="s">
         <v>471</v>
       </c>
     </row>
@@ -8158,42 +8158,42 @@
         <v>347</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="I69" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P69" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q69" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q69" s="3" t="s">
+      <c r="R69" s="3" t="s">
         <v>471</v>
       </c>
     </row>
@@ -8208,42 +8208,42 @@
         <v>347</v>
       </c>
       <c r="D70" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H70" s="3" t="s">
+      <c r="I70" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P70" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q70" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q70" s="3" t="s">
+      <c r="R70" s="3" t="s">
         <v>471</v>
       </c>
     </row>
@@ -8258,42 +8258,42 @@
         <v>347</v>
       </c>
       <c r="D71" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H71" s="3" t="s">
+      <c r="I71" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P71" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q71" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q71" s="3" t="s">
+      <c r="R71" s="3" t="s">
         <v>471</v>
       </c>
     </row>
@@ -8308,46 +8308,46 @@
         <v>347</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P72" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q72" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q72" s="3" t="s">
+      <c r="R72" s="3" t="s">
         <v>471</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -8361,42 +8361,42 @@
         <v>347</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H73" s="3" t="s">
+      <c r="I73" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P73" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q73" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q73" s="3" t="s">
+      <c r="R73" s="3" t="s">
         <v>471</v>
       </c>
       <c r="S73" s="3" t="s">
@@ -8414,42 +8414,42 @@
         <v>347</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H74" s="3" t="s">
+      <c r="I74" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P74" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q74" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q74" s="3" t="s">
+      <c r="R74" s="3" t="s">
         <v>471</v>
       </c>
       <c r="S74" s="3" t="s">
@@ -8467,42 +8467,42 @@
         <v>347</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H75" s="3" t="s">
+      <c r="I75" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>345</v>
+        <v>457</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P75" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q75" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q75" s="3" t="s">
+      <c r="R75" s="3" t="s">
         <v>471</v>
       </c>
       <c r="S75" s="3" t="s">
@@ -8520,46 +8520,46 @@
         <v>347</v>
       </c>
       <c r="D76" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>461</v>
+        <v>368</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="P76" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q76" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q76" s="3" t="s">
+      <c r="R76" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>352</v>
@@ -8576,46 +8576,46 @@
         <v>347</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H77" s="3" t="s">
+      <c r="I77" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>461</v>
+        <v>368</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="P77" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q77" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q77" s="3" t="s">
+      <c r="R77" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R77" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>352</v>
@@ -8632,46 +8632,46 @@
         <v>347</v>
       </c>
       <c r="D78" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="I78" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>461</v>
+        <v>368</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="P78" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q78" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q78" s="3" t="s">
+      <c r="R78" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R78" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>352</v>
@@ -8688,46 +8688,46 @@
         <v>448</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H79" s="3" t="s">
+      <c r="I79" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>461</v>
+        <v>368</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="P79" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q79" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q79" s="3" t="s">
+      <c r="R79" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R79" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S79" s="3" t="s">
         <v>352</v>
@@ -8744,46 +8744,46 @@
         <v>448</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H80" s="3" t="s">
+      <c r="I80" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>461</v>
+        <v>368</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="P80" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q80" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q80" s="3" t="s">
+      <c r="R80" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R80" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S80" s="3" t="s">
         <v>352</v>
@@ -8800,49 +8800,49 @@
         <v>448</v>
       </c>
       <c r="D81" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H81" s="3" t="s">
+      <c r="I81" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>461</v>
+        <v>368</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="P81" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q81" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q81" s="3" t="s">
+      <c r="R81" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>352</v>
@@ -8859,49 +8859,49 @@
         <v>448</v>
       </c>
       <c r="D82" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H82" s="3" t="s">
+      <c r="I82" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="P82" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q82" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q82" s="3" t="s">
+      <c r="R82" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R82" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S82" s="3" t="s">
         <v>352</v>
@@ -8918,49 +8918,49 @@
         <v>448</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H83" s="3" t="s">
+      <c r="I83" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="P83" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q83" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q83" s="3" t="s">
+      <c r="R83" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>352</v>
@@ -8977,49 +8977,49 @@
         <v>448</v>
       </c>
       <c r="D84" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H84" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="H84" s="3" t="s">
+      <c r="I84" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L84" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="P84" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q84" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q84" s="3" t="s">
+      <c r="R84" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R84" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S84" s="3" t="s">
         <v>352</v>
@@ -9036,49 +9036,49 @@
         <v>354</v>
       </c>
       <c r="D85" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E85" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H85" s="3" t="s">
+      <c r="I85" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P85" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q85" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q85" s="3" t="s">
+      <c r="R85" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R85" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S85" s="3" t="s">
         <v>352</v>
@@ -9095,49 +9095,49 @@
         <v>354</v>
       </c>
       <c r="D86" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H86" s="3" t="s">
+      <c r="I86" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P86" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q86" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q86" s="3" t="s">
+      <c r="R86" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R86" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S86" s="3" t="s">
         <v>352</v>
@@ -9154,49 +9154,49 @@
         <v>354</v>
       </c>
       <c r="D87" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H87" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H87" s="3" t="s">
+      <c r="I87" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P87" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q87" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q87" s="3" t="s">
+      <c r="R87" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R87" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S87" s="3" t="s">
         <v>352</v>
@@ -9213,49 +9213,49 @@
         <v>354</v>
       </c>
       <c r="D88" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H88" s="3" t="s">
+      <c r="I88" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L88" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P88" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q88" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q88" s="3" t="s">
+      <c r="R88" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R88" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S88" s="3" t="s">
         <v>352</v>
@@ -9272,49 +9272,49 @@
         <v>354</v>
       </c>
       <c r="D89" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H89" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H89" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P89" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q89" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q89" s="3" t="s">
+      <c r="R89" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>352</v>
@@ -9331,49 +9331,49 @@
         <v>354</v>
       </c>
       <c r="D90" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H90" s="3" t="s">
+      <c r="I90" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P90" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q90" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q90" s="3" t="s">
+      <c r="R90" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R90" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S90" s="3" t="s">
         <v>352</v>
@@ -9390,49 +9390,49 @@
         <v>354</v>
       </c>
       <c r="D91" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H91" s="3" t="s">
+      <c r="I91" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>348</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P91" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q91" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q91" s="3" t="s">
+      <c r="R91" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>352</v>
@@ -9449,43 +9449,43 @@
         <v>354</v>
       </c>
       <c r="D92" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F92" s="3" t="s">
+      <c r="K92" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="L92" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P92" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q92" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q92" s="3" t="s">
+      <c r="R92" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R92" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S92" s="3" t="s">
         <v>352</v>
@@ -9502,43 +9502,43 @@
         <v>354</v>
       </c>
       <c r="D93" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F93" s="3" t="s">
+      <c r="K93" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="P93" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q93" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q93" s="3" t="s">
+      <c r="R93" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R93" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S93" s="3" t="s">
         <v>352</v>
@@ -9555,37 +9555,37 @@
         <v>354</v>
       </c>
       <c r="D94" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G94" s="3" t="s">
+      <c r="M94" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O94" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P94" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q94" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q94" s="3" t="s">
+      <c r="R94" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>352</v>
@@ -9602,37 +9602,37 @@
         <v>354</v>
       </c>
       <c r="D95" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G95" s="3" t="s">
+      <c r="M95" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O95" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I95" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N95" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O95" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P95" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q95" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q95" s="3" t="s">
+      <c r="R95" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R95" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S95" s="3" t="s">
         <v>352</v>
@@ -9649,37 +9649,37 @@
         <v>354</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G96" s="3" t="s">
+      <c r="M96" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O96" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P96" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q96" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q96" s="3" t="s">
+      <c r="R96" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R96" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S96" s="3" t="s">
         <v>352</v>
@@ -9696,37 +9696,37 @@
         <v>354</v>
       </c>
       <c r="D97" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G97" s="3" t="s">
+      <c r="M97" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O97" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I97" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N97" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O97" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P97" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q97" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q97" s="3" t="s">
+      <c r="R97" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R97" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S97" s="3" t="s">
         <v>352</v>
@@ -9743,37 +9743,37 @@
         <v>354</v>
       </c>
       <c r="D98" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G98" s="3" t="s">
+      <c r="M98" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I98" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K98" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N98" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O98" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P98" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q98" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q98" s="3" t="s">
+      <c r="R98" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="R98" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S98" s="3" t="s">
         <v>474</v>
@@ -9790,37 +9790,37 @@
         <v>354</v>
       </c>
       <c r="D99" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H99" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G99" s="3" t="s">
+      <c r="M99" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O99" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I99" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N99" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O99" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P99" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q99" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q99" s="3" t="s">
+      <c r="R99" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="R99" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S99" s="3" t="s">
         <v>475</v>
@@ -9837,37 +9837,37 @@
         <v>354</v>
       </c>
       <c r="D100" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G100" s="3" t="s">
+      <c r="M100" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O100" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P100" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q100" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q100" s="3" t="s">
+      <c r="R100" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>475</v>
@@ -9884,37 +9884,37 @@
         <v>354</v>
       </c>
       <c r="D101" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G101" s="3" t="s">
+      <c r="M101" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O101" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P101" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q101" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q101" s="3" t="s">
+      <c r="R101" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>475</v>
@@ -9931,37 +9931,37 @@
         <v>354</v>
       </c>
       <c r="D102" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H102" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G102" s="3" t="s">
+      <c r="M102" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="R102" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>475</v>
@@ -9977,29 +9977,29 @@
       <c r="C103" s="3" t="s">
         <v>354</v>
       </c>
+      <c r="D103" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="E103" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F103" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="N103" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O103" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="M103" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O103" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P103" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q103" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q103" s="3" t="s">
+      <c r="R103" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R103" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S103" s="3" t="s">
         <v>475</v>
@@ -10015,29 +10015,29 @@
       <c r="C104" s="3" t="s">
         <v>354</v>
       </c>
+      <c r="D104" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="E104" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F104" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="N104" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O104" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="M104" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N104" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="O104" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="P104" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q104" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q104" s="3" t="s">
+      <c r="R104" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R104" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S104" s="3" t="s">
         <v>475</v>
@@ -10053,26 +10053,26 @@
       <c r="C105" s="3" t="s">
         <v>354</v>
       </c>
+      <c r="D105" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="E105" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F105" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="O105" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="M105" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>353</v>
-      </c>
       <c r="P105" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q105" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q105" s="3" t="s">
+      <c r="R105" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R105" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S105" s="3" t="s">
         <v>475</v>
@@ -10088,26 +10088,26 @@
       <c r="C106" s="3" t="s">
         <v>449</v>
       </c>
+      <c r="D106" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="E106" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F106" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="O106" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="M106" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N106" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="P106" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q106" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q106" s="3" t="s">
+      <c r="R106" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R106" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S106" s="3" t="s">
         <v>475</v>
@@ -10123,26 +10123,26 @@
       <c r="C107" s="3" t="s">
         <v>449</v>
       </c>
+      <c r="D107" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="E107" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F107" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="O107" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="M107" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N107" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="P107" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q107" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q107" s="3" t="s">
+      <c r="R107" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R107" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S107" s="3" t="s">
         <v>475</v>
@@ -10158,26 +10158,26 @@
       <c r="C108" s="3" t="s">
         <v>449</v>
       </c>
+      <c r="D108" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="E108" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="O108" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="M108" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N108" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="P108" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q108" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q108" s="3" t="s">
+      <c r="R108" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R108" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S108" s="3" t="s">
         <v>475</v>
@@ -10193,32 +10193,32 @@
       <c r="C109" s="3" t="s">
         <v>449</v>
       </c>
+      <c r="D109" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="E109" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F109" s="3" t="s">
         <v>370</v>
       </c>
       <c r="G109" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="O109" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="I109" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K109" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N109" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="P109" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q109" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="Q109" s="3" t="s">
+      <c r="R109" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R109" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S109" s="3" t="s">
         <v>475</v>
@@ -10234,32 +10234,32 @@
       <c r="C110" s="3" t="s">
         <v>449</v>
       </c>
+      <c r="D110" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="E110" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F110" s="3" t="s">
         <v>370</v>
       </c>
       <c r="G110" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="O110" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="I110" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="P110" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q110" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="Q110" s="3" t="s">
+      <c r="R110" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R110" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S110" s="3" t="s">
         <v>475</v>
@@ -10275,32 +10275,32 @@
       <c r="C111" s="3" t="s">
         <v>449</v>
       </c>
+      <c r="D111" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="E111" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>370</v>
       </c>
       <c r="G111" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M111" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="O111" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="I111" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K111" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M111" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="P111" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q111" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q111" s="3" t="s">
+      <c r="R111" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R111" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S111" s="3" t="s">
         <v>352</v>
@@ -10316,32 +10316,32 @@
       <c r="C112" s="3" t="s">
         <v>357</v>
       </c>
+      <c r="D112" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="E112" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>370</v>
       </c>
       <c r="G112" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M112" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="O112" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="I112" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M112" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N112" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="P112" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q112" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q112" s="3" t="s">
+      <c r="R112" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R112" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S112" s="3" t="s">
         <v>352</v>
@@ -10357,32 +10357,32 @@
       <c r="C113" s="3" t="s">
         <v>357</v>
       </c>
+      <c r="D113" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E113" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F113" s="3" t="s">
         <v>370</v>
       </c>
       <c r="G113" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="O113" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="I113" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="M113" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="N113" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P113" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q113" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q113" s="3" t="s">
+      <c r="R113" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R113" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S113" s="3" t="s">
         <v>476</v>
@@ -10398,29 +10398,29 @@
       <c r="C114" s="3" t="s">
         <v>357</v>
       </c>
+      <c r="D114" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="G114" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="O114" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="I114" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K114" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="M114" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="N114" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P114" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q114" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q114" s="3" t="s">
+      <c r="R114" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R114" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S114" s="3" t="s">
         <v>476</v>
@@ -10436,29 +10436,29 @@
       <c r="C115" s="3" t="s">
         <v>357</v>
       </c>
+      <c r="D115" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="G115" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="O115" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="I115" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K115" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="M115" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="N115" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P115" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q115" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q115" s="3" t="s">
+      <c r="R115" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R115" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S115" s="3" t="s">
         <v>476</v>
@@ -10472,31 +10472,31 @@
         <v>157</v>
       </c>
       <c r="C116" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="M116" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="O116" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K116" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="M116" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="N116" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P116" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q116" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q116" s="3" t="s">
+      <c r="R116" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R116" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S116" s="3" t="s">
         <v>476</v>
@@ -10510,31 +10510,31 @@
         <v>157</v>
       </c>
       <c r="C117" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="M117" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="O117" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K117" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="M117" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="N117" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P117" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q117" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q117" s="3" t="s">
+      <c r="R117" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R117" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S117" s="3" t="s">
         <v>359</v>
@@ -10548,31 +10548,31 @@
         <v>157</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>357</v>
+        <v>450</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>455</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K118" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="N118" s="3" t="s">
-        <v>373</v>
+      <c r="O118" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="P118" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q118" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q118" s="3" t="s">
+      <c r="R118" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R118" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S118" s="3" t="s">
         <v>359</v>
@@ -10588,14 +10588,14 @@
       <c r="C119" s="3" t="s">
         <v>450</v>
       </c>
+      <c r="D119" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>455</v>
+      </c>
       <c r="G119" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K119" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L119" s="3" t="s">
         <v>361</v>
@@ -10603,17 +10603,17 @@
       <c r="M119" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="N119" s="3" t="s">
-        <v>373</v>
+      <c r="O119" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="P119" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q119" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q119" s="3" t="s">
+      <c r="R119" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R119" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S119" s="3" t="s">
         <v>359</v>
@@ -10629,32 +10629,32 @@
       <c r="C120" s="3" t="s">
         <v>450</v>
       </c>
+      <c r="D120" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>376</v>
+      </c>
       <c r="G120" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K120" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L120" s="3" t="s">
         <v>361</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N120" s="3" t="s">
-        <v>373</v>
+        <v>463</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="P120" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q120" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q120" s="3" t="s">
+      <c r="R120" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R120" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S120" s="3" t="s">
         <v>359</v>
@@ -10668,34 +10668,34 @@
         <v>157</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>376</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K121" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L121" s="3" t="s">
         <v>361</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N121" s="3" t="s">
-        <v>373</v>
+        <v>463</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="P121" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q121" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q121" s="3" t="s">
+      <c r="R121" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R121" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S121" s="3" t="s">
         <v>359</v>
@@ -10709,37 +10709,37 @@
         <v>157</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E122" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F122" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K122" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L122" s="3" t="s">
         <v>361</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N122" s="3" t="s">
-        <v>373</v>
+        <v>463</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="P122" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q122" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q122" s="3" t="s">
+      <c r="R122" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R122" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S122" s="3" t="s">
         <v>359</v>
@@ -10753,37 +10753,37 @@
         <v>157</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E123" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I123" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K123" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="L123" s="3" t="s">
         <v>361</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N123" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O123" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="P123" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q123" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q123" s="3" t="s">
+      <c r="R123" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R123" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S123" s="3" t="s">
         <v>359</v>
@@ -10797,37 +10797,37 @@
         <v>157</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E124" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I124" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K124" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="L124" s="3" t="s">
         <v>361</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N124" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="P124" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q124" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q124" s="3" t="s">
+      <c r="R124" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R124" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S124" s="3" t="s">
         <v>359</v>
@@ -10841,37 +10841,37 @@
         <v>157</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E125" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F125" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I125" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K125" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="L125" s="3" t="s">
         <v>361</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N125" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O125" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="P125" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q125" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q125" s="3" t="s">
+      <c r="R125" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R125" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S125" s="3" t="s">
         <v>359</v>
@@ -10885,37 +10885,37 @@
         <v>157</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>451</v>
+        <v>360</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E126" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F126" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I126" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K126" s="3" t="s">
+      <c r="L126" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M126" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L126" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M126" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N126" s="3" t="s">
-        <v>373</v>
+      <c r="O126" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="P126" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q126" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q126" s="3" t="s">
+      <c r="R126" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R126" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -10926,37 +10926,37 @@
         <v>158</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>451</v>
+        <v>360</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E127" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F127" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I127" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K127" s="3" t="s">
+      <c r="L127" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M127" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L127" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M127" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N127" s="3" t="s">
-        <v>373</v>
+      <c r="O127" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="P127" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q127" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q127" s="3" t="s">
+      <c r="R127" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R127" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -10967,37 +10967,37 @@
         <v>158</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>451</v>
+        <v>360</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E128" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I128" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K128" s="3" t="s">
+      <c r="L128" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M128" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L128" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M128" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N128" s="3" t="s">
-        <v>373</v>
+      <c r="O128" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="P128" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q128" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q128" s="3" t="s">
+      <c r="R128" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R128" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -11008,37 +11008,37 @@
         <v>158</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>451</v>
+        <v>360</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E129" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F129" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="I129" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="K129" s="3" t="s">
+      <c r="L129" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M129" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L129" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M129" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N129" s="3" t="s">
-        <v>373</v>
+      <c r="O129" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="P129" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q129" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q129" s="3" t="s">
+      <c r="R129" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R129" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -11048,32 +11048,32 @@
       <c r="B130" t="s">
         <v>158</v>
       </c>
-      <c r="C130" s="3" t="s">
-        <v>451</v>
+      <c r="D130" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E130" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F130" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K130" s="3" t="s">
+      <c r="L130" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M130" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L130" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M130" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N130" s="3" t="s">
-        <v>373</v>
+      <c r="O130" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="P130" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q130" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q130" s="3" t="s">
+      <c r="R130" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R130" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -11083,32 +11083,32 @@
       <c r="B131" t="s">
         <v>158</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>451</v>
+      <c r="D131" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E131" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F131" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K131" s="3" t="s">
+      <c r="L131" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M131" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L131" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M131" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N131" s="3" t="s">
-        <v>373</v>
+      <c r="O131" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="P131" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q131" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q131" s="3" t="s">
+      <c r="R131" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R131" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -11118,32 +11118,32 @@
       <c r="B132" t="s">
         <v>158</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>451</v>
+      <c r="D132" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E132" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F132" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K132" s="3" t="s">
+      <c r="L132" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M132" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L132" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M132" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N132" s="3" t="s">
-        <v>373</v>
+      <c r="O132" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="P132" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q132" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q132" s="3" t="s">
+      <c r="R132" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R132" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -11153,32 +11153,32 @@
       <c r="B133" t="s">
         <v>158</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>362</v>
+      <c r="D133" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E133" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F133" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="L133" s="3" t="s">
         <v>362</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N133" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O133" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="P133" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q133" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q133" s="3" t="s">
+      <c r="R133" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R133" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -11188,32 +11188,32 @@
       <c r="B134" t="s">
         <v>158</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>362</v>
+      <c r="D134" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E134" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F134" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="K134" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="L134" s="3" t="s">
         <v>362</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N134" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="P134" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q134" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q134" s="3" t="s">
+      <c r="R134" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R134" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -11223,32 +11223,32 @@
       <c r="B135" t="s">
         <v>158</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>362</v>
+      <c r="D135" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E135" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F135" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="K135" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="L135" s="3" t="s">
         <v>362</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N135" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="P135" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q135" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q135" s="3" t="s">
+      <c r="R135" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R135" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -11258,32 +11258,32 @@
       <c r="B136" t="s">
         <v>158</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>362</v>
+      <c r="D136" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E136" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F136" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="K136" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="L136" s="3" t="s">
         <v>362</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N136" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="P136" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q136" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q136" s="3" t="s">
+      <c r="R136" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R136" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -11293,32 +11293,32 @@
       <c r="B137" t="s">
         <v>158</v>
       </c>
-      <c r="C137" s="3" t="s">
-        <v>362</v>
+      <c r="D137" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="E137" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F137" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="K137" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="L137" s="3" t="s">
         <v>362</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N137" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="P137" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q137" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q137" s="3" t="s">
+      <c r="R137" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R137" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -11328,26 +11328,26 @@
       <c r="B138" t="s">
         <v>158</v>
       </c>
+      <c r="D138" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E138" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F138" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M138" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N138" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P138" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q138" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q138" s="3" t="s">
+      <c r="R138" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R138" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -11357,26 +11357,26 @@
       <c r="B139" t="s">
         <v>158</v>
       </c>
+      <c r="D139" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E139" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F139" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="M139" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M139" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N139" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P139" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q139" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q139" s="3" t="s">
+      <c r="R139" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R139" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -11386,26 +11386,26 @@
       <c r="B140" t="s">
         <v>158</v>
       </c>
+      <c r="D140" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E140" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F140" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K140" s="3" t="s">
+      <c r="M140" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M140" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N140" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P140" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q140" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q140" s="3" t="s">
+      <c r="R140" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R140" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -11415,26 +11415,26 @@
       <c r="B141" t="s">
         <v>158</v>
       </c>
+      <c r="D141" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E141" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F141" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K141" s="3" t="s">
+      <c r="M141" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M141" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N141" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P141" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q141" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q141" s="3" t="s">
+      <c r="R141" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R141" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -11444,26 +11444,26 @@
       <c r="B142" t="s">
         <v>158</v>
       </c>
+      <c r="D142" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E142" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F142" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K142" s="3" t="s">
+      <c r="M142" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M142" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N142" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P142" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q142" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q142" s="3" t="s">
+      <c r="R142" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R142" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -11473,26 +11473,26 @@
       <c r="B143" t="s">
         <v>156</v>
       </c>
+      <c r="D143" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E143" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F143" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K143" s="3" t="s">
+      <c r="M143" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M143" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N143" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P143" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q143" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q143" s="3" t="s">
+      <c r="R143" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R143" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S143" s="3" t="s">
         <v>363</v>
@@ -11505,26 +11505,26 @@
       <c r="B144" t="s">
         <v>156</v>
       </c>
+      <c r="D144" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E144" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F144" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K144" s="3" t="s">
+      <c r="M144" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M144" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N144" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P144" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q144" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q144" s="3" t="s">
+      <c r="R144" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R144" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S144" s="3" t="s">
         <v>363</v>
@@ -11537,26 +11537,26 @@
       <c r="B145" t="s">
         <v>156</v>
       </c>
+      <c r="D145" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E145" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F145" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K145" s="3" t="s">
+      <c r="M145" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M145" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N145" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P145" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q145" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q145" s="3" t="s">
+      <c r="R145" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R145" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S145" s="3" t="s">
         <v>363</v>
@@ -11569,26 +11569,26 @@
       <c r="B146" t="s">
         <v>156</v>
       </c>
+      <c r="D146" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="E146" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F146" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K146" s="3" t="s">
+      <c r="M146" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M146" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N146" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="P146" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q146" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q146" s="3" t="s">
+      <c r="R146" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R146" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S146" s="3" t="s">
         <v>363</v>
@@ -11602,22 +11602,22 @@
         <v>156</v>
       </c>
       <c r="E147" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F147" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K147" s="3" t="s">
+      <c r="M147" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M147" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P147" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q147" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q147" s="3" t="s">
+      <c r="R147" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R147" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S147" s="3" t="s">
         <v>363</v>
@@ -11631,22 +11631,22 @@
         <v>156</v>
       </c>
       <c r="E148" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F148" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K148" s="3" t="s">
+      <c r="M148" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M148" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P148" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q148" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="Q148" s="3" t="s">
+      <c r="R148" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R148" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S148" s="3" t="s">
         <v>363</v>
@@ -11660,22 +11660,22 @@
         <v>156</v>
       </c>
       <c r="E149" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F149" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K149" s="3" t="s">
+      <c r="M149" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M149" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P149" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q149" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q149" s="3" t="s">
+      <c r="R149" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R149" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S149" s="3" t="s">
         <v>363</v>
@@ -11689,22 +11689,22 @@
         <v>156</v>
       </c>
       <c r="E150" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F150" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K150" s="3" t="s">
+      <c r="M150" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M150" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P150" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q150" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q150" s="3" t="s">
+      <c r="R150" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R150" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S150" s="3" t="s">
         <v>363</v>
@@ -11718,22 +11718,22 @@
         <v>156</v>
       </c>
       <c r="E151" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F151" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K151" s="3" t="s">
+      <c r="M151" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M151" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P151" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q151" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q151" s="3" t="s">
+      <c r="R151" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R151" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S151" s="3" t="s">
         <v>363</v>
@@ -11747,22 +11747,22 @@
         <v>156</v>
       </c>
       <c r="E152" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F152" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K152" s="3" t="s">
+      <c r="M152" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M152" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P152" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q152" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q152" s="3" t="s">
+      <c r="R152" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R152" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S152" s="3" t="s">
         <v>363</v>
@@ -11776,22 +11776,22 @@
         <v>156</v>
       </c>
       <c r="E153" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F153" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K153" s="3" t="s">
+      <c r="M153" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M153" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P153" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q153" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q153" s="3" t="s">
+      <c r="R153" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R153" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S153" s="3" t="s">
         <v>363</v>
@@ -11805,22 +11805,22 @@
         <v>156</v>
       </c>
       <c r="E154" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F154" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K154" s="3" t="s">
+      <c r="M154" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M154" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P154" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q154" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q154" s="3" t="s">
+      <c r="R154" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R154" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -11831,22 +11831,22 @@
         <v>156</v>
       </c>
       <c r="E155" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F155" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K155" s="3" t="s">
+      <c r="M155" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M155" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P155" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q155" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q155" s="3" t="s">
+      <c r="R155" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R155" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -11857,22 +11857,22 @@
         <v>156</v>
       </c>
       <c r="E156" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F156" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K156" s="3" t="s">
+      <c r="M156" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M156" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="P156" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q156" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="Q156" s="3" t="s">
+      <c r="R156" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R156" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -11883,19 +11883,19 @@
         <v>156</v>
       </c>
       <c r="E157" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F157" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K157" s="3" t="s">
+      <c r="M157" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M157" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q157" s="3" t="s">
+      <c r="P157" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="R157" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="R157" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -11906,15 +11906,15 @@
         <v>156</v>
       </c>
       <c r="E158" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F158" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K158" s="3" t="s">
+      <c r="M158" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M158" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q158" s="3" t="s">
+      <c r="R158" s="3" t="s">
         <v>371</v>
       </c>
     </row>
@@ -11926,15 +11926,15 @@
         <v>157</v>
       </c>
       <c r="E159" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F159" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="K159" s="3" t="s">
+      <c r="M159" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M159" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q159" s="3" t="s">
+      <c r="R159" s="3" t="s">
         <v>371</v>
       </c>
     </row>
@@ -11946,16 +11946,16 @@
         <v>157</v>
       </c>
       <c r="E160" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F160" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="M160" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q160" s="3" t="s">
+      <c r="R160" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="161" spans="1:17">
+    <row r="161" spans="1:18">
       <c r="A161" t="s">
         <v>406</v>
       </c>
@@ -11963,16 +11963,16 @@
         <v>157</v>
       </c>
       <c r="E161" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F161" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="M161" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q161" s="3" t="s">
+      <c r="R161" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="162" spans="1:17">
+    <row r="162" spans="1:18">
       <c r="A162" t="s">
         <v>407</v>
       </c>
@@ -11980,399 +11980,399 @@
         <v>157</v>
       </c>
       <c r="E162" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F162" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="M162" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q162" s="3" t="s">
+      <c r="R162" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="163" spans="1:17">
+    <row r="163" spans="1:18">
       <c r="A163" t="s">
         <v>408</v>
       </c>
       <c r="B163" t="s">
         <v>157</v>
       </c>
-      <c r="E163" s="3" t="s">
+      <c r="F163" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="Q163" s="3" t="s">
+      <c r="R163" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="164" spans="1:17">
+    <row r="164" spans="1:18">
       <c r="A164" t="s">
         <v>409</v>
       </c>
       <c r="B164" t="s">
         <v>157</v>
       </c>
-      <c r="E164" s="3" t="s">
+      <c r="F164" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="Q164" s="3" t="s">
+      <c r="R164" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="165" spans="1:17">
+    <row r="165" spans="1:18">
       <c r="A165" t="s">
         <v>410</v>
       </c>
       <c r="B165" t="s">
         <v>157</v>
       </c>
-      <c r="E165" s="3" t="s">
+      <c r="F165" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="Q165" s="3" t="s">
+      <c r="R165" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="166" spans="1:17">
+    <row r="166" spans="1:18">
       <c r="A166" t="s">
         <v>411</v>
       </c>
       <c r="B166" t="s">
         <v>157</v>
       </c>
-      <c r="Q166" s="3" t="s">
+      <c r="R166" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="167" spans="1:17">
+    <row r="167" spans="1:18">
       <c r="A167" t="s">
         <v>412</v>
       </c>
       <c r="B167" t="s">
         <v>157</v>
       </c>
-      <c r="Q167" s="3" t="s">
+      <c r="R167" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="168" spans="1:17">
+    <row r="168" spans="1:18">
       <c r="A168" t="s">
         <v>413</v>
       </c>
       <c r="B168" t="s">
         <v>157</v>
       </c>
-      <c r="Q168" s="3" t="s">
+      <c r="R168" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="169" spans="1:17">
+    <row r="169" spans="1:18">
       <c r="A169" t="s">
         <v>414</v>
       </c>
       <c r="B169" t="s">
         <v>157</v>
       </c>
-      <c r="Q169" s="3" t="s">
+      <c r="R169" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="170" spans="1:17">
+    <row r="170" spans="1:18">
       <c r="A170" t="s">
         <v>415</v>
       </c>
       <c r="B170" t="s">
         <v>157</v>
       </c>
-      <c r="Q170" s="3" t="s">
+      <c r="R170" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="171" spans="1:17">
+    <row r="171" spans="1:18">
       <c r="A171" t="s">
         <v>416</v>
       </c>
       <c r="B171" t="s">
         <v>157</v>
       </c>
-      <c r="Q171" s="3" t="s">
+      <c r="R171" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="172" spans="1:17">
+    <row r="172" spans="1:18">
       <c r="A172" t="s">
         <v>417</v>
       </c>
       <c r="B172" t="s">
         <v>157</v>
       </c>
-      <c r="Q172" s="3" t="s">
+      <c r="R172" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="173" spans="1:17">
+    <row r="173" spans="1:18">
       <c r="A173" t="s">
         <v>418</v>
       </c>
       <c r="B173" t="s">
         <v>157</v>
       </c>
-      <c r="Q173" s="3" t="s">
+      <c r="R173" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="174" spans="1:17">
+    <row r="174" spans="1:18">
       <c r="A174" t="s">
         <v>419</v>
       </c>
       <c r="B174" t="s">
         <v>157</v>
       </c>
-      <c r="Q174" s="3" t="s">
+      <c r="R174" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="175" spans="1:17">
+    <row r="175" spans="1:18">
       <c r="A175" t="s">
         <v>420</v>
       </c>
       <c r="B175" t="s">
         <v>158</v>
       </c>
-      <c r="Q175" s="3" t="s">
+      <c r="R175" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="176" spans="1:17">
+    <row r="176" spans="1:18">
       <c r="A176" t="s">
         <v>421</v>
       </c>
       <c r="B176" t="s">
         <v>158</v>
       </c>
-      <c r="Q176" s="3" t="s">
+      <c r="R176" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="177" spans="1:17">
+    <row r="177" spans="1:18">
       <c r="A177" t="s">
         <v>422</v>
       </c>
       <c r="B177" t="s">
         <v>158</v>
       </c>
-      <c r="Q177" s="3" t="s">
+      <c r="R177" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="178" spans="1:17">
+    <row r="178" spans="1:18">
       <c r="A178" t="s">
         <v>423</v>
       </c>
       <c r="B178" t="s">
         <v>158</v>
       </c>
-      <c r="Q178" s="3" t="s">
+      <c r="R178" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="179" spans="1:17">
+    <row r="179" spans="1:18">
       <c r="A179" t="s">
         <v>424</v>
       </c>
       <c r="B179" t="s">
         <v>158</v>
       </c>
-      <c r="Q179" s="3" t="s">
+      <c r="R179" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="180" spans="1:17">
+    <row r="180" spans="1:18">
       <c r="A180" t="s">
         <v>425</v>
       </c>
       <c r="B180" t="s">
         <v>158</v>
       </c>
-      <c r="Q180" s="3" t="s">
+      <c r="R180" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="181" spans="1:17">
+    <row r="181" spans="1:18">
       <c r="A181" t="s">
         <v>426</v>
       </c>
       <c r="B181" t="s">
         <v>158</v>
       </c>
-      <c r="Q181" s="3" t="s">
+      <c r="R181" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="182" spans="1:17">
+    <row r="182" spans="1:18">
       <c r="A182" t="s">
         <v>427</v>
       </c>
       <c r="B182" t="s">
         <v>158</v>
       </c>
-      <c r="Q182" s="3" t="s">
+      <c r="R182" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="183" spans="1:17">
+    <row r="183" spans="1:18">
       <c r="A183" t="s">
         <v>428</v>
       </c>
       <c r="B183" t="s">
         <v>158</v>
       </c>
-      <c r="Q183" s="3" t="s">
+      <c r="R183" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="184" spans="1:17">
+    <row r="184" spans="1:18">
       <c r="A184" t="s">
         <v>429</v>
       </c>
       <c r="B184" t="s">
         <v>158</v>
       </c>
-      <c r="Q184" s="3" t="s">
+      <c r="R184" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="185" spans="1:17">
+    <row r="185" spans="1:18">
       <c r="A185" t="s">
         <v>430</v>
       </c>
       <c r="B185" t="s">
         <v>158</v>
       </c>
-      <c r="Q185" s="3" t="s">
+      <c r="R185" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="186" spans="1:17">
+    <row r="186" spans="1:18">
       <c r="A186" t="s">
         <v>431</v>
       </c>
       <c r="B186" t="s">
         <v>158</v>
       </c>
-      <c r="Q186" s="3" t="s">
+      <c r="R186" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:17">
+    <row r="187" spans="1:18">
       <c r="A187" t="s">
         <v>432</v>
       </c>
       <c r="B187" t="s">
         <v>158</v>
       </c>
-      <c r="Q187" s="3" t="s">
+      <c r="R187" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="188" spans="1:17">
+    <row r="188" spans="1:18">
       <c r="A188" t="s">
         <v>433</v>
       </c>
       <c r="B188" t="s">
         <v>158</v>
       </c>
-      <c r="Q188" s="3" t="s">
+      <c r="R188" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="189" spans="1:17">
+    <row r="189" spans="1:18">
       <c r="A189" t="s">
         <v>434</v>
       </c>
       <c r="B189" t="s">
         <v>158</v>
       </c>
-      <c r="Q189" s="3" t="s">
+      <c r="R189" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="190" spans="1:17">
+    <row r="190" spans="1:18">
       <c r="A190" t="s">
         <v>435</v>
       </c>
       <c r="B190" t="s">
         <v>158</v>
       </c>
-      <c r="Q190" s="3" t="s">
+      <c r="R190" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="191" spans="1:17">
+    <row r="191" spans="1:18">
       <c r="A191" t="s">
         <v>436</v>
       </c>
       <c r="B191" t="s">
         <v>156</v>
       </c>
-      <c r="Q191" s="3" t="s">
+      <c r="R191" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="192" spans="1:17">
+    <row r="192" spans="1:18">
       <c r="A192" t="s">
         <v>437</v>
       </c>
       <c r="B192" t="s">
         <v>156</v>
       </c>
-      <c r="Q192" s="3" t="s">
+      <c r="R192" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="193" spans="1:17">
+    <row r="193" spans="1:18">
       <c r="A193" t="s">
         <v>438</v>
       </c>
       <c r="B193" t="s">
         <v>156</v>
       </c>
-      <c r="Q193" s="3" t="s">
+      <c r="R193" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="194" spans="1:17">
+    <row r="194" spans="1:18">
       <c r="A194" t="s">
         <v>439</v>
       </c>
       <c r="B194" t="s">
         <v>156</v>
       </c>
-      <c r="Q194" s="3" t="s">
+      <c r="R194" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="195" spans="1:17">
+    <row r="195" spans="1:18">
       <c r="A195" t="s">
         <v>440</v>
       </c>
       <c r="B195" t="s">
         <v>156</v>
       </c>
-      <c r="Q195" s="3" t="s">
+      <c r="R195" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="196" spans="1:17">
+    <row r="196" spans="1:18">
       <c r="A196" t="s">
         <v>441</v>
       </c>
       <c r="B196" t="s">
         <v>156</v>
       </c>
-      <c r="Q196" s="3" t="s">
+      <c r="R196" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="197" spans="1:17">
+    <row r="197" spans="1:18">
       <c r="A197" t="s">
         <v>442</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="198" spans="1:17">
+    <row r="198" spans="1:18">
       <c r="A198" t="s">
         <v>443</v>
       </c>
@@ -12388,7 +12388,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="199" spans="1:17">
+    <row r="199" spans="1:18">
       <c r="A199" t="s">
         <v>444</v>
       </c>
@@ -12396,7 +12396,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="200" spans="1:17">
+    <row r="200" spans="1:18">
       <c r="A200" t="s">
         <v>445</v>
       </c>
